--- a/2026/ITALIA/Junio/Junio ITALIA.xlsx
+++ b/2026/ITALIA/Junio/Junio ITALIA.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\2026\ITALIA\Junio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FECA8A3-2AAA-403A-9B01-5E7FD62EA85B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5757D03-316B-4A33-A6E2-9038371DFC9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="4" r:id="rId1"/>
@@ -19,14 +19,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="1">PRORRATEO!$A$1:$N$125</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$E$135</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$E$143</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="316" uniqueCount="261">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="330" uniqueCount="275">
   <si>
     <t>TOTAL</t>
   </si>
@@ -554,9 +554,6 @@
     <t>Silvana Valeria Arredondo - Braian Brito</t>
   </si>
   <si>
-    <t>Fotocopias - Librería</t>
-  </si>
-  <si>
     <t>Cliente 4873380</t>
   </si>
   <si>
@@ -662,45 +659,18 @@
     <t xml:space="preserve">Plan de pago de 11C: Consta de 10 Cuotas de $165.000 + expensas en curso </t>
   </si>
   <si>
-    <t>VTO 18/06</t>
-  </si>
-  <si>
-    <t>PERÍODO: MAYO</t>
-  </si>
-  <si>
-    <t>Gustavo Padron -  Sr. Contador - MAYO</t>
-  </si>
-  <si>
     <t>Transf 21/05</t>
   </si>
   <si>
-    <t>Cuello Natalia - Desobstruccion columna cocina 3A</t>
-  </si>
-  <si>
     <t>Transf 22/5</t>
   </si>
   <si>
-    <t>Cuello Natalia - Desobstruccion colectora cloacal</t>
-  </si>
-  <si>
-    <t>Cuello Natalia - Desobstruccion columna cocina 8C</t>
-  </si>
-  <si>
-    <t>Cuello Natalia - Desobstruccion columna cocina 3G</t>
-  </si>
-  <si>
     <t>Transf 12/05</t>
   </si>
   <si>
     <t>Articulos de limpieza</t>
   </si>
   <si>
-    <t>Transf 27/05</t>
-  </si>
-  <si>
-    <t>Ascensores Lema - Adelanto cambio cables de acero</t>
-  </si>
-  <si>
     <t>PMC 21/05</t>
   </si>
   <si>
@@ -716,18 +686,6 @@
     <t>Ef 26/05</t>
   </si>
   <si>
-    <t>InOut Control - Comando control y camaras - Mayo</t>
-  </si>
-  <si>
-    <t>InOut Control - Comando control y camaras - Abril</t>
-  </si>
-  <si>
-    <t>Debito 12/05</t>
-  </si>
-  <si>
-    <t>Honorarios administracion - Se adeuda mes de MAYO</t>
-  </si>
-  <si>
     <t xml:space="preserve">  </t>
   </si>
   <si>
@@ -773,9 +731,6 @@
     <t>Transf 11/05 - 26/05</t>
   </si>
   <si>
-    <t>Suarez Agustin Ignacio - Fumigacion se adeuda mayo</t>
-  </si>
-  <si>
     <t>Debito 27/05</t>
   </si>
   <si>
@@ -819,6 +774,93 @@
   </si>
   <si>
     <t xml:space="preserve">Fernando daniel Minxxo  / Osvaldo </t>
+  </si>
+  <si>
+    <t>VTO 17/07</t>
+  </si>
+  <si>
+    <t>PERÍODO: JUNIO</t>
+  </si>
+  <si>
+    <t>Suarez Agustin Ignacio - Fumigacion se adeuda JUNIO</t>
+  </si>
+  <si>
+    <t>InOut Control - Comando control y camaras - JUNIO</t>
+  </si>
+  <si>
+    <t>Honorarios administracion - Se adeuda mes de JUNIO</t>
+  </si>
+  <si>
+    <t>Gustavo Padron -  Sr. Contador - JUNIO</t>
+  </si>
+  <si>
+    <t>Galvan Zaffalon - Compra de bombachupadora de calle de 1hp monofasica</t>
+  </si>
+  <si>
+    <t>Transf 26/06</t>
+  </si>
+  <si>
+    <t>Incluye SAC</t>
+  </si>
+  <si>
+    <t>Transf 25/06</t>
+  </si>
+  <si>
+    <t>Quotteri Mateo - Certificacion de deuda de expensas UF 68</t>
+  </si>
+  <si>
+    <t>Cordoba Matias - A cuenta de trabajo de plomeria, albañileria y pintura</t>
+  </si>
+  <si>
+    <t>Fire - Compra de pantalon, remera, buzo para Sr. Encargado</t>
+  </si>
+  <si>
+    <t>Cuello Natalia - Desobstruccion lavadero 9C</t>
+  </si>
+  <si>
+    <t>Transf 19/06</t>
+  </si>
+  <si>
+    <t>Cuello Natalia - Desobstruccion lavadero 9D</t>
+  </si>
+  <si>
+    <t>Cuello Natalia - Desobstruccion lavadero 6D</t>
+  </si>
+  <si>
+    <t>Doartero Julio - Visita electrica</t>
+  </si>
+  <si>
+    <t>Transf 04/06</t>
+  </si>
+  <si>
+    <t>Debito 12/06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Servisur - 4 termicas unipolares - </t>
+  </si>
+  <si>
+    <t>Transf 05/06</t>
+  </si>
+  <si>
+    <t>Ascensores Lema - Arreglo</t>
+  </si>
+  <si>
+    <t>Ferreteria La 95 - Copia de llave</t>
+  </si>
+  <si>
+    <t>Arias Mirta -</t>
+  </si>
+  <si>
+    <t>Sra. Arias mirta - Confieccion de formulario 931 - periodo 04/2025</t>
+  </si>
+  <si>
+    <t>Transf 11/06</t>
+  </si>
+  <si>
+    <t>Transf 17/06</t>
+  </si>
+  <si>
+    <t>Transf 18/06</t>
   </si>
 </sst>
 </file>
@@ -1644,7 +1686,7 @@
     <xf numFmtId="44" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="288">
+  <cellXfs count="294">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1924,9 +1966,6 @@
     <xf numFmtId="44" fontId="17" fillId="2" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="8" fontId="10" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="8" fontId="10" fillId="2" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -1989,186 +2028,6 @@
     <xf numFmtId="0" fontId="0" fillId="18" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="18" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="18" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="40" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="41" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="42" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="44" fontId="10" fillId="2" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="10" fillId="2" borderId="19" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="19" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="12" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="12" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="18" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
@@ -2176,6 +2035,203 @@
     <xf numFmtId="0" fontId="16" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="16" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="19" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="40" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="41" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="42" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="44" fontId="10" fillId="2" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="10" fillId="2" borderId="19" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="8" fontId="7" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="44" fontId="7" fillId="2" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="7" fillId="2" borderId="20" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="8" fontId="7" fillId="2" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -2547,7 +2603,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E413A25D-5161-4141-BE0B-6E37A2A76CA5}">
-  <dimension ref="A1:M136"/>
+  <dimension ref="A1:M144"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="37.5546875" customWidth="1"/>
@@ -2565,12 +2621,12 @@
   <sheetData>
     <row r="1" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1"/>
-      <c r="B1" s="233" t="s">
+      <c r="B1" s="231" t="s">
         <v>147</v>
       </c>
-      <c r="C1" s="233"/>
-      <c r="D1" s="233"/>
-      <c r="E1" s="234"/>
+      <c r="C1" s="231"/>
+      <c r="D1" s="231"/>
+      <c r="E1" s="232"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="2"/>
@@ -2584,7 +2640,7 @@
     <row r="3" spans="1:5" ht="51.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="2"/>
       <c r="B3" s="237" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C3" s="237"/>
       <c r="D3" s="237"/>
@@ -2606,7 +2662,7 @@
         <v>148</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>209</v>
+        <v>247</v>
       </c>
       <c r="C5" s="9"/>
       <c r="D5" s="3" t="s">
@@ -2621,14 +2677,14 @@
       <c r="B6" s="7"/>
       <c r="C6" s="7"/>
       <c r="D6" s="7" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="E6" s="8"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" s="48"/>
       <c r="B8" s="239" t="s">
-        <v>208</v>
+        <v>246</v>
       </c>
       <c r="C8" s="239"/>
       <c r="D8" s="48"/>
@@ -2700,7 +2756,7 @@
       <c r="E17" s="48"/>
     </row>
     <row r="18" spans="1:8" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="182"/>
+      <c r="A18" s="181"/>
       <c r="B18" s="48"/>
       <c r="C18" s="48"/>
       <c r="D18" s="48"/>
@@ -2714,11 +2770,11 @@
       <c r="E19" s="48"/>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A20" s="183" t="s">
+      <c r="A20" s="182" t="s">
         <v>104</v>
       </c>
-      <c r="B20" s="184"/>
-      <c r="C20" s="185"/>
+      <c r="B20" s="183"/>
+      <c r="C20" s="184"/>
       <c r="D20" s="58"/>
       <c r="E20" s="59"/>
     </row>
@@ -2732,96 +2788,98 @@
       <c r="E21" s="153"/>
     </row>
     <row r="22" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="235" t="s">
+      <c r="A22" s="233" t="s">
         <v>165</v>
       </c>
-      <c r="B22" s="236"/>
-      <c r="C22" s="186"/>
-      <c r="D22" s="187">
-        <v>2096955.5</v>
-      </c>
-      <c r="E22" s="154"/>
+      <c r="B22" s="234"/>
+      <c r="C22" s="185"/>
+      <c r="D22" s="186">
+        <v>3382992.69</v>
+      </c>
+      <c r="E22" s="154" t="s">
+        <v>254</v>
+      </c>
       <c r="H22" s="19"/>
     </row>
     <row r="23" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="235" t="s">
+      <c r="A23" s="233" t="s">
         <v>166</v>
       </c>
-      <c r="B23" s="236"/>
-      <c r="C23" s="186"/>
-      <c r="D23" s="187">
-        <v>-456087.85</v>
+      <c r="B23" s="234"/>
+      <c r="C23" s="185"/>
+      <c r="D23" s="186">
+        <v>-735800.92</v>
       </c>
       <c r="E23" s="20"/>
       <c r="H23" s="19"/>
     </row>
     <row r="24" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="235" t="s">
+      <c r="A24" s="233" t="s">
         <v>1</v>
       </c>
-      <c r="B24" s="236"/>
-      <c r="C24" s="186"/>
-      <c r="D24" s="188">
-        <v>0.35</v>
+      <c r="B24" s="234"/>
+      <c r="C24" s="185"/>
+      <c r="D24" s="187">
+        <v>0.23</v>
       </c>
       <c r="E24" s="20"/>
       <c r="H24" s="19"/>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A25" s="189" t="s">
+      <c r="A25" s="188" t="s">
         <v>105</v>
       </c>
-      <c r="B25" s="189"/>
-      <c r="C25" s="189"/>
+      <c r="B25" s="188"/>
+      <c r="C25" s="188"/>
       <c r="D25" s="22"/>
       <c r="E25" s="155">
         <f>SUM(D22:D24)</f>
-        <v>1640868</v>
+        <v>2647192</v>
       </c>
     </row>
     <row r="26" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="189" t="s">
-        <v>181</v>
-      </c>
-      <c r="B26" s="189"/>
-      <c r="C26" s="189"/>
+      <c r="A26" s="188" t="s">
+        <v>180</v>
+      </c>
+      <c r="B26" s="188"/>
+      <c r="C26" s="188"/>
       <c r="D26" s="22"/>
       <c r="E26" s="156"/>
     </row>
     <row r="27" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="186"/>
-      <c r="B27" s="186"/>
-      <c r="C27" s="186"/>
+      <c r="A27" s="185"/>
+      <c r="B27" s="185"/>
+      <c r="C27" s="185"/>
       <c r="D27" s="35"/>
       <c r="E27" s="169"/>
     </row>
     <row r="28" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="186"/>
-      <c r="B28" s="186"/>
-      <c r="C28" s="186"/>
+      <c r="A28" s="185"/>
+      <c r="B28" s="185"/>
+      <c r="C28" s="185"/>
       <c r="D28" s="35"/>
       <c r="E28" s="169"/>
     </row>
     <row r="29" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="186"/>
-      <c r="B29" s="186"/>
-      <c r="C29" s="186"/>
+      <c r="A29" s="185"/>
+      <c r="B29" s="185"/>
+      <c r="C29" s="185"/>
       <c r="D29" s="35"/>
       <c r="E29" s="169"/>
     </row>
     <row r="30" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="186"/>
-      <c r="B30" s="186"/>
-      <c r="C30" s="186"/>
+      <c r="A30" s="185"/>
+      <c r="B30" s="185"/>
+      <c r="C30" s="185"/>
       <c r="D30" s="35"/>
       <c r="E30" s="157"/>
     </row>
     <row r="31" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="189" t="s">
+      <c r="A31" s="188" t="s">
         <v>105</v>
       </c>
-      <c r="B31" s="190"/>
-      <c r="C31" s="190"/>
+      <c r="B31" s="189"/>
+      <c r="C31" s="189"/>
       <c r="D31" s="107"/>
       <c r="E31" s="158">
         <f>D27+D30</f>
@@ -2832,102 +2890,102 @@
       <c r="A32" s="36" t="s">
         <v>140</v>
       </c>
-      <c r="B32" s="189"/>
-      <c r="C32" s="189"/>
+      <c r="B32" s="188"/>
+      <c r="C32" s="188"/>
       <c r="D32" s="22"/>
       <c r="E32" s="156"/>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A33" s="186" t="s">
-        <v>192</v>
-      </c>
-      <c r="B33" s="191"/>
-      <c r="C33" s="191"/>
+      <c r="A33" s="185" t="s">
+        <v>191</v>
+      </c>
+      <c r="B33" s="190"/>
+      <c r="C33" s="190"/>
       <c r="D33" s="35">
         <v>12537.94</v>
       </c>
       <c r="E33" s="157" t="str">
         <f>E35</f>
-        <v>Debito 12/05</v>
+        <v>Debito 12/06</v>
       </c>
       <c r="G33" s="66"/>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A34" s="186" t="s">
+      <c r="A34" s="185" t="s">
         <v>152</v>
       </c>
-      <c r="B34" s="191"/>
-      <c r="C34" s="191"/>
+      <c r="B34" s="190"/>
+      <c r="C34" s="190"/>
       <c r="D34" s="35">
         <v>898456.64</v>
       </c>
       <c r="E34" s="157" t="s">
-        <v>246</v>
+        <v>231</v>
       </c>
       <c r="G34" s="66"/>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A35" s="186" t="s">
+      <c r="A35" s="185" t="s">
         <v>142</v>
       </c>
-      <c r="B35" s="191"/>
-      <c r="C35" s="191"/>
-      <c r="D35" s="35">
-        <v>175717.53</v>
+      <c r="B35" s="190"/>
+      <c r="C35" s="190"/>
+      <c r="D35" s="289">
+        <v>181264.12</v>
       </c>
       <c r="E35" s="157" t="s">
-        <v>228</v>
+        <v>265</v>
       </c>
       <c r="G35" s="66"/>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A36" s="186" t="s">
+      <c r="A36" s="185" t="s">
         <v>144</v>
       </c>
-      <c r="B36" s="191"/>
-      <c r="C36" s="191"/>
-      <c r="D36" s="35">
-        <v>91719.37</v>
+      <c r="B36" s="190"/>
+      <c r="C36" s="190"/>
+      <c r="D36" s="289">
+        <v>94363</v>
       </c>
       <c r="E36" s="157" t="str">
         <f>E35</f>
-        <v>Debito 12/05</v>
+        <v>Debito 12/06</v>
       </c>
       <c r="G36" s="50"/>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A37" s="186" t="s">
+      <c r="A37" s="185" t="s">
         <v>143</v>
       </c>
-      <c r="B37" s="191"/>
-      <c r="C37" s="191"/>
-      <c r="D37" s="35">
-        <v>10191.040000000001</v>
+      <c r="B37" s="190"/>
+      <c r="C37" s="190"/>
+      <c r="D37" s="289">
+        <v>10484.780000000001</v>
       </c>
       <c r="E37" s="157" t="str">
         <f>E35</f>
-        <v>Debito 12/05</v>
+        <v>Debito 12/06</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A38" s="186" t="s">
+      <c r="A38" s="185" t="s">
         <v>153</v>
       </c>
-      <c r="B38" s="191"/>
-      <c r="C38" s="191"/>
+      <c r="B38" s="190"/>
+      <c r="C38" s="190"/>
       <c r="D38" s="35"/>
       <c r="E38" s="157"/>
     </row>
     <row r="39" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="189" t="s">
+      <c r="A39" s="188" t="s">
         <v>141</v>
       </c>
-      <c r="B39" s="189"/>
-      <c r="C39" s="189"/>
+      <c r="B39" s="188"/>
+      <c r="C39" s="188"/>
       <c r="D39" s="22"/>
       <c r="E39" s="41">
         <f>SUM(D33:D38)</f>
-        <v>1188622.52</v>
+        <v>1197106.48</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.3">
@@ -2941,28 +2999,28 @@
     </row>
     <row r="41" spans="1:7" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="241" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B41" s="242"/>
       <c r="C41" s="26"/>
-      <c r="D41" s="181">
+      <c r="D41" s="180">
         <v>7805</v>
       </c>
       <c r="E41" s="20" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="42" spans="1:7" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="241" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B42" s="242"/>
       <c r="C42" s="26"/>
-      <c r="D42" s="181">
+      <c r="D42" s="180">
         <v>214164</v>
       </c>
       <c r="E42" s="20" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.3">
@@ -2991,14 +3049,14 @@
         <v>109</v>
       </c>
       <c r="B45" s="29" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C45" s="29"/>
       <c r="D45" s="30">
         <v>662323</v>
       </c>
       <c r="E45" s="20" t="s">
-        <v>224</v>
+        <v>214</v>
       </c>
     </row>
     <row r="46" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -3006,22 +3064,22 @@
         <v>109</v>
       </c>
       <c r="B46" s="29" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C46" s="29"/>
       <c r="D46" s="30">
         <v>13831.45</v>
       </c>
       <c r="E46" s="20" t="s">
-        <v>225</v>
+        <v>215</v>
       </c>
     </row>
     <row r="47" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="29" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B47" s="29" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C47" s="29"/>
       <c r="D47" s="30">
@@ -3031,7 +3089,7 @@
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A48" s="29" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B48" s="31"/>
       <c r="C48" s="29"/>
@@ -3050,7 +3108,7 @@
         <v>4499070.47</v>
       </c>
       <c r="E49" s="118" t="s">
-        <v>221</v>
+        <v>211</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.3">
@@ -3082,49 +3140,49 @@
       <c r="E52" s="161"/>
     </row>
     <row r="53" spans="1:6" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A53" s="222" t="s">
+      <c r="A53" s="235" t="s">
         <v>168</v>
       </c>
-      <c r="B53" s="223"/>
+      <c r="B53" s="236"/>
       <c r="C53" s="29"/>
-      <c r="D53" s="30">
+      <c r="D53" s="288">
         <v>285000</v>
       </c>
-      <c r="E53" s="34" t="s">
-        <v>217</v>
+      <c r="E53" s="168" t="s">
+        <v>267</v>
       </c>
     </row>
     <row r="54" spans="1:6" ht="33" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="222" t="s">
-        <v>220</v>
-      </c>
-      <c r="B54" s="223"/>
+      <c r="A54" s="291" t="s">
+        <v>268</v>
+      </c>
+      <c r="B54" s="292"/>
       <c r="C54" s="29"/>
-      <c r="D54" s="30">
+      <c r="D54" s="288">
         <v>1000000</v>
       </c>
       <c r="E54" s="34" t="s">
-        <v>217</v>
+        <v>209</v>
       </c>
     </row>
     <row r="55" spans="1:6" ht="103.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A55" s="222" t="s">
-        <v>243</v>
-      </c>
-      <c r="B55" s="223"/>
+      <c r="A55" s="235" t="s">
+        <v>229</v>
+      </c>
+      <c r="B55" s="236"/>
       <c r="C55" s="29"/>
       <c r="D55" s="30">
         <f>2800000+1400000</f>
         <v>4200000</v>
       </c>
       <c r="E55" s="168" t="s">
-        <v>244</v>
+        <v>230</v>
       </c>
       <c r="F55" s="50"/>
     </row>
     <row r="56" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="16" t="s">
-        <v>240</v>
+        <v>226</v>
       </c>
       <c r="B56" s="17"/>
       <c r="C56" s="29"/>
@@ -3134,712 +3192,815 @@
       <c r="E56" s="168"/>
       <c r="F56" s="50"/>
     </row>
-    <row r="57" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A57" s="16" t="s">
-        <v>172</v>
+    <row r="57" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A57" s="290" t="s">
+        <v>266</v>
       </c>
       <c r="B57" s="17"/>
       <c r="C57" s="29"/>
-      <c r="D57" s="30">
-        <f>5200+5500</f>
-        <v>10700</v>
-      </c>
-      <c r="E57" s="34"/>
+      <c r="D57" s="288">
+        <v>160000</v>
+      </c>
+      <c r="E57" s="168" t="s">
+        <v>267</v>
+      </c>
       <c r="F57" s="50"/>
     </row>
-    <row r="58" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="92" t="s">
-        <v>212</v>
+    <row r="58" spans="1:6" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A58" s="16" t="s">
+        <v>270</v>
       </c>
       <c r="B58" s="17"/>
       <c r="C58" s="29"/>
       <c r="D58" s="30">
-        <v>31400</v>
-      </c>
-      <c r="E58" s="34" t="s">
-        <v>213</v>
-      </c>
+        <f>5200+5500</f>
+        <v>10700</v>
+      </c>
+      <c r="E58" s="34"/>
       <c r="F58" s="50"/>
     </row>
-    <row r="59" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A59" s="92" t="s">
-        <v>214</v>
+    <row r="59" spans="1:6" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A59" s="16" t="s">
+        <v>269</v>
       </c>
       <c r="B59" s="17"/>
       <c r="C59" s="29"/>
-      <c r="D59" s="30">
-        <v>95700</v>
-      </c>
-      <c r="E59" s="34" t="s">
-        <v>213</v>
-      </c>
+      <c r="D59" s="288">
+        <v>3000</v>
+      </c>
+      <c r="E59" s="34"/>
       <c r="F59" s="50"/>
     </row>
-    <row r="60" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:6" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A60" s="92" t="s">
-        <v>215</v>
+        <v>252</v>
       </c>
       <c r="B60" s="17"/>
       <c r="C60" s="29"/>
-      <c r="D60" s="30">
-        <v>31400</v>
+      <c r="D60" s="288">
+        <v>324000</v>
       </c>
       <c r="E60" s="34" t="s">
-        <v>213</v>
+        <v>253</v>
       </c>
       <c r="F60" s="50"/>
     </row>
     <row r="61" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A61" s="92" t="s">
-        <v>216</v>
+        <v>257</v>
       </c>
       <c r="B61" s="17"/>
       <c r="C61" s="29"/>
-      <c r="D61" s="30">
-        <v>31400</v>
+      <c r="D61" s="288">
+        <v>2800000</v>
       </c>
       <c r="E61" s="34" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="F61" s="50"/>
     </row>
-    <row r="62" spans="1:6" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A62" s="92" t="s">
-        <v>245</v>
+        <v>258</v>
       </c>
       <c r="B62" s="17"/>
       <c r="C62" s="29"/>
-      <c r="D62" s="30">
-        <v>0</v>
-      </c>
-      <c r="E62" s="168"/>
+      <c r="D62" s="288">
+        <v>67900</v>
+      </c>
+      <c r="E62" s="34" t="s">
+        <v>273</v>
+      </c>
       <c r="F62" s="50"/>
     </row>
-    <row r="63" spans="1:6" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A63" s="92" t="s">
-        <v>218</v>
+        <v>259</v>
       </c>
       <c r="B63" s="17"/>
       <c r="C63" s="29"/>
-      <c r="D63" s="30">
-        <v>322500</v>
-      </c>
-      <c r="E63" s="168" t="s">
-        <v>219</v>
+      <c r="D63" s="288">
+        <v>31400</v>
+      </c>
+      <c r="E63" s="34" t="s">
+        <v>260</v>
       </c>
       <c r="F63" s="50"/>
     </row>
-    <row r="64" spans="1:6" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A64" s="222" t="s">
-        <v>227</v>
-      </c>
-      <c r="B64" s="223"/>
+    <row r="64" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A64" s="92" t="s">
+        <v>261</v>
+      </c>
+      <c r="B64" s="17"/>
       <c r="C64" s="29"/>
-      <c r="D64" s="30">
+      <c r="D64" s="288">
+        <v>31400</v>
+      </c>
+      <c r="E64" s="34"/>
+      <c r="F64" s="50"/>
+    </row>
+    <row r="65" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A65" s="92" t="s">
+        <v>262</v>
+      </c>
+      <c r="B65" s="17"/>
+      <c r="C65" s="29"/>
+      <c r="D65" s="288">
+        <v>31400</v>
+      </c>
+      <c r="E65" s="34"/>
+      <c r="F65" s="50"/>
+    </row>
+    <row r="66" spans="1:6" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A66" s="92" t="s">
+        <v>248</v>
+      </c>
+      <c r="B66" s="17"/>
+      <c r="C66" s="29"/>
+      <c r="D66" s="288">
+        <v>150000</v>
+      </c>
+      <c r="E66" s="154" t="s">
+        <v>272</v>
+      </c>
+      <c r="F66" s="50"/>
+    </row>
+    <row r="67" spans="1:6" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A67" s="92" t="s">
+        <v>210</v>
+      </c>
+      <c r="B67" s="17"/>
+      <c r="C67" s="29"/>
+      <c r="D67" s="288">
+        <v>292300</v>
+      </c>
+      <c r="E67" s="168" t="s">
+        <v>255</v>
+      </c>
+      <c r="F67" s="50"/>
+    </row>
+    <row r="68" spans="1:6" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A68" s="92" t="s">
+        <v>210</v>
+      </c>
+      <c r="B68" s="17"/>
+      <c r="C68" s="29"/>
+      <c r="D68" s="288">
+        <v>467850</v>
+      </c>
+      <c r="E68" s="168" t="s">
+        <v>267</v>
+      </c>
+      <c r="F68" s="50"/>
+    </row>
+    <row r="69" spans="1:6" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A69" s="92" t="s">
+        <v>210</v>
+      </c>
+      <c r="B69" s="17"/>
+      <c r="C69" s="29"/>
+      <c r="D69" s="288">
+        <v>380000</v>
+      </c>
+      <c r="E69" s="168" t="s">
+        <v>274</v>
+      </c>
+      <c r="F69" s="50"/>
+    </row>
+    <row r="70" spans="1:6" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A70" s="235" t="s">
+        <v>263</v>
+      </c>
+      <c r="B70" s="236"/>
+      <c r="C70" s="29"/>
+      <c r="D70" s="288">
+        <v>25000</v>
+      </c>
+      <c r="E70" s="168" t="s">
+        <v>264</v>
+      </c>
+      <c r="F70" s="50"/>
+    </row>
+    <row r="71" spans="1:6" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A71" s="235" t="s">
+        <v>249</v>
+      </c>
+      <c r="B71" s="236"/>
+      <c r="C71" s="29"/>
+      <c r="D71" s="30">
         <v>105602.65</v>
       </c>
-      <c r="E64" s="168" t="s">
-        <v>211</v>
-      </c>
-      <c r="F64" s="50"/>
-    </row>
-    <row r="65" spans="1:7" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A65" s="222" t="s">
-        <v>226</v>
-      </c>
-      <c r="B65" s="223"/>
-      <c r="C65" s="29"/>
-      <c r="D65" s="30">
-        <v>105602.65</v>
-      </c>
-      <c r="E65" s="168" t="s">
-        <v>211</v>
-      </c>
-      <c r="F65" s="50"/>
-    </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A66" s="21" t="s">
-        <v>0</v>
-      </c>
-      <c r="B66" s="14"/>
-      <c r="C66" s="14"/>
-      <c r="D66" s="36"/>
-      <c r="E66" s="41">
-        <f>SUM(D53:D65)</f>
-        <v>6226295.3000000007</v>
-      </c>
-    </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A67" s="14" t="s">
+      <c r="E71" s="168" t="s">
+        <v>207</v>
+      </c>
+      <c r="F71" s="50"/>
+    </row>
+    <row r="72" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A72" s="21" t="s">
+        <v>0</v>
+      </c>
+      <c r="B72" s="14"/>
+      <c r="C72" s="14"/>
+      <c r="D72" s="36"/>
+      <c r="E72" s="41">
+        <f>SUM(D53:D71)</f>
+        <v>10372542.65</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A73" s="14" t="s">
         <v>113</v>
       </c>
-      <c r="B67" s="14"/>
-      <c r="C67" s="14"/>
-      <c r="D67" s="15"/>
-      <c r="E67" s="153"/>
-    </row>
-    <row r="68" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A68" s="222" t="s">
-        <v>229</v>
-      </c>
-      <c r="B68" s="223"/>
-      <c r="C68" s="18"/>
-      <c r="D68" s="179">
+      <c r="B73" s="14"/>
+      <c r="C73" s="14"/>
+      <c r="D73" s="15"/>
+      <c r="E73" s="153"/>
+    </row>
+    <row r="74" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A74" s="235" t="s">
+        <v>250</v>
+      </c>
+      <c r="B74" s="236"/>
+      <c r="C74" s="18"/>
+      <c r="D74" s="287">
         <v>650000</v>
       </c>
-      <c r="E68" s="154" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="69" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A69" s="16" t="s">
+      <c r="E74" s="154" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A75" s="16" t="s">
         <v>167</v>
       </c>
-      <c r="B69" s="17"/>
-      <c r="C69" s="18"/>
-      <c r="D69" s="180">
+      <c r="B75" s="17"/>
+      <c r="C75" s="18"/>
+      <c r="D75" s="293">
         <v>250000</v>
       </c>
-      <c r="E69" s="154" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="70" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A70" s="92" t="s">
-        <v>210</v>
-      </c>
-      <c r="B70" s="17"/>
-      <c r="C70" s="18"/>
-      <c r="D70" s="180">
+      <c r="E75" s="154" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A76" s="92" t="s">
+        <v>271</v>
+      </c>
+      <c r="B76" s="17"/>
+      <c r="C76" s="18"/>
+      <c r="D76" s="293">
+        <v>100000</v>
+      </c>
+      <c r="E76" s="154" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A77" s="92" t="s">
+        <v>251</v>
+      </c>
+      <c r="B77" s="17"/>
+      <c r="C77" s="18"/>
+      <c r="D77" s="179">
         <v>45000</v>
       </c>
-      <c r="E70" s="154" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A71" s="21" t="s">
+      <c r="E77" s="154" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A78" s="21" t="s">
         <v>105</v>
       </c>
-      <c r="B71" s="21"/>
-      <c r="C71" s="21"/>
-      <c r="D71" s="22"/>
-      <c r="E71" s="155">
-        <f>SUM(D68:D70)</f>
-        <v>945000</v>
-      </c>
-    </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A72" s="14" t="s">
+      <c r="B78" s="21"/>
+      <c r="C78" s="21"/>
+      <c r="D78" s="22"/>
+      <c r="E78" s="155">
+        <f>SUM(D74:D77)</f>
+        <v>1045000</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A79" s="14" t="s">
         <v>114</v>
       </c>
-      <c r="B72" s="37"/>
-      <c r="C72" s="21"/>
-      <c r="D72" s="38"/>
-      <c r="E72" s="41"/>
-    </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A73" s="29" t="s">
+      <c r="B79" s="37"/>
+      <c r="C79" s="21"/>
+      <c r="D79" s="38"/>
+      <c r="E79" s="41"/>
+    </row>
+    <row r="80" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A80" s="29" t="s">
         <v>150</v>
       </c>
-      <c r="B73" s="91"/>
-      <c r="C73" s="91"/>
-      <c r="D73" s="125">
+      <c r="B80" s="91"/>
+      <c r="C80" s="91"/>
+      <c r="D80" s="125">
         <v>52000</v>
       </c>
-      <c r="E73" s="162"/>
-    </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A74" s="29" t="s">
+      <c r="E80" s="162"/>
+    </row>
+    <row r="81" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A81" s="29" t="s">
         <v>151</v>
       </c>
-      <c r="B74" s="91"/>
-      <c r="C74" s="91"/>
-      <c r="D74" s="125">
+      <c r="B81" s="91"/>
+      <c r="C81" s="91"/>
+      <c r="D81" s="125">
         <v>208770.83</v>
       </c>
-      <c r="E74" s="162"/>
-    </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A75" s="39" t="s">
+      <c r="E81" s="162"/>
+    </row>
+    <row r="82" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A82" s="39" t="s">
         <v>105</v>
       </c>
-      <c r="B75" s="39"/>
-      <c r="C75" s="39"/>
-      <c r="D75" s="40"/>
-      <c r="E75" s="41">
-        <f>SUM(D73:D74)</f>
+      <c r="B82" s="39"/>
+      <c r="C82" s="39"/>
+      <c r="D82" s="40"/>
+      <c r="E82" s="41">
+        <f>SUM(D80:D81)</f>
         <v>260770.83</v>
       </c>
     </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A76" s="29"/>
-      <c r="B76" s="29"/>
-      <c r="C76" s="29"/>
-      <c r="D76" s="42"/>
-      <c r="E76" s="43"/>
-    </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A77" s="44" t="s">
+    <row r="83" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A83" s="29"/>
+      <c r="B83" s="29"/>
+      <c r="C83" s="29"/>
+      <c r="D83" s="42"/>
+      <c r="E83" s="43"/>
+    </row>
+    <row r="84" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A84" s="44" t="s">
         <v>115</v>
       </c>
-      <c r="B77" s="44"/>
-      <c r="C77" s="44"/>
-      <c r="D77" s="45"/>
-      <c r="E77" s="46"/>
-    </row>
-    <row r="78" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A78" s="47"/>
-      <c r="D78" s="48"/>
-      <c r="E78" s="49"/>
-      <c r="F78" s="50"/>
-    </row>
-    <row r="79" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A79" s="51" t="s">
+      <c r="B84" s="44"/>
+      <c r="C84" s="44"/>
+      <c r="D84" s="45"/>
+      <c r="E84" s="46"/>
+    </row>
+    <row r="85" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A85" s="47"/>
+      <c r="D85" s="48"/>
+      <c r="E85" s="49"/>
+      <c r="F85" s="50"/>
+    </row>
+    <row r="86" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A86" s="51" t="s">
         <v>116</v>
       </c>
-      <c r="B79" s="52"/>
-      <c r="C79" s="53"/>
-      <c r="D79" s="54"/>
-      <c r="E79" s="55">
-        <f>(SUM(E21:E77))</f>
-        <v>15658750.57</v>
-      </c>
-      <c r="F79" s="56"/>
-      <c r="G79" s="50"/>
-    </row>
-    <row r="80" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="D80" s="48"/>
-      <c r="E80" s="48"/>
-    </row>
-    <row r="81" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="D81" s="48"/>
-      <c r="E81" s="48"/>
-      <c r="H81" s="57"/>
-    </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A82" s="11" t="s">
-        <v>117</v>
-      </c>
-      <c r="B82" s="12"/>
-      <c r="C82" s="13"/>
-      <c r="D82" s="58"/>
-      <c r="E82" s="59"/>
-    </row>
-    <row r="83" spans="1:8" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A83" s="224" t="s">
-        <v>222</v>
-      </c>
-      <c r="B83" s="225"/>
-      <c r="C83" s="29"/>
-      <c r="D83" s="228">
-        <v>2015700</v>
-      </c>
-      <c r="E83" s="230" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="84" spans="1:8" ht="1.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A84" s="226"/>
-      <c r="B84" s="227"/>
-      <c r="C84" s="29"/>
-      <c r="D84" s="229"/>
-      <c r="E84" s="231"/>
-    </row>
-    <row r="85" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D85" s="42"/>
-      <c r="E85" s="42"/>
-    </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A86" s="24"/>
-      <c r="B86" s="61"/>
-      <c r="C86" s="29"/>
-      <c r="D86" s="35"/>
-      <c r="E86" s="60"/>
+      <c r="B86" s="52"/>
+      <c r="C86" s="53"/>
+      <c r="D86" s="54"/>
+      <c r="E86" s="55">
+        <f>(SUM(E21:E84))</f>
+        <v>20919805.879999999</v>
+      </c>
+      <c r="F86" s="56"/>
+      <c r="G86" s="50"/>
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A87" s="62" t="s">
-        <v>146</v>
-      </c>
-      <c r="B87" s="63"/>
-      <c r="C87" s="63"/>
-      <c r="D87" s="116"/>
-      <c r="E87" s="163">
-        <f>SUM(D83:D86)</f>
-        <v>2015700</v>
-      </c>
-    </row>
-    <row r="88" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D87" s="48"/>
+      <c r="E87" s="48"/>
+    </row>
+    <row r="88" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D88" s="48"/>
       <c r="E88" s="48"/>
-    </row>
-    <row r="89" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
-      <c r="D89" s="48"/>
-      <c r="E89" s="48"/>
-    </row>
-    <row r="90" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A90" s="44" t="s">
+      <c r="H88" s="57"/>
+    </row>
+    <row r="89" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A89" s="11" t="s">
+        <v>117</v>
+      </c>
+      <c r="B89" s="12"/>
+      <c r="C89" s="13"/>
+      <c r="D89" s="58"/>
+      <c r="E89" s="59"/>
+    </row>
+    <row r="90" spans="1:8" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A90" s="243" t="s">
+        <v>212</v>
+      </c>
+      <c r="B90" s="244"/>
+      <c r="C90" s="29"/>
+      <c r="D90" s="247">
+        <v>2015700</v>
+      </c>
+      <c r="E90" s="229" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="91" spans="1:8" ht="1.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A91" s="245"/>
+      <c r="B91" s="246"/>
+      <c r="C91" s="29"/>
+      <c r="D91" s="248"/>
+      <c r="E91" s="230"/>
+    </row>
+    <row r="92" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D92" s="42"/>
+      <c r="E92" s="42"/>
+    </row>
+    <row r="93" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A93" s="24"/>
+      <c r="B93" s="61"/>
+      <c r="C93" s="29"/>
+      <c r="D93" s="35"/>
+      <c r="E93" s="60"/>
+    </row>
+    <row r="94" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A94" s="62" t="s">
+        <v>146</v>
+      </c>
+      <c r="B94" s="63"/>
+      <c r="C94" s="63"/>
+      <c r="D94" s="116"/>
+      <c r="E94" s="163">
+        <f>SUM(D90:D93)</f>
+        <v>2015700</v>
+      </c>
+    </row>
+    <row r="95" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D95" s="48"/>
+      <c r="E95" s="48"/>
+    </row>
+    <row r="96" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="D96" s="48"/>
+      <c r="E96" s="48"/>
+    </row>
+    <row r="97" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A97" s="44" t="s">
         <v>118</v>
       </c>
-      <c r="B90" s="44"/>
-      <c r="C90" s="44"/>
-      <c r="D90" s="45"/>
-      <c r="E90" s="167">
+      <c r="B97" s="44"/>
+      <c r="C97" s="44"/>
+      <c r="D97" s="45"/>
+      <c r="E97" s="167">
         <f>3000000-2015700</f>
         <v>984300</v>
       </c>
     </row>
-    <row r="91" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="D91" s="48"/>
-      <c r="E91" s="48"/>
-    </row>
-    <row r="92" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A92" s="51" t="s">
-        <v>119</v>
-      </c>
-      <c r="B92" s="52"/>
-      <c r="C92" s="53"/>
-      <c r="D92" s="54"/>
-      <c r="E92" s="55">
-        <f>E87+E90</f>
-        <v>3000000</v>
-      </c>
-    </row>
-    <row r="93" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="D93" s="48"/>
-      <c r="E93" s="48"/>
-    </row>
-    <row r="94" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A94" s="64" t="s">
-        <v>120</v>
-      </c>
-      <c r="B94" s="65">
-        <f>E79</f>
-        <v>15658750.57</v>
-      </c>
-      <c r="D94" s="48"/>
-      <c r="E94" s="48"/>
-    </row>
-    <row r="95" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A95" s="64" t="s">
-        <v>121</v>
-      </c>
-      <c r="B95" s="65">
-        <f>E79-E77</f>
-        <v>15658750.57</v>
-      </c>
-      <c r="D95" s="48"/>
-      <c r="E95" s="48"/>
-    </row>
-    <row r="96" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A96" s="64" t="s">
-        <v>122</v>
-      </c>
-      <c r="B96" s="65">
-        <f>E92-E90</f>
-        <v>2015700</v>
-      </c>
-      <c r="D96" s="48"/>
-      <c r="E96" s="48"/>
-    </row>
-    <row r="97" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A97" s="64" t="s">
-        <v>123</v>
-      </c>
-      <c r="B97" s="65">
-        <f>E92</f>
-        <v>3000000</v>
-      </c>
-      <c r="D97" s="48"/>
-      <c r="E97" s="48"/>
-    </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D98" s="48"/>
       <c r="E98" s="48"/>
     </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="D99" s="48"/>
-      <c r="E99" s="48"/>
-    </row>
-    <row r="100" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A100" s="232" t="s">
-        <v>177</v>
-      </c>
-      <c r="B100" s="232"/>
+    <row r="99" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A99" s="51" t="s">
+        <v>119</v>
+      </c>
+      <c r="B99" s="52"/>
+      <c r="C99" s="53"/>
+      <c r="D99" s="54"/>
+      <c r="E99" s="55">
+        <f>E94+E97</f>
+        <v>3000000</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D100" s="48"/>
       <c r="E100" s="48"/>
     </row>
-    <row r="101" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A101" s="232"/>
-      <c r="B101" s="232"/>
+    <row r="101" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A101" s="64" t="s">
+        <v>120</v>
+      </c>
+      <c r="B101" s="65">
+        <f>E86</f>
+        <v>20919805.879999999</v>
+      </c>
       <c r="D101" s="48"/>
       <c r="E101" s="48"/>
     </row>
-    <row r="102" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A102" s="232"/>
-      <c r="B102" s="232"/>
+    <row r="102" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A102" s="64" t="s">
+        <v>121</v>
+      </c>
+      <c r="B102" s="65">
+        <f>E86-E84</f>
+        <v>20919805.879999999</v>
+      </c>
       <c r="D102" s="48"/>
       <c r="E102" s="48"/>
     </row>
-    <row r="103" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A103" s="64" t="s">
+        <v>122</v>
+      </c>
+      <c r="B103" s="65">
+        <f>E99-E97</f>
+        <v>2015700</v>
+      </c>
       <c r="D103" s="48"/>
       <c r="E103" s="48"/>
     </row>
-    <row r="104" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A104" s="232" t="s">
-        <v>207</v>
-      </c>
-      <c r="B104" s="232"/>
+    <row r="104" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A104" s="64" t="s">
+        <v>123</v>
+      </c>
+      <c r="B104" s="65">
+        <f>E99</f>
+        <v>3000000</v>
+      </c>
       <c r="D104" s="48"/>
       <c r="E104" s="48"/>
     </row>
-    <row r="105" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A105" s="232"/>
-      <c r="B105" s="232"/>
+    <row r="105" spans="1:5" x14ac:dyDescent="0.3">
       <c r="D105" s="48"/>
       <c r="E105" s="48"/>
     </row>
-    <row r="106" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A106" s="232"/>
-      <c r="B106" s="232"/>
+    <row r="106" spans="1:5" x14ac:dyDescent="0.3">
       <c r="D106" s="48"/>
       <c r="E106" s="48"/>
     </row>
-    <row r="107" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A107" s="228" t="s">
+        <v>176</v>
+      </c>
+      <c r="B107" s="228"/>
       <c r="D107" s="48"/>
       <c r="E107" s="48"/>
     </row>
-    <row r="108" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A108" s="232" t="s">
-        <v>184</v>
-      </c>
-      <c r="B108" s="232"/>
+    <row r="108" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A108" s="228"/>
+      <c r="B108" s="228"/>
       <c r="D108" s="48"/>
       <c r="E108" s="48"/>
     </row>
-    <row r="109" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A109" s="232"/>
-      <c r="B109" s="232"/>
+    <row r="109" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A109" s="228"/>
+      <c r="B109" s="228"/>
       <c r="D109" s="48"/>
       <c r="E109" s="48"/>
     </row>
-    <row r="110" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A110" s="232"/>
-      <c r="B110" s="232"/>
+    <row r="110" spans="1:5" x14ac:dyDescent="0.3">
       <c r="D110" s="48"/>
       <c r="E110" s="48"/>
     </row>
-    <row r="111" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A111" s="228" t="s">
+        <v>206</v>
+      </c>
+      <c r="B111" s="228"/>
       <c r="D111" s="48"/>
       <c r="E111" s="48"/>
     </row>
-    <row r="112" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A112" s="232" t="s">
-        <v>187</v>
-      </c>
-      <c r="B112" s="232"/>
+    <row r="112" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A112" s="228"/>
+      <c r="B112" s="228"/>
       <c r="D112" s="48"/>
       <c r="E112" s="48"/>
     </row>
-    <row r="113" spans="1:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A113" s="232"/>
-      <c r="B113" s="232"/>
+    <row r="113" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A113" s="228"/>
+      <c r="B113" s="228"/>
       <c r="D113" s="48"/>
       <c r="E113" s="48"/>
     </row>
-    <row r="114" spans="1:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A114" s="232"/>
-      <c r="B114" s="232"/>
+    <row r="114" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D114" s="48"/>
       <c r="E114" s="48"/>
     </row>
-    <row r="115" spans="1:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A115" s="228" t="s">
+        <v>183</v>
+      </c>
+      <c r="B115" s="228"/>
       <c r="D115" s="48"/>
       <c r="E115" s="48"/>
     </row>
-    <row r="116" spans="1:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A116" s="232" t="s">
-        <v>186</v>
-      </c>
-      <c r="B116" s="232"/>
+    <row r="116" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A116" s="228"/>
+      <c r="B116" s="228"/>
       <c r="D116" s="48"/>
       <c r="E116" s="48"/>
     </row>
-    <row r="117" spans="1:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A117" s="232"/>
-      <c r="B117" s="232"/>
+    <row r="117" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A117" s="228"/>
+      <c r="B117" s="228"/>
       <c r="D117" s="48"/>
       <c r="E117" s="48"/>
     </row>
-    <row r="118" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A118" s="232"/>
-      <c r="B118" s="232"/>
+    <row r="118" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D118" s="48"/>
       <c r="E118" s="48"/>
     </row>
-    <row r="119" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A119" s="228" t="s">
+        <v>186</v>
+      </c>
+      <c r="B119" s="228"/>
       <c r="D119" s="48"/>
       <c r="E119" s="48"/>
     </row>
-    <row r="120" spans="1:6" s="68" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A120"/>
-      <c r="B120" s="66"/>
-      <c r="C120" s="67"/>
-      <c r="D120" s="164"/>
-      <c r="E120" s="164"/>
-    </row>
-    <row r="121" spans="1:6" s="68" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A121" s="170" t="s">
-        <v>196</v>
-      </c>
-      <c r="B121" s="69">
-        <v>-846287.22</v>
-      </c>
-      <c r="C121" s="67"/>
-      <c r="D121" s="165"/>
-      <c r="E121" s="165"/>
-    </row>
-    <row r="122" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A122" s="26" t="s">
-        <v>145</v>
-      </c>
-      <c r="B122" s="70">
-        <f>-B95-B96</f>
-        <v>-17674450.57</v>
-      </c>
+    <row r="120" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A120" s="228"/>
+      <c r="B120" s="228"/>
+      <c r="D120" s="48"/>
+      <c r="E120" s="48"/>
+    </row>
+    <row r="121" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A121" s="228"/>
+      <c r="B121" s="228"/>
+      <c r="D121" s="48"/>
+      <c r="E121" s="48"/>
+    </row>
+    <row r="122" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D122" s="48"/>
       <c r="E122" s="48"/>
     </row>
-    <row r="123" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A123" s="26" t="s">
-        <v>124</v>
-      </c>
-      <c r="B123" s="70">
-        <f>B135</f>
-        <v>0</v>
-      </c>
+    <row r="123" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A123" s="228" t="s">
+        <v>185</v>
+      </c>
+      <c r="B123" s="228"/>
       <c r="D123" s="48"/>
       <c r="E123" s="48"/>
-      <c r="F123" s="66"/>
-    </row>
-    <row r="124" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A124" s="26" t="s">
+    </row>
+    <row r="124" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A124" s="228"/>
+      <c r="B124" s="228"/>
+      <c r="D124" s="48"/>
+      <c r="E124" s="48"/>
+    </row>
+    <row r="125" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A125" s="228"/>
+      <c r="B125" s="228"/>
+      <c r="D125" s="48"/>
+      <c r="E125" s="48"/>
+    </row>
+    <row r="126" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="D126" s="48"/>
+      <c r="E126" s="48"/>
+    </row>
+    <row r="127" spans="1:5" s="68" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A127"/>
+      <c r="B127" s="66"/>
+      <c r="C127" s="67"/>
+      <c r="D127" s="164"/>
+      <c r="E127" s="164"/>
+    </row>
+    <row r="128" spans="1:5" s="68" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A128" s="170" t="s">
+        <v>195</v>
+      </c>
+      <c r="B128" s="69">
+        <v>-846287.22</v>
+      </c>
+      <c r="C128" s="67"/>
+      <c r="D128" s="165"/>
+      <c r="E128" s="165"/>
+    </row>
+    <row r="129" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A129" s="26" t="s">
+        <v>145</v>
+      </c>
+      <c r="B129" s="70">
+        <f>-B102-B103</f>
+        <v>-22935505.879999999</v>
+      </c>
+      <c r="D129" s="48"/>
+      <c r="E129" s="48"/>
+    </row>
+    <row r="130" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A130" s="26" t="s">
+        <v>124</v>
+      </c>
+      <c r="B130" s="70">
+        <f>B143</f>
+        <v>0</v>
+      </c>
+      <c r="D130" s="48"/>
+      <c r="E130" s="48"/>
+      <c r="F130" s="66"/>
+    </row>
+    <row r="131" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A131" s="26" t="s">
         <v>2</v>
       </c>
-      <c r="B124" s="71">
+      <c r="B131" s="71">
         <f>PRORRATEO!F117</f>
         <v>17773395.250000004</v>
       </c>
-      <c r="D124" s="48"/>
-      <c r="E124" s="48"/>
-      <c r="F124" s="66"/>
-    </row>
-    <row r="125" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A125" s="26" t="s">
-        <v>247</v>
-      </c>
-      <c r="B125" s="147">
+      <c r="D131" s="48"/>
+      <c r="E131" s="48"/>
+      <c r="F131" s="66"/>
+    </row>
+    <row r="132" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A132" s="26" t="s">
+        <v>256</v>
+      </c>
+      <c r="B132" s="147">
+        <v>-95000</v>
+      </c>
+      <c r="D132" s="48"/>
+      <c r="E132" s="48"/>
+      <c r="F132" s="66"/>
+    </row>
+    <row r="133" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A133" s="26" t="s">
+        <v>232</v>
+      </c>
+      <c r="B133" s="147">
         <v>-101088</v>
       </c>
-      <c r="D125" s="48"/>
-      <c r="E125" s="48"/>
-      <c r="F125" s="66"/>
-    </row>
-    <row r="126" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A126" s="26" t="s">
-        <v>231</v>
-      </c>
-      <c r="B126" s="71">
+      <c r="D133" s="48"/>
+      <c r="E133" s="48"/>
+      <c r="F133" s="66"/>
+    </row>
+    <row r="134" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A134" s="26" t="s">
+        <v>217</v>
+      </c>
+      <c r="B134" s="71">
         <v>400000</v>
       </c>
-      <c r="D126" s="48"/>
-      <c r="E126" s="48"/>
-      <c r="F126" s="66"/>
-    </row>
-    <row r="127" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A127" s="26" t="s">
-        <v>235</v>
-      </c>
-      <c r="B127" s="147">
+      <c r="D134" s="48"/>
+      <c r="E134" s="48"/>
+      <c r="F134" s="66"/>
+    </row>
+    <row r="135" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A135" s="26" t="s">
+        <v>221</v>
+      </c>
+      <c r="B135" s="147">
         <v>-90199</v>
       </c>
-      <c r="D127" s="48"/>
-      <c r="E127" s="48"/>
-      <c r="F127" s="66"/>
-    </row>
-    <row r="128" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A128" s="26" t="s">
-        <v>238</v>
-      </c>
-      <c r="B128" s="147">
+      <c r="D135" s="48"/>
+      <c r="E135" s="48"/>
+      <c r="F135" s="66"/>
+    </row>
+    <row r="136" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A136" s="26" t="s">
+        <v>224</v>
+      </c>
+      <c r="B136" s="147">
         <v>-130000</v>
       </c>
-      <c r="D128" s="48"/>
-      <c r="E128" s="48"/>
-      <c r="F128" s="66"/>
-    </row>
-    <row r="129" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A129" s="72" t="s">
+      <c r="D136" s="48"/>
+      <c r="E136" s="48"/>
+      <c r="F136" s="66"/>
+    </row>
+    <row r="137" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A137" s="72" t="s">
         <v>164</v>
       </c>
-      <c r="B129" s="73">
-        <f>SUM(B121:C128)</f>
-        <v>-668629.53999999538</v>
-      </c>
-      <c r="D129" s="66"/>
-      <c r="E129" s="50"/>
-      <c r="F129" s="50"/>
-    </row>
-    <row r="130" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="131" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A131" s="243" t="s">
+      <c r="B137" s="73">
+        <f>SUM(B128:C136)</f>
+        <v>-6024684.849999994</v>
+      </c>
+      <c r="D137" s="66"/>
+      <c r="E137" s="50"/>
+      <c r="F137" s="50"/>
+    </row>
+    <row r="138" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="139" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A139" s="227" t="s">
         <v>125</v>
       </c>
-      <c r="B131" s="243"/>
-      <c r="C131" s="243"/>
-    </row>
-    <row r="132" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A132" s="243"/>
-      <c r="B132" s="243"/>
-      <c r="C132" s="243"/>
-    </row>
-    <row r="133" spans="1:13" ht="27" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A133" s="74"/>
-      <c r="B133" s="115"/>
-      <c r="C133" s="75"/>
-      <c r="D133" s="56"/>
-    </row>
-    <row r="134" spans="1:13" ht="27" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A134" s="148"/>
-      <c r="B134" s="115"/>
-      <c r="C134" s="75"/>
-      <c r="D134" s="56"/>
-    </row>
-    <row r="135" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A135" s="76" t="s">
-        <v>0</v>
-      </c>
-      <c r="B135" s="77">
-        <f>SUM(B133:B134)</f>
-        <v>0</v>
-      </c>
-      <c r="C135" s="78"/>
-    </row>
-    <row r="136" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="M136" s="79"/>
+      <c r="B139" s="227"/>
+      <c r="C139" s="227"/>
+    </row>
+    <row r="140" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A140" s="227"/>
+      <c r="B140" s="227"/>
+      <c r="C140" s="227"/>
+    </row>
+    <row r="141" spans="1:13" ht="27" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A141" s="74"/>
+      <c r="B141" s="115"/>
+      <c r="C141" s="75"/>
+      <c r="D141" s="56"/>
+    </row>
+    <row r="142" spans="1:13" ht="27" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A142" s="148"/>
+      <c r="B142" s="115"/>
+      <c r="C142" s="75"/>
+      <c r="D142" s="56"/>
+    </row>
+    <row r="143" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A143" s="76" t="s">
+        <v>0</v>
+      </c>
+      <c r="B143" s="77">
+        <f>SUM(B141:B142)</f>
+        <v>0</v>
+      </c>
+      <c r="C143" s="78"/>
+    </row>
+    <row r="144" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="M144" s="79"/>
     </row>
   </sheetData>
   <mergeCells count="25">
-    <mergeCell ref="A131:C132"/>
-    <mergeCell ref="A104:B106"/>
-    <mergeCell ref="A116:B118"/>
-    <mergeCell ref="A112:B114"/>
-    <mergeCell ref="A100:B102"/>
-    <mergeCell ref="E83:E84"/>
-    <mergeCell ref="A108:B110"/>
+    <mergeCell ref="A54:B54"/>
+    <mergeCell ref="A71:B71"/>
+    <mergeCell ref="A90:B91"/>
+    <mergeCell ref="D90:D91"/>
+    <mergeCell ref="E90:E91"/>
+    <mergeCell ref="A115:B117"/>
     <mergeCell ref="B1:E1"/>
     <mergeCell ref="A24:B24"/>
-    <mergeCell ref="A68:B68"/>
+    <mergeCell ref="A74:B74"/>
     <mergeCell ref="B3:E3"/>
     <mergeCell ref="B8:C10"/>
     <mergeCell ref="A13:E16"/>
@@ -3848,13 +4009,14 @@
     <mergeCell ref="A49:B49"/>
     <mergeCell ref="A41:B41"/>
     <mergeCell ref="A42:B42"/>
-    <mergeCell ref="A64:B64"/>
+    <mergeCell ref="A70:B70"/>
     <mergeCell ref="A53:B53"/>
     <mergeCell ref="A55:B55"/>
-    <mergeCell ref="A54:B54"/>
-    <mergeCell ref="A65:B65"/>
-    <mergeCell ref="A83:B84"/>
-    <mergeCell ref="D83:D84"/>
+    <mergeCell ref="A139:C140"/>
+    <mergeCell ref="A111:B113"/>
+    <mergeCell ref="A123:B125"/>
+    <mergeCell ref="A119:B121"/>
+    <mergeCell ref="A107:B109"/>
   </mergeCells>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="5" scale="90" orientation="portrait" r:id="rId1"/>
@@ -3889,16 +4051,16 @@
       <c r="A1" s="93"/>
       <c r="B1" s="94"/>
       <c r="C1" s="94"/>
-      <c r="D1" s="251"/>
-      <c r="E1" s="251"/>
-      <c r="F1" s="251"/>
-      <c r="G1" s="251"/>
-      <c r="H1" s="251"/>
-      <c r="I1" s="251"/>
-      <c r="J1" s="251"/>
-      <c r="K1" s="251"/>
-      <c r="L1" s="251"/>
-      <c r="M1" s="251"/>
+      <c r="D1" s="259"/>
+      <c r="E1" s="259"/>
+      <c r="F1" s="259"/>
+      <c r="G1" s="259"/>
+      <c r="H1" s="259"/>
+      <c r="I1" s="259"/>
+      <c r="J1" s="259"/>
+      <c r="K1" s="259"/>
+      <c r="L1" s="259"/>
+      <c r="M1" s="259"/>
       <c r="N1" s="95"/>
     </row>
     <row r="2" spans="1:16" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
@@ -3908,10 +4070,10 @@
       <c r="D2" s="98" t="s">
         <v>126</v>
       </c>
-      <c r="E2" s="273">
+      <c r="E2" s="249">
         <v>3000000</v>
       </c>
-      <c r="F2" s="273"/>
+      <c r="F2" s="249"/>
       <c r="G2" s="98"/>
       <c r="H2" s="98"/>
       <c r="I2" s="98" t="s">
@@ -3948,189 +4110,189 @@
       <c r="O3" s="80"/>
     </row>
     <row r="4" spans="1:16" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="252" t="s">
+      <c r="A4" s="260" t="s">
         <v>163</v>
       </c>
-      <c r="B4" s="253"/>
-      <c r="C4" s="253"/>
-      <c r="D4" s="253"/>
-      <c r="E4" s="253"/>
-      <c r="F4" s="253"/>
-      <c r="G4" s="253"/>
-      <c r="H4" s="253"/>
-      <c r="I4" s="253"/>
-      <c r="J4" s="253"/>
-      <c r="K4" s="253"/>
-      <c r="L4" s="253"/>
-      <c r="M4" s="253"/>
-      <c r="N4" s="254"/>
+      <c r="B4" s="261"/>
+      <c r="C4" s="261"/>
+      <c r="D4" s="261"/>
+      <c r="E4" s="261"/>
+      <c r="F4" s="261"/>
+      <c r="G4" s="261"/>
+      <c r="H4" s="261"/>
+      <c r="I4" s="261"/>
+      <c r="J4" s="261"/>
+      <c r="K4" s="261"/>
+      <c r="L4" s="261"/>
+      <c r="M4" s="261"/>
+      <c r="N4" s="262"/>
       <c r="O4" s="80"/>
     </row>
     <row r="5" spans="1:16" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="255"/>
-      <c r="B5" s="256"/>
-      <c r="C5" s="256"/>
-      <c r="D5" s="256"/>
-      <c r="E5" s="256"/>
-      <c r="F5" s="256"/>
-      <c r="G5" s="256"/>
-      <c r="H5" s="256"/>
-      <c r="I5" s="256"/>
-      <c r="J5" s="256"/>
-      <c r="K5" s="256"/>
-      <c r="L5" s="256"/>
-      <c r="M5" s="256"/>
-      <c r="N5" s="257"/>
+      <c r="A5" s="263"/>
+      <c r="B5" s="264"/>
+      <c r="C5" s="264"/>
+      <c r="D5" s="264"/>
+      <c r="E5" s="264"/>
+      <c r="F5" s="264"/>
+      <c r="G5" s="264"/>
+      <c r="H5" s="264"/>
+      <c r="I5" s="264"/>
+      <c r="J5" s="264"/>
+      <c r="K5" s="264"/>
+      <c r="L5" s="264"/>
+      <c r="M5" s="264"/>
+      <c r="N5" s="265"/>
       <c r="O5" s="80"/>
     </row>
     <row r="6" spans="1:16" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="255"/>
-      <c r="B6" s="256"/>
-      <c r="C6" s="256"/>
-      <c r="D6" s="256"/>
-      <c r="E6" s="256"/>
-      <c r="F6" s="256"/>
-      <c r="G6" s="256"/>
-      <c r="H6" s="256"/>
-      <c r="I6" s="256"/>
-      <c r="J6" s="256"/>
-      <c r="K6" s="256"/>
-      <c r="L6" s="256"/>
-      <c r="M6" s="256"/>
-      <c r="N6" s="257"/>
+      <c r="A6" s="263"/>
+      <c r="B6" s="264"/>
+      <c r="C6" s="264"/>
+      <c r="D6" s="264"/>
+      <c r="E6" s="264"/>
+      <c r="F6" s="264"/>
+      <c r="G6" s="264"/>
+      <c r="H6" s="264"/>
+      <c r="I6" s="264"/>
+      <c r="J6" s="264"/>
+      <c r="K6" s="264"/>
+      <c r="L6" s="264"/>
+      <c r="M6" s="264"/>
+      <c r="N6" s="265"/>
       <c r="O6" s="80"/>
     </row>
     <row r="7" spans="1:16" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="255"/>
-      <c r="B7" s="256"/>
-      <c r="C7" s="256"/>
-      <c r="D7" s="256"/>
-      <c r="E7" s="256"/>
-      <c r="F7" s="256"/>
-      <c r="G7" s="256"/>
-      <c r="H7" s="256"/>
-      <c r="I7" s="256"/>
-      <c r="J7" s="256"/>
-      <c r="K7" s="256"/>
-      <c r="L7" s="256"/>
-      <c r="M7" s="256"/>
-      <c r="N7" s="257"/>
+      <c r="A7" s="263"/>
+      <c r="B7" s="264"/>
+      <c r="C7" s="264"/>
+      <c r="D7" s="264"/>
+      <c r="E7" s="264"/>
+      <c r="F7" s="264"/>
+      <c r="G7" s="264"/>
+      <c r="H7" s="264"/>
+      <c r="I7" s="264"/>
+      <c r="J7" s="264"/>
+      <c r="K7" s="264"/>
+      <c r="L7" s="264"/>
+      <c r="M7" s="264"/>
+      <c r="N7" s="265"/>
       <c r="O7" s="80"/>
     </row>
     <row r="8" spans="1:16" ht="192" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="258"/>
-      <c r="B8" s="259"/>
-      <c r="C8" s="259"/>
-      <c r="D8" s="259"/>
-      <c r="E8" s="259"/>
-      <c r="F8" s="259"/>
-      <c r="G8" s="259"/>
-      <c r="H8" s="259"/>
-      <c r="I8" s="259"/>
-      <c r="J8" s="259"/>
-      <c r="K8" s="259"/>
-      <c r="L8" s="259"/>
-      <c r="M8" s="259"/>
-      <c r="N8" s="260"/>
+      <c r="A8" s="266"/>
+      <c r="B8" s="267"/>
+      <c r="C8" s="267"/>
+      <c r="D8" s="267"/>
+      <c r="E8" s="267"/>
+      <c r="F8" s="267"/>
+      <c r="G8" s="267"/>
+      <c r="H8" s="267"/>
+      <c r="I8" s="267"/>
+      <c r="J8" s="267"/>
+      <c r="K8" s="267"/>
+      <c r="L8" s="267"/>
+      <c r="M8" s="267"/>
+      <c r="N8" s="268"/>
     </row>
     <row r="9" spans="1:16" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="267" t="s">
+      <c r="A9" s="275" t="s">
         <v>161</v>
       </c>
-      <c r="B9" s="268"/>
-      <c r="C9" s="268"/>
-      <c r="D9" s="268"/>
-      <c r="E9" s="268"/>
-      <c r="F9" s="268"/>
-      <c r="G9" s="268"/>
-      <c r="H9" s="268"/>
-      <c r="I9" s="268"/>
-      <c r="J9" s="268"/>
-      <c r="K9" s="268"/>
-      <c r="L9" s="268"/>
-      <c r="M9" s="268"/>
-      <c r="N9" s="269"/>
+      <c r="B9" s="276"/>
+      <c r="C9" s="276"/>
+      <c r="D9" s="276"/>
+      <c r="E9" s="276"/>
+      <c r="F9" s="276"/>
+      <c r="G9" s="276"/>
+      <c r="H9" s="276"/>
+      <c r="I9" s="276"/>
+      <c r="J9" s="276"/>
+      <c r="K9" s="276"/>
+      <c r="L9" s="276"/>
+      <c r="M9" s="276"/>
+      <c r="N9" s="277"/>
     </row>
     <row r="10" spans="1:16" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="270" t="s">
+      <c r="A10" s="278" t="s">
         <v>162</v>
       </c>
-      <c r="B10" s="271"/>
-      <c r="C10" s="271"/>
-      <c r="D10" s="271"/>
-      <c r="E10" s="271"/>
-      <c r="F10" s="271"/>
-      <c r="G10" s="271"/>
-      <c r="H10" s="271"/>
-      <c r="I10" s="271"/>
-      <c r="J10" s="271"/>
-      <c r="K10" s="271"/>
-      <c r="L10" s="271"/>
-      <c r="M10" s="271"/>
-      <c r="N10" s="272"/>
+      <c r="B10" s="279"/>
+      <c r="C10" s="279"/>
+      <c r="D10" s="279"/>
+      <c r="E10" s="279"/>
+      <c r="F10" s="279"/>
+      <c r="G10" s="279"/>
+      <c r="H10" s="279"/>
+      <c r="I10" s="279"/>
+      <c r="J10" s="279"/>
+      <c r="K10" s="279"/>
+      <c r="L10" s="279"/>
+      <c r="M10" s="279"/>
+      <c r="N10" s="280"/>
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A11" s="261" t="s">
+      <c r="A11" s="269" t="s">
         <v>128</v>
       </c>
-      <c r="B11" s="263" t="s">
+      <c r="B11" s="271" t="s">
         <v>129</v>
       </c>
-      <c r="C11" s="263" t="s">
+      <c r="C11" s="271" t="s">
         <v>130</v>
       </c>
-      <c r="D11" s="263" t="s">
+      <c r="D11" s="271" t="s">
         <v>131</v>
       </c>
-      <c r="E11" s="246" t="s">
+      <c r="E11" s="250" t="s">
         <v>132</v>
       </c>
-      <c r="F11" s="263" t="s">
+      <c r="F11" s="271" t="s">
         <v>133</v>
       </c>
-      <c r="G11" s="265" t="s">
+      <c r="G11" s="273" t="s">
         <v>134</v>
       </c>
-      <c r="H11" s="246" t="s">
+      <c r="H11" s="250" t="s">
         <v>135</v>
       </c>
-      <c r="I11" s="246" t="s">
+      <c r="I11" s="250" t="s">
         <v>127</v>
       </c>
-      <c r="J11" s="246" t="s">
+      <c r="J11" s="250" t="s">
         <v>126</v>
       </c>
-      <c r="K11" s="274" t="s">
-        <v>179</v>
-      </c>
-      <c r="L11" s="244" t="s">
-        <v>185</v>
+      <c r="K11" s="252" t="s">
+        <v>178</v>
+      </c>
+      <c r="L11" s="254" t="s">
+        <v>184</v>
       </c>
       <c r="M11" s="144" t="s">
         <v>136</v>
       </c>
-      <c r="N11" s="248" t="s">
+      <c r="N11" s="256" t="s">
         <v>137</v>
       </c>
     </row>
     <row r="12" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="262"/>
-      <c r="B12" s="264"/>
-      <c r="C12" s="264"/>
-      <c r="D12" s="264"/>
-      <c r="E12" s="247"/>
-      <c r="F12" s="264"/>
-      <c r="G12" s="266"/>
-      <c r="H12" s="247"/>
-      <c r="I12" s="247"/>
-      <c r="J12" s="247"/>
-      <c r="K12" s="275"/>
-      <c r="L12" s="245"/>
+      <c r="A12" s="270"/>
+      <c r="B12" s="272"/>
+      <c r="C12" s="272"/>
+      <c r="D12" s="272"/>
+      <c r="E12" s="251"/>
+      <c r="F12" s="272"/>
+      <c r="G12" s="274"/>
+      <c r="H12" s="251"/>
+      <c r="I12" s="251"/>
+      <c r="J12" s="251"/>
+      <c r="K12" s="253"/>
+      <c r="L12" s="255"/>
       <c r="M12" s="145" t="str">
         <f>RESUMEN!B8</f>
-        <v>VTO 18/06</v>
-      </c>
-      <c r="N12" s="249"/>
+        <v>VTO 17/07</v>
+      </c>
+      <c r="N12" s="257"/>
     </row>
     <row r="13" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="130">
@@ -4595,7 +4757,7 @@
         <v>0</v>
       </c>
       <c r="I22" s="126" t="s">
-        <v>230</v>
+        <v>216</v>
       </c>
       <c r="J22" s="126">
         <f t="shared" si="2"/>
@@ -5101,7 +5263,7 @@
         <v>0.20000000000000004</v>
       </c>
       <c r="P32" t="s">
-        <v>237</v>
+        <v>223</v>
       </c>
     </row>
     <row r="33" spans="1:16" x14ac:dyDescent="0.3">
@@ -5159,7 +5321,7 @@
         <v>22</v>
       </c>
       <c r="B34" s="114" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C34" s="87"/>
       <c r="D34" s="82">
@@ -5748,7 +5910,7 @@
         <v>0.33000000000000013</v>
       </c>
       <c r="P45" t="s">
-        <v>232</v>
+        <v>218</v>
       </c>
     </row>
     <row r="46" spans="1:16" x14ac:dyDescent="0.3">
@@ -5802,47 +5964,47 @@
       </c>
     </row>
     <row r="47" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A47" s="192">
+      <c r="A47" s="191">
         <f t="shared" si="10"/>
         <v>35</v>
       </c>
-      <c r="B47" s="193" t="s">
+      <c r="B47" s="192" t="s">
         <v>36</v>
       </c>
-      <c r="C47" s="194"/>
-      <c r="D47" s="195">
+      <c r="C47" s="193"/>
+      <c r="D47" s="194">
         <v>1.1200000000000001</v>
       </c>
-      <c r="E47" s="196">
+      <c r="E47" s="195">
         <v>183161.35</v>
       </c>
-      <c r="F47" s="196">
+      <c r="F47" s="195">
         <f>190000</f>
         <v>190000</v>
       </c>
-      <c r="G47" s="197">
+      <c r="G47" s="196">
         <f t="shared" si="0"/>
         <v>-6838.6499999999942</v>
       </c>
-      <c r="H47" s="197">
+      <c r="H47" s="196">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="I47" s="198">
+      <c r="I47" s="197">
         <f t="shared" si="12"/>
         <v>156552.34341600002</v>
       </c>
-      <c r="J47" s="198">
+      <c r="J47" s="197">
         <f t="shared" si="13"/>
         <v>33600.000000000007</v>
       </c>
-      <c r="K47" s="198"/>
-      <c r="L47" s="199"/>
-      <c r="M47" s="200">
+      <c r="K47" s="197"/>
+      <c r="L47" s="198"/>
+      <c r="M47" s="199">
         <f t="shared" si="5"/>
         <v>183314.35</v>
       </c>
-      <c r="N47" s="201">
+      <c r="N47" s="200">
         <f t="shared" si="9"/>
         <v>188813.35</v>
       </c>
@@ -5957,7 +6119,7 @@
         <v>0.37000000000000016</v>
       </c>
       <c r="P49" t="s">
-        <v>239</v>
+        <v>225</v>
       </c>
     </row>
     <row r="50" spans="1:16" x14ac:dyDescent="0.3">
@@ -6007,7 +6169,7 @@
         <v>0.38000000000000017</v>
       </c>
       <c r="P50" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="51" spans="1:16" x14ac:dyDescent="0.3">
@@ -6207,7 +6369,7 @@
         <v>0.42000000000000021</v>
       </c>
       <c r="P54" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="55" spans="1:16" x14ac:dyDescent="0.3">
@@ -6262,7 +6424,7 @@
         <v>0.43000000000000022</v>
       </c>
       <c r="P55" t="s">
-        <v>233</v>
+        <v>219</v>
       </c>
     </row>
     <row r="56" spans="1:16" x14ac:dyDescent="0.3">
@@ -6321,7 +6483,7 @@
         <v>45</v>
       </c>
       <c r="B57" s="88" t="s">
-        <v>249</v>
+        <v>234</v>
       </c>
       <c r="C57" s="87"/>
       <c r="D57" s="82">
@@ -6366,11 +6528,11 @@
       </c>
     </row>
     <row r="58" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A58" s="214">
+      <c r="A58" s="213">
         <f t="shared" si="10"/>
         <v>46</v>
       </c>
-      <c r="B58" s="215" t="s">
+      <c r="B58" s="214" t="s">
         <v>45</v>
       </c>
       <c r="C58" s="87"/>
@@ -6465,7 +6627,7 @@
         <v>0.47000000000000025</v>
       </c>
       <c r="P59" t="s">
-        <v>236</v>
+        <v>222</v>
       </c>
     </row>
     <row r="60" spans="1:16" x14ac:dyDescent="0.3">
@@ -7016,7 +7178,7 @@
         <v>0.58000000000000029</v>
       </c>
       <c r="P70" t="s">
-        <v>248</v>
+        <v>233</v>
       </c>
     </row>
     <row r="71" spans="1:16" x14ac:dyDescent="0.3">
@@ -7268,7 +7430,7 @@
         <v>0.63000000000000034</v>
       </c>
       <c r="P75" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="76" spans="1:16" x14ac:dyDescent="0.3">
@@ -7322,11 +7484,11 @@
       </c>
     </row>
     <row r="77" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A77" s="208">
+      <c r="A77" s="207">
         <f t="shared" si="10"/>
         <v>65</v>
       </c>
-      <c r="B77" s="209" t="s">
+      <c r="B77" s="208" t="s">
         <v>64</v>
       </c>
       <c r="C77" s="113"/>
@@ -7370,7 +7532,7 @@
         <v>0.65000000000000036</v>
       </c>
       <c r="P77" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="78" spans="1:16" x14ac:dyDescent="0.3">
@@ -7520,11 +7682,11 @@
       </c>
     </row>
     <row r="81" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A81" s="202">
+      <c r="A81" s="201">
         <f t="shared" si="10"/>
         <v>69</v>
       </c>
-      <c r="B81" s="203" t="s">
+      <c r="B81" s="202" t="s">
         <v>68</v>
       </c>
       <c r="C81" s="87"/>
@@ -7970,11 +8132,11 @@
       </c>
     </row>
     <row r="90" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A90" s="286">
+      <c r="A90" s="225">
         <f t="shared" si="10"/>
         <v>78</v>
       </c>
-      <c r="B90" s="287" t="s">
+      <c r="B90" s="226" t="s">
         <v>77</v>
       </c>
       <c r="C90" s="120"/>
@@ -8018,7 +8180,7 @@
         <v>0.78000000000000047</v>
       </c>
       <c r="P90" t="s">
-        <v>234</v>
+        <v>220</v>
       </c>
     </row>
     <row r="91" spans="1:16" x14ac:dyDescent="0.3">
@@ -8027,7 +8189,7 @@
         <v>79</v>
       </c>
       <c r="B91" s="88" t="s">
-        <v>241</v>
+        <v>227</v>
       </c>
       <c r="C91" s="87"/>
       <c r="D91" s="82">
@@ -8071,7 +8233,7 @@
         <v>0.79000000000000048</v>
       </c>
       <c r="P91" t="s">
-        <v>242</v>
+        <v>228</v>
       </c>
     </row>
     <row r="92" spans="1:16" x14ac:dyDescent="0.3">
@@ -8174,15 +8336,15 @@
         <v>0.8100000000000005</v>
       </c>
       <c r="P93" t="s">
-        <v>260</v>
+        <v>245</v>
       </c>
     </row>
     <row r="94" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A94" s="216">
+      <c r="A94" s="215">
         <f t="shared" si="10"/>
         <v>82</v>
       </c>
-      <c r="B94" s="217" t="s">
+      <c r="B94" s="216" t="s">
         <v>80</v>
       </c>
       <c r="C94" s="87"/>
@@ -9227,7 +9389,7 @@
         <v>103</v>
       </c>
       <c r="B115" s="114" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C115" s="113"/>
       <c r="D115" s="110">
@@ -9337,98 +9499,93 @@
     </row>
     <row r="119" spans="1:15" hidden="1" x14ac:dyDescent="0.3"/>
     <row r="120" spans="1:15" ht="9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B120" s="250" t="s">
+      <c r="B120" s="258" t="s">
         <v>103</v>
       </c>
-      <c r="C120" s="250"/>
-      <c r="D120" s="250"/>
-      <c r="E120" s="250"/>
-      <c r="F120" s="250"/>
-      <c r="G120" s="250"/>
-      <c r="H120" s="250"/>
-      <c r="I120" s="250"/>
-      <c r="J120" s="250"/>
-      <c r="K120" s="250"/>
-      <c r="L120" s="250"/>
-      <c r="M120" s="250"/>
+      <c r="C120" s="258"/>
+      <c r="D120" s="258"/>
+      <c r="E120" s="258"/>
+      <c r="F120" s="258"/>
+      <c r="G120" s="258"/>
+      <c r="H120" s="258"/>
+      <c r="I120" s="258"/>
+      <c r="J120" s="258"/>
+      <c r="K120" s="258"/>
+      <c r="L120" s="258"/>
+      <c r="M120" s="258"/>
     </row>
     <row r="121" spans="1:15" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B121" s="250"/>
-      <c r="C121" s="250"/>
-      <c r="D121" s="250"/>
-      <c r="E121" s="250"/>
-      <c r="F121" s="250"/>
-      <c r="G121" s="250"/>
-      <c r="H121" s="250"/>
-      <c r="I121" s="250"/>
-      <c r="J121" s="250"/>
-      <c r="K121" s="250"/>
-      <c r="L121" s="250"/>
-      <c r="M121" s="250"/>
+      <c r="B121" s="258"/>
+      <c r="C121" s="258"/>
+      <c r="D121" s="258"/>
+      <c r="E121" s="258"/>
+      <c r="F121" s="258"/>
+      <c r="G121" s="258"/>
+      <c r="H121" s="258"/>
+      <c r="I121" s="258"/>
+      <c r="J121" s="258"/>
+      <c r="K121" s="258"/>
+      <c r="L121" s="258"/>
+      <c r="M121" s="258"/>
     </row>
     <row r="122" spans="1:15" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B122" s="250"/>
-      <c r="C122" s="250"/>
-      <c r="D122" s="250"/>
-      <c r="E122" s="250"/>
-      <c r="F122" s="250"/>
-      <c r="G122" s="250"/>
-      <c r="H122" s="250"/>
-      <c r="I122" s="250"/>
-      <c r="J122" s="250"/>
-      <c r="K122" s="250"/>
-      <c r="L122" s="250"/>
-      <c r="M122" s="250"/>
+      <c r="B122" s="258"/>
+      <c r="C122" s="258"/>
+      <c r="D122" s="258"/>
+      <c r="E122" s="258"/>
+      <c r="F122" s="258"/>
+      <c r="G122" s="258"/>
+      <c r="H122" s="258"/>
+      <c r="I122" s="258"/>
+      <c r="J122" s="258"/>
+      <c r="K122" s="258"/>
+      <c r="L122" s="258"/>
+      <c r="M122" s="258"/>
     </row>
     <row r="123" spans="1:15" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B123" s="250"/>
-      <c r="C123" s="250"/>
-      <c r="D123" s="250"/>
-      <c r="E123" s="250"/>
-      <c r="F123" s="250"/>
-      <c r="G123" s="250"/>
-      <c r="H123" s="250"/>
-      <c r="I123" s="250"/>
-      <c r="J123" s="250"/>
-      <c r="K123" s="250"/>
-      <c r="L123" s="250"/>
-      <c r="M123" s="250"/>
+      <c r="B123" s="258"/>
+      <c r="C123" s="258"/>
+      <c r="D123" s="258"/>
+      <c r="E123" s="258"/>
+      <c r="F123" s="258"/>
+      <c r="G123" s="258"/>
+      <c r="H123" s="258"/>
+      <c r="I123" s="258"/>
+      <c r="J123" s="258"/>
+      <c r="K123" s="258"/>
+      <c r="L123" s="258"/>
+      <c r="M123" s="258"/>
     </row>
     <row r="124" spans="1:15" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B124" s="250"/>
-      <c r="C124" s="250"/>
-      <c r="D124" s="250"/>
-      <c r="E124" s="250"/>
-      <c r="F124" s="250"/>
-      <c r="G124" s="250"/>
-      <c r="H124" s="250"/>
-      <c r="I124" s="250"/>
-      <c r="J124" s="250"/>
-      <c r="K124" s="250"/>
-      <c r="L124" s="250"/>
-      <c r="M124" s="250"/>
+      <c r="B124" s="258"/>
+      <c r="C124" s="258"/>
+      <c r="D124" s="258"/>
+      <c r="E124" s="258"/>
+      <c r="F124" s="258"/>
+      <c r="G124" s="258"/>
+      <c r="H124" s="258"/>
+      <c r="I124" s="258"/>
+      <c r="J124" s="258"/>
+      <c r="K124" s="258"/>
+      <c r="L124" s="258"/>
+      <c r="M124" s="258"/>
     </row>
     <row r="125" spans="1:15" ht="67.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B125" s="250"/>
-      <c r="C125" s="250"/>
-      <c r="D125" s="250"/>
-      <c r="E125" s="250"/>
-      <c r="F125" s="250"/>
-      <c r="G125" s="250"/>
-      <c r="H125" s="250"/>
-      <c r="I125" s="250"/>
-      <c r="J125" s="250"/>
-      <c r="K125" s="250"/>
-      <c r="L125" s="250"/>
-      <c r="M125" s="250"/>
+      <c r="B125" s="258"/>
+      <c r="C125" s="258"/>
+      <c r="D125" s="258"/>
+      <c r="E125" s="258"/>
+      <c r="F125" s="258"/>
+      <c r="G125" s="258"/>
+      <c r="H125" s="258"/>
+      <c r="I125" s="258"/>
+      <c r="J125" s="258"/>
+      <c r="K125" s="258"/>
+      <c r="L125" s="258"/>
+      <c r="M125" s="258"/>
     </row>
   </sheetData>
   <mergeCells count="19">
-    <mergeCell ref="E2:F2"/>
-    <mergeCell ref="I11:I12"/>
-    <mergeCell ref="K11:K12"/>
-    <mergeCell ref="L11:L12"/>
-    <mergeCell ref="J11:J12"/>
     <mergeCell ref="N11:N12"/>
     <mergeCell ref="B120:M125"/>
     <mergeCell ref="D1:M1"/>
@@ -9443,6 +9600,11 @@
     <mergeCell ref="H11:H12"/>
     <mergeCell ref="A9:N9"/>
     <mergeCell ref="A10:N10"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="I11:I12"/>
+    <mergeCell ref="K11:K12"/>
+    <mergeCell ref="L11:L12"/>
+    <mergeCell ref="J11:J12"/>
   </mergeCells>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="3" scale="80" orientation="portrait" r:id="rId1"/>
@@ -9463,7 +9625,7 @@
     </row>
     <row r="4" spans="3:12" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C4" s="174" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="D4" s="175">
         <v>1</v>
@@ -9479,14 +9641,14 @@
     </row>
     <row r="5" spans="3:12" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C5" s="176" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="D5" s="177"/>
       <c r="E5" t="s">
+        <v>198</v>
+      </c>
+      <c r="G5" t="s">
         <v>199</v>
-      </c>
-      <c r="G5" t="s">
-        <v>200</v>
       </c>
       <c r="J5" s="173"/>
       <c r="K5" s="19"/>
@@ -9494,19 +9656,19 @@
     </row>
     <row r="6" spans="3:12" x14ac:dyDescent="0.3">
       <c r="C6" s="176" t="s">
+        <v>200</v>
+      </c>
+      <c r="D6" s="177" t="s">
         <v>201</v>
       </c>
-      <c r="D6" s="177" t="s">
+      <c r="E6" t="s">
         <v>202</v>
-      </c>
-      <c r="E6" t="s">
-        <v>203</v>
       </c>
       <c r="G6" t="s">
         <v>128</v>
       </c>
       <c r="H6" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="J6" s="173"/>
       <c r="K6" s="19"/>
@@ -9514,42 +9676,42 @@
     </row>
     <row r="7" spans="3:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C7" s="47" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="J7" s="173"/>
       <c r="K7" s="19"/>
       <c r="L7" s="19"/>
     </row>
     <row r="8" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C8" s="276" t="s">
-        <v>250</v>
-      </c>
-      <c r="D8" s="277"/>
-      <c r="E8" s="277"/>
-      <c r="F8" s="277"/>
-      <c r="G8" s="277"/>
-      <c r="H8" s="277"/>
-      <c r="I8" s="277"/>
-      <c r="J8" s="278"/>
+      <c r="C8" s="281" t="s">
+        <v>235</v>
+      </c>
+      <c r="D8" s="282"/>
+      <c r="E8" s="282"/>
+      <c r="F8" s="282"/>
+      <c r="G8" s="282"/>
+      <c r="H8" s="282"/>
+      <c r="I8" s="282"/>
+      <c r="J8" s="283"/>
       <c r="K8" s="19"/>
       <c r="L8" s="19"/>
     </row>
     <row r="9" spans="3:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C9" s="279"/>
-      <c r="D9" s="280"/>
-      <c r="E9" s="280"/>
-      <c r="F9" s="280"/>
-      <c r="G9" s="280"/>
-      <c r="H9" s="280"/>
-      <c r="I9" s="280"/>
-      <c r="J9" s="281"/>
+      <c r="C9" s="284"/>
+      <c r="D9" s="285"/>
+      <c r="E9" s="285"/>
+      <c r="F9" s="285"/>
+      <c r="G9" s="285"/>
+      <c r="H9" s="285"/>
+      <c r="I9" s="285"/>
+      <c r="J9" s="286"/>
     </row>
     <row r="11" spans="3:12" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="12" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C12" s="204" t="s">
-        <v>197</v>
-      </c>
-      <c r="D12" s="205">
+      <c r="C12" s="203" t="s">
+        <v>196</v>
+      </c>
+      <c r="D12" s="204">
         <v>1</v>
       </c>
       <c r="E12" s="171"/>
@@ -9560,70 +9722,70 @@
       <c r="J12" s="172"/>
     </row>
     <row r="13" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C13" s="206" t="s">
+      <c r="C13" s="205" t="s">
+        <v>197</v>
+      </c>
+      <c r="D13" s="206"/>
+      <c r="E13" t="s">
         <v>198</v>
       </c>
-      <c r="D13" s="207"/>
-      <c r="E13" t="s">
+      <c r="G13" t="s">
         <v>199</v>
       </c>
-      <c r="G13" t="s">
+      <c r="J13" s="173"/>
+    </row>
+    <row r="14" spans="3:12" x14ac:dyDescent="0.3">
+      <c r="C14" s="205" t="s">
         <v>200</v>
       </c>
-      <c r="J13" s="173"/>
-    </row>
-    <row r="14" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C14" s="206" t="s">
+      <c r="D14" s="206" t="s">
         <v>201</v>
       </c>
-      <c r="D14" s="207" t="s">
+      <c r="E14" t="s">
         <v>202</v>
-      </c>
-      <c r="E14" t="s">
-        <v>203</v>
       </c>
       <c r="G14" t="s">
         <v>128</v>
       </c>
       <c r="H14" t="s">
-        <v>251</v>
+        <v>236</v>
       </c>
       <c r="J14" s="173"/>
     </row>
     <row r="15" spans="3:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C15" s="47" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="J15" s="173"/>
     </row>
     <row r="16" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C16" s="276" t="s">
-        <v>252</v>
-      </c>
-      <c r="D16" s="277"/>
-      <c r="E16" s="277"/>
-      <c r="F16" s="277"/>
-      <c r="G16" s="277"/>
-      <c r="H16" s="277"/>
-      <c r="I16" s="277"/>
-      <c r="J16" s="278"/>
+      <c r="C16" s="281" t="s">
+        <v>237</v>
+      </c>
+      <c r="D16" s="282"/>
+      <c r="E16" s="282"/>
+      <c r="F16" s="282"/>
+      <c r="G16" s="282"/>
+      <c r="H16" s="282"/>
+      <c r="I16" s="282"/>
+      <c r="J16" s="283"/>
     </row>
     <row r="17" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C17" s="279"/>
-      <c r="D17" s="280"/>
-      <c r="E17" s="280"/>
-      <c r="F17" s="280"/>
-      <c r="G17" s="280"/>
-      <c r="H17" s="280"/>
-      <c r="I17" s="280"/>
-      <c r="J17" s="281"/>
+      <c r="C17" s="284"/>
+      <c r="D17" s="285"/>
+      <c r="E17" s="285"/>
+      <c r="F17" s="285"/>
+      <c r="G17" s="285"/>
+      <c r="H17" s="285"/>
+      <c r="I17" s="285"/>
+      <c r="J17" s="286"/>
     </row>
     <row r="19" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="20" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C20" s="210" t="s">
-        <v>197</v>
-      </c>
-      <c r="D20" s="211">
+      <c r="C20" s="209" t="s">
+        <v>196</v>
+      </c>
+      <c r="D20" s="210">
         <v>1</v>
       </c>
       <c r="E20" s="171"/>
@@ -9634,70 +9796,70 @@
       <c r="J20" s="172"/>
     </row>
     <row r="21" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C21" s="212" t="s">
+      <c r="C21" s="211" t="s">
+        <v>197</v>
+      </c>
+      <c r="D21" s="212"/>
+      <c r="E21" t="s">
         <v>198</v>
       </c>
-      <c r="D21" s="213"/>
-      <c r="E21" t="s">
+      <c r="G21" t="s">
         <v>199</v>
       </c>
-      <c r="G21" t="s">
+      <c r="J21" s="173"/>
+    </row>
+    <row r="22" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C22" s="211" t="s">
         <v>200</v>
       </c>
-      <c r="J21" s="173"/>
-    </row>
-    <row r="22" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C22" s="212" t="s">
+      <c r="D22" s="212" t="s">
         <v>201</v>
       </c>
-      <c r="D22" s="213" t="s">
+      <c r="E22" t="s">
         <v>202</v>
-      </c>
-      <c r="E22" t="s">
-        <v>203</v>
       </c>
       <c r="G22" t="s">
         <v>128</v>
       </c>
       <c r="H22" t="s">
-        <v>253</v>
+        <v>238</v>
       </c>
       <c r="J22" s="173"/>
     </row>
     <row r="23" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C23" s="47" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="J23" s="173"/>
     </row>
     <row r="24" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C24" s="276" t="s">
-        <v>254</v>
-      </c>
-      <c r="D24" s="277"/>
-      <c r="E24" s="277"/>
-      <c r="F24" s="277"/>
-      <c r="G24" s="277"/>
-      <c r="H24" s="277"/>
-      <c r="I24" s="277"/>
-      <c r="J24" s="278"/>
+      <c r="C24" s="281" t="s">
+        <v>239</v>
+      </c>
+      <c r="D24" s="282"/>
+      <c r="E24" s="282"/>
+      <c r="F24" s="282"/>
+      <c r="G24" s="282"/>
+      <c r="H24" s="282"/>
+      <c r="I24" s="282"/>
+      <c r="J24" s="283"/>
     </row>
     <row r="25" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C25" s="279"/>
-      <c r="D25" s="280"/>
-      <c r="E25" s="280"/>
-      <c r="F25" s="280"/>
-      <c r="G25" s="280"/>
-      <c r="H25" s="280"/>
-      <c r="I25" s="280"/>
-      <c r="J25" s="281"/>
+      <c r="C25" s="284"/>
+      <c r="D25" s="285"/>
+      <c r="E25" s="285"/>
+      <c r="F25" s="285"/>
+      <c r="G25" s="285"/>
+      <c r="H25" s="285"/>
+      <c r="I25" s="285"/>
+      <c r="J25" s="286"/>
     </row>
     <row r="27" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="28" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C28" s="218" t="s">
-        <v>197</v>
-      </c>
-      <c r="D28" s="219">
+      <c r="C28" s="217" t="s">
+        <v>196</v>
+      </c>
+      <c r="D28" s="218">
         <v>1</v>
       </c>
       <c r="E28" s="171"/>
@@ -9708,70 +9870,70 @@
       <c r="J28" s="172"/>
     </row>
     <row r="29" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C29" s="220" t="s">
+      <c r="C29" s="219" t="s">
+        <v>197</v>
+      </c>
+      <c r="D29" s="220"/>
+      <c r="E29" t="s">
         <v>198</v>
       </c>
-      <c r="D29" s="221"/>
-      <c r="E29" t="s">
+      <c r="G29" t="s">
         <v>199</v>
       </c>
-      <c r="G29" t="s">
+      <c r="J29" s="173"/>
+    </row>
+    <row r="30" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C30" s="219" t="s">
         <v>200</v>
       </c>
-      <c r="J29" s="173"/>
-    </row>
-    <row r="30" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C30" s="220" t="s">
+      <c r="D30" s="220" t="s">
         <v>201</v>
       </c>
-      <c r="D30" s="221" t="s">
+      <c r="E30" t="s">
         <v>202</v>
-      </c>
-      <c r="E30" t="s">
-        <v>203</v>
       </c>
       <c r="G30" t="s">
         <v>128</v>
       </c>
       <c r="H30" t="s">
-        <v>255</v>
+        <v>240</v>
       </c>
       <c r="J30" s="173"/>
     </row>
     <row r="31" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C31" s="47" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="J31" s="173"/>
     </row>
     <row r="32" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C32" s="276" t="s">
-        <v>256</v>
-      </c>
-      <c r="D32" s="277"/>
-      <c r="E32" s="277"/>
-      <c r="F32" s="277"/>
-      <c r="G32" s="277"/>
-      <c r="H32" s="277"/>
-      <c r="I32" s="277"/>
-      <c r="J32" s="278"/>
+      <c r="C32" s="281" t="s">
+        <v>241</v>
+      </c>
+      <c r="D32" s="282"/>
+      <c r="E32" s="282"/>
+      <c r="F32" s="282"/>
+      <c r="G32" s="282"/>
+      <c r="H32" s="282"/>
+      <c r="I32" s="282"/>
+      <c r="J32" s="283"/>
     </row>
     <row r="33" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C33" s="279"/>
-      <c r="D33" s="280"/>
-      <c r="E33" s="280"/>
-      <c r="F33" s="280"/>
-      <c r="G33" s="280"/>
-      <c r="H33" s="280"/>
-      <c r="I33" s="280"/>
-      <c r="J33" s="281"/>
+      <c r="C33" s="284"/>
+      <c r="D33" s="285"/>
+      <c r="E33" s="285"/>
+      <c r="F33" s="285"/>
+      <c r="G33" s="285"/>
+      <c r="H33" s="285"/>
+      <c r="I33" s="285"/>
+      <c r="J33" s="286"/>
     </row>
     <row r="35" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="36" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C36" s="282" t="s">
-        <v>197</v>
-      </c>
-      <c r="D36" s="283">
+      <c r="C36" s="221" t="s">
+        <v>196</v>
+      </c>
+      <c r="D36" s="222">
         <v>1</v>
       </c>
       <c r="E36" s="171"/>
@@ -9782,66 +9944,66 @@
       <c r="J36" s="172"/>
     </row>
     <row r="37" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C37" s="284" t="s">
+      <c r="C37" s="223" t="s">
+        <v>197</v>
+      </c>
+      <c r="D37" s="224"/>
+      <c r="E37" t="s">
         <v>198</v>
       </c>
-      <c r="D37" s="285"/>
-      <c r="E37" t="s">
+      <c r="G37" t="s">
         <v>199</v>
       </c>
-      <c r="G37" t="s">
+      <c r="H37" t="s">
+        <v>242</v>
+      </c>
+      <c r="J37" s="173"/>
+    </row>
+    <row r="38" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C38" s="223" t="s">
         <v>200</v>
       </c>
-      <c r="H37" t="s">
-        <v>257</v>
-      </c>
-      <c r="J37" s="173"/>
-    </row>
-    <row r="38" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C38" s="284" t="s">
+      <c r="D38" s="224" t="s">
         <v>201</v>
       </c>
-      <c r="D38" s="285" t="s">
+      <c r="E38" t="s">
         <v>202</v>
-      </c>
-      <c r="E38" t="s">
-        <v>203</v>
       </c>
       <c r="G38" t="s">
         <v>128</v>
       </c>
       <c r="H38" t="s">
-        <v>259</v>
+        <v>244</v>
       </c>
       <c r="J38" s="173"/>
     </row>
     <row r="39" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C39" s="47" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="J39" s="173"/>
     </row>
     <row r="40" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C40" s="276" t="s">
-        <v>258</v>
-      </c>
-      <c r="D40" s="277"/>
-      <c r="E40" s="277"/>
-      <c r="F40" s="277"/>
-      <c r="G40" s="277"/>
-      <c r="H40" s="277"/>
-      <c r="I40" s="277"/>
-      <c r="J40" s="278"/>
+      <c r="C40" s="281" t="s">
+        <v>243</v>
+      </c>
+      <c r="D40" s="282"/>
+      <c r="E40" s="282"/>
+      <c r="F40" s="282"/>
+      <c r="G40" s="282"/>
+      <c r="H40" s="282"/>
+      <c r="I40" s="282"/>
+      <c r="J40" s="283"/>
     </row>
     <row r="41" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C41" s="279"/>
-      <c r="D41" s="280"/>
-      <c r="E41" s="280"/>
-      <c r="F41" s="280"/>
-      <c r="G41" s="280"/>
-      <c r="H41" s="280"/>
-      <c r="I41" s="280"/>
-      <c r="J41" s="281"/>
+      <c r="C41" s="284"/>
+      <c r="D41" s="285"/>
+      <c r="E41" s="285"/>
+      <c r="F41" s="285"/>
+      <c r="G41" s="285"/>
+      <c r="H41" s="285"/>
+      <c r="I41" s="285"/>
+      <c r="J41" s="286"/>
     </row>
   </sheetData>
   <mergeCells count="5">

--- a/2026/ITALIA/Junio/Junio ITALIA.xlsx
+++ b/2026/ITALIA/Junio/Junio ITALIA.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\2026\ITALIA\Junio\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistemax\Desktop\rc-consorcio2025\2026\ITALIA\Junio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5757D03-316B-4A33-A6E2-9038371DFC9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC7A3661-CFE2-4172-AFF5-60B4D3D0E716}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="4" r:id="rId1"/>
@@ -22,11 +22,16 @@
     <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$E$143</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
+  <extLst>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="330" uniqueCount="275">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="337" uniqueCount="276">
   <si>
     <t>TOTAL</t>
   </si>
@@ -662,30 +667,15 @@
     <t>Transf 21/05</t>
   </si>
   <si>
-    <t>Transf 22/5</t>
-  </si>
-  <si>
-    <t>Transf 12/05</t>
-  </si>
-  <si>
     <t>Articulos de limpieza</t>
   </si>
   <si>
-    <t>PMC 21/05</t>
-  </si>
-  <si>
     <t>Solicitud segundo testimonio (40 fojas/80 carillas) - La plata - Tramite abreviado</t>
   </si>
   <si>
     <t>Transf 14/05</t>
   </si>
   <si>
-    <t>Transf 26/05</t>
-  </si>
-  <si>
-    <t>Ef 26/05</t>
-  </si>
-  <si>
     <t xml:space="preserve">  </t>
   </si>
   <si>
@@ -716,24 +706,12 @@
     <t>Horacio (inquilino)</t>
   </si>
   <si>
-    <t xml:space="preserve">Subscripcion Periodo Accion </t>
-  </si>
-  <si>
     <t>11 D ANTUNEZ FRANCISCO</t>
   </si>
   <si>
     <t xml:space="preserve"> Osvaldo </t>
   </si>
   <si>
-    <t>Oscar Colmeiro – Obra de plomería: se realiza el cambio de desagües de cocinas y lavaderos en las unidades E y F de los pisos 7°, 6°, 5°, 4°, 3°, incluyendo además el cambio de bajada y desagües de cocina y lavadero en las unidades E y F del piso 2°, del piso 1° y de Planta Baja, realizándose en todos los casos el mismo tipo de trabajo - Se pudo abonar $2.800.000 + $1.400.000</t>
-  </si>
-  <si>
-    <t>Transf 11/05 - 26/05</t>
-  </si>
-  <si>
-    <t>Debito 27/05</t>
-  </si>
-  <si>
     <t>Gastos particulares mal cobrados 9C</t>
   </si>
   <si>
@@ -809,9 +787,6 @@
     <t>Quotteri Mateo - Certificacion de deuda de expensas UF 68</t>
   </si>
   <si>
-    <t>Cordoba Matias - A cuenta de trabajo de plomeria, albañileria y pintura</t>
-  </si>
-  <si>
     <t>Fire - Compra de pantalon, remera, buzo para Sr. Encargado</t>
   </si>
   <si>
@@ -836,21 +811,12 @@
     <t>Debito 12/06</t>
   </si>
   <si>
-    <t xml:space="preserve">Servisur - 4 termicas unipolares - </t>
-  </si>
-  <si>
     <t>Transf 05/06</t>
   </si>
   <si>
-    <t>Ascensores Lema - Arreglo</t>
-  </si>
-  <si>
     <t>Ferreteria La 95 - Copia de llave</t>
   </si>
   <si>
-    <t>Arias Mirta -</t>
-  </si>
-  <si>
     <t>Sra. Arias mirta - Confieccion de formulario 931 - periodo 04/2025</t>
   </si>
   <si>
@@ -861,6 +827,48 @@
   </si>
   <si>
     <t>Transf 18/06</t>
+  </si>
+  <si>
+    <t>Suplente Sr. Cristian Del Pezzo</t>
+  </si>
+  <si>
+    <t>Ascensores Lema - Arreglo finalizacion pago cambio cables de acero</t>
+  </si>
+  <si>
+    <t>Servisur - 4 termicas unipolares, cambio de fusbiles en barra de fases</t>
+  </si>
+  <si>
+    <t>Suplente Sr Lucas Ezequiel Dominguez</t>
+  </si>
+  <si>
+    <t>Seguro Sr. Lucas</t>
+  </si>
+  <si>
+    <t>Seguro Sr. Cristan</t>
+  </si>
+  <si>
+    <t>Efectivo</t>
+  </si>
+  <si>
+    <t>Oscar Colmeiro / Cordoba Matias - A cuenta de trabajo de plomeria, albañileria y pintura</t>
+  </si>
+  <si>
+    <t>Transf 08/06 - 11/06</t>
+  </si>
+  <si>
+    <t>Transf 08/06 - 16/06</t>
+  </si>
+  <si>
+    <t>Sra. Arias mirta - Confieccion de formulario 931 - periodo 05/2025</t>
+  </si>
+  <si>
+    <t>Debito 30/06</t>
+  </si>
+  <si>
+    <t>Falta de fondos</t>
+  </si>
+  <si>
+    <t>Efectivo por falta de fondos en banco</t>
   </si>
 </sst>
 </file>
@@ -1686,7 +1694,7 @@
     <xf numFmtId="44" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="294">
+  <cellXfs count="295">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1966,10 +1974,6 @@
     <xf numFmtId="44" fontId="17" fillId="2" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="8" fontId="10" fillId="2" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="44" fontId="10" fillId="2" borderId="20" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="12" fillId="6" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -2036,81 +2040,160 @@
     <xf numFmtId="0" fontId="16" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="44" fontId="7" fillId="2" borderId="20" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="40" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="41" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="42" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="44" fontId="10" fillId="2" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="10" fillId="2" borderId="19" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="19" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="19" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="40" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="41" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="42" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="44" fontId="10" fillId="2" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="10" fillId="2" borderId="19" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="15" fillId="3" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2123,81 +2206,6 @@
     <xf numFmtId="0" fontId="15" fillId="3" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="12" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="12" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -2216,22 +2224,19 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="8" fontId="7" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="7" fillId="15" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="7" fillId="15" borderId="20" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="8" fontId="7" fillId="15" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="44" fontId="7" fillId="2" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="7" fillId="2" borderId="20" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="8" fontId="7" fillId="2" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="7" fillId="15" borderId="20" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="44" fontId="14" fillId="7" borderId="19" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="8" fontId="7" fillId="15" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="44" fontId="7" fillId="15" borderId="22" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -2317,9 +2322,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -2357,9 +2362,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -2392,9 +2397,26 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -2427,9 +2449,26 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -2604,31 +2643,31 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E413A25D-5161-4141-BE0B-6E37A2A76CA5}">
   <dimension ref="A1:M144"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="37.5546875" customWidth="1"/>
-    <col min="2" max="2" width="24.6640625" customWidth="1"/>
-    <col min="3" max="3" width="15.88671875" hidden="1" customWidth="1"/>
-    <col min="4" max="4" width="21.6640625" customWidth="1"/>
-    <col min="5" max="5" width="16.6640625" customWidth="1"/>
-    <col min="6" max="6" width="15.5546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="37.5703125" customWidth="1"/>
+    <col min="2" max="2" width="24.7109375" customWidth="1"/>
+    <col min="3" max="3" width="15.85546875" hidden="1" customWidth="1"/>
+    <col min="4" max="4" width="21.7109375" customWidth="1"/>
+    <col min="5" max="5" width="16.7109375" customWidth="1"/>
+    <col min="6" max="6" width="15.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5703125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="12" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="22.6640625" customWidth="1"/>
+    <col min="10" max="10" width="22.7109375" customWidth="1"/>
     <col min="11" max="11" width="18" customWidth="1"/>
-    <col min="12" max="12" width="18.33203125" customWidth="1"/>
+    <col min="12" max="12" width="18.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1"/>
-      <c r="B1" s="231" t="s">
+      <c r="B1" s="238" t="s">
         <v>147</v>
       </c>
-      <c r="C1" s="231"/>
-      <c r="D1" s="231"/>
-      <c r="E1" s="232"/>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="C1" s="238"/>
+      <c r="D1" s="238"/>
+      <c r="E1" s="239"/>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="2"/>
       <c r="B2" s="9" t="s">
         <v>149</v>
@@ -2637,16 +2676,16 @@
       <c r="D2" s="3"/>
       <c r="E2" s="4"/>
     </row>
-    <row r="3" spans="1:5" ht="51.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:5" ht="51.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="2"/>
-      <c r="B3" s="237" t="s">
+      <c r="B3" s="242" t="s">
         <v>194</v>
       </c>
-      <c r="C3" s="237"/>
-      <c r="D3" s="237"/>
-      <c r="E3" s="238"/>
-    </row>
-    <row r="4" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C3" s="242"/>
+      <c r="D3" s="242"/>
+      <c r="E3" s="243"/>
+    </row>
+    <row r="4" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="5" t="s">
         <v>100</v>
       </c>
@@ -2657,12 +2696,12 @@
       <c r="D4" s="7"/>
       <c r="E4" s="8"/>
     </row>
-    <row r="5" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
         <v>148</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>247</v>
+        <v>238</v>
       </c>
       <c r="C5" s="9"/>
       <c r="D5" s="3" t="s">
@@ -2670,7 +2709,7 @@
       </c>
       <c r="E5" s="10"/>
     </row>
-    <row r="6" spans="1:5" ht="16.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:5" ht="16.149999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="90" t="s">
         <v>138</v>
       </c>
@@ -2681,104 +2720,104 @@
       </c>
       <c r="E6" s="8"/>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="48"/>
-      <c r="B8" s="239" t="s">
-        <v>246</v>
-      </c>
-      <c r="C8" s="239"/>
+      <c r="B8" s="244" t="s">
+        <v>237</v>
+      </c>
+      <c r="C8" s="244"/>
       <c r="D8" s="48"/>
       <c r="E8" s="48"/>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="48"/>
-      <c r="B9" s="239"/>
-      <c r="C9" s="239"/>
+      <c r="B9" s="244"/>
+      <c r="C9" s="244"/>
       <c r="D9" s="48"/>
       <c r="E9" s="48"/>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="48"/>
-      <c r="B10" s="239"/>
-      <c r="C10" s="239"/>
+      <c r="B10" s="244"/>
+      <c r="C10" s="244"/>
       <c r="D10" s="48"/>
       <c r="E10" s="48"/>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="48"/>
       <c r="B11" s="48"/>
       <c r="C11" s="48"/>
       <c r="D11" s="48"/>
       <c r="E11" s="48"/>
     </row>
-    <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A12" s="48"/>
       <c r="B12" s="48"/>
       <c r="C12" s="48"/>
       <c r="D12" s="48"/>
       <c r="E12" s="48"/>
     </row>
-    <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="240" t="s">
+    <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="245" t="s">
         <v>103</v>
       </c>
-      <c r="B13" s="240"/>
-      <c r="C13" s="240"/>
-      <c r="D13" s="240"/>
-      <c r="E13" s="240"/>
-    </row>
-    <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="240"/>
-      <c r="B14" s="240"/>
-      <c r="C14" s="240"/>
-      <c r="D14" s="240"/>
-      <c r="E14" s="240"/>
-    </row>
-    <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="240"/>
-      <c r="B15" s="240"/>
-      <c r="C15" s="240"/>
-      <c r="D15" s="240"/>
-      <c r="E15" s="240"/>
-    </row>
-    <row r="16" spans="1:5" ht="53.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="240"/>
-      <c r="B16" s="240"/>
-      <c r="C16" s="240"/>
-      <c r="D16" s="240"/>
-      <c r="E16" s="240"/>
-    </row>
-    <row r="17" spans="1:8" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B13" s="245"/>
+      <c r="C13" s="245"/>
+      <c r="D13" s="245"/>
+      <c r="E13" s="245"/>
+    </row>
+    <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="245"/>
+      <c r="B14" s="245"/>
+      <c r="C14" s="245"/>
+      <c r="D14" s="245"/>
+      <c r="E14" s="245"/>
+    </row>
+    <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="245"/>
+      <c r="B15" s="245"/>
+      <c r="C15" s="245"/>
+      <c r="D15" s="245"/>
+      <c r="E15" s="245"/>
+    </row>
+    <row r="16" spans="1:5" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="245"/>
+      <c r="B16" s="245"/>
+      <c r="C16" s="245"/>
+      <c r="D16" s="245"/>
+      <c r="E16" s="245"/>
+    </row>
+    <row r="17" spans="1:8" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" s="48"/>
       <c r="B17" s="48"/>
       <c r="C17" s="48"/>
       <c r="D17" s="48"/>
       <c r="E17" s="48"/>
     </row>
-    <row r="18" spans="1:8" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="181"/>
+    <row r="18" spans="1:8" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="179"/>
       <c r="B18" s="48"/>
       <c r="C18" s="48"/>
       <c r="D18" s="48"/>
       <c r="E18" s="48"/>
     </row>
-    <row r="19" spans="1:8" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:8" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="48"/>
       <c r="B19" s="48"/>
       <c r="C19" s="48"/>
       <c r="D19" s="48"/>
       <c r="E19" s="48"/>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A20" s="182" t="s">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20" s="180" t="s">
         <v>104</v>
       </c>
-      <c r="B20" s="183"/>
-      <c r="C20" s="184"/>
+      <c r="B20" s="181"/>
+      <c r="C20" s="182"/>
       <c r="D20" s="58"/>
       <c r="E20" s="59"/>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="36" t="s">
         <v>139</v>
       </c>
@@ -2787,688 +2826,702 @@
       <c r="D21" s="117"/>
       <c r="E21" s="153"/>
     </row>
-    <row r="22" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="233" t="s">
+    <row r="22" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="240" t="s">
         <v>165</v>
       </c>
-      <c r="B22" s="234"/>
-      <c r="C22" s="185"/>
-      <c r="D22" s="186">
+      <c r="B22" s="241"/>
+      <c r="C22" s="183"/>
+      <c r="D22" s="184">
         <v>3382992.69</v>
       </c>
       <c r="E22" s="154" t="s">
-        <v>254</v>
+        <v>245</v>
       </c>
       <c r="H22" s="19"/>
     </row>
-    <row r="23" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="233" t="s">
+    <row r="23" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="240" t="s">
         <v>166</v>
       </c>
-      <c r="B23" s="234"/>
-      <c r="C23" s="185"/>
-      <c r="D23" s="186">
+      <c r="B23" s="241"/>
+      <c r="C23" s="183"/>
+      <c r="D23" s="184">
         <v>-735800.92</v>
       </c>
       <c r="E23" s="20"/>
       <c r="H23" s="19"/>
     </row>
-    <row r="24" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="233" t="s">
+    <row r="24" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="240" t="s">
         <v>1</v>
       </c>
-      <c r="B24" s="234"/>
-      <c r="C24" s="185"/>
-      <c r="D24" s="187">
+      <c r="B24" s="241"/>
+      <c r="C24" s="183"/>
+      <c r="D24" s="185">
         <v>0.23</v>
       </c>
       <c r="E24" s="20"/>
       <c r="H24" s="19"/>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A25" s="188" t="s">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A25" s="186" t="s">
         <v>105</v>
       </c>
-      <c r="B25" s="188"/>
-      <c r="C25" s="188"/>
+      <c r="B25" s="186"/>
+      <c r="C25" s="186"/>
       <c r="D25" s="22"/>
       <c r="E25" s="155">
         <f>SUM(D22:D24)</f>
         <v>2647192</v>
       </c>
     </row>
-    <row r="26" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="188" t="s">
+    <row r="26" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="186" t="s">
         <v>180</v>
       </c>
-      <c r="B26" s="188"/>
-      <c r="C26" s="188"/>
+      <c r="B26" s="186"/>
+      <c r="C26" s="186"/>
       <c r="D26" s="22"/>
       <c r="E26" s="156"/>
     </row>
-    <row r="27" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="185"/>
-      <c r="B27" s="185"/>
-      <c r="C27" s="185"/>
+    <row r="27" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="183"/>
+      <c r="B27" s="183"/>
+      <c r="C27" s="183"/>
       <c r="D27" s="35"/>
       <c r="E27" s="169"/>
     </row>
-    <row r="28" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="185"/>
-      <c r="B28" s="185"/>
-      <c r="C28" s="185"/>
+    <row r="28" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="183"/>
+      <c r="B28" s="183"/>
+      <c r="C28" s="183"/>
       <c r="D28" s="35"/>
       <c r="E28" s="169"/>
     </row>
-    <row r="29" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="185"/>
-      <c r="B29" s="185"/>
-      <c r="C29" s="185"/>
-      <c r="D29" s="35"/>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A29" s="183" t="s">
+        <v>262</v>
+      </c>
+      <c r="B29" s="183"/>
+      <c r="C29" s="183"/>
+      <c r="D29" s="288">
+        <v>37000</v>
+      </c>
       <c r="E29" s="169"/>
     </row>
-    <row r="30" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="185"/>
-      <c r="B30" s="185"/>
-      <c r="C30" s="185"/>
-      <c r="D30" s="35"/>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A30" s="183" t="s">
+        <v>265</v>
+      </c>
+      <c r="B30" s="183"/>
+      <c r="C30" s="183"/>
+      <c r="D30" s="288">
+        <f>53000+480000</f>
+        <v>533000</v>
+      </c>
       <c r="E30" s="157"/>
     </row>
-    <row r="31" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="188" t="s">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A31" s="183" t="s">
+        <v>266</v>
+      </c>
+      <c r="B31" s="183"/>
+      <c r="C31" s="183"/>
+      <c r="D31" s="288">
+        <v>5837</v>
+      </c>
+      <c r="E31" s="157" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A32" s="183" t="s">
+        <v>267</v>
+      </c>
+      <c r="B32" s="183"/>
+      <c r="C32" s="183"/>
+      <c r="D32" s="288">
+        <v>5837</v>
+      </c>
+      <c r="E32" s="157" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A33" s="186" t="s">
         <v>105</v>
       </c>
-      <c r="B31" s="189"/>
-      <c r="C31" s="189"/>
-      <c r="D31" s="107"/>
-      <c r="E31" s="158">
-        <f>D27+D30</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A32" s="36" t="s">
+      <c r="B33" s="187"/>
+      <c r="C33" s="187"/>
+      <c r="D33" s="107"/>
+      <c r="E33" s="291">
+        <f>SUM(D29:D32)</f>
+        <v>581674</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A34" s="36" t="s">
         <v>140</v>
       </c>
-      <c r="B32" s="188"/>
-      <c r="C32" s="188"/>
-      <c r="D32" s="22"/>
-      <c r="E32" s="156"/>
-    </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A33" s="185" t="s">
+      <c r="B34" s="186"/>
+      <c r="C34" s="186"/>
+      <c r="D34" s="22"/>
+      <c r="E34" s="156"/>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A35" s="183" t="s">
         <v>191</v>
       </c>
-      <c r="B33" s="190"/>
-      <c r="C33" s="190"/>
-      <c r="D33" s="35">
+      <c r="B35" s="188"/>
+      <c r="C35" s="188"/>
+      <c r="D35" s="35">
         <v>12537.94</v>
       </c>
-      <c r="E33" s="157" t="str">
-        <f>E35</f>
+      <c r="E35" s="157" t="str">
+        <f>E37</f>
         <v>Debito 12/06</v>
       </c>
-      <c r="G33" s="66"/>
-    </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A34" s="185" t="s">
+      <c r="G35" s="66"/>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A36" s="183" t="s">
         <v>152</v>
       </c>
-      <c r="B34" s="190"/>
-      <c r="C34" s="190"/>
-      <c r="D34" s="35">
-        <v>898456.64</v>
-      </c>
-      <c r="E34" s="157" t="s">
-        <v>231</v>
-      </c>
-      <c r="G34" s="66"/>
-    </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A35" s="185" t="s">
+      <c r="B36" s="188"/>
+      <c r="C36" s="188"/>
+      <c r="D36" s="288">
+        <v>923050.1</v>
+      </c>
+      <c r="E36" s="157" t="s">
+        <v>273</v>
+      </c>
+      <c r="G36" s="66"/>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A37" s="183" t="s">
         <v>142</v>
       </c>
-      <c r="B35" s="190"/>
-      <c r="C35" s="190"/>
-      <c r="D35" s="289">
+      <c r="B37" s="188"/>
+      <c r="C37" s="188"/>
+      <c r="D37" s="226">
         <v>181264.12</v>
       </c>
-      <c r="E35" s="157" t="s">
-        <v>265</v>
-      </c>
-      <c r="G35" s="66"/>
-    </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A36" s="185" t="s">
+      <c r="E37" s="157" t="s">
+        <v>255</v>
+      </c>
+      <c r="G37" s="66"/>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A38" s="183" t="s">
         <v>144</v>
       </c>
-      <c r="B36" s="190"/>
-      <c r="C36" s="190"/>
-      <c r="D36" s="289">
+      <c r="B38" s="188"/>
+      <c r="C38" s="188"/>
+      <c r="D38" s="226">
         <v>94363</v>
       </c>
-      <c r="E36" s="157" t="str">
-        <f>E35</f>
+      <c r="E38" s="157" t="str">
+        <f>E37</f>
         <v>Debito 12/06</v>
       </c>
-      <c r="G36" s="50"/>
-    </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A37" s="185" t="s">
+      <c r="G38" s="50"/>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A39" s="183" t="s">
         <v>143</v>
-      </c>
-      <c r="B37" s="190"/>
-      <c r="C37" s="190"/>
-      <c r="D37" s="289">
-        <v>10484.780000000001</v>
-      </c>
-      <c r="E37" s="157" t="str">
-        <f>E35</f>
-        <v>Debito 12/06</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A38" s="185" t="s">
-        <v>153</v>
-      </c>
-      <c r="B38" s="190"/>
-      <c r="C38" s="190"/>
-      <c r="D38" s="35"/>
-      <c r="E38" s="157"/>
-    </row>
-    <row r="39" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="188" t="s">
-        <v>141</v>
       </c>
       <c r="B39" s="188"/>
       <c r="C39" s="188"/>
-      <c r="D39" s="22"/>
-      <c r="E39" s="41">
-        <f>SUM(D33:D38)</f>
-        <v>1197106.48</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A40" s="14" t="s">
+      <c r="D39" s="226">
+        <v>10484.780000000001</v>
+      </c>
+      <c r="E39" s="157" t="str">
+        <f>E37</f>
+        <v>Debito 12/06</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A40" s="183" t="s">
+        <v>153</v>
+      </c>
+      <c r="B40" s="188"/>
+      <c r="C40" s="188"/>
+      <c r="D40" s="35"/>
+      <c r="E40" s="157"/>
+    </row>
+    <row r="41" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="186" t="s">
+        <v>141</v>
+      </c>
+      <c r="B41" s="186"/>
+      <c r="C41" s="186"/>
+      <c r="D41" s="22"/>
+      <c r="E41" s="41">
+        <f>SUM(D35:D40)</f>
+        <v>1221699.94</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A42" s="14" t="s">
         <v>106</v>
       </c>
-      <c r="B40" s="21"/>
-      <c r="C40" s="21"/>
-      <c r="D40" s="23"/>
-      <c r="E40" s="158"/>
-    </row>
-    <row r="41" spans="1:7" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="241" t="s">
+      <c r="B42" s="21"/>
+      <c r="C42" s="21"/>
+      <c r="D42" s="23"/>
+      <c r="E42" s="158"/>
+    </row>
+    <row r="43" spans="1:7" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="246" t="s">
         <v>187</v>
       </c>
-      <c r="B41" s="242"/>
-      <c r="C41" s="26"/>
-      <c r="D41" s="180">
+      <c r="B43" s="247"/>
+      <c r="C43" s="26"/>
+      <c r="D43" s="290">
         <v>7805</v>
       </c>
-      <c r="E41" s="20" t="s">
+      <c r="E43" s="20" t="s">
         <v>188</v>
       </c>
     </row>
-    <row r="42" spans="1:7" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="241" t="s">
+    <row r="44" spans="1:7" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="246" t="s">
         <v>189</v>
       </c>
-      <c r="B42" s="242"/>
-      <c r="C42" s="26"/>
-      <c r="D42" s="180">
+      <c r="B44" s="247"/>
+      <c r="C44" s="26"/>
+      <c r="D44" s="290">
         <v>214164</v>
       </c>
-      <c r="E42" s="20" t="s">
+      <c r="E44" s="20" t="s">
         <v>188</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A43" s="21" t="s">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A45" s="21" t="s">
         <v>107</v>
       </c>
-      <c r="B43" s="21"/>
-      <c r="C43" s="21"/>
-      <c r="D43" s="22"/>
-      <c r="E43" s="41">
-        <f>SUM(D41:D42)</f>
+      <c r="B45" s="21"/>
+      <c r="C45" s="21"/>
+      <c r="D45" s="22"/>
+      <c r="E45" s="41">
+        <f>SUM(D43:D44)</f>
         <v>221969</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A44" s="14" t="s">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A46" s="14" t="s">
         <v>108</v>
       </c>
-      <c r="B44" s="27"/>
-      <c r="C44" s="27"/>
-      <c r="D44" s="28"/>
-      <c r="E44" s="159"/>
-    </row>
-    <row r="45" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="29" t="s">
+      <c r="B46" s="27"/>
+      <c r="C46" s="27"/>
+      <c r="D46" s="28"/>
+      <c r="E46" s="159"/>
+    </row>
+    <row r="47" spans="1:7" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="29" t="s">
         <v>109</v>
       </c>
-      <c r="B45" s="29" t="s">
+      <c r="B47" s="29" t="s">
         <v>172</v>
-      </c>
-      <c r="C45" s="29"/>
-      <c r="D45" s="30">
-        <v>662323</v>
-      </c>
-      <c r="E45" s="20" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="46" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="29" t="s">
-        <v>109</v>
-      </c>
-      <c r="B46" s="29" t="s">
-        <v>174</v>
-      </c>
-      <c r="C46" s="29"/>
-      <c r="D46" s="30">
-        <v>13831.45</v>
-      </c>
-      <c r="E46" s="20" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="47" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="29" t="s">
-        <v>181</v>
-      </c>
-      <c r="B47" s="29" t="s">
-        <v>173</v>
       </c>
       <c r="C47" s="29"/>
       <c r="D47" s="30">
-        <v>0</v>
-      </c>
-      <c r="E47" s="20"/>
-    </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
+        <v>662323</v>
+      </c>
+      <c r="E47" s="294" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="29" t="s">
-        <v>182</v>
-      </c>
-      <c r="B48" s="31"/>
+        <v>109</v>
+      </c>
+      <c r="B48" s="29" t="s">
+        <v>174</v>
+      </c>
       <c r="C48" s="29"/>
       <c r="D48" s="30">
-        <v>0</v>
+        <v>13831.45</v>
       </c>
       <c r="E48" s="20"/>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A49" s="241" t="s">
-        <v>110</v>
-      </c>
-      <c r="B49" s="242"/>
+    <row r="49" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A49" s="29" t="s">
+        <v>181</v>
+      </c>
+      <c r="B49" s="29" t="s">
+        <v>173</v>
+      </c>
       <c r="C49" s="29"/>
       <c r="D49" s="30">
-        <v>4499070.47</v>
-      </c>
-      <c r="E49" s="118" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A50" s="32" t="s">
+        <v>0</v>
+      </c>
+      <c r="E49" s="20"/>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A50" s="29" t="s">
+        <v>182</v>
+      </c>
+      <c r="B50" s="31"/>
+      <c r="C50" s="29"/>
+      <c r="D50" s="30">
+        <v>0</v>
+      </c>
+      <c r="E50" s="20"/>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A51" s="246" t="s">
+        <v>110</v>
+      </c>
+      <c r="B51" s="247"/>
+      <c r="C51" s="29"/>
+      <c r="D51" s="30">
+        <v>0</v>
+      </c>
+      <c r="E51" s="118" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A52" s="32" t="s">
         <v>111</v>
       </c>
-      <c r="B50" s="25"/>
-      <c r="C50" s="29"/>
-      <c r="D50" s="30"/>
-      <c r="E50" s="20"/>
-    </row>
-    <row r="51" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A51" s="21" t="s">
+      <c r="B52" s="25"/>
+      <c r="C52" s="29"/>
+      <c r="D52" s="30"/>
+      <c r="E52" s="20"/>
+    </row>
+    <row r="53" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A53" s="21" t="s">
         <v>112</v>
       </c>
-      <c r="B51" s="21"/>
-      <c r="C51" s="21"/>
-      <c r="D51" s="33"/>
-      <c r="E51" s="160">
-        <f>SUM(D45:D50)</f>
-        <v>5175224.92</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A52" s="14"/>
-      <c r="B52" s="21"/>
-      <c r="C52" s="21"/>
-      <c r="D52" s="22"/>
-      <c r="E52" s="161"/>
-    </row>
-    <row r="53" spans="1:6" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A53" s="235" t="s">
+      <c r="B53" s="21"/>
+      <c r="C53" s="21"/>
+      <c r="D53" s="33"/>
+      <c r="E53" s="160">
+        <f>SUM(D47:D52)</f>
+        <v>676154.45</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A54" s="14"/>
+      <c r="B54" s="21"/>
+      <c r="C54" s="21"/>
+      <c r="D54" s="22"/>
+      <c r="E54" s="161"/>
+    </row>
+    <row r="55" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A55" s="227" t="s">
         <v>168</v>
       </c>
-      <c r="B53" s="236"/>
-      <c r="C53" s="29"/>
-      <c r="D53" s="288">
+      <c r="B55" s="228"/>
+      <c r="C55" s="29"/>
+      <c r="D55" s="287">
         <v>285000</v>
       </c>
-      <c r="E53" s="168" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6" ht="33" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="291" t="s">
-        <v>268</v>
-      </c>
-      <c r="B54" s="292"/>
-      <c r="C54" s="29"/>
-      <c r="D54" s="288">
-        <v>1000000</v>
-      </c>
-      <c r="E54" s="34" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="55" spans="1:6" ht="103.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A55" s="235" t="s">
-        <v>229</v>
-      </c>
-      <c r="B55" s="236"/>
-      <c r="C55" s="29"/>
-      <c r="D55" s="30">
+      <c r="E55" s="168" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A56" s="227" t="s">
+        <v>263</v>
+      </c>
+      <c r="B56" s="228"/>
+      <c r="C56" s="29"/>
+      <c r="D56" s="287">
+        <f>660000+1400000</f>
+        <v>2060000</v>
+      </c>
+      <c r="E56" s="168" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A57" s="227" t="s">
+        <v>269</v>
+      </c>
+      <c r="B57" s="228"/>
+      <c r="C57" s="29"/>
+      <c r="D57" s="287">
         <f>2800000+1400000</f>
         <v>4200000</v>
       </c>
-      <c r="E55" s="168" t="s">
-        <v>230</v>
-      </c>
-      <c r="F55" s="50"/>
-    </row>
-    <row r="56" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="16" t="s">
-        <v>226</v>
-      </c>
-      <c r="B56" s="17"/>
-      <c r="C56" s="29"/>
-      <c r="D56" s="30">
-        <v>6990</v>
-      </c>
-      <c r="E56" s="168"/>
-      <c r="F56" s="50"/>
-    </row>
-    <row r="57" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A57" s="290" t="s">
-        <v>266</v>
-      </c>
-      <c r="B57" s="17"/>
-      <c r="C57" s="29"/>
-      <c r="D57" s="288">
-        <v>160000</v>
-      </c>
       <c r="E57" s="168" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="F57" s="50"/>
     </row>
-    <row r="58" spans="1:6" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="16" t="s">
-        <v>270</v>
+    <row r="58" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A58" s="92" t="s">
+        <v>264</v>
       </c>
       <c r="B58" s="17"/>
       <c r="C58" s="29"/>
-      <c r="D58" s="30">
-        <f>5200+5500</f>
-        <v>10700</v>
-      </c>
-      <c r="E58" s="34"/>
+      <c r="D58" s="287">
+        <v>160000</v>
+      </c>
+      <c r="E58" s="168" t="s">
+        <v>256</v>
+      </c>
       <c r="F58" s="50"/>
     </row>
-    <row r="59" spans="1:6" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:6" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="16" t="s">
-        <v>269</v>
+        <v>257</v>
       </c>
       <c r="B59" s="17"/>
       <c r="C59" s="29"/>
-      <c r="D59" s="288">
+      <c r="D59" s="287">
         <v>3000</v>
       </c>
-      <c r="E59" s="34"/>
+      <c r="E59" s="34" t="s">
+        <v>268</v>
+      </c>
       <c r="F59" s="50"/>
     </row>
-    <row r="60" spans="1:6" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A60" s="92" t="s">
-        <v>252</v>
-      </c>
-      <c r="B60" s="17"/>
+    <row r="60" spans="1:6" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A60" s="227" t="s">
+        <v>243</v>
+      </c>
+      <c r="B60" s="228"/>
       <c r="C60" s="29"/>
-      <c r="D60" s="288">
-        <v>324000</v>
+      <c r="D60" s="287">
+        <v>342000</v>
       </c>
       <c r="E60" s="34" t="s">
-        <v>253</v>
+        <v>244</v>
       </c>
       <c r="F60" s="50"/>
     </row>
-    <row r="61" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="92" t="s">
-        <v>257</v>
+        <v>248</v>
       </c>
       <c r="B61" s="17"/>
       <c r="C61" s="29"/>
-      <c r="D61" s="288">
-        <v>2800000</v>
+      <c r="D61" s="287">
+        <v>67900</v>
       </c>
       <c r="E61" s="34" t="s">
-        <v>208</v>
+        <v>260</v>
       </c>
       <c r="F61" s="50"/>
     </row>
-    <row r="62" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="92" t="s">
-        <v>258</v>
+        <v>249</v>
       </c>
       <c r="B62" s="17"/>
       <c r="C62" s="29"/>
-      <c r="D62" s="288">
-        <v>67900</v>
+      <c r="D62" s="287">
+        <v>31400</v>
       </c>
       <c r="E62" s="34" t="s">
-        <v>273</v>
+        <v>250</v>
       </c>
       <c r="F62" s="50"/>
     </row>
-    <row r="63" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="92" t="s">
-        <v>259</v>
+        <v>251</v>
       </c>
       <c r="B63" s="17"/>
       <c r="C63" s="29"/>
-      <c r="D63" s="288">
+      <c r="D63" s="287">
         <v>31400</v>
       </c>
       <c r="E63" s="34" t="s">
-        <v>260</v>
+        <v>250</v>
       </c>
       <c r="F63" s="50"/>
     </row>
-    <row r="64" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="92" t="s">
-        <v>261</v>
+        <v>252</v>
       </c>
       <c r="B64" s="17"/>
       <c r="C64" s="29"/>
-      <c r="D64" s="288">
+      <c r="D64" s="287">
         <v>31400</v>
       </c>
-      <c r="E64" s="34"/>
+      <c r="E64" s="34" t="s">
+        <v>250</v>
+      </c>
       <c r="F64" s="50"/>
     </row>
-    <row r="65" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="92" t="s">
-        <v>262</v>
+        <v>239</v>
       </c>
       <c r="B65" s="17"/>
       <c r="C65" s="29"/>
-      <c r="D65" s="288">
-        <v>31400</v>
-      </c>
-      <c r="E65" s="34"/>
+      <c r="D65" s="287">
+        <v>150000</v>
+      </c>
+      <c r="E65" s="154" t="s">
+        <v>259</v>
+      </c>
       <c r="F65" s="50"/>
     </row>
-    <row r="66" spans="1:6" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="92" t="s">
-        <v>248</v>
+        <v>208</v>
       </c>
       <c r="B66" s="17"/>
       <c r="C66" s="29"/>
-      <c r="D66" s="288">
-        <v>150000</v>
-      </c>
-      <c r="E66" s="154" t="s">
-        <v>272</v>
+      <c r="D66" s="287">
+        <v>292300</v>
+      </c>
+      <c r="E66" s="168" t="s">
+        <v>246</v>
       </c>
       <c r="F66" s="50"/>
     </row>
-    <row r="67" spans="1:6" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="92" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="B67" s="17"/>
       <c r="C67" s="29"/>
-      <c r="D67" s="288">
-        <v>292300</v>
+      <c r="D67" s="287">
+        <v>467850</v>
       </c>
       <c r="E67" s="168" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="F67" s="50"/>
     </row>
-    <row r="68" spans="1:6" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="92" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="B68" s="17"/>
       <c r="C68" s="29"/>
-      <c r="D68" s="288">
-        <v>467850</v>
+      <c r="D68" s="287">
+        <v>380000</v>
       </c>
       <c r="E68" s="168" t="s">
-        <v>267</v>
+        <v>261</v>
       </c>
       <c r="F68" s="50"/>
     </row>
-    <row r="69" spans="1:6" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A69" s="92" t="s">
-        <v>210</v>
-      </c>
-      <c r="B69" s="17"/>
+    <row r="69" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A69" s="227" t="s">
+        <v>253</v>
+      </c>
+      <c r="B69" s="228"/>
       <c r="C69" s="29"/>
-      <c r="D69" s="288">
-        <v>380000</v>
+      <c r="D69" s="287">
+        <v>25000</v>
       </c>
       <c r="E69" s="168" t="s">
-        <v>274</v>
+        <v>254</v>
       </c>
       <c r="F69" s="50"/>
     </row>
-    <row r="70" spans="1:6" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A70" s="235" t="s">
-        <v>263</v>
-      </c>
-      <c r="B70" s="236"/>
+    <row r="70" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A70" s="227" t="s">
+        <v>240</v>
+      </c>
+      <c r="B70" s="228"/>
       <c r="C70" s="29"/>
-      <c r="D70" s="288">
-        <v>25000</v>
+      <c r="D70" s="30">
+        <v>0</v>
       </c>
       <c r="E70" s="168" t="s">
-        <v>264</v>
+        <v>207</v>
       </c>
       <c r="F70" s="50"/>
     </row>
-    <row r="71" spans="1:6" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A71" s="235" t="s">
-        <v>249</v>
-      </c>
-      <c r="B71" s="236"/>
-      <c r="C71" s="29"/>
-      <c r="D71" s="30">
-        <v>105602.65</v>
-      </c>
-      <c r="E71" s="168" t="s">
-        <v>207</v>
-      </c>
-      <c r="F71" s="50"/>
-    </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A72" s="21" t="s">
-        <v>0</v>
+    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A71" s="21" t="s">
+        <v>0</v>
+      </c>
+      <c r="B71" s="14"/>
+      <c r="C71" s="14"/>
+      <c r="D71" s="36"/>
+      <c r="E71" s="41">
+        <f>SUM(D55:D70)</f>
+        <v>8527250</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A72" s="14" t="s">
+        <v>113</v>
       </c>
       <c r="B72" s="14"/>
       <c r="C72" s="14"/>
-      <c r="D72" s="36"/>
-      <c r="E72" s="41">
-        <f>SUM(D53:D71)</f>
-        <v>10372542.65</v>
-      </c>
-    </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A73" s="14" t="s">
-        <v>113</v>
-      </c>
-      <c r="B73" s="14"/>
-      <c r="C73" s="14"/>
-      <c r="D73" s="15"/>
-      <c r="E73" s="153"/>
-    </row>
-    <row r="74" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A74" s="235" t="s">
-        <v>250</v>
-      </c>
-      <c r="B74" s="236"/>
+      <c r="D72" s="15"/>
+      <c r="E72" s="153"/>
+    </row>
+    <row r="73" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A73" s="227" t="s">
+        <v>241</v>
+      </c>
+      <c r="B73" s="228"/>
+      <c r="C73" s="18"/>
+      <c r="D73" s="292">
+        <v>650000</v>
+      </c>
+      <c r="E73" s="168" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A74" s="16" t="s">
+        <v>167</v>
+      </c>
+      <c r="B74" s="17"/>
       <c r="C74" s="18"/>
-      <c r="D74" s="287">
-        <v>650000</v>
+      <c r="D74" s="289">
+        <v>250000</v>
       </c>
       <c r="E74" s="154" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="75" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A75" s="16" t="s">
-        <v>167</v>
-      </c>
-      <c r="B75" s="17"/>
+        <v>259</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A75" s="92" t="s">
+        <v>272</v>
+      </c>
+      <c r="B75" s="225"/>
       <c r="C75" s="18"/>
-      <c r="D75" s="293">
-        <v>250000</v>
-      </c>
-      <c r="E75" s="154" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="76" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D75" s="289">
+        <v>100000</v>
+      </c>
+      <c r="E75" s="168" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="92" t="s">
-        <v>271</v>
+        <v>258</v>
       </c>
       <c r="B76" s="17"/>
       <c r="C76" s="18"/>
-      <c r="D76" s="293">
+      <c r="D76" s="289">
         <v>100000</v>
       </c>
       <c r="E76" s="154" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="77" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="92" t="s">
-        <v>251</v>
+        <v>242</v>
       </c>
       <c r="B77" s="17"/>
       <c r="C77" s="18"/>
-      <c r="D77" s="179">
+      <c r="D77" s="289">
         <v>45000</v>
       </c>
-      <c r="E77" s="154" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="E77" s="168" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" s="21" t="s">
         <v>105</v>
       </c>
@@ -3476,11 +3529,11 @@
       <c r="C78" s="21"/>
       <c r="D78" s="22"/>
       <c r="E78" s="155">
-        <f>SUM(D74:D77)</f>
-        <v>1045000</v>
-      </c>
-    </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.3">
+        <f>SUM(D73:D77)</f>
+        <v>1145000</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" s="14" t="s">
         <v>114</v>
       </c>
@@ -3489,29 +3542,29 @@
       <c r="D79" s="38"/>
       <c r="E79" s="41"/>
     </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" s="29" t="s">
         <v>150</v>
       </c>
       <c r="B80" s="91"/>
       <c r="C80" s="91"/>
       <c r="D80" s="125">
-        <v>52000</v>
+        <v>0</v>
       </c>
       <c r="E80" s="162"/>
     </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A81" s="29" t="s">
         <v>151</v>
       </c>
       <c r="B81" s="91"/>
       <c r="C81" s="91"/>
-      <c r="D81" s="125">
-        <v>208770.83</v>
+      <c r="D81" s="293">
+        <v>201766.98</v>
       </c>
       <c r="E81" s="162"/>
     </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A82" s="39" t="s">
         <v>105</v>
       </c>
@@ -3520,17 +3573,17 @@
       <c r="D82" s="40"/>
       <c r="E82" s="41">
         <f>SUM(D80:D81)</f>
-        <v>260770.83</v>
-      </c>
-    </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.3">
+        <v>201766.98</v>
+      </c>
+    </row>
+    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A83" s="29"/>
       <c r="B83" s="29"/>
       <c r="C83" s="29"/>
       <c r="D83" s="42"/>
       <c r="E83" s="43"/>
     </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A84" s="44" t="s">
         <v>115</v>
       </c>
@@ -3539,13 +3592,13 @@
       <c r="D84" s="45"/>
       <c r="E84" s="46"/>
     </row>
-    <row r="85" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A85" s="47"/>
       <c r="D85" s="48"/>
       <c r="E85" s="49"/>
       <c r="F85" s="50"/>
     </row>
-    <row r="86" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A86" s="51" t="s">
         <v>116</v>
       </c>
@@ -3554,21 +3607,21 @@
       <c r="D86" s="54"/>
       <c r="E86" s="55">
         <f>(SUM(E21:E84))</f>
-        <v>20919805.879999999</v>
+        <v>15222706.370000001</v>
       </c>
       <c r="F86" s="56"/>
       <c r="G86" s="50"/>
     </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
       <c r="D87" s="48"/>
       <c r="E87" s="48"/>
     </row>
-    <row r="88" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="D88" s="48"/>
       <c r="E88" s="48"/>
       <c r="H88" s="57"/>
     </row>
-    <row r="89" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A89" s="11" t="s">
         <v>117</v>
       </c>
@@ -3577,38 +3630,38 @@
       <c r="D89" s="58"/>
       <c r="E89" s="59"/>
     </row>
-    <row r="90" spans="1:8" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A90" s="243" t="s">
-        <v>212</v>
-      </c>
-      <c r="B90" s="244"/>
+    <row r="90" spans="1:8" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A90" s="229" t="s">
+        <v>209</v>
+      </c>
+      <c r="B90" s="230"/>
       <c r="C90" s="29"/>
-      <c r="D90" s="247">
+      <c r="D90" s="233">
         <v>2015700</v>
       </c>
-      <c r="E90" s="229" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="91" spans="1:8" ht="1.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A91" s="245"/>
-      <c r="B91" s="246"/>
+      <c r="E90" s="235" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="91" spans="1:8" ht="1.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A91" s="231"/>
+      <c r="B91" s="232"/>
       <c r="C91" s="29"/>
-      <c r="D91" s="248"/>
-      <c r="E91" s="230"/>
-    </row>
-    <row r="92" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D91" s="234"/>
+      <c r="E91" s="236"/>
+    </row>
+    <row r="92" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D92" s="42"/>
       <c r="E92" s="42"/>
     </row>
-    <row r="93" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A93" s="24"/>
       <c r="B93" s="61"/>
       <c r="C93" s="29"/>
       <c r="D93" s="35"/>
       <c r="E93" s="60"/>
     </row>
-    <row r="94" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A94" s="62" t="s">
         <v>146</v>
       </c>
@@ -3620,15 +3673,15 @@
         <v>2015700</v>
       </c>
     </row>
-    <row r="95" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D95" s="48"/>
       <c r="E95" s="48"/>
     </row>
-    <row r="96" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="D96" s="48"/>
       <c r="E96" s="48"/>
     </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A97" s="44" t="s">
         <v>118</v>
       </c>
@@ -3640,11 +3693,11 @@
         <v>984300</v>
       </c>
     </row>
-    <row r="98" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="D98" s="48"/>
       <c r="E98" s="48"/>
     </row>
-    <row r="99" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A99" s="51" t="s">
         <v>119</v>
       </c>
@@ -3656,33 +3709,33 @@
         <v>3000000</v>
       </c>
     </row>
-    <row r="100" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="D100" s="48"/>
       <c r="E100" s="48"/>
     </row>
-    <row r="101" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A101" s="64" t="s">
         <v>120</v>
       </c>
       <c r="B101" s="65">
         <f>E86</f>
-        <v>20919805.879999999</v>
+        <v>15222706.370000001</v>
       </c>
       <c r="D101" s="48"/>
       <c r="E101" s="48"/>
     </row>
-    <row r="102" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A102" s="64" t="s">
         <v>121</v>
       </c>
       <c r="B102" s="65">
         <f>E86-E84</f>
-        <v>20919805.879999999</v>
+        <v>15222706.370000001</v>
       </c>
       <c r="D102" s="48"/>
       <c r="E102" s="48"/>
     </row>
-    <row r="103" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A103" s="64" t="s">
         <v>122</v>
       </c>
@@ -3693,7 +3746,7 @@
       <c r="D103" s="48"/>
       <c r="E103" s="48"/>
     </row>
-    <row r="104" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A104" s="64" t="s">
         <v>123</v>
       </c>
@@ -3704,142 +3757,142 @@
       <c r="D104" s="48"/>
       <c r="E104" s="48"/>
     </row>
-    <row r="105" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:5" x14ac:dyDescent="0.25">
       <c r="D105" s="48"/>
       <c r="E105" s="48"/>
     </row>
-    <row r="106" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:5" x14ac:dyDescent="0.25">
       <c r="D106" s="48"/>
       <c r="E106" s="48"/>
     </row>
-    <row r="107" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A107" s="228" t="s">
+    <row r="107" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A107" s="237" t="s">
         <v>176</v>
       </c>
-      <c r="B107" s="228"/>
+      <c r="B107" s="237"/>
       <c r="D107" s="48"/>
       <c r="E107" s="48"/>
     </row>
-    <row r="108" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A108" s="228"/>
-      <c r="B108" s="228"/>
+    <row r="108" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A108" s="237"/>
+      <c r="B108" s="237"/>
       <c r="D108" s="48"/>
       <c r="E108" s="48"/>
     </row>
-    <row r="109" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A109" s="228"/>
-      <c r="B109" s="228"/>
+    <row r="109" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A109" s="237"/>
+      <c r="B109" s="237"/>
       <c r="D109" s="48"/>
       <c r="E109" s="48"/>
     </row>
-    <row r="110" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:5" x14ac:dyDescent="0.25">
       <c r="D110" s="48"/>
       <c r="E110" s="48"/>
     </row>
-    <row r="111" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A111" s="228" t="s">
+    <row r="111" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A111" s="237" t="s">
         <v>206</v>
       </c>
-      <c r="B111" s="228"/>
+      <c r="B111" s="237"/>
       <c r="D111" s="48"/>
       <c r="E111" s="48"/>
     </row>
-    <row r="112" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A112" s="228"/>
-      <c r="B112" s="228"/>
+    <row r="112" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A112" s="237"/>
+      <c r="B112" s="237"/>
       <c r="D112" s="48"/>
       <c r="E112" s="48"/>
     </row>
-    <row r="113" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A113" s="228"/>
-      <c r="B113" s="228"/>
+    <row r="113" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A113" s="237"/>
+      <c r="B113" s="237"/>
       <c r="D113" s="48"/>
       <c r="E113" s="48"/>
     </row>
-    <row r="114" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D114" s="48"/>
       <c r="E114" s="48"/>
     </row>
-    <row r="115" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A115" s="228" t="s">
+    <row r="115" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A115" s="237" t="s">
         <v>183</v>
       </c>
-      <c r="B115" s="228"/>
+      <c r="B115" s="237"/>
       <c r="D115" s="48"/>
       <c r="E115" s="48"/>
     </row>
-    <row r="116" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A116" s="228"/>
-      <c r="B116" s="228"/>
+    <row r="116" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A116" s="237"/>
+      <c r="B116" s="237"/>
       <c r="D116" s="48"/>
       <c r="E116" s="48"/>
     </row>
-    <row r="117" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A117" s="228"/>
-      <c r="B117" s="228"/>
+    <row r="117" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A117" s="237"/>
+      <c r="B117" s="237"/>
       <c r="D117" s="48"/>
       <c r="E117" s="48"/>
     </row>
-    <row r="118" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D118" s="48"/>
       <c r="E118" s="48"/>
     </row>
-    <row r="119" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A119" s="228" t="s">
+    <row r="119" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A119" s="237" t="s">
         <v>186</v>
       </c>
-      <c r="B119" s="228"/>
+      <c r="B119" s="237"/>
       <c r="D119" s="48"/>
       <c r="E119" s="48"/>
     </row>
-    <row r="120" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A120" s="228"/>
-      <c r="B120" s="228"/>
+    <row r="120" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A120" s="237"/>
+      <c r="B120" s="237"/>
       <c r="D120" s="48"/>
       <c r="E120" s="48"/>
     </row>
-    <row r="121" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A121" s="228"/>
-      <c r="B121" s="228"/>
+    <row r="121" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A121" s="237"/>
+      <c r="B121" s="237"/>
       <c r="D121" s="48"/>
       <c r="E121" s="48"/>
     </row>
-    <row r="122" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D122" s="48"/>
       <c r="E122" s="48"/>
     </row>
-    <row r="123" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A123" s="228" t="s">
+    <row r="123" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A123" s="237" t="s">
         <v>185</v>
       </c>
-      <c r="B123" s="228"/>
+      <c r="B123" s="237"/>
       <c r="D123" s="48"/>
       <c r="E123" s="48"/>
     </row>
-    <row r="124" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A124" s="228"/>
-      <c r="B124" s="228"/>
+    <row r="124" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A124" s="237"/>
+      <c r="B124" s="237"/>
       <c r="D124" s="48"/>
       <c r="E124" s="48"/>
     </row>
-    <row r="125" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A125" s="228"/>
-      <c r="B125" s="228"/>
+    <row r="125" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A125" s="237"/>
+      <c r="B125" s="237"/>
       <c r="D125" s="48"/>
       <c r="E125" s="48"/>
     </row>
-    <row r="126" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:5" x14ac:dyDescent="0.25">
       <c r="D126" s="48"/>
       <c r="E126" s="48"/>
     </row>
-    <row r="127" spans="1:5" s="68" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:5" s="68" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A127"/>
       <c r="B127" s="66"/>
       <c r="C127" s="67"/>
       <c r="D127" s="164"/>
       <c r="E127" s="164"/>
     </row>
-    <row r="128" spans="1:5" s="68" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:5" s="68" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A128" s="170" t="s">
         <v>195</v>
       </c>
@@ -3850,18 +3903,18 @@
       <c r="D128" s="165"/>
       <c r="E128" s="165"/>
     </row>
-    <row r="129" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A129" s="26" t="s">
         <v>145</v>
       </c>
       <c r="B129" s="70">
         <f>-B102-B103</f>
-        <v>-22935505.879999999</v>
+        <v>-17238406.370000001</v>
       </c>
       <c r="D129" s="48"/>
       <c r="E129" s="48"/>
     </row>
-    <row r="130" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A130" s="26" t="s">
         <v>124</v>
       </c>
@@ -3873,21 +3926,21 @@
       <c r="E130" s="48"/>
       <c r="F130" s="66"/>
     </row>
-    <row r="131" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A131" s="26" t="s">
         <v>2</v>
       </c>
       <c r="B131" s="71">
         <f>PRORRATEO!F117</f>
-        <v>17773395.250000004</v>
+        <v>16770189.25</v>
       </c>
       <c r="D131" s="48"/>
       <c r="E131" s="48"/>
       <c r="F131" s="66"/>
     </row>
-    <row r="132" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A132" s="26" t="s">
-        <v>256</v>
+        <v>247</v>
       </c>
       <c r="B132" s="147">
         <v>-95000</v>
@@ -3896,9 +3949,9 @@
       <c r="E132" s="48"/>
       <c r="F132" s="66"/>
     </row>
-    <row r="133" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A133" s="26" t="s">
-        <v>232</v>
+        <v>223</v>
       </c>
       <c r="B133" s="147">
         <v>-101088</v>
@@ -3907,9 +3960,9 @@
       <c r="E133" s="48"/>
       <c r="F133" s="66"/>
     </row>
-    <row r="134" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A134" s="26" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="B134" s="71">
         <v>400000</v>
@@ -3918,9 +3971,9 @@
       <c r="E134" s="48"/>
       <c r="F134" s="66"/>
     </row>
-    <row r="135" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A135" s="26" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="B135" s="147">
         <v>-90199</v>
@@ -3929,9 +3982,9 @@
       <c r="E135" s="48"/>
       <c r="F135" s="66"/>
     </row>
-    <row r="136" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A136" s="26" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="B136" s="147">
         <v>-130000</v>
@@ -3940,44 +3993,44 @@
       <c r="E136" s="48"/>
       <c r="F136" s="66"/>
     </row>
-    <row r="137" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A137" s="72" t="s">
         <v>164</v>
       </c>
       <c r="B137" s="73">
         <f>SUM(B128:C136)</f>
-        <v>-6024684.849999994</v>
+        <v>-1330791.3399999999</v>
       </c>
       <c r="D137" s="66"/>
       <c r="E137" s="50"/>
       <c r="F137" s="50"/>
     </row>
-    <row r="138" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="139" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A139" s="227" t="s">
+    <row r="138" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="139" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A139" s="248" t="s">
         <v>125</v>
       </c>
-      <c r="B139" s="227"/>
-      <c r="C139" s="227"/>
-    </row>
-    <row r="140" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A140" s="227"/>
-      <c r="B140" s="227"/>
-      <c r="C140" s="227"/>
-    </row>
-    <row r="141" spans="1:13" ht="27" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B139" s="248"/>
+      <c r="C139" s="248"/>
+    </row>
+    <row r="140" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A140" s="248"/>
+      <c r="B140" s="248"/>
+      <c r="C140" s="248"/>
+    </row>
+    <row r="141" spans="1:13" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A141" s="74"/>
       <c r="B141" s="115"/>
       <c r="C141" s="75"/>
       <c r="D141" s="56"/>
     </row>
-    <row r="142" spans="1:13" ht="27" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:13" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A142" s="148"/>
       <c r="B142" s="115"/>
       <c r="C142" s="75"/>
       <c r="D142" s="56"/>
     </row>
-    <row r="143" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A143" s="76" t="s">
         <v>0</v>
       </c>
@@ -3987,36 +4040,37 @@
       </c>
       <c r="C143" s="78"/>
     </row>
-    <row r="144" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:13" x14ac:dyDescent="0.25">
       <c r="M144" s="79"/>
     </row>
   </sheetData>
-  <mergeCells count="25">
-    <mergeCell ref="A54:B54"/>
-    <mergeCell ref="A71:B71"/>
-    <mergeCell ref="A90:B91"/>
-    <mergeCell ref="D90:D91"/>
-    <mergeCell ref="E90:E91"/>
+  <mergeCells count="26">
+    <mergeCell ref="A139:C140"/>
+    <mergeCell ref="A111:B113"/>
+    <mergeCell ref="A123:B125"/>
+    <mergeCell ref="A119:B121"/>
+    <mergeCell ref="A107:B109"/>
     <mergeCell ref="A115:B117"/>
     <mergeCell ref="B1:E1"/>
     <mergeCell ref="A24:B24"/>
-    <mergeCell ref="A74:B74"/>
+    <mergeCell ref="A73:B73"/>
     <mergeCell ref="B3:E3"/>
     <mergeCell ref="B8:C10"/>
     <mergeCell ref="A13:E16"/>
     <mergeCell ref="A22:B22"/>
     <mergeCell ref="A23:B23"/>
-    <mergeCell ref="A49:B49"/>
-    <mergeCell ref="A41:B41"/>
-    <mergeCell ref="A42:B42"/>
+    <mergeCell ref="A51:B51"/>
+    <mergeCell ref="A43:B43"/>
+    <mergeCell ref="A44:B44"/>
+    <mergeCell ref="A69:B69"/>
+    <mergeCell ref="A55:B55"/>
+    <mergeCell ref="A57:B57"/>
+    <mergeCell ref="A60:B60"/>
+    <mergeCell ref="A56:B56"/>
     <mergeCell ref="A70:B70"/>
-    <mergeCell ref="A53:B53"/>
-    <mergeCell ref="A55:B55"/>
-    <mergeCell ref="A139:C140"/>
-    <mergeCell ref="A111:B113"/>
-    <mergeCell ref="A123:B125"/>
-    <mergeCell ref="A119:B121"/>
-    <mergeCell ref="A107:B109"/>
+    <mergeCell ref="A90:B91"/>
+    <mergeCell ref="D90:D91"/>
+    <mergeCell ref="E90:E91"/>
   </mergeCells>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="5" scale="90" orientation="portrait" r:id="rId1"/>
@@ -4027,53 +4081,53 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{533DB7A7-09F4-49CF-B824-70F15C1FF525}">
   <dimension ref="A1:P125"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="4.33203125" customWidth="1"/>
-    <col min="2" max="2" width="25.5546875" customWidth="1"/>
-    <col min="3" max="3" width="0.109375" customWidth="1"/>
-    <col min="4" max="4" width="8.44140625" customWidth="1"/>
-    <col min="5" max="5" width="14.109375" customWidth="1"/>
-    <col min="6" max="6" width="12.33203125" customWidth="1"/>
-    <col min="7" max="7" width="10.5546875" customWidth="1"/>
-    <col min="8" max="8" width="9.5546875" customWidth="1"/>
-    <col min="9" max="9" width="12.44140625" customWidth="1"/>
-    <col min="10" max="10" width="14.44140625" customWidth="1"/>
-    <col min="11" max="12" width="12.33203125" customWidth="1"/>
-    <col min="13" max="13" width="14.6640625" customWidth="1"/>
-    <col min="14" max="14" width="14.33203125" customWidth="1"/>
-    <col min="15" max="15" width="7.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="4.28515625" customWidth="1"/>
+    <col min="2" max="2" width="25.5703125" customWidth="1"/>
+    <col min="3" max="3" width="0.140625" customWidth="1"/>
+    <col min="4" max="4" width="8.42578125" customWidth="1"/>
+    <col min="5" max="5" width="14.140625" customWidth="1"/>
+    <col min="6" max="6" width="12.28515625" customWidth="1"/>
+    <col min="7" max="7" width="10.5703125" customWidth="1"/>
+    <col min="8" max="8" width="9.5703125" customWidth="1"/>
+    <col min="9" max="9" width="12.42578125" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" customWidth="1"/>
+    <col min="11" max="12" width="12.28515625" customWidth="1"/>
+    <col min="13" max="13" width="14.7109375" customWidth="1"/>
+    <col min="14" max="14" width="14.28515625" customWidth="1"/>
+    <col min="15" max="15" width="7.28515625" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="12" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="13" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:16" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="93"/>
       <c r="B1" s="94"/>
       <c r="C1" s="94"/>
-      <c r="D1" s="259"/>
-      <c r="E1" s="259"/>
-      <c r="F1" s="259"/>
-      <c r="G1" s="259"/>
-      <c r="H1" s="259"/>
-      <c r="I1" s="259"/>
-      <c r="J1" s="259"/>
-      <c r="K1" s="259"/>
-      <c r="L1" s="259"/>
-      <c r="M1" s="259"/>
+      <c r="D1" s="252"/>
+      <c r="E1" s="252"/>
+      <c r="F1" s="252"/>
+      <c r="G1" s="252"/>
+      <c r="H1" s="252"/>
+      <c r="I1" s="252"/>
+      <c r="J1" s="252"/>
+      <c r="K1" s="252"/>
+      <c r="L1" s="252"/>
+      <c r="M1" s="252"/>
       <c r="N1" s="95"/>
     </row>
-    <row r="2" spans="1:16" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:16" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="96"/>
       <c r="B2" s="97"/>
       <c r="C2" s="98"/>
       <c r="D2" s="98" t="s">
         <v>126</v>
       </c>
-      <c r="E2" s="249">
+      <c r="E2" s="276">
         <v>3000000</v>
       </c>
-      <c r="F2" s="249"/>
+      <c r="F2" s="276"/>
       <c r="G2" s="98"/>
       <c r="H2" s="98"/>
       <c r="I2" s="98" t="s">
@@ -4092,7 +4146,7 @@
         <v>13312274.1</v>
       </c>
     </row>
-    <row r="3" spans="1:16" ht="12.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:16" ht="12.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="102"/>
       <c r="B3" s="103"/>
       <c r="C3" s="103"/>
@@ -4109,192 +4163,192 @@
       <c r="N3" s="106"/>
       <c r="O3" s="80"/>
     </row>
-    <row r="4" spans="1:16" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="260" t="s">
+    <row r="4" spans="1:16" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="253" t="s">
         <v>163</v>
       </c>
-      <c r="B4" s="261"/>
-      <c r="C4" s="261"/>
-      <c r="D4" s="261"/>
-      <c r="E4" s="261"/>
-      <c r="F4" s="261"/>
-      <c r="G4" s="261"/>
-      <c r="H4" s="261"/>
-      <c r="I4" s="261"/>
-      <c r="J4" s="261"/>
-      <c r="K4" s="261"/>
-      <c r="L4" s="261"/>
-      <c r="M4" s="261"/>
-      <c r="N4" s="262"/>
+      <c r="B4" s="254"/>
+      <c r="C4" s="254"/>
+      <c r="D4" s="254"/>
+      <c r="E4" s="254"/>
+      <c r="F4" s="254"/>
+      <c r="G4" s="254"/>
+      <c r="H4" s="254"/>
+      <c r="I4" s="254"/>
+      <c r="J4" s="254"/>
+      <c r="K4" s="254"/>
+      <c r="L4" s="254"/>
+      <c r="M4" s="254"/>
+      <c r="N4" s="255"/>
       <c r="O4" s="80"/>
     </row>
-    <row r="5" spans="1:16" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="263"/>
-      <c r="B5" s="264"/>
-      <c r="C5" s="264"/>
-      <c r="D5" s="264"/>
-      <c r="E5" s="264"/>
-      <c r="F5" s="264"/>
-      <c r="G5" s="264"/>
-      <c r="H5" s="264"/>
-      <c r="I5" s="264"/>
-      <c r="J5" s="264"/>
-      <c r="K5" s="264"/>
-      <c r="L5" s="264"/>
-      <c r="M5" s="264"/>
-      <c r="N5" s="265"/>
+    <row r="5" spans="1:16" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="256"/>
+      <c r="B5" s="257"/>
+      <c r="C5" s="257"/>
+      <c r="D5" s="257"/>
+      <c r="E5" s="257"/>
+      <c r="F5" s="257"/>
+      <c r="G5" s="257"/>
+      <c r="H5" s="257"/>
+      <c r="I5" s="257"/>
+      <c r="J5" s="257"/>
+      <c r="K5" s="257"/>
+      <c r="L5" s="257"/>
+      <c r="M5" s="257"/>
+      <c r="N5" s="258"/>
       <c r="O5" s="80"/>
     </row>
-    <row r="6" spans="1:16" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="263"/>
-      <c r="B6" s="264"/>
-      <c r="C6" s="264"/>
-      <c r="D6" s="264"/>
-      <c r="E6" s="264"/>
-      <c r="F6" s="264"/>
-      <c r="G6" s="264"/>
-      <c r="H6" s="264"/>
-      <c r="I6" s="264"/>
-      <c r="J6" s="264"/>
-      <c r="K6" s="264"/>
-      <c r="L6" s="264"/>
-      <c r="M6" s="264"/>
-      <c r="N6" s="265"/>
+    <row r="6" spans="1:16" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="256"/>
+      <c r="B6" s="257"/>
+      <c r="C6" s="257"/>
+      <c r="D6" s="257"/>
+      <c r="E6" s="257"/>
+      <c r="F6" s="257"/>
+      <c r="G6" s="257"/>
+      <c r="H6" s="257"/>
+      <c r="I6" s="257"/>
+      <c r="J6" s="257"/>
+      <c r="K6" s="257"/>
+      <c r="L6" s="257"/>
+      <c r="M6" s="257"/>
+      <c r="N6" s="258"/>
       <c r="O6" s="80"/>
     </row>
-    <row r="7" spans="1:16" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="263"/>
-      <c r="B7" s="264"/>
-      <c r="C7" s="264"/>
-      <c r="D7" s="264"/>
-      <c r="E7" s="264"/>
-      <c r="F7" s="264"/>
-      <c r="G7" s="264"/>
-      <c r="H7" s="264"/>
-      <c r="I7" s="264"/>
-      <c r="J7" s="264"/>
-      <c r="K7" s="264"/>
-      <c r="L7" s="264"/>
-      <c r="M7" s="264"/>
-      <c r="N7" s="265"/>
+    <row r="7" spans="1:16" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="256"/>
+      <c r="B7" s="257"/>
+      <c r="C7" s="257"/>
+      <c r="D7" s="257"/>
+      <c r="E7" s="257"/>
+      <c r="F7" s="257"/>
+      <c r="G7" s="257"/>
+      <c r="H7" s="257"/>
+      <c r="I7" s="257"/>
+      <c r="J7" s="257"/>
+      <c r="K7" s="257"/>
+      <c r="L7" s="257"/>
+      <c r="M7" s="257"/>
+      <c r="N7" s="258"/>
       <c r="O7" s="80"/>
     </row>
-    <row r="8" spans="1:16" ht="192" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="266"/>
-      <c r="B8" s="267"/>
-      <c r="C8" s="267"/>
-      <c r="D8" s="267"/>
-      <c r="E8" s="267"/>
-      <c r="F8" s="267"/>
-      <c r="G8" s="267"/>
-      <c r="H8" s="267"/>
-      <c r="I8" s="267"/>
-      <c r="J8" s="267"/>
-      <c r="K8" s="267"/>
-      <c r="L8" s="267"/>
-      <c r="M8" s="267"/>
-      <c r="N8" s="268"/>
-    </row>
-    <row r="9" spans="1:16" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="275" t="s">
+    <row r="8" spans="1:16" ht="192" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="259"/>
+      <c r="B8" s="260"/>
+      <c r="C8" s="260"/>
+      <c r="D8" s="260"/>
+      <c r="E8" s="260"/>
+      <c r="F8" s="260"/>
+      <c r="G8" s="260"/>
+      <c r="H8" s="260"/>
+      <c r="I8" s="260"/>
+      <c r="J8" s="260"/>
+      <c r="K8" s="260"/>
+      <c r="L8" s="260"/>
+      <c r="M8" s="260"/>
+      <c r="N8" s="261"/>
+    </row>
+    <row r="9" spans="1:16" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="270" t="s">
         <v>161</v>
       </c>
-      <c r="B9" s="276"/>
-      <c r="C9" s="276"/>
-      <c r="D9" s="276"/>
-      <c r="E9" s="276"/>
-      <c r="F9" s="276"/>
-      <c r="G9" s="276"/>
-      <c r="H9" s="276"/>
-      <c r="I9" s="276"/>
-      <c r="J9" s="276"/>
-      <c r="K9" s="276"/>
-      <c r="L9" s="276"/>
-      <c r="M9" s="276"/>
-      <c r="N9" s="277"/>
-    </row>
-    <row r="10" spans="1:16" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="278" t="s">
+      <c r="B9" s="271"/>
+      <c r="C9" s="271"/>
+      <c r="D9" s="271"/>
+      <c r="E9" s="271"/>
+      <c r="F9" s="271"/>
+      <c r="G9" s="271"/>
+      <c r="H9" s="271"/>
+      <c r="I9" s="271"/>
+      <c r="J9" s="271"/>
+      <c r="K9" s="271"/>
+      <c r="L9" s="271"/>
+      <c r="M9" s="271"/>
+      <c r="N9" s="272"/>
+    </row>
+    <row r="10" spans="1:16" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="273" t="s">
         <v>162</v>
       </c>
-      <c r="B10" s="279"/>
-      <c r="C10" s="279"/>
-      <c r="D10" s="279"/>
-      <c r="E10" s="279"/>
-      <c r="F10" s="279"/>
-      <c r="G10" s="279"/>
-      <c r="H10" s="279"/>
-      <c r="I10" s="279"/>
-      <c r="J10" s="279"/>
-      <c r="K10" s="279"/>
-      <c r="L10" s="279"/>
-      <c r="M10" s="279"/>
-      <c r="N10" s="280"/>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A11" s="269" t="s">
+      <c r="B10" s="274"/>
+      <c r="C10" s="274"/>
+      <c r="D10" s="274"/>
+      <c r="E10" s="274"/>
+      <c r="F10" s="274"/>
+      <c r="G10" s="274"/>
+      <c r="H10" s="274"/>
+      <c r="I10" s="274"/>
+      <c r="J10" s="274"/>
+      <c r="K10" s="274"/>
+      <c r="L10" s="274"/>
+      <c r="M10" s="274"/>
+      <c r="N10" s="275"/>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A11" s="262" t="s">
         <v>128</v>
       </c>
-      <c r="B11" s="271" t="s">
+      <c r="B11" s="264" t="s">
         <v>129</v>
       </c>
-      <c r="C11" s="271" t="s">
+      <c r="C11" s="264" t="s">
         <v>130</v>
       </c>
-      <c r="D11" s="271" t="s">
+      <c r="D11" s="264" t="s">
         <v>131</v>
       </c>
-      <c r="E11" s="250" t="s">
+      <c r="E11" s="266" t="s">
         <v>132</v>
       </c>
-      <c r="F11" s="271" t="s">
+      <c r="F11" s="264" t="s">
         <v>133</v>
       </c>
-      <c r="G11" s="273" t="s">
+      <c r="G11" s="268" t="s">
         <v>134</v>
       </c>
-      <c r="H11" s="250" t="s">
+      <c r="H11" s="266" t="s">
         <v>135</v>
       </c>
-      <c r="I11" s="250" t="s">
+      <c r="I11" s="266" t="s">
         <v>127</v>
       </c>
-      <c r="J11" s="250" t="s">
+      <c r="J11" s="266" t="s">
         <v>126</v>
       </c>
-      <c r="K11" s="252" t="s">
+      <c r="K11" s="277" t="s">
         <v>178</v>
       </c>
-      <c r="L11" s="254" t="s">
+      <c r="L11" s="279" t="s">
         <v>184</v>
       </c>
       <c r="M11" s="144" t="s">
         <v>136</v>
       </c>
-      <c r="N11" s="256" t="s">
+      <c r="N11" s="249" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="12" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="270"/>
-      <c r="B12" s="272"/>
-      <c r="C12" s="272"/>
-      <c r="D12" s="272"/>
-      <c r="E12" s="251"/>
-      <c r="F12" s="272"/>
-      <c r="G12" s="274"/>
-      <c r="H12" s="251"/>
-      <c r="I12" s="251"/>
-      <c r="J12" s="251"/>
-      <c r="K12" s="253"/>
-      <c r="L12" s="255"/>
+    <row r="12" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="263"/>
+      <c r="B12" s="265"/>
+      <c r="C12" s="265"/>
+      <c r="D12" s="265"/>
+      <c r="E12" s="267"/>
+      <c r="F12" s="265"/>
+      <c r="G12" s="269"/>
+      <c r="H12" s="267"/>
+      <c r="I12" s="267"/>
+      <c r="J12" s="267"/>
+      <c r="K12" s="278"/>
+      <c r="L12" s="280"/>
       <c r="M12" s="145" t="str">
         <f>RESUMEN!B8</f>
         <v>VTO 17/07</v>
       </c>
-      <c r="N12" s="257"/>
-    </row>
-    <row r="13" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N12" s="250"/>
+    </row>
+    <row r="13" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="130">
         <v>1</v>
       </c>
@@ -4306,11 +4360,11 @@
         <v>1.37</v>
       </c>
       <c r="E13" s="83">
-        <v>223478.01</v>
+        <v>232597.01</v>
       </c>
       <c r="F13" s="84">
         <f>E13</f>
-        <v>223478.01</v>
+        <v>232597.01</v>
       </c>
       <c r="G13" s="85">
         <f t="shared" ref="G13:G76" si="0">E13-F13</f>
@@ -4342,7 +4396,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="14" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="131">
         <v>2</v>
       </c>
@@ -4354,16 +4408,16 @@
         <v>1.18</v>
       </c>
       <c r="E14" s="84">
-        <v>3209597.02</v>
+        <v>3506224.02</v>
       </c>
       <c r="F14" s="84"/>
       <c r="G14" s="111">
         <f t="shared" si="0"/>
-        <v>3209597.02</v>
+        <v>3506224.02</v>
       </c>
       <c r="H14" s="111">
         <f t="shared" ref="H14:H77" si="4">IF(G14&gt;0,G14*3%,0)</f>
-        <v>96287.910600000003</v>
+        <v>105186.7206</v>
       </c>
       <c r="I14" s="127">
         <f t="shared" si="1"/>
@@ -4377,11 +4431,11 @@
       <c r="L14" s="150"/>
       <c r="M14" s="112">
         <f>ROUND(SUM(G14:L14),0) + O14</f>
-        <v>3506224.02</v>
+        <v>3811750.02</v>
       </c>
       <c r="N14" s="141">
         <f t="shared" si="3"/>
-        <v>3611411.02</v>
+        <v>3926103.02</v>
       </c>
       <c r="O14" s="50">
         <f>O13+0.01</f>
@@ -4391,7 +4445,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="15" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="130">
         <v>3</v>
       </c>
@@ -4403,11 +4457,11 @@
         <v>0.74</v>
       </c>
       <c r="E15" s="83">
-        <v>120711.03</v>
+        <v>125636.03</v>
       </c>
       <c r="F15" s="84">
         <f>E15</f>
-        <v>120711.03</v>
+        <v>125636.03</v>
       </c>
       <c r="G15" s="85">
         <f t="shared" si="0"/>
@@ -4440,7 +4494,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="16" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="131">
         <v>4</v>
       </c>
@@ -4452,11 +4506,11 @@
         <v>1.47</v>
       </c>
       <c r="E16" s="84">
-        <v>239790.04</v>
+        <v>249575.04000000001</v>
       </c>
       <c r="F16" s="84">
         <f>E16</f>
-        <v>239790.04</v>
+        <v>249575.04000000001</v>
       </c>
       <c r="G16" s="111">
         <f t="shared" si="0"/>
@@ -4489,7 +4543,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="17" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="130">
         <v>5</v>
       </c>
@@ -4501,14 +4555,14 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="E17" s="84">
-        <v>182697.05</v>
+        <v>184671.05</v>
       </c>
       <c r="F17" s="84">
         <v>188178.05</v>
       </c>
       <c r="G17" s="85">
         <f t="shared" si="0"/>
-        <v>-5481</v>
+        <v>-3507</v>
       </c>
       <c r="H17" s="85">
         <f t="shared" si="4"/>
@@ -4526,18 +4580,18 @@
       <c r="L17" s="149"/>
       <c r="M17" s="86">
         <f t="shared" si="5"/>
-        <v>184671.05</v>
+        <v>186645.05</v>
       </c>
       <c r="N17" s="140">
         <f t="shared" si="3"/>
-        <v>190211.05</v>
+        <v>192244.05</v>
       </c>
       <c r="O17" s="50">
         <f t="shared" si="6"/>
         <v>0.05</v>
       </c>
     </row>
-    <row r="18" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="130">
         <v>6</v>
       </c>
@@ -4549,18 +4603,18 @@
         <v>1.35</v>
       </c>
       <c r="E18" s="83">
-        <v>219381.06</v>
+        <v>228582.06</v>
       </c>
       <c r="F18" s="84">
         <v>220000.06</v>
       </c>
       <c r="G18" s="85">
         <f t="shared" si="0"/>
-        <v>-619</v>
+        <v>8582</v>
       </c>
       <c r="H18" s="85">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>257.45999999999998</v>
       </c>
       <c r="I18" s="126">
         <f t="shared" si="1"/>
@@ -4574,18 +4628,18 @@
       <c r="L18" s="149"/>
       <c r="M18" s="86">
         <f t="shared" si="5"/>
-        <v>228582.06</v>
+        <v>238041.06</v>
       </c>
       <c r="N18" s="140">
         <f t="shared" si="3"/>
-        <v>235439.06</v>
+        <v>245182.06</v>
       </c>
       <c r="O18" s="50">
         <f t="shared" si="6"/>
         <v>6.0000000000000005E-2</v>
       </c>
     </row>
-    <row r="19" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="130">
         <v>7</v>
       </c>
@@ -4597,11 +4651,11 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="E19" s="83">
-        <v>182697.07</v>
+        <v>190152.07</v>
       </c>
       <c r="F19" s="84">
         <f>E19</f>
-        <v>182697.07</v>
+        <v>190152.07</v>
       </c>
       <c r="G19" s="85">
         <f t="shared" si="0"/>
@@ -4634,7 +4688,7 @@
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="20" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="130">
         <v>8</v>
       </c>
@@ -4646,18 +4700,18 @@
         <v>0.82</v>
       </c>
       <c r="E20" s="83">
-        <v>129904.08</v>
+        <v>135322.07999999999</v>
       </c>
       <c r="F20" s="84">
         <v>133801.07999999999</v>
       </c>
       <c r="G20" s="85">
         <f t="shared" si="0"/>
-        <v>-3896.9999999999854</v>
+        <v>1521</v>
       </c>
       <c r="H20" s="85">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>45.629999999999995</v>
       </c>
       <c r="I20" s="126">
         <f t="shared" si="1"/>
@@ -4671,18 +4725,18 @@
       <c r="L20" s="149"/>
       <c r="M20" s="86">
         <f t="shared" si="5"/>
-        <v>135322.07999999999</v>
+        <v>140785.07999999999</v>
       </c>
       <c r="N20" s="140">
         <f t="shared" si="3"/>
-        <v>139382.07999999999</v>
+        <v>145009.07999999999</v>
       </c>
       <c r="O20" s="50">
         <f t="shared" si="6"/>
         <v>0.08</v>
       </c>
     </row>
-    <row r="21" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="130">
         <v>9</v>
       </c>
@@ -4694,14 +4748,14 @@
         <v>0.82</v>
       </c>
       <c r="E21" s="83">
-        <v>262473.09000000003</v>
+        <v>131345.09</v>
       </c>
       <c r="F21" s="84">
         <v>270347.09000000003</v>
       </c>
       <c r="G21" s="85">
         <f t="shared" si="0"/>
-        <v>-7874</v>
+        <v>-139002.00000000003</v>
       </c>
       <c r="H21" s="85">
         <f t="shared" si="4"/>
@@ -4719,18 +4773,18 @@
       <c r="L21" s="149"/>
       <c r="M21" s="86">
         <f t="shared" si="5"/>
-        <v>131345.09</v>
+        <v>217.09</v>
       </c>
       <c r="N21" s="140">
         <f t="shared" si="3"/>
-        <v>135285.09</v>
+        <v>224.09</v>
       </c>
       <c r="O21" s="50">
         <f t="shared" si="6"/>
         <v>0.09</v>
       </c>
     </row>
-    <row r="22" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="130">
         <v>10</v>
       </c>
@@ -4742,11 +4796,11 @@
         <v>1.34</v>
       </c>
       <c r="E22" s="83">
-        <v>218584.1</v>
+        <v>40200.1</v>
       </c>
       <c r="F22" s="84">
         <f>E22</f>
-        <v>218584.1</v>
+        <v>40200.1</v>
       </c>
       <c r="G22" s="85">
         <f t="shared" si="0"/>
@@ -4757,7 +4811,7 @@
         <v>0</v>
       </c>
       <c r="I22" s="126" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="J22" s="126">
         <f t="shared" si="2"/>
@@ -4778,7 +4832,7 @@
         <v>9.9999999999999992E-2</v>
       </c>
     </row>
-    <row r="23" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="130">
         <v>11</v>
       </c>
@@ -4790,11 +4844,11 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="E23" s="83">
-        <v>182697.11</v>
+        <v>190152.11</v>
       </c>
       <c r="F23" s="84">
         <f>E23</f>
-        <v>182697.11</v>
+        <v>190152.11</v>
       </c>
       <c r="G23" s="85">
         <f t="shared" si="0"/>
@@ -4827,7 +4881,7 @@
         <v>0.10999999999999999</v>
       </c>
     </row>
-    <row r="24" spans="1:16" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:16" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="130">
         <v>12</v>
       </c>
@@ -4839,18 +4893,18 @@
         <v>1.17</v>
       </c>
       <c r="E24" s="83">
-        <v>4151089.12</v>
+        <v>4474263.12</v>
       </c>
       <c r="F24" s="84">
         <v>0</v>
       </c>
       <c r="G24" s="85">
         <f t="shared" si="0"/>
-        <v>4151089.12</v>
+        <v>4474263.12</v>
       </c>
       <c r="H24" s="85">
         <f t="shared" si="4"/>
-        <v>124532.67359999999</v>
+        <v>134227.89360000001</v>
       </c>
       <c r="I24" s="126">
         <f t="shared" si="1"/>
@@ -4864,18 +4918,18 @@
       <c r="L24" s="149"/>
       <c r="M24" s="86">
         <f t="shared" si="5"/>
-        <v>4474263.12</v>
+        <v>4807132.12</v>
       </c>
       <c r="N24" s="140">
         <f t="shared" si="3"/>
-        <v>4608491.12</v>
+        <v>4951346.12</v>
       </c>
       <c r="O24" s="50">
         <f t="shared" si="6"/>
         <v>0.11999999999999998</v>
       </c>
     </row>
-    <row r="25" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="130">
         <v>13</v>
       </c>
@@ -4887,11 +4941,11 @@
         <v>1.35</v>
       </c>
       <c r="E25" s="83">
-        <v>220216.13</v>
+        <v>229201.13</v>
       </c>
       <c r="F25" s="84">
         <f>E25</f>
-        <v>220216.13</v>
+        <v>229201.13</v>
       </c>
       <c r="G25" s="85">
         <f t="shared" si="0"/>
@@ -4924,7 +4978,7 @@
         <v>0.12999999999999998</v>
       </c>
     </row>
-    <row r="26" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="130">
         <v>14</v>
       </c>
@@ -4936,16 +4990,16 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="E26" s="83">
-        <v>182697.14</v>
+        <v>378330.14</v>
       </c>
       <c r="F26" s="84"/>
       <c r="G26" s="85">
         <f t="shared" si="0"/>
-        <v>182697.14</v>
+        <v>378330.14</v>
       </c>
       <c r="H26" s="85">
         <f t="shared" si="4"/>
-        <v>5480.9142000000002</v>
+        <v>11349.904200000001</v>
       </c>
       <c r="I26" s="126">
         <f t="shared" si="1"/>
@@ -4959,18 +5013,18 @@
       <c r="L26" s="149"/>
       <c r="M26" s="86">
         <f t="shared" si="5"/>
-        <v>378330.14</v>
+        <v>579832.14</v>
       </c>
       <c r="N26" s="140">
         <f t="shared" si="3"/>
-        <v>389680.14</v>
+        <v>597227.14</v>
       </c>
       <c r="O26" s="50">
         <f t="shared" si="6"/>
         <v>0.13999999999999999</v>
       </c>
     </row>
-    <row r="27" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="131">
         <v>15</v>
       </c>
@@ -4982,11 +5036,11 @@
         <v>0.82</v>
       </c>
       <c r="E27" s="84">
-        <v>133761.15</v>
+        <v>139219.15</v>
       </c>
       <c r="F27" s="84">
         <f>E27</f>
-        <v>133761.15</v>
+        <v>139219.15</v>
       </c>
       <c r="G27" s="85">
         <f t="shared" si="0"/>
@@ -5019,7 +5073,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="28" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="130">
         <v>16</v>
       </c>
@@ -5031,11 +5085,11 @@
         <v>0.82</v>
       </c>
       <c r="E28" s="83">
-        <v>133761.16</v>
+        <v>139219.16</v>
       </c>
       <c r="F28" s="84">
         <f t="shared" ref="F28" si="7">E28</f>
-        <v>133761.16</v>
+        <v>139219.16</v>
       </c>
       <c r="G28" s="85">
         <f t="shared" si="0"/>
@@ -5068,7 +5122,7 @@
         <v>0.16</v>
       </c>
     </row>
-    <row r="29" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="130">
         <v>17</v>
       </c>
@@ -5080,11 +5134,11 @@
         <v>1.34</v>
       </c>
       <c r="E29" s="83">
-        <v>227142.17</v>
+        <v>227504.17</v>
       </c>
       <c r="F29" s="84">
         <f>E29</f>
-        <v>227142.17</v>
+        <v>227504.17</v>
       </c>
       <c r="G29" s="85">
         <f t="shared" si="0"/>
@@ -5117,7 +5171,7 @@
         <v>0.17</v>
       </c>
     </row>
-    <row r="30" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="131">
         <v>18</v>
       </c>
@@ -5129,11 +5183,11 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="E30" s="84">
-        <v>182697.18</v>
+        <v>190152.18</v>
       </c>
       <c r="F30" s="84">
         <f>E30</f>
-        <v>182697.18</v>
+        <v>190152.18</v>
       </c>
       <c r="G30" s="111">
         <f t="shared" si="0"/>
@@ -5166,7 +5220,7 @@
         <v>0.18000000000000002</v>
       </c>
     </row>
-    <row r="31" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A31" s="131">
         <v>19</v>
       </c>
@@ -5178,16 +5232,16 @@
         <v>1.17</v>
       </c>
       <c r="E31" s="83">
-        <v>190854.19</v>
+        <v>395221.19</v>
       </c>
       <c r="F31" s="84"/>
       <c r="G31" s="85">
         <f t="shared" si="0"/>
-        <v>190854.19</v>
+        <v>395221.19</v>
       </c>
       <c r="H31" s="85">
         <f t="shared" si="4"/>
-        <v>5725.6256999999996</v>
+        <v>11856.635699999999</v>
       </c>
       <c r="I31" s="126">
         <f t="shared" si="1"/>
@@ -5201,11 +5255,11 @@
       <c r="L31" s="149"/>
       <c r="M31" s="86">
         <f t="shared" si="5"/>
-        <v>395221.19</v>
+        <v>605719.18999999994</v>
       </c>
       <c r="N31" s="140">
         <f t="shared" si="3"/>
-        <v>407078.19</v>
+        <v>623891.18999999994</v>
       </c>
       <c r="O31" s="50">
         <f>O30+0.01</f>
@@ -5215,7 +5269,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="32" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A32" s="132">
         <v>20</v>
       </c>
@@ -5227,7 +5281,7 @@
         <v>1.35</v>
       </c>
       <c r="E32" s="122">
-        <v>761594.2</v>
+        <v>779138.2</v>
       </c>
       <c r="F32" s="122">
         <f>211658+123300</f>
@@ -5235,7 +5289,7 @@
       </c>
       <c r="G32" s="123">
         <f t="shared" si="0"/>
-        <v>426636.19999999995</v>
+        <v>444180.19999999995</v>
       </c>
       <c r="H32" s="123"/>
       <c r="I32" s="129">
@@ -5252,21 +5306,21 @@
       </c>
       <c r="M32" s="124">
         <f t="shared" si="5"/>
-        <v>779138.2</v>
+        <v>796682.2</v>
       </c>
       <c r="N32" s="142">
         <f t="shared" si="3"/>
-        <v>802512.2</v>
+        <v>820582.2</v>
       </c>
       <c r="O32" s="50">
         <f t="shared" ref="O32:O95" si="8">O31+0.01</f>
         <v>0.20000000000000004</v>
       </c>
       <c r="P32" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="33" spans="1:16" x14ac:dyDescent="0.3">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="33" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A33" s="131">
         <v>21</v>
       </c>
@@ -5278,11 +5332,11 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="E33" s="84">
-        <v>182697.21</v>
+        <v>190152.21</v>
       </c>
       <c r="F33" s="84">
         <f>E33</f>
-        <v>182697.21</v>
+        <v>190152.21</v>
       </c>
       <c r="G33" s="111">
         <f t="shared" si="0"/>
@@ -5315,7 +5369,7 @@
         <v>0.21000000000000005</v>
       </c>
     </row>
-    <row r="34" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A34" s="131">
         <f>A33+1</f>
         <v>22</v>
@@ -5328,11 +5382,11 @@
         <v>0.82</v>
       </c>
       <c r="E34" s="83">
-        <v>128727.22</v>
+        <v>139219.22</v>
       </c>
       <c r="F34" s="84">
         <f>E34</f>
-        <v>128727.22</v>
+        <v>139219.22</v>
       </c>
       <c r="G34" s="85">
         <f t="shared" si="0"/>
@@ -5365,7 +5419,7 @@
         <v>0.22000000000000006</v>
       </c>
     </row>
-    <row r="35" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A35" s="130">
         <f t="shared" ref="A35:A98" si="10">A34+1</f>
         <v>23</v>
@@ -5378,11 +5432,11 @@
         <v>0.82</v>
       </c>
       <c r="E35" s="83">
-        <v>133761.23000000001</v>
+        <v>139219.23000000001</v>
       </c>
       <c r="F35" s="84">
         <f>E35</f>
-        <v>133761.23000000001</v>
+        <v>139219.23000000001</v>
       </c>
       <c r="G35" s="85">
         <f t="shared" si="0"/>
@@ -5415,7 +5469,7 @@
         <v>0.23000000000000007</v>
       </c>
     </row>
-    <row r="36" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A36" s="130">
         <f t="shared" si="10"/>
         <v>24</v>
@@ -5428,11 +5482,11 @@
         <v>1.34</v>
       </c>
       <c r="E36" s="83">
-        <v>218584.24</v>
+        <v>227504.24</v>
       </c>
       <c r="F36" s="84">
         <f>E36</f>
-        <v>218584.24</v>
+        <v>227504.24</v>
       </c>
       <c r="G36" s="85">
         <f t="shared" si="0"/>
@@ -5465,7 +5519,7 @@
         <v>0.24000000000000007</v>
       </c>
     </row>
-    <row r="37" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A37" s="130">
         <f t="shared" si="10"/>
         <v>25</v>
@@ -5478,16 +5532,16 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="E37" s="83">
-        <v>707300.25</v>
+        <v>918672.25</v>
       </c>
       <c r="F37" s="84"/>
       <c r="G37" s="85">
         <f t="shared" si="0"/>
-        <v>707300.25</v>
+        <v>918672.25</v>
       </c>
       <c r="H37" s="85">
         <f t="shared" si="4"/>
-        <v>21219.0075</v>
+        <v>27560.1675</v>
       </c>
       <c r="I37" s="126">
         <f t="shared" si="1"/>
@@ -5501,18 +5555,18 @@
       <c r="L37" s="149"/>
       <c r="M37" s="86">
         <f t="shared" si="5"/>
-        <v>918672.25</v>
+        <v>1136385.25</v>
       </c>
       <c r="N37" s="140">
         <f t="shared" si="9"/>
-        <v>946232.25</v>
+        <v>1170477.25</v>
       </c>
       <c r="O37" s="50">
         <f t="shared" si="8"/>
         <v>0.25000000000000006</v>
       </c>
     </row>
-    <row r="38" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A38" s="130">
         <f t="shared" si="10"/>
         <v>26</v>
@@ -5525,11 +5579,11 @@
         <v>1.17</v>
       </c>
       <c r="E38" s="83">
-        <v>196580.26</v>
+        <v>198641.26</v>
       </c>
       <c r="F38" s="84">
         <f>E38</f>
-        <v>196580.26</v>
+        <v>198641.26</v>
       </c>
       <c r="G38" s="85">
         <f t="shared" si="0"/>
@@ -5562,7 +5616,7 @@
         <v>0.26000000000000006</v>
       </c>
     </row>
-    <row r="39" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A39" s="130">
         <f t="shared" si="10"/>
         <v>27</v>
@@ -5575,11 +5629,11 @@
         <v>1.35</v>
       </c>
       <c r="E39" s="83">
-        <v>270216.27</v>
+        <v>229201.27</v>
       </c>
       <c r="F39" s="84">
         <f t="shared" ref="F39" si="11">E39</f>
-        <v>270216.27</v>
+        <v>229201.27</v>
       </c>
       <c r="G39" s="85">
         <f t="shared" si="0"/>
@@ -5612,7 +5666,7 @@
         <v>0.27000000000000007</v>
       </c>
     </row>
-    <row r="40" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A40" s="130">
         <f t="shared" si="10"/>
         <v>28</v>
@@ -5625,16 +5679,16 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="E40" s="83">
-        <v>358498.28</v>
+        <v>559406.28</v>
       </c>
       <c r="F40" s="84"/>
       <c r="G40" s="85">
         <f t="shared" si="0"/>
-        <v>358498.28</v>
+        <v>559406.28</v>
       </c>
       <c r="H40" s="85">
         <f t="shared" si="4"/>
-        <v>10754.948400000001</v>
+        <v>16782.188399999999</v>
       </c>
       <c r="I40" s="126">
         <f t="shared" si="1"/>
@@ -5648,18 +5702,18 @@
       <c r="L40" s="149"/>
       <c r="M40" s="86">
         <f t="shared" si="5"/>
-        <v>559406.28</v>
+        <v>766341.28</v>
       </c>
       <c r="N40" s="140">
         <f t="shared" si="9"/>
-        <v>576188.28</v>
+        <v>789331.28</v>
       </c>
       <c r="O40" s="50">
         <f t="shared" si="8"/>
         <v>0.28000000000000008</v>
       </c>
     </row>
-    <row r="41" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A41" s="131">
         <f t="shared" si="10"/>
         <v>29</v>
@@ -5672,11 +5726,11 @@
         <v>0.82</v>
       </c>
       <c r="E41" s="84">
-        <v>137774.29</v>
+        <v>139219.29</v>
       </c>
       <c r="F41" s="84">
         <f>E41</f>
-        <v>137774.29</v>
+        <v>139219.29</v>
       </c>
       <c r="G41" s="111">
         <f t="shared" si="0"/>
@@ -5712,7 +5766,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="42" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A42" s="131">
         <f t="shared" si="10"/>
         <v>30</v>
@@ -5725,18 +5779,18 @@
         <v>0.82</v>
       </c>
       <c r="E42" s="84">
-        <v>129892.3</v>
+        <v>135322.29999999999</v>
       </c>
       <c r="F42" s="84">
         <v>133789.29999999999</v>
       </c>
       <c r="G42" s="111">
         <f t="shared" si="0"/>
-        <v>-3896.9999999999854</v>
+        <v>1533</v>
       </c>
       <c r="H42" s="111">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>45.989999999999995</v>
       </c>
       <c r="I42" s="127">
         <f t="shared" si="1"/>
@@ -5750,18 +5804,18 @@
       <c r="L42" s="150"/>
       <c r="M42" s="112">
         <f t="shared" si="5"/>
-        <v>135322.29999999999</v>
+        <v>140798.29999999999</v>
       </c>
       <c r="N42" s="141">
         <f t="shared" si="9"/>
-        <v>139382.29999999999</v>
+        <v>145022.29999999999</v>
       </c>
       <c r="O42" s="50">
         <f t="shared" si="8"/>
         <v>0.3000000000000001</v>
       </c>
     </row>
-    <row r="43" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A43" s="130">
         <f t="shared" si="10"/>
         <v>31</v>
@@ -5774,11 +5828,11 @@
         <v>1.34</v>
       </c>
       <c r="E43" s="83">
-        <v>218584.31</v>
+        <v>227504.31</v>
       </c>
       <c r="F43" s="84">
         <f>E43</f>
-        <v>218584.31</v>
+        <v>227504.31</v>
       </c>
       <c r="G43" s="85">
         <f t="shared" si="0"/>
@@ -5811,7 +5865,7 @@
         <v>0.31000000000000011</v>
       </c>
     </row>
-    <row r="44" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A44" s="130">
         <f t="shared" si="10"/>
         <v>32</v>
@@ -5824,7 +5878,7 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="E44" s="83">
-        <v>541055.31999999995</v>
+        <v>350346.32</v>
       </c>
       <c r="F44" s="84">
         <f>205220.32+65307.32+115000</f>
@@ -5832,11 +5886,11 @@
       </c>
       <c r="G44" s="85">
         <f t="shared" si="0"/>
-        <v>155527.67999999993</v>
+        <v>-35181.320000000007</v>
       </c>
       <c r="H44" s="85">
         <f t="shared" si="4"/>
-        <v>4665.830399999998</v>
+        <v>0</v>
       </c>
       <c r="I44" s="126">
         <f t="shared" si="1"/>
@@ -5850,18 +5904,18 @@
       <c r="L44" s="149"/>
       <c r="M44" s="86">
         <f t="shared" si="5"/>
-        <v>350346.32</v>
+        <v>154971.32</v>
       </c>
       <c r="N44" s="140">
         <f t="shared" si="9"/>
-        <v>360856.32000000001</v>
+        <v>159620.32</v>
       </c>
       <c r="O44" s="50">
         <f t="shared" si="8"/>
         <v>0.32000000000000012</v>
       </c>
     </row>
-    <row r="45" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A45" s="132">
         <f t="shared" si="10"/>
         <v>33</v>
@@ -5874,11 +5928,11 @@
         <v>1.17</v>
       </c>
       <c r="E45" s="122">
-        <v>360854.33</v>
+        <v>368641.33</v>
       </c>
       <c r="F45" s="122">
         <f>E45</f>
-        <v>360854.33</v>
+        <v>368641.33</v>
       </c>
       <c r="G45" s="123">
         <f t="shared" si="0"/>
@@ -5910,10 +5964,10 @@
         <v>0.33000000000000013</v>
       </c>
       <c r="P45" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="46" spans="1:16" x14ac:dyDescent="0.3">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="46" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A46" s="130">
         <f t="shared" si="10"/>
         <v>34</v>
@@ -5926,11 +5980,11 @@
         <v>1.35</v>
       </c>
       <c r="E46" s="83">
-        <v>220216.34</v>
+        <v>229201.34</v>
       </c>
       <c r="F46" s="84">
         <f>E46</f>
-        <v>220216.34</v>
+        <v>229201.34</v>
       </c>
       <c r="G46" s="85">
         <f t="shared" si="0"/>
@@ -5963,50 +6017,50 @@
         <v>0.34000000000000014</v>
       </c>
     </row>
-    <row r="47" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A47" s="191">
+    <row r="47" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A47" s="189">
         <f t="shared" si="10"/>
         <v>35</v>
       </c>
-      <c r="B47" s="192" t="s">
+      <c r="B47" s="190" t="s">
         <v>36</v>
       </c>
-      <c r="C47" s="193"/>
-      <c r="D47" s="194">
+      <c r="C47" s="191"/>
+      <c r="D47" s="192">
         <v>1.1200000000000001</v>
       </c>
-      <c r="E47" s="195">
-        <v>183161.35</v>
-      </c>
-      <c r="F47" s="195">
+      <c r="E47" s="193">
+        <v>183314.35</v>
+      </c>
+      <c r="F47" s="193">
         <f>190000</f>
         <v>190000</v>
       </c>
-      <c r="G47" s="196">
+      <c r="G47" s="194">
         <f t="shared" si="0"/>
-        <v>-6838.6499999999942</v>
-      </c>
-      <c r="H47" s="196">
+        <v>-6685.6499999999942</v>
+      </c>
+      <c r="H47" s="194">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="I47" s="197">
+      <c r="I47" s="195">
         <f t="shared" si="12"/>
         <v>156552.34341600002</v>
       </c>
-      <c r="J47" s="197">
+      <c r="J47" s="195">
         <f t="shared" si="13"/>
         <v>33600.000000000007</v>
       </c>
-      <c r="K47" s="197"/>
-      <c r="L47" s="198"/>
-      <c r="M47" s="199">
+      <c r="K47" s="195"/>
+      <c r="L47" s="196"/>
+      <c r="M47" s="197">
         <f t="shared" si="5"/>
-        <v>183314.35</v>
-      </c>
-      <c r="N47" s="200">
+        <v>183467.35</v>
+      </c>
+      <c r="N47" s="198">
         <f t="shared" si="9"/>
-        <v>188813.35</v>
+        <v>188971.35</v>
       </c>
       <c r="O47" s="50">
         <f t="shared" si="8"/>
@@ -6016,7 +6070,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="48" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A48" s="130">
         <f t="shared" si="10"/>
         <v>36</v>
@@ -6029,11 +6083,11 @@
         <v>0.82</v>
       </c>
       <c r="E48" s="83">
-        <v>133761.35999999999</v>
+        <v>139219.35999999999</v>
       </c>
       <c r="F48" s="84">
         <f>E48</f>
-        <v>133761.35999999999</v>
+        <v>139219.35999999999</v>
       </c>
       <c r="G48" s="85">
         <f t="shared" si="0"/>
@@ -6069,7 +6123,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="49" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A49" s="130">
         <f t="shared" si="10"/>
         <v>37</v>
@@ -6082,7 +6136,7 @@
         <v>0.82</v>
       </c>
       <c r="E49" s="84">
-        <v>266181.37</v>
+        <v>131400.37</v>
       </c>
       <c r="F49" s="84">
         <f>130000+144000</f>
@@ -6090,7 +6144,7 @@
       </c>
       <c r="G49" s="85">
         <f t="shared" si="0"/>
-        <v>-7818.6300000000047</v>
+        <v>-142599.63</v>
       </c>
       <c r="H49" s="85">
         <f t="shared" si="4"/>
@@ -6108,21 +6162,21 @@
       <c r="L49" s="149"/>
       <c r="M49" s="86">
         <f t="shared" si="5"/>
-        <v>131400.37</v>
+        <v>-3380.63</v>
       </c>
       <c r="N49" s="140">
         <f t="shared" si="9"/>
-        <v>135342.37</v>
+        <v>-3481.63</v>
       </c>
       <c r="O49" s="50">
         <f t="shared" si="8"/>
         <v>0.37000000000000016</v>
       </c>
       <c r="P49" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="50" spans="1:16" x14ac:dyDescent="0.3">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="50" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A50" s="130">
         <f t="shared" si="10"/>
         <v>38</v>
@@ -6135,16 +6189,16 @@
         <v>1.34</v>
       </c>
       <c r="E50" s="83">
-        <v>257934.38</v>
+        <v>493176.38</v>
       </c>
       <c r="F50" s="84"/>
       <c r="G50" s="85">
         <f t="shared" si="0"/>
-        <v>257934.38</v>
+        <v>493176.38</v>
       </c>
       <c r="H50" s="85">
         <f t="shared" si="4"/>
-        <v>7738.0313999999998</v>
+        <v>14795.2914</v>
       </c>
       <c r="I50" s="126">
         <f t="shared" si="12"/>
@@ -6158,11 +6212,11 @@
       <c r="L50" s="149"/>
       <c r="M50" s="86">
         <f t="shared" si="5"/>
-        <v>493176.38</v>
+        <v>735475.38</v>
       </c>
       <c r="N50" s="140">
         <f t="shared" si="9"/>
-        <v>507971.38</v>
+        <v>757539.38</v>
       </c>
       <c r="O50" s="50">
         <f t="shared" si="8"/>
@@ -6172,7 +6226,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="51" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A51" s="130">
         <f t="shared" si="10"/>
         <v>39</v>
@@ -6185,11 +6239,11 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="E51" s="83">
-        <v>363564.39</v>
+        <v>190152.39</v>
       </c>
       <c r="F51" s="84">
         <f>E51</f>
-        <v>363564.39</v>
+        <v>190152.39</v>
       </c>
       <c r="G51" s="85">
         <f t="shared" si="0"/>
@@ -6222,7 +6276,7 @@
         <v>0.39000000000000018</v>
       </c>
     </row>
-    <row r="52" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A52" s="130">
         <f t="shared" si="10"/>
         <v>40</v>
@@ -6235,18 +6289,18 @@
         <v>1.17</v>
       </c>
       <c r="E52" s="83">
-        <v>958147.4</v>
+        <v>395221.4</v>
       </c>
       <c r="F52" s="84">
         <v>767293.4</v>
       </c>
       <c r="G52" s="85">
         <f t="shared" si="0"/>
-        <v>190854</v>
+        <v>-372072</v>
       </c>
       <c r="H52" s="85">
         <f t="shared" si="4"/>
-        <v>5725.62</v>
+        <v>0</v>
       </c>
       <c r="I52" s="126">
         <f t="shared" si="12"/>
@@ -6260,18 +6314,18 @@
       <c r="L52" s="149"/>
       <c r="M52" s="86">
         <f t="shared" si="5"/>
-        <v>395221.4</v>
+        <v>-173430.6</v>
       </c>
       <c r="N52" s="140">
         <f t="shared" si="9"/>
-        <v>407078.40000000002</v>
+        <v>-178633.60000000001</v>
       </c>
       <c r="O52" s="50">
         <f t="shared" si="8"/>
         <v>0.40000000000000019</v>
       </c>
     </row>
-    <row r="53" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A53" s="130">
         <f t="shared" si="10"/>
         <v>41</v>
@@ -6284,18 +6338,18 @@
         <v>1.35</v>
       </c>
       <c r="E53" s="83">
-        <v>220216.41</v>
+        <v>244116.41</v>
       </c>
       <c r="F53" s="84">
         <v>205736.41</v>
       </c>
       <c r="G53" s="85">
         <f t="shared" si="0"/>
-        <v>14480</v>
+        <v>38380</v>
       </c>
       <c r="H53" s="85">
         <f t="shared" si="4"/>
-        <v>434.4</v>
+        <v>1151.3999999999999</v>
       </c>
       <c r="I53" s="126">
         <f t="shared" si="12"/>
@@ -6309,18 +6363,18 @@
       <c r="L53" s="149"/>
       <c r="M53" s="86">
         <f t="shared" si="5"/>
-        <v>244116.41</v>
+        <v>268733.40999999997</v>
       </c>
       <c r="N53" s="140">
         <f t="shared" si="9"/>
-        <v>251439.41</v>
+        <v>276795.40999999997</v>
       </c>
       <c r="O53" s="50">
         <f t="shared" si="8"/>
         <v>0.4100000000000002</v>
       </c>
     </row>
-    <row r="54" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A54" s="132">
         <f t="shared" si="10"/>
         <v>42</v>
@@ -6333,11 +6387,11 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="E54" s="122">
-        <v>215697.42</v>
+        <v>223152.42</v>
       </c>
       <c r="F54" s="122">
         <f>E54</f>
-        <v>215697.42</v>
+        <v>223152.42</v>
       </c>
       <c r="G54" s="123">
         <f t="shared" si="0"/>
@@ -6372,7 +6426,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="55" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A55" s="132">
         <f t="shared" si="10"/>
         <v>43</v>
@@ -6385,11 +6439,11 @@
         <v>0.82</v>
       </c>
       <c r="E55" s="166">
-        <v>433761.43</v>
+        <v>439219.43</v>
       </c>
       <c r="F55" s="122">
         <f>E55</f>
-        <v>433761.43</v>
+        <v>439219.43</v>
       </c>
       <c r="G55" s="123">
         <f t="shared" si="0"/>
@@ -6424,10 +6478,10 @@
         <v>0.43000000000000022</v>
       </c>
       <c r="P55" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="56" spans="1:16" x14ac:dyDescent="0.3">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="56" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A56" s="130">
         <f t="shared" si="10"/>
         <v>44</v>
@@ -6440,7 +6494,7 @@
         <v>0.82</v>
       </c>
       <c r="E56" s="83">
-        <v>133752.44</v>
+        <v>97371.44</v>
       </c>
       <c r="F56" s="84">
         <f>37835+137765.44</f>
@@ -6448,7 +6502,7 @@
       </c>
       <c r="G56" s="85">
         <f t="shared" si="0"/>
-        <v>-41848</v>
+        <v>-78229</v>
       </c>
       <c r="H56" s="85">
         <f t="shared" si="4"/>
@@ -6466,35 +6520,35 @@
       <c r="L56" s="149"/>
       <c r="M56" s="86">
         <f t="shared" si="5"/>
-        <v>97371.44</v>
+        <v>60990.44</v>
       </c>
       <c r="N56" s="140">
         <f t="shared" si="9"/>
-        <v>100292.44</v>
+        <v>62820.44</v>
       </c>
       <c r="O56" s="50">
         <f t="shared" si="8"/>
         <v>0.44000000000000022</v>
       </c>
     </row>
-    <row r="57" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A57" s="130">
         <f t="shared" si="10"/>
         <v>45</v>
       </c>
       <c r="B57" s="88" t="s">
-        <v>234</v>
+        <v>225</v>
       </c>
       <c r="C57" s="87"/>
       <c r="D57" s="82">
         <v>1.34</v>
       </c>
       <c r="E57" s="83">
-        <v>218584.45</v>
+        <v>227504.45</v>
       </c>
       <c r="F57" s="84">
         <f>E57</f>
-        <v>218584.45</v>
+        <v>227504.45</v>
       </c>
       <c r="G57" s="85">
         <f t="shared" si="0"/>
@@ -6527,12 +6581,12 @@
         <v>0.45000000000000023</v>
       </c>
     </row>
-    <row r="58" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A58" s="213">
+    <row r="58" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A58" s="211">
         <f t="shared" si="10"/>
         <v>46</v>
       </c>
-      <c r="B58" s="214" t="s">
+      <c r="B58" s="212" t="s">
         <v>45</v>
       </c>
       <c r="C58" s="87"/>
@@ -6540,18 +6594,18 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="E58" s="83">
-        <v>200795.46</v>
+        <v>232172.46</v>
       </c>
       <c r="F58" s="84">
         <v>160000</v>
       </c>
       <c r="G58" s="85">
         <f t="shared" si="0"/>
-        <v>40795.459999999992</v>
+        <v>72172.459999999992</v>
       </c>
       <c r="H58" s="85">
         <f t="shared" si="4"/>
-        <v>1223.8637999999996</v>
+        <v>2165.1737999999996</v>
       </c>
       <c r="I58" s="126">
         <f t="shared" si="12"/>
@@ -6565,11 +6619,11 @@
       <c r="L58" s="149"/>
       <c r="M58" s="86">
         <f t="shared" si="5"/>
-        <v>232172.46</v>
+        <v>264490.46000000002</v>
       </c>
       <c r="N58" s="140">
         <f t="shared" si="9"/>
-        <v>239137.46</v>
+        <v>272425.46000000002</v>
       </c>
       <c r="O58" s="50">
         <f t="shared" si="8"/>
@@ -6579,7 +6633,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="59" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A59" s="132">
         <f t="shared" si="10"/>
         <v>47</v>
@@ -6592,14 +6646,14 @@
         <v>1.17</v>
       </c>
       <c r="E59" s="122">
-        <v>509291.47</v>
+        <v>524495.47</v>
       </c>
       <c r="F59" s="122">
         <v>318437.46999999997</v>
       </c>
       <c r="G59" s="123">
         <f t="shared" si="0"/>
-        <v>190854</v>
+        <v>206058</v>
       </c>
       <c r="H59" s="123"/>
       <c r="I59" s="129">
@@ -6616,21 +6670,21 @@
       </c>
       <c r="M59" s="124">
         <f t="shared" si="5"/>
-        <v>524495.47</v>
+        <v>539699.47</v>
       </c>
       <c r="N59" s="142">
         <f t="shared" si="9"/>
-        <v>540230.47</v>
+        <v>555890.47</v>
       </c>
       <c r="O59" s="50">
         <f t="shared" si="8"/>
         <v>0.47000000000000025</v>
       </c>
       <c r="P59" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="60" spans="1:16" x14ac:dyDescent="0.3">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="60" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A60" s="131">
         <f t="shared" si="10"/>
         <v>48</v>
@@ -6643,11 +6697,11 @@
         <v>1.35</v>
       </c>
       <c r="E60" s="84">
-        <v>226822.48</v>
+        <v>229201.48</v>
       </c>
       <c r="F60" s="84">
         <f t="shared" ref="F60:F66" si="14">E60</f>
-        <v>226822.48</v>
+        <v>229201.48</v>
       </c>
       <c r="G60" s="111">
         <f t="shared" si="0"/>
@@ -6683,7 +6737,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="61" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A61" s="131">
         <f t="shared" si="10"/>
         <v>49</v>
@@ -6696,11 +6750,11 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="E61" s="83">
-        <v>182697.49</v>
+        <v>190152.49</v>
       </c>
       <c r="F61" s="84">
         <f t="shared" si="14"/>
-        <v>182697.49</v>
+        <v>190152.49</v>
       </c>
       <c r="G61" s="85">
         <f t="shared" si="0"/>
@@ -6733,7 +6787,7 @@
         <v>0.49000000000000027</v>
       </c>
     </row>
-    <row r="62" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A62" s="131">
         <f t="shared" si="10"/>
         <v>50</v>
@@ -6746,16 +6800,16 @@
         <v>0.82</v>
       </c>
       <c r="E62" s="83">
-        <v>133761.5</v>
+        <v>276993.5</v>
       </c>
       <c r="F62" s="84"/>
       <c r="G62" s="85">
         <f t="shared" si="0"/>
-        <v>133761.5</v>
+        <v>276993.5</v>
       </c>
       <c r="H62" s="85">
         <f t="shared" si="4"/>
-        <v>4012.8449999999998</v>
+        <v>8309.8050000000003</v>
       </c>
       <c r="I62" s="126">
         <f t="shared" si="12"/>
@@ -6769,18 +6823,18 @@
       <c r="L62" s="149"/>
       <c r="M62" s="86">
         <f t="shared" si="5"/>
-        <v>276993.5</v>
+        <v>424522.5</v>
       </c>
       <c r="N62" s="140">
         <f t="shared" si="9"/>
-        <v>285303.5</v>
+        <v>437258.5</v>
       </c>
       <c r="O62" s="50">
         <f t="shared" si="8"/>
         <v>0.50000000000000022</v>
       </c>
     </row>
-    <row r="63" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A63" s="131">
         <f t="shared" si="10"/>
         <v>51</v>
@@ -6793,11 +6847,11 @@
         <v>0.82</v>
       </c>
       <c r="E63" s="83">
-        <v>133761.51</v>
+        <v>139219.51</v>
       </c>
       <c r="F63" s="84">
         <f t="shared" si="14"/>
-        <v>133761.51</v>
+        <v>139219.51</v>
       </c>
       <c r="G63" s="85">
         <f t="shared" si="0"/>
@@ -6830,7 +6884,7 @@
         <v>0.51000000000000023</v>
       </c>
     </row>
-    <row r="64" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A64" s="131">
         <f t="shared" si="10"/>
         <v>52</v>
@@ -6843,11 +6897,11 @@
         <v>1.34</v>
       </c>
       <c r="E64" s="83">
-        <v>218584.52</v>
+        <v>227504.52</v>
       </c>
       <c r="F64" s="84">
         <f t="shared" si="14"/>
-        <v>218584.52</v>
+        <v>227504.52</v>
       </c>
       <c r="G64" s="85">
         <f t="shared" si="0"/>
@@ -6880,7 +6934,7 @@
         <v>0.52000000000000024</v>
       </c>
     </row>
-    <row r="65" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A65" s="131">
         <f t="shared" si="10"/>
         <v>53</v>
@@ -6893,11 +6947,11 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="E65" s="84">
-        <v>188178.53</v>
+        <v>190152.53</v>
       </c>
       <c r="F65" s="84">
         <f t="shared" si="14"/>
-        <v>188178.53</v>
+        <v>190152.53</v>
       </c>
       <c r="G65" s="85">
         <f t="shared" si="0"/>
@@ -6930,7 +6984,7 @@
         <v>0.53000000000000025</v>
       </c>
     </row>
-    <row r="66" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A66" s="131">
         <f t="shared" si="10"/>
         <v>54</v>
@@ -6943,11 +6997,11 @@
         <v>1.17</v>
       </c>
       <c r="E66" s="83">
-        <v>190854.54</v>
+        <v>198641.54</v>
       </c>
       <c r="F66" s="84">
         <f t="shared" si="14"/>
-        <v>190854.54</v>
+        <v>198641.54</v>
       </c>
       <c r="G66" s="85">
         <f t="shared" si="0"/>
@@ -6980,7 +7034,7 @@
         <v>0.54000000000000026</v>
       </c>
     </row>
-    <row r="67" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A67" s="131">
         <f t="shared" si="10"/>
         <v>55</v>
@@ -6993,11 +7047,11 @@
         <v>1.35</v>
       </c>
       <c r="E67" s="83">
-        <v>214044.55</v>
+        <v>229201.55</v>
       </c>
       <c r="F67" s="84">
         <f>E67</f>
-        <v>214044.55</v>
+        <v>229201.55</v>
       </c>
       <c r="G67" s="85">
         <f t="shared" si="0"/>
@@ -7030,7 +7084,7 @@
         <v>0.55000000000000027</v>
       </c>
     </row>
-    <row r="68" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A68" s="131">
         <f t="shared" si="10"/>
         <v>56</v>
@@ -7043,18 +7097,18 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="E68" s="83">
-        <v>497429.56</v>
+        <v>508681.56</v>
       </c>
       <c r="F68" s="84">
         <v>188178.56</v>
       </c>
       <c r="G68" s="85">
         <f t="shared" si="0"/>
-        <v>309251</v>
+        <v>320503</v>
       </c>
       <c r="H68" s="85">
         <f t="shared" si="4"/>
-        <v>9277.5299999999988</v>
+        <v>9615.09</v>
       </c>
       <c r="I68" s="126">
         <f t="shared" si="12"/>
@@ -7068,18 +7122,18 @@
       <c r="L68" s="149"/>
       <c r="M68" s="86">
         <f t="shared" si="5"/>
-        <v>508681.56</v>
+        <v>520270.56</v>
       </c>
       <c r="N68" s="140">
         <f t="shared" si="9"/>
-        <v>523941.56</v>
+        <v>535878.56000000006</v>
       </c>
       <c r="O68" s="50">
         <f t="shared" si="8"/>
         <v>0.56000000000000028</v>
       </c>
     </row>
-    <row r="69" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A69" s="131">
         <f t="shared" si="10"/>
         <v>57</v>
@@ -7092,14 +7146,14 @@
         <v>0.82</v>
       </c>
       <c r="E69" s="83">
-        <v>133714.57</v>
+        <v>125933.57</v>
       </c>
       <c r="F69" s="84">
         <v>147000</v>
       </c>
       <c r="G69" s="85">
         <f t="shared" si="0"/>
-        <v>-13285.429999999993</v>
+        <v>-21066.429999999993</v>
       </c>
       <c r="H69" s="85">
         <f t="shared" si="4"/>
@@ -7117,18 +7171,18 @@
       <c r="L69" s="149"/>
       <c r="M69" s="86">
         <f t="shared" si="5"/>
-        <v>125933.57</v>
+        <v>118152.57</v>
       </c>
       <c r="N69" s="140">
         <f t="shared" si="9"/>
-        <v>129711.57</v>
+        <v>121697.57</v>
       </c>
       <c r="O69" s="50">
         <f t="shared" si="8"/>
         <v>0.57000000000000028</v>
       </c>
     </row>
-    <row r="70" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A70" s="131">
         <f t="shared" si="10"/>
         <v>58</v>
@@ -7141,11 +7195,11 @@
         <v>0.82</v>
       </c>
       <c r="E70" s="83">
-        <v>133761.57999999999</v>
+        <v>139219.57999999999</v>
       </c>
       <c r="F70" s="84">
         <f t="shared" ref="F70:F71" si="15">E70</f>
-        <v>133761.57999999999</v>
+        <v>139219.57999999999</v>
       </c>
       <c r="G70" s="85">
         <f t="shared" si="0"/>
@@ -7178,10 +7232,10 @@
         <v>0.58000000000000029</v>
       </c>
       <c r="P70" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="71" spans="1:16" x14ac:dyDescent="0.3">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="71" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A71" s="131">
         <f t="shared" si="10"/>
         <v>59</v>
@@ -7194,11 +7248,11 @@
         <v>1.34</v>
       </c>
       <c r="E71" s="84">
-        <v>212463.59</v>
+        <v>227504.59</v>
       </c>
       <c r="F71" s="84">
         <f t="shared" si="15"/>
-        <v>212463.59</v>
+        <v>227504.59</v>
       </c>
       <c r="G71" s="111">
         <f t="shared" si="0"/>
@@ -7231,7 +7285,7 @@
         <v>0.5900000000000003</v>
       </c>
     </row>
-    <row r="72" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A72" s="131">
         <f t="shared" si="10"/>
         <v>60</v>
@@ -7244,18 +7298,18 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="E72" s="83">
-        <v>177577.60000000001</v>
+        <v>184825.60000000001</v>
       </c>
       <c r="F72" s="84">
         <v>182904.6</v>
       </c>
       <c r="G72" s="85">
         <f t="shared" si="0"/>
-        <v>-5327</v>
+        <v>1921</v>
       </c>
       <c r="H72" s="85">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>57.629999999999995</v>
       </c>
       <c r="I72" s="126">
         <f t="shared" si="12"/>
@@ -7269,18 +7323,18 @@
       <c r="L72" s="149"/>
       <c r="M72" s="86">
         <f t="shared" si="5"/>
-        <v>184825.60000000001</v>
+        <v>192131.6</v>
       </c>
       <c r="N72" s="140">
         <f t="shared" si="9"/>
-        <v>190370.6</v>
+        <v>197895.6</v>
       </c>
       <c r="O72" s="50">
         <f t="shared" si="8"/>
         <v>0.60000000000000031</v>
       </c>
     </row>
-    <row r="73" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A73" s="130">
         <f t="shared" si="10"/>
         <v>61</v>
@@ -7293,11 +7347,11 @@
         <v>1.17</v>
       </c>
       <c r="E73" s="83">
-        <v>190854.61</v>
+        <v>198641.61</v>
       </c>
       <c r="F73" s="84">
         <f>E73</f>
-        <v>190854.61</v>
+        <v>198641.61</v>
       </c>
       <c r="G73" s="85">
         <f t="shared" si="0"/>
@@ -7330,7 +7384,7 @@
         <v>0.61000000000000032</v>
       </c>
     </row>
-    <row r="74" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A74" s="130">
         <f t="shared" si="10"/>
         <v>62</v>
@@ -7343,11 +7397,11 @@
         <v>1.35</v>
       </c>
       <c r="E74" s="83">
-        <v>214044.62</v>
+        <v>229201.62</v>
       </c>
       <c r="F74" s="84">
         <f>E74</f>
-        <v>214044.62</v>
+        <v>229201.62</v>
       </c>
       <c r="G74" s="85">
         <f t="shared" si="0"/>
@@ -7380,7 +7434,7 @@
         <v>0.62000000000000033</v>
       </c>
     </row>
-    <row r="75" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A75" s="130">
         <f t="shared" si="10"/>
         <v>63</v>
@@ -7393,11 +7447,11 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="E75" s="83">
-        <v>182697.63</v>
+        <v>190152.63</v>
       </c>
       <c r="F75" s="84">
         <f>E75</f>
-        <v>182697.63</v>
+        <v>190152.63</v>
       </c>
       <c r="G75" s="85">
         <f t="shared" si="0"/>
@@ -7433,7 +7487,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="76" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A76" s="130">
         <f t="shared" si="10"/>
         <v>64</v>
@@ -7446,7 +7500,7 @@
         <v>0.82</v>
       </c>
       <c r="E76" s="83">
-        <v>234849.64</v>
+        <v>139219.64000000001</v>
       </c>
       <c r="F76" s="84">
         <f>133761.64+101088</f>
@@ -7454,7 +7508,7 @@
       </c>
       <c r="G76" s="85">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>-95630</v>
       </c>
       <c r="H76" s="85">
         <f t="shared" si="4"/>
@@ -7472,23 +7526,23 @@
       <c r="L76" s="149"/>
       <c r="M76" s="86">
         <f t="shared" si="5"/>
-        <v>139219.64000000001</v>
+        <v>43589.64</v>
       </c>
       <c r="N76" s="140">
         <f t="shared" si="9"/>
-        <v>143396.64000000001</v>
+        <v>44897.64</v>
       </c>
       <c r="O76" s="50">
         <f t="shared" si="8"/>
         <v>0.64000000000000035</v>
       </c>
     </row>
-    <row r="77" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A77" s="207">
+    <row r="77" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A77" s="205">
         <f t="shared" si="10"/>
         <v>65</v>
       </c>
-      <c r="B77" s="208" t="s">
+      <c r="B77" s="206" t="s">
         <v>64</v>
       </c>
       <c r="C77" s="113"/>
@@ -7496,18 +7550,18 @@
         <v>0.82</v>
       </c>
       <c r="E77" s="84">
-        <v>1146090.6499999999</v>
+        <v>907691.65</v>
       </c>
       <c r="F77" s="178">
         <v>400000.65</v>
       </c>
       <c r="G77" s="111">
         <f t="shared" ref="G77:G115" si="16">E77-F77</f>
-        <v>746089.99999999988</v>
+        <v>507691</v>
       </c>
       <c r="H77" s="111">
         <f t="shared" si="4"/>
-        <v>22382.699999999997</v>
+        <v>15230.73</v>
       </c>
       <c r="I77" s="127">
         <f t="shared" ref="I77:I108" si="17">J$2*D77/100</f>
@@ -7521,11 +7575,11 @@
       <c r="L77" s="150"/>
       <c r="M77" s="86">
         <f t="shared" si="5"/>
-        <v>907691.65</v>
+        <v>662140.65</v>
       </c>
       <c r="N77" s="141">
         <f t="shared" si="9"/>
-        <v>934922.65</v>
+        <v>682004.65</v>
       </c>
       <c r="O77" s="50">
         <f t="shared" si="8"/>
@@ -7535,7 +7589,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="78" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A78" s="130">
         <f t="shared" si="10"/>
         <v>66</v>
@@ -7548,16 +7602,16 @@
         <v>1.34</v>
       </c>
       <c r="E78" s="83">
-        <v>302420.65999999997</v>
+        <v>538997.66</v>
       </c>
       <c r="F78" s="84"/>
       <c r="G78" s="85">
         <f t="shared" si="16"/>
-        <v>302420.65999999997</v>
+        <v>538997.66</v>
       </c>
       <c r="H78" s="85">
         <f t="shared" ref="H78:H115" si="19">IF(G78&gt;0,G78*3%,0)</f>
-        <v>9072.6197999999986</v>
+        <v>16169.9298</v>
       </c>
       <c r="I78" s="126">
         <f t="shared" si="17"/>
@@ -7571,18 +7625,18 @@
       <c r="L78" s="149"/>
       <c r="M78" s="86">
         <f t="shared" si="5"/>
-        <v>538997.66</v>
+        <v>782671.66</v>
       </c>
       <c r="N78" s="140">
         <f t="shared" si="9"/>
-        <v>555167.66</v>
+        <v>806151.66</v>
       </c>
       <c r="O78" s="50">
         <f t="shared" si="8"/>
         <v>0.66000000000000036</v>
       </c>
     </row>
-    <row r="79" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A79" s="130">
         <f t="shared" si="10"/>
         <v>67</v>
@@ -7595,11 +7649,11 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="E79" s="83">
-        <v>210481.67</v>
+        <v>190152.67</v>
       </c>
       <c r="F79" s="84">
         <f>E79</f>
-        <v>210481.67</v>
+        <v>190152.67</v>
       </c>
       <c r="G79" s="85">
         <f t="shared" si="16"/>
@@ -7632,7 +7686,7 @@
         <v>0.67000000000000037</v>
       </c>
     </row>
-    <row r="80" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A80" s="131">
         <f t="shared" si="10"/>
         <v>68</v>
@@ -7645,18 +7699,18 @@
         <v>1.17</v>
       </c>
       <c r="E80" s="83">
-        <v>6436034.6799999997</v>
+        <v>6827757.6799999997</v>
       </c>
       <c r="F80" s="84">
         <v>0</v>
       </c>
       <c r="G80" s="85">
         <f t="shared" si="16"/>
-        <v>6436034.6799999997</v>
+        <v>6827757.6799999997</v>
       </c>
       <c r="H80" s="85">
         <f t="shared" si="19"/>
-        <v>193081.0404</v>
+        <v>204832.73039999997</v>
       </c>
       <c r="I80" s="126">
         <f t="shared" si="17"/>
@@ -7666,27 +7720,29 @@
         <f t="shared" si="18"/>
         <v>35100</v>
       </c>
-      <c r="K80" s="126"/>
+      <c r="K80" s="126">
+        <v>95000</v>
+      </c>
       <c r="L80" s="149"/>
       <c r="M80" s="86">
         <f t="shared" si="20"/>
-        <v>6827757.6799999997</v>
+        <v>7326232.6799999997</v>
       </c>
       <c r="N80" s="140">
         <f t="shared" si="9"/>
-        <v>7032590.6799999997</v>
+        <v>7546019.6799999997</v>
       </c>
       <c r="O80" s="50">
         <f t="shared" si="8"/>
         <v>0.68000000000000038</v>
       </c>
     </row>
-    <row r="81" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A81" s="201">
+    <row r="81" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A81" s="199">
         <f t="shared" si="10"/>
         <v>69</v>
       </c>
-      <c r="B81" s="202" t="s">
+      <c r="B81" s="200" t="s">
         <v>68</v>
       </c>
       <c r="C81" s="87"/>
@@ -7694,18 +7750,18 @@
         <v>1.35</v>
       </c>
       <c r="E81" s="83">
-        <v>220216.69</v>
+        <v>229118.69</v>
       </c>
       <c r="F81" s="84">
         <v>220300</v>
       </c>
       <c r="G81" s="85">
         <f t="shared" si="16"/>
-        <v>-83.309999999997672</v>
+        <v>8818.6900000000023</v>
       </c>
       <c r="H81" s="85">
         <f t="shared" si="19"/>
-        <v>0</v>
+        <v>264.56070000000005</v>
       </c>
       <c r="I81" s="126">
         <f t="shared" si="17"/>
@@ -7715,22 +7771,24 @@
         <f t="shared" si="18"/>
         <v>40500.000000000007</v>
       </c>
-      <c r="K81" s="126"/>
+      <c r="K81" s="126" t="s">
+        <v>211</v>
+      </c>
       <c r="L81" s="149"/>
       <c r="M81" s="86">
         <f t="shared" si="20"/>
-        <v>229118.69</v>
+        <v>238285.69</v>
       </c>
       <c r="N81" s="140">
         <f t="shared" si="9"/>
-        <v>235992.69</v>
+        <v>245434.69</v>
       </c>
       <c r="O81" s="50">
         <f t="shared" si="8"/>
         <v>0.69000000000000039</v>
       </c>
     </row>
-    <row r="82" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A82" s="131">
         <f t="shared" si="10"/>
         <v>70</v>
@@ -7743,18 +7801,18 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="E82" s="84">
-        <v>182697.7</v>
+        <v>192038.7</v>
       </c>
       <c r="F82" s="84">
         <v>180866.7</v>
       </c>
       <c r="G82" s="111">
         <f t="shared" si="16"/>
-        <v>1831</v>
+        <v>11172</v>
       </c>
       <c r="H82" s="111">
         <f t="shared" si="19"/>
-        <v>54.93</v>
+        <v>335.15999999999997</v>
       </c>
       <c r="I82" s="127">
         <f t="shared" si="17"/>
@@ -7768,11 +7826,11 @@
       <c r="L82" s="150"/>
       <c r="M82" s="86">
         <f t="shared" si="20"/>
-        <v>192038.7</v>
+        <v>201660.7</v>
       </c>
       <c r="N82" s="141">
         <f t="shared" si="9"/>
-        <v>197799.7</v>
+        <v>207710.7</v>
       </c>
       <c r="O82" s="50">
         <f t="shared" si="8"/>
@@ -7782,7 +7840,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="83" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A83" s="131">
         <f t="shared" si="10"/>
         <v>71</v>
@@ -7795,11 +7853,11 @@
         <v>0.82</v>
       </c>
       <c r="E83" s="83">
-        <v>130084.71</v>
+        <v>139219.71</v>
       </c>
       <c r="F83" s="84">
         <f>E83</f>
-        <v>130084.71</v>
+        <v>139219.71</v>
       </c>
       <c r="G83" s="85">
         <f t="shared" si="16"/>
@@ -7832,7 +7890,7 @@
         <v>0.71000000000000041</v>
       </c>
     </row>
-    <row r="84" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A84" s="131">
         <f t="shared" si="10"/>
         <v>72</v>
@@ -7845,11 +7903,11 @@
         <v>0.82</v>
       </c>
       <c r="E84" s="83">
-        <v>133761.72</v>
+        <v>139219.72</v>
       </c>
       <c r="F84" s="84">
         <f t="shared" ref="F84:F85" si="21">E84</f>
-        <v>133761.72</v>
+        <v>139219.72</v>
       </c>
       <c r="G84" s="85">
         <f t="shared" si="16"/>
@@ -7882,7 +7940,7 @@
         <v>0.72000000000000042</v>
       </c>
     </row>
-    <row r="85" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A85" s="130">
         <f t="shared" si="10"/>
         <v>73</v>
@@ -7895,11 +7953,11 @@
         <v>1.34</v>
       </c>
       <c r="E85" s="83">
-        <v>218584.73</v>
+        <v>227504.73</v>
       </c>
       <c r="F85" s="84">
         <f t="shared" si="21"/>
-        <v>218584.73</v>
+        <v>227504.73</v>
       </c>
       <c r="G85" s="85">
         <f t="shared" si="16"/>
@@ -7932,7 +7990,7 @@
         <v>0.73000000000000043</v>
       </c>
     </row>
-    <row r="86" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A86" s="130">
         <f t="shared" si="10"/>
         <v>74</v>
@@ -7945,7 +8003,7 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="E86" s="83">
-        <v>710321.74</v>
+        <v>900804.74</v>
       </c>
       <c r="F86" s="84">
         <f>20368.59</f>
@@ -7953,11 +8011,11 @@
       </c>
       <c r="G86" s="85">
         <f t="shared" si="16"/>
-        <v>689953.15</v>
+        <v>880436.15</v>
       </c>
       <c r="H86" s="85">
         <f t="shared" si="19"/>
-        <v>20698.594499999999</v>
+        <v>26413.084500000001</v>
       </c>
       <c r="I86" s="126">
         <f t="shared" si="17"/>
@@ -7971,18 +8029,18 @@
       <c r="L86" s="149"/>
       <c r="M86" s="86">
         <f t="shared" si="20"/>
-        <v>900804.74</v>
+        <v>1097002.74</v>
       </c>
       <c r="N86" s="140">
         <f t="shared" si="9"/>
-        <v>927828.74</v>
+        <v>1129912.74</v>
       </c>
       <c r="O86" s="50">
         <f t="shared" si="8"/>
         <v>0.74000000000000044</v>
       </c>
     </row>
-    <row r="87" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A87" s="130">
         <f t="shared" si="10"/>
         <v>75</v>
@@ -7995,18 +8053,18 @@
         <v>1.17</v>
       </c>
       <c r="E87" s="83">
-        <v>185351.75</v>
+        <v>193080.75</v>
       </c>
       <c r="F87" s="84">
         <v>190912.75</v>
       </c>
       <c r="G87" s="85">
         <f t="shared" si="16"/>
-        <v>-5561</v>
+        <v>2168</v>
       </c>
       <c r="H87" s="85">
         <f t="shared" si="19"/>
-        <v>0</v>
+        <v>65.039999999999992</v>
       </c>
       <c r="I87" s="126">
         <f t="shared" si="17"/>
@@ -8020,18 +8078,18 @@
       <c r="L87" s="149"/>
       <c r="M87" s="86">
         <f t="shared" si="20"/>
-        <v>193080.75</v>
+        <v>200874.75</v>
       </c>
       <c r="N87" s="140">
         <f t="shared" si="9"/>
-        <v>198872.75</v>
+        <v>206900.75</v>
       </c>
       <c r="O87" s="50">
         <f t="shared" si="8"/>
         <v>0.75000000000000044</v>
       </c>
     </row>
-    <row r="88" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A88" s="130">
         <f t="shared" si="10"/>
         <v>76</v>
@@ -8044,11 +8102,11 @@
         <v>1.35</v>
       </c>
       <c r="E88" s="83">
-        <v>220216.76</v>
+        <v>229201.76</v>
       </c>
       <c r="F88" s="84">
         <f>E88</f>
-        <v>220216.76</v>
+        <v>229201.76</v>
       </c>
       <c r="G88" s="85">
         <f t="shared" si="16"/>
@@ -8081,7 +8139,7 @@
         <v>0.76000000000000045</v>
       </c>
     </row>
-    <row r="89" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A89" s="130">
         <f t="shared" si="10"/>
         <v>77</v>
@@ -8094,11 +8152,11 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="E89" s="83">
-        <v>177572.77</v>
+        <v>190152.77</v>
       </c>
       <c r="F89" s="84">
         <f>E89</f>
-        <v>177572.77</v>
+        <v>190152.77</v>
       </c>
       <c r="G89" s="85">
         <f t="shared" si="16"/>
@@ -8131,12 +8189,12 @@
         <v>0.77000000000000046</v>
       </c>
     </row>
-    <row r="90" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A90" s="225">
+    <row r="90" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A90" s="223">
         <f t="shared" si="10"/>
         <v>78</v>
       </c>
-      <c r="B90" s="226" t="s">
+      <c r="B90" s="224" t="s">
         <v>77</v>
       </c>
       <c r="C90" s="120"/>
@@ -8144,7 +8202,7 @@
         <v>0.82</v>
       </c>
       <c r="E90" s="122">
-        <v>383761.78</v>
+        <v>389218.78</v>
       </c>
       <c r="F90" s="122">
         <f>293563+90199</f>
@@ -8152,7 +8210,7 @@
       </c>
       <c r="G90" s="123">
         <f t="shared" si="16"/>
-        <v>-0.21999999997206032</v>
+        <v>5456.7800000000279</v>
       </c>
       <c r="H90" s="123"/>
       <c r="I90" s="129">
@@ -8169,38 +8227,38 @@
       </c>
       <c r="M90" s="124">
         <f t="shared" si="20"/>
-        <v>304218.78000000003</v>
+        <v>309675.78000000003</v>
       </c>
       <c r="N90" s="142">
         <f t="shared" si="9"/>
-        <v>313345.78000000003</v>
+        <v>318965.78000000003</v>
       </c>
       <c r="O90" s="50">
         <f t="shared" si="8"/>
         <v>0.78000000000000047</v>
       </c>
       <c r="P90" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="91" spans="1:16" x14ac:dyDescent="0.3">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="91" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A91" s="130">
         <f t="shared" si="10"/>
         <v>79</v>
       </c>
       <c r="B91" s="88" t="s">
-        <v>227</v>
+        <v>221</v>
       </c>
       <c r="C91" s="87"/>
       <c r="D91" s="82">
         <v>0.82</v>
       </c>
       <c r="E91" s="83">
-        <v>133761.79</v>
+        <v>139219.79</v>
       </c>
       <c r="F91" s="84">
         <f>E91</f>
-        <v>133761.79</v>
+        <v>139219.79</v>
       </c>
       <c r="G91" s="85">
         <f t="shared" si="16"/>
@@ -8233,10 +8291,10 @@
         <v>0.79000000000000048</v>
       </c>
       <c r="P91" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="92" spans="1:16" x14ac:dyDescent="0.3">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="92" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A92" s="131">
         <f t="shared" si="10"/>
         <v>80</v>
@@ -8249,11 +8307,11 @@
         <v>1.34</v>
       </c>
       <c r="E92" s="84">
-        <v>398877.8</v>
+        <v>227504.8</v>
       </c>
       <c r="F92" s="84">
         <f>E92</f>
-        <v>398877.8</v>
+        <v>227504.8</v>
       </c>
       <c r="G92" s="85">
         <f>E92-F92</f>
@@ -8286,7 +8344,7 @@
         <v>0.80000000000000049</v>
       </c>
     </row>
-    <row r="93" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A93" s="131">
         <f t="shared" si="10"/>
         <v>81</v>
@@ -8299,11 +8357,11 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="E93" s="84">
-        <v>967453.81</v>
+        <v>190152.81</v>
       </c>
       <c r="F93" s="84">
         <f>E93</f>
-        <v>967453.81</v>
+        <v>190152.81</v>
       </c>
       <c r="G93" s="111">
         <f t="shared" si="16"/>
@@ -8336,15 +8394,15 @@
         <v>0.8100000000000005</v>
       </c>
       <c r="P93" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="94" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A94" s="215">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="94" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A94" s="213">
         <f t="shared" si="10"/>
         <v>82</v>
       </c>
-      <c r="B94" s="216" t="s">
+      <c r="B94" s="214" t="s">
         <v>80</v>
       </c>
       <c r="C94" s="87"/>
@@ -8352,14 +8410,14 @@
         <v>1.17</v>
       </c>
       <c r="E94" s="83">
-        <v>190854.82</v>
+        <v>192915.82</v>
       </c>
       <c r="F94" s="84">
         <v>196580.82</v>
       </c>
       <c r="G94" s="85">
         <f t="shared" si="16"/>
-        <v>-5726</v>
+        <v>-3665</v>
       </c>
       <c r="H94" s="85">
         <f t="shared" si="19"/>
@@ -8377,18 +8435,18 @@
       <c r="L94" s="149"/>
       <c r="M94" s="86">
         <f t="shared" si="20"/>
-        <v>192915.82</v>
+        <v>194976.82</v>
       </c>
       <c r="N94" s="140">
         <f t="shared" si="9"/>
-        <v>198702.82</v>
+        <v>200825.82</v>
       </c>
       <c r="O94" s="50">
         <f t="shared" si="8"/>
         <v>0.82000000000000051</v>
       </c>
     </row>
-    <row r="95" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A95" s="131">
         <f t="shared" si="10"/>
         <v>83</v>
@@ -8401,11 +8459,11 @@
         <v>1.35</v>
       </c>
       <c r="E95" s="84">
-        <v>220216.83</v>
+        <v>229201.83</v>
       </c>
       <c r="F95" s="84">
         <f>E95</f>
-        <v>220216.83</v>
+        <v>229201.83</v>
       </c>
       <c r="G95" s="85">
         <f t="shared" si="16"/>
@@ -8438,7 +8496,7 @@
         <v>0.83000000000000052</v>
       </c>
     </row>
-    <row r="96" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A96" s="131">
         <f t="shared" si="10"/>
         <v>84</v>
@@ -8451,12 +8509,12 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="E96" s="84">
-        <v>-453689.16</v>
+        <v>-263536.15999999997</v>
       </c>
       <c r="F96" s="84"/>
       <c r="G96" s="85">
         <f t="shared" si="16"/>
-        <v>-453689.16</v>
+        <v>-263536.15999999997</v>
       </c>
       <c r="H96" s="85">
         <f t="shared" si="19"/>
@@ -8474,18 +8532,18 @@
       <c r="L96" s="149"/>
       <c r="M96" s="86">
         <f t="shared" si="20"/>
-        <v>-263536.15999999997</v>
+        <v>-73383.16</v>
       </c>
       <c r="N96" s="140">
         <f t="shared" si="9"/>
-        <v>-271442.15999999997</v>
+        <v>-75584.160000000003</v>
       </c>
       <c r="O96" s="50">
         <f t="shared" ref="O96:O115" si="22">O95+0.01</f>
         <v>0.84000000000000052</v>
       </c>
     </row>
-    <row r="97" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A97" s="130">
         <f t="shared" si="10"/>
         <v>85</v>
@@ -8498,11 +8556,11 @@
         <v>0.82</v>
       </c>
       <c r="E97" s="83">
-        <v>133761.85</v>
+        <v>139219.85</v>
       </c>
       <c r="F97" s="84">
         <f t="shared" ref="F97:F102" si="23">E97</f>
-        <v>133761.85</v>
+        <v>139219.85</v>
       </c>
       <c r="G97" s="85">
         <f t="shared" si="16"/>
@@ -8535,7 +8593,7 @@
         <v>0.85000000000000053</v>
       </c>
     </row>
-    <row r="98" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A98" s="130">
         <f t="shared" si="10"/>
         <v>86</v>
@@ -8548,11 +8606,11 @@
         <v>0.82</v>
       </c>
       <c r="E98" s="83">
-        <v>133761.85999999999</v>
+        <v>139219.85999999999</v>
       </c>
       <c r="F98" s="84">
         <f t="shared" si="23"/>
-        <v>133761.85999999999</v>
+        <v>139219.85999999999</v>
       </c>
       <c r="G98" s="85">
         <f t="shared" si="16"/>
@@ -8585,7 +8643,7 @@
         <v>0.86000000000000054</v>
       </c>
     </row>
-    <row r="99" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A99" s="130">
         <f t="shared" ref="A99:A115" si="25">A98+1</f>
         <v>87</v>
@@ -8598,11 +8656,11 @@
         <v>1.34</v>
       </c>
       <c r="E99" s="83">
-        <v>218584.87</v>
+        <v>227504.87</v>
       </c>
       <c r="F99" s="84">
         <f t="shared" si="23"/>
-        <v>218584.87</v>
+        <v>227504.87</v>
       </c>
       <c r="G99" s="85">
         <f t="shared" si="16"/>
@@ -8635,7 +8693,7 @@
         <v>0.87000000000000055</v>
       </c>
     </row>
-    <row r="100" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A100" s="130">
         <f t="shared" si="25"/>
         <v>88</v>
@@ -8648,11 +8706,11 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="E100" s="83">
-        <v>182697.88</v>
+        <v>190152.88</v>
       </c>
       <c r="F100" s="84">
         <f t="shared" si="23"/>
-        <v>182697.88</v>
+        <v>190152.88</v>
       </c>
       <c r="G100" s="85">
         <f t="shared" si="16"/>
@@ -8685,7 +8743,7 @@
         <v>0.88000000000000056</v>
       </c>
     </row>
-    <row r="101" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A101" s="130">
         <f t="shared" si="25"/>
         <v>89</v>
@@ -8698,11 +8756,11 @@
         <v>1.17</v>
       </c>
       <c r="E101" s="83">
-        <v>190854.89</v>
+        <v>198641.89</v>
       </c>
       <c r="F101" s="84">
         <f t="shared" si="23"/>
-        <v>190854.89</v>
+        <v>198641.89</v>
       </c>
       <c r="G101" s="85">
         <f t="shared" si="16"/>
@@ -8735,7 +8793,7 @@
         <v>0.89000000000000057</v>
       </c>
     </row>
-    <row r="102" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A102" s="130">
         <f t="shared" si="25"/>
         <v>90</v>
@@ -8748,11 +8806,11 @@
         <v>0.1</v>
       </c>
       <c r="E102" s="83">
-        <v>16312.9</v>
+        <v>16978.900000000001</v>
       </c>
       <c r="F102" s="84">
         <f t="shared" si="23"/>
-        <v>16312.9</v>
+        <v>16978.900000000001</v>
       </c>
       <c r="G102" s="85">
         <f t="shared" si="16"/>
@@ -8785,7 +8843,7 @@
         <v>0.90000000000000058</v>
       </c>
     </row>
-    <row r="103" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A103" s="130">
         <f t="shared" si="25"/>
         <v>91</v>
@@ -8798,14 +8856,14 @@
         <v>0.1</v>
       </c>
       <c r="E103" s="83">
-        <v>16312.91</v>
+        <v>16489.91</v>
       </c>
       <c r="F103" s="84">
         <v>16801.91</v>
       </c>
       <c r="G103" s="85">
         <f t="shared" si="16"/>
-        <v>-489</v>
+        <v>-312</v>
       </c>
       <c r="H103" s="85">
         <f t="shared" si="19"/>
@@ -8823,18 +8881,18 @@
       <c r="L103" s="149"/>
       <c r="M103" s="86">
         <f t="shared" si="20"/>
-        <v>16489.91</v>
+        <v>16666.91</v>
       </c>
       <c r="N103" s="140">
         <f t="shared" si="24"/>
-        <v>16984.91</v>
+        <v>17166.91</v>
       </c>
       <c r="O103" s="50">
         <f t="shared" si="22"/>
         <v>0.91000000000000059</v>
       </c>
     </row>
-    <row r="104" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A104" s="130">
         <f t="shared" si="25"/>
         <v>92</v>
@@ -8847,14 +8905,14 @@
         <v>0.1</v>
       </c>
       <c r="E104" s="83">
-        <v>16312.92</v>
+        <v>16489.919999999998</v>
       </c>
       <c r="F104" s="84">
         <v>16801.919999999998</v>
       </c>
       <c r="G104" s="85">
         <f t="shared" si="16"/>
-        <v>-488.99999999999818</v>
+        <v>-312</v>
       </c>
       <c r="H104" s="85">
         <f t="shared" si="19"/>
@@ -8872,18 +8930,18 @@
       <c r="L104" s="149"/>
       <c r="M104" s="86">
         <f t="shared" si="20"/>
-        <v>16489.919999999998</v>
+        <v>16666.919999999998</v>
       </c>
       <c r="N104" s="140">
         <f t="shared" si="24"/>
-        <v>16984.919999999998</v>
+        <v>17166.919999999998</v>
       </c>
       <c r="O104" s="50">
         <f t="shared" si="22"/>
         <v>0.9200000000000006</v>
       </c>
     </row>
-    <row r="105" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A105" s="131">
         <f t="shared" si="25"/>
         <v>93</v>
@@ -8896,11 +8954,11 @@
         <v>0.1</v>
       </c>
       <c r="E105" s="84">
-        <v>15855.93</v>
+        <v>16978.93</v>
       </c>
       <c r="F105" s="84">
         <f t="shared" ref="F105" si="26">E105</f>
-        <v>15855.93</v>
+        <v>16978.93</v>
       </c>
       <c r="G105" s="111">
         <f t="shared" si="16"/>
@@ -8933,7 +8991,7 @@
         <v>0.9300000000000006</v>
       </c>
     </row>
-    <row r="106" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A106" s="131">
         <f t="shared" si="25"/>
         <v>94</v>
@@ -8946,11 +9004,11 @@
         <v>0.1</v>
       </c>
       <c r="E106" s="84">
-        <v>16312.94</v>
+        <v>16978.939999999999</v>
       </c>
       <c r="F106" s="84">
         <f>E106</f>
-        <v>16312.94</v>
+        <v>16978.939999999999</v>
       </c>
       <c r="G106" s="111">
         <f t="shared" si="16"/>
@@ -8983,7 +9041,7 @@
         <v>0.94000000000000061</v>
       </c>
     </row>
-    <row r="107" spans="1:16" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:16" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107" s="131">
         <f t="shared" si="25"/>
         <v>95</v>
@@ -8996,11 +9054,11 @@
         <v>0.1</v>
       </c>
       <c r="E107" s="84">
-        <v>16312.95</v>
+        <v>16978.95</v>
       </c>
       <c r="F107" s="84">
         <f>E107</f>
-        <v>16312.95</v>
+        <v>16978.95</v>
       </c>
       <c r="G107" s="111">
         <f t="shared" si="16"/>
@@ -9033,7 +9091,7 @@
         <v>0.95000000000000062</v>
       </c>
     </row>
-    <row r="108" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A108" s="131">
         <f t="shared" si="25"/>
         <v>96</v>
@@ -9046,11 +9104,11 @@
         <v>0.1</v>
       </c>
       <c r="E108" s="84">
-        <v>15842.96</v>
+        <v>16978.96</v>
       </c>
       <c r="F108" s="84">
         <f>E108</f>
-        <v>15842.96</v>
+        <v>16978.96</v>
       </c>
       <c r="G108" s="111">
         <f t="shared" si="16"/>
@@ -9086,7 +9144,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="109" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A109" s="131">
         <f t="shared" si="25"/>
         <v>97</v>
@@ -9099,11 +9157,11 @@
         <v>0.1</v>
       </c>
       <c r="E109" s="84">
-        <v>16312.97</v>
+        <v>16978.97</v>
       </c>
       <c r="F109" s="84">
         <f>E109</f>
-        <v>16312.97</v>
+        <v>16978.97</v>
       </c>
       <c r="G109" s="111">
         <f t="shared" si="16"/>
@@ -9136,7 +9194,7 @@
         <v>0.97000000000000064</v>
       </c>
     </row>
-    <row r="110" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A110" s="131">
         <f t="shared" si="25"/>
         <v>98</v>
@@ -9149,11 +9207,11 @@
         <v>0.1</v>
       </c>
       <c r="E110" s="84">
-        <v>16312.98</v>
+        <v>16978.98</v>
       </c>
       <c r="F110" s="84">
         <f>E110</f>
-        <v>16312.98</v>
+        <v>16978.98</v>
       </c>
       <c r="G110" s="111">
         <f t="shared" si="16"/>
@@ -9186,7 +9244,7 @@
         <v>0.98000000000000065</v>
       </c>
     </row>
-    <row r="111" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A111" s="131">
         <f t="shared" si="25"/>
         <v>99</v>
@@ -9199,11 +9257,11 @@
         <v>0.1</v>
       </c>
       <c r="E111" s="84">
-        <v>16312.99</v>
+        <v>16978.990000000002</v>
       </c>
       <c r="F111" s="84">
         <f t="shared" ref="F111" si="29">E111</f>
-        <v>16312.99</v>
+        <v>16978.990000000002</v>
       </c>
       <c r="G111" s="111">
         <f t="shared" si="16"/>
@@ -9236,7 +9294,7 @@
         <v>0.99000000000000066</v>
       </c>
     </row>
-    <row r="112" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A112" s="131">
         <f t="shared" si="25"/>
         <v>100</v>
@@ -9249,16 +9307,16 @@
         <v>0.1</v>
       </c>
       <c r="E112" s="84">
-        <v>16313</v>
+        <v>33781</v>
       </c>
       <c r="F112" s="84"/>
       <c r="G112" s="111">
         <f t="shared" si="16"/>
-        <v>16313</v>
+        <v>33781</v>
       </c>
       <c r="H112" s="111">
         <f t="shared" si="19"/>
-        <v>489.39</v>
+        <v>1013.43</v>
       </c>
       <c r="I112" s="127">
         <f t="shared" si="27"/>
@@ -9272,18 +9330,18 @@
       <c r="L112" s="150"/>
       <c r="M112" s="86">
         <f t="shared" si="20"/>
-        <v>33781</v>
+        <v>51773</v>
       </c>
       <c r="N112" s="141">
         <f t="shared" si="24"/>
-        <v>34794</v>
+        <v>53326</v>
       </c>
       <c r="O112" s="50">
         <f t="shared" si="22"/>
         <v>1.0000000000000007</v>
       </c>
     </row>
-    <row r="113" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A113" s="131">
         <f t="shared" si="25"/>
         <v>101</v>
@@ -9296,11 +9354,11 @@
         <v>0.1</v>
       </c>
       <c r="E113" s="84">
-        <v>15856.01</v>
+        <v>16979.009999999998</v>
       </c>
       <c r="F113" s="84">
         <f t="shared" ref="F113" si="30">E113</f>
-        <v>15856.01</v>
+        <v>16979.009999999998</v>
       </c>
       <c r="G113" s="111">
         <f t="shared" si="16"/>
@@ -9333,7 +9391,7 @@
         <v>1.0100000000000007</v>
       </c>
     </row>
-    <row r="114" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A114" s="131">
         <f t="shared" si="25"/>
         <v>102</v>
@@ -9346,11 +9404,11 @@
         <v>0.1</v>
       </c>
       <c r="E114" s="84">
-        <v>16313.02</v>
+        <v>16979.02</v>
       </c>
       <c r="F114" s="84">
         <f>E114</f>
-        <v>16313.02</v>
+        <v>16979.02</v>
       </c>
       <c r="G114" s="111">
         <f t="shared" si="16"/>
@@ -9383,7 +9441,7 @@
         <v>1.0200000000000007</v>
       </c>
     </row>
-    <row r="115" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A115" s="131">
         <f t="shared" si="25"/>
         <v>103</v>
@@ -9396,11 +9454,11 @@
         <v>0.1</v>
       </c>
       <c r="E115" s="84">
-        <v>16313.03</v>
+        <v>16979.03</v>
       </c>
       <c r="F115" s="84">
         <f>E115</f>
-        <v>16313.03</v>
+        <v>16979.03</v>
       </c>
       <c r="G115" s="111">
         <f t="shared" si="16"/>
@@ -9433,7 +9491,7 @@
         <v>1.0300000000000007</v>
       </c>
     </row>
-    <row r="116" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A116" s="131"/>
       <c r="B116" s="108"/>
       <c r="C116" s="113"/>
@@ -9450,7 +9508,7 @@
       <c r="N116" s="141"/>
       <c r="O116" s="50"/>
     </row>
-    <row r="117" spans="1:15" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:15" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A117" s="133"/>
       <c r="B117" s="134"/>
       <c r="C117" s="134"/>
@@ -9460,19 +9518,19 @@
       </c>
       <c r="E117" s="136">
         <f t="shared" si="31"/>
-        <v>35923244.56000001</v>
+        <v>36521807.560000002</v>
       </c>
       <c r="F117" s="137">
         <f>SUM(F13:F116)</f>
-        <v>17773395.250000004</v>
+        <v>16770189.25</v>
       </c>
       <c r="G117" s="137">
         <f t="shared" si="31"/>
-        <v>18149849.310000002</v>
+        <v>19751618.310000002</v>
       </c>
       <c r="H117" s="137">
         <f t="shared" si="31"/>
-        <v>542858.47529999993</v>
+        <v>607731.64560000005</v>
       </c>
       <c r="I117" s="138">
         <f t="shared" si="31"/>
@@ -9486,106 +9544,109 @@
       <c r="L117" s="152"/>
       <c r="M117" s="146">
         <f t="shared" si="31"/>
-        <v>36436807.560000002</v>
+        <v>38198449.560000002</v>
       </c>
       <c r="N117" s="143">
         <f t="shared" si="31"/>
-        <v>37529915.560000002</v>
-      </c>
-    </row>
-    <row r="118" spans="1:15" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>39344409.560000002</v>
+      </c>
+    </row>
+    <row r="118" spans="1:15" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B118" s="89"/>
       <c r="C118" s="89"/>
     </row>
-    <row r="119" spans="1:15" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="120" spans="1:15" ht="9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B120" s="258" t="s">
+    <row r="119" spans="1:15" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="120" spans="1:15" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B120" s="251" t="s">
         <v>103</v>
       </c>
-      <c r="C120" s="258"/>
-      <c r="D120" s="258"/>
-      <c r="E120" s="258"/>
-      <c r="F120" s="258"/>
-      <c r="G120" s="258"/>
-      <c r="H120" s="258"/>
-      <c r="I120" s="258"/>
-      <c r="J120" s="258"/>
-      <c r="K120" s="258"/>
-      <c r="L120" s="258"/>
-      <c r="M120" s="258"/>
-    </row>
-    <row r="121" spans="1:15" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B121" s="258"/>
-      <c r="C121" s="258"/>
-      <c r="D121" s="258"/>
-      <c r="E121" s="258"/>
-      <c r="F121" s="258"/>
-      <c r="G121" s="258"/>
-      <c r="H121" s="258"/>
-      <c r="I121" s="258"/>
-      <c r="J121" s="258"/>
-      <c r="K121" s="258"/>
-      <c r="L121" s="258"/>
-      <c r="M121" s="258"/>
-    </row>
-    <row r="122" spans="1:15" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B122" s="258"/>
-      <c r="C122" s="258"/>
-      <c r="D122" s="258"/>
-      <c r="E122" s="258"/>
-      <c r="F122" s="258"/>
-      <c r="G122" s="258"/>
-      <c r="H122" s="258"/>
-      <c r="I122" s="258"/>
-      <c r="J122" s="258"/>
-      <c r="K122" s="258"/>
-      <c r="L122" s="258"/>
-      <c r="M122" s="258"/>
-    </row>
-    <row r="123" spans="1:15" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B123" s="258"/>
-      <c r="C123" s="258"/>
-      <c r="D123" s="258"/>
-      <c r="E123" s="258"/>
-      <c r="F123" s="258"/>
-      <c r="G123" s="258"/>
-      <c r="H123" s="258"/>
-      <c r="I123" s="258"/>
-      <c r="J123" s="258"/>
-      <c r="K123" s="258"/>
-      <c r="L123" s="258"/>
-      <c r="M123" s="258"/>
-    </row>
-    <row r="124" spans="1:15" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B124" s="258"/>
-      <c r="C124" s="258"/>
-      <c r="D124" s="258"/>
-      <c r="E124" s="258"/>
-      <c r="F124" s="258"/>
-      <c r="G124" s="258"/>
-      <c r="H124" s="258"/>
-      <c r="I124" s="258"/>
-      <c r="J124" s="258"/>
-      <c r="K124" s="258"/>
-      <c r="L124" s="258"/>
-      <c r="M124" s="258"/>
-    </row>
-    <row r="125" spans="1:15" ht="67.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B125" s="258"/>
-      <c r="C125" s="258"/>
-      <c r="D125" s="258"/>
-      <c r="E125" s="258"/>
-      <c r="F125" s="258"/>
-      <c r="G125" s="258"/>
-      <c r="H125" s="258"/>
-      <c r="I125" s="258"/>
-      <c r="J125" s="258"/>
-      <c r="K125" s="258"/>
-      <c r="L125" s="258"/>
-      <c r="M125" s="258"/>
+      <c r="C120" s="251"/>
+      <c r="D120" s="251"/>
+      <c r="E120" s="251"/>
+      <c r="F120" s="251"/>
+      <c r="G120" s="251"/>
+      <c r="H120" s="251"/>
+      <c r="I120" s="251"/>
+      <c r="J120" s="251"/>
+      <c r="K120" s="251"/>
+      <c r="L120" s="251"/>
+      <c r="M120" s="251"/>
+    </row>
+    <row r="121" spans="1:15" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B121" s="251"/>
+      <c r="C121" s="251"/>
+      <c r="D121" s="251"/>
+      <c r="E121" s="251"/>
+      <c r="F121" s="251"/>
+      <c r="G121" s="251"/>
+      <c r="H121" s="251"/>
+      <c r="I121" s="251"/>
+      <c r="J121" s="251"/>
+      <c r="K121" s="251"/>
+      <c r="L121" s="251"/>
+      <c r="M121" s="251"/>
+    </row>
+    <row r="122" spans="1:15" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B122" s="251"/>
+      <c r="C122" s="251"/>
+      <c r="D122" s="251"/>
+      <c r="E122" s="251"/>
+      <c r="F122" s="251"/>
+      <c r="G122" s="251"/>
+      <c r="H122" s="251"/>
+      <c r="I122" s="251"/>
+      <c r="J122" s="251"/>
+      <c r="K122" s="251"/>
+      <c r="L122" s="251"/>
+      <c r="M122" s="251"/>
+    </row>
+    <row r="123" spans="1:15" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B123" s="251"/>
+      <c r="C123" s="251"/>
+      <c r="D123" s="251"/>
+      <c r="E123" s="251"/>
+      <c r="F123" s="251"/>
+      <c r="G123" s="251"/>
+      <c r="H123" s="251"/>
+      <c r="I123" s="251"/>
+      <c r="J123" s="251"/>
+      <c r="K123" s="251"/>
+      <c r="L123" s="251"/>
+      <c r="M123" s="251"/>
+    </row>
+    <row r="124" spans="1:15" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B124" s="251"/>
+      <c r="C124" s="251"/>
+      <c r="D124" s="251"/>
+      <c r="E124" s="251"/>
+      <c r="F124" s="251"/>
+      <c r="G124" s="251"/>
+      <c r="H124" s="251"/>
+      <c r="I124" s="251"/>
+      <c r="J124" s="251"/>
+      <c r="K124" s="251"/>
+      <c r="L124" s="251"/>
+      <c r="M124" s="251"/>
+    </row>
+    <row r="125" spans="1:15" ht="67.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B125" s="251"/>
+      <c r="C125" s="251"/>
+      <c r="D125" s="251"/>
+      <c r="E125" s="251"/>
+      <c r="F125" s="251"/>
+      <c r="G125" s="251"/>
+      <c r="H125" s="251"/>
+      <c r="I125" s="251"/>
+      <c r="J125" s="251"/>
+      <c r="K125" s="251"/>
+      <c r="L125" s="251"/>
+      <c r="M125" s="251"/>
     </row>
   </sheetData>
   <mergeCells count="19">
+    <mergeCell ref="K11:K12"/>
+    <mergeCell ref="L11:L12"/>
+    <mergeCell ref="J11:J12"/>
     <mergeCell ref="N11:N12"/>
     <mergeCell ref="B120:M125"/>
     <mergeCell ref="D1:M1"/>
@@ -9602,9 +9663,6 @@
     <mergeCell ref="A10:N10"/>
     <mergeCell ref="E2:F2"/>
     <mergeCell ref="I11:I12"/>
-    <mergeCell ref="K11:K12"/>
-    <mergeCell ref="L11:L12"/>
-    <mergeCell ref="J11:J12"/>
   </mergeCells>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="3" scale="80" orientation="portrait" r:id="rId1"/>
@@ -9614,16 +9672,16 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{56D35F41-74CB-4294-A7A2-EC3C67574818}">
   <dimension ref="C3:L41"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="3" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.7109375" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="13" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="3:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C3" s="19"/>
     </row>
-    <row r="4" spans="3:12" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="3:12" ht="13.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C4" s="174" t="s">
         <v>196</v>
       </c>
@@ -9639,7 +9697,7 @@
       <c r="K4" s="19"/>
       <c r="L4" s="19"/>
     </row>
-    <row r="5" spans="3:12" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="3:12" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C5" s="176" t="s">
         <v>197</v>
       </c>
@@ -9654,7 +9712,7 @@
       <c r="K5" s="19"/>
       <c r="L5" s="19"/>
     </row>
-    <row r="6" spans="3:12" x14ac:dyDescent="0.3">
+    <row r="6" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C6" s="176" t="s">
         <v>200</v>
       </c>
@@ -9674,7 +9732,7 @@
       <c r="K6" s="19"/>
       <c r="L6" s="19"/>
     </row>
-    <row r="7" spans="3:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C7" s="47" t="s">
         <v>203</v>
       </c>
@@ -9682,9 +9740,9 @@
       <c r="K7" s="19"/>
       <c r="L7" s="19"/>
     </row>
-    <row r="8" spans="3:12" x14ac:dyDescent="0.3">
+    <row r="8" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C8" s="281" t="s">
-        <v>235</v>
+        <v>226</v>
       </c>
       <c r="D8" s="282"/>
       <c r="E8" s="282"/>
@@ -9696,7 +9754,7 @@
       <c r="K8" s="19"/>
       <c r="L8" s="19"/>
     </row>
-    <row r="9" spans="3:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C9" s="284"/>
       <c r="D9" s="285"/>
       <c r="E9" s="285"/>
@@ -9706,12 +9764,12 @@
       <c r="I9" s="285"/>
       <c r="J9" s="286"/>
     </row>
-    <row r="11" spans="3:12" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="12" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C12" s="203" t="s">
+    <row r="11" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="12" spans="3:12" x14ac:dyDescent="0.25">
+      <c r="C12" s="201" t="s">
         <v>196</v>
       </c>
-      <c r="D12" s="204">
+      <c r="D12" s="202">
         <v>1</v>
       </c>
       <c r="E12" s="171"/>
@@ -9721,11 +9779,11 @@
       <c r="I12" s="171"/>
       <c r="J12" s="172"/>
     </row>
-    <row r="13" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C13" s="205" t="s">
+    <row r="13" spans="3:12" x14ac:dyDescent="0.25">
+      <c r="C13" s="203" t="s">
         <v>197</v>
       </c>
-      <c r="D13" s="206"/>
+      <c r="D13" s="204"/>
       <c r="E13" t="s">
         <v>198</v>
       </c>
@@ -9734,11 +9792,11 @@
       </c>
       <c r="J13" s="173"/>
     </row>
-    <row r="14" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C14" s="205" t="s">
+    <row r="14" spans="3:12" x14ac:dyDescent="0.25">
+      <c r="C14" s="203" t="s">
         <v>200</v>
       </c>
-      <c r="D14" s="206" t="s">
+      <c r="D14" s="204" t="s">
         <v>201</v>
       </c>
       <c r="E14" t="s">
@@ -9748,19 +9806,19 @@
         <v>128</v>
       </c>
       <c r="H14" t="s">
-        <v>236</v>
+        <v>227</v>
       </c>
       <c r="J14" s="173"/>
     </row>
-    <row r="15" spans="3:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C15" s="47" t="s">
         <v>203</v>
       </c>
       <c r="J15" s="173"/>
     </row>
-    <row r="16" spans="3:12" x14ac:dyDescent="0.3">
+    <row r="16" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C16" s="281" t="s">
-        <v>237</v>
+        <v>228</v>
       </c>
       <c r="D16" s="282"/>
       <c r="E16" s="282"/>
@@ -9770,7 +9828,7 @@
       <c r="I16" s="282"/>
       <c r="J16" s="283"/>
     </row>
-    <row r="17" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="3:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C17" s="284"/>
       <c r="D17" s="285"/>
       <c r="E17" s="285"/>
@@ -9780,12 +9838,12 @@
       <c r="I17" s="285"/>
       <c r="J17" s="286"/>
     </row>
-    <row r="19" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="20" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C20" s="209" t="s">
+    <row r="19" spans="3:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="20" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="C20" s="207" t="s">
         <v>196</v>
       </c>
-      <c r="D20" s="210">
+      <c r="D20" s="208">
         <v>1</v>
       </c>
       <c r="E20" s="171"/>
@@ -9795,11 +9853,11 @@
       <c r="I20" s="171"/>
       <c r="J20" s="172"/>
     </row>
-    <row r="21" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C21" s="211" t="s">
+    <row r="21" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="C21" s="209" t="s">
         <v>197</v>
       </c>
-      <c r="D21" s="212"/>
+      <c r="D21" s="210"/>
       <c r="E21" t="s">
         <v>198</v>
       </c>
@@ -9808,11 +9866,11 @@
       </c>
       <c r="J21" s="173"/>
     </row>
-    <row r="22" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C22" s="211" t="s">
+    <row r="22" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="C22" s="209" t="s">
         <v>200</v>
       </c>
-      <c r="D22" s="212" t="s">
+      <c r="D22" s="210" t="s">
         <v>201</v>
       </c>
       <c r="E22" t="s">
@@ -9822,19 +9880,19 @@
         <v>128</v>
       </c>
       <c r="H22" t="s">
-        <v>238</v>
+        <v>229</v>
       </c>
       <c r="J22" s="173"/>
     </row>
-    <row r="23" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="3:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C23" s="47" t="s">
         <v>203</v>
       </c>
       <c r="J23" s="173"/>
     </row>
-    <row r="24" spans="3:10" x14ac:dyDescent="0.3">
+    <row r="24" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C24" s="281" t="s">
-        <v>239</v>
+        <v>230</v>
       </c>
       <c r="D24" s="282"/>
       <c r="E24" s="282"/>
@@ -9844,7 +9902,7 @@
       <c r="I24" s="282"/>
       <c r="J24" s="283"/>
     </row>
-    <row r="25" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="3:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C25" s="284"/>
       <c r="D25" s="285"/>
       <c r="E25" s="285"/>
@@ -9854,12 +9912,12 @@
       <c r="I25" s="285"/>
       <c r="J25" s="286"/>
     </row>
-    <row r="27" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="28" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C28" s="217" t="s">
+    <row r="27" spans="3:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="28" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="C28" s="215" t="s">
         <v>196</v>
       </c>
-      <c r="D28" s="218">
+      <c r="D28" s="216">
         <v>1</v>
       </c>
       <c r="E28" s="171"/>
@@ -9869,11 +9927,11 @@
       <c r="I28" s="171"/>
       <c r="J28" s="172"/>
     </row>
-    <row r="29" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C29" s="219" t="s">
+    <row r="29" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="C29" s="217" t="s">
         <v>197</v>
       </c>
-      <c r="D29" s="220"/>
+      <c r="D29" s="218"/>
       <c r="E29" t="s">
         <v>198</v>
       </c>
@@ -9882,11 +9940,11 @@
       </c>
       <c r="J29" s="173"/>
     </row>
-    <row r="30" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C30" s="219" t="s">
+    <row r="30" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="C30" s="217" t="s">
         <v>200</v>
       </c>
-      <c r="D30" s="220" t="s">
+      <c r="D30" s="218" t="s">
         <v>201</v>
       </c>
       <c r="E30" t="s">
@@ -9896,19 +9954,19 @@
         <v>128</v>
       </c>
       <c r="H30" t="s">
-        <v>240</v>
+        <v>231</v>
       </c>
       <c r="J30" s="173"/>
     </row>
-    <row r="31" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="3:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C31" s="47" t="s">
         <v>203</v>
       </c>
       <c r="J31" s="173"/>
     </row>
-    <row r="32" spans="3:10" x14ac:dyDescent="0.3">
+    <row r="32" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C32" s="281" t="s">
-        <v>241</v>
+        <v>232</v>
       </c>
       <c r="D32" s="282"/>
       <c r="E32" s="282"/>
@@ -9918,7 +9976,7 @@
       <c r="I32" s="282"/>
       <c r="J32" s="283"/>
     </row>
-    <row r="33" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="3:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C33" s="284"/>
       <c r="D33" s="285"/>
       <c r="E33" s="285"/>
@@ -9928,12 +9986,12 @@
       <c r="I33" s="285"/>
       <c r="J33" s="286"/>
     </row>
-    <row r="35" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="36" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C36" s="221" t="s">
+    <row r="35" spans="3:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="36" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="C36" s="219" t="s">
         <v>196</v>
       </c>
-      <c r="D36" s="222">
+      <c r="D36" s="220">
         <v>1</v>
       </c>
       <c r="E36" s="171"/>
@@ -9943,11 +10001,11 @@
       <c r="I36" s="171"/>
       <c r="J36" s="172"/>
     </row>
-    <row r="37" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C37" s="223" t="s">
+    <row r="37" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="C37" s="221" t="s">
         <v>197</v>
       </c>
-      <c r="D37" s="224"/>
+      <c r="D37" s="222"/>
       <c r="E37" t="s">
         <v>198</v>
       </c>
@@ -9955,15 +10013,15 @@
         <v>199</v>
       </c>
       <c r="H37" t="s">
-        <v>242</v>
+        <v>233</v>
       </c>
       <c r="J37" s="173"/>
     </row>
-    <row r="38" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C38" s="223" t="s">
+    <row r="38" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="C38" s="221" t="s">
         <v>200</v>
       </c>
-      <c r="D38" s="224" t="s">
+      <c r="D38" s="222" t="s">
         <v>201</v>
       </c>
       <c r="E38" t="s">
@@ -9973,19 +10031,19 @@
         <v>128</v>
       </c>
       <c r="H38" t="s">
-        <v>244</v>
+        <v>235</v>
       </c>
       <c r="J38" s="173"/>
     </row>
-    <row r="39" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="39" spans="3:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C39" s="47" t="s">
         <v>203</v>
       </c>
       <c r="J39" s="173"/>
     </row>
-    <row r="40" spans="3:10" x14ac:dyDescent="0.3">
+    <row r="40" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C40" s="281" t="s">
-        <v>243</v>
+        <v>234</v>
       </c>
       <c r="D40" s="282"/>
       <c r="E40" s="282"/>
@@ -9995,7 +10053,7 @@
       <c r="I40" s="282"/>
       <c r="J40" s="283"/>
     </row>
-    <row r="41" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="41" spans="3:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C41" s="284"/>
       <c r="D41" s="285"/>
       <c r="E41" s="285"/>

--- a/2026/ITALIA/Junio/Junio ITALIA.xlsx
+++ b/2026/ITALIA/Junio/Junio ITALIA.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistemax\Desktop\rc-consorcio2025\2026\ITALIA\Junio\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\2026\ITALIA\Junio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DFBFEE1-FEB3-44D8-BCF5-1D4BE51FE94E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80F98B45-C46E-4D13-83CC-F62569811E89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="4" r:id="rId1"/>
@@ -22,16 +22,11 @@
     <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$E$140</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
-  <extLst>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="336" uniqueCount="276">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="290" uniqueCount="266">
   <si>
     <t>TOTAL</t>
   </si>
@@ -646,9 +641,6 @@
     <t>MOTIVO DE LA QUEJA:</t>
   </si>
   <si>
-    <t>10A</t>
-  </si>
-  <si>
     <t>Gustavo Peker</t>
   </si>
   <si>
@@ -682,36 +674,6 @@
     <t>6 E DORIN GABRIEL DAVID</t>
   </si>
   <si>
-    <t>Deposito $230.000 el 05/06</t>
-  </si>
-  <si>
-    <t>9D</t>
-  </si>
-  <si>
-    <t>Deposito $520.000 el 06/06</t>
-  </si>
-  <si>
-    <t>6F</t>
-  </si>
-  <si>
-    <t>Deposito $220.000 a fin de mes</t>
-  </si>
-  <si>
-    <t>82 -11G</t>
-  </si>
-  <si>
-    <t>Transfirio con centavos erroneos, tenia que transferir $,82 y transfirio $ 215.688,11 el 27/06</t>
-  </si>
-  <si>
-    <t>Jeremy Naguel</t>
-  </si>
-  <si>
-    <t>Su cuota a abonar todos los meses no es de $250.000 es de $165,000 (ya corregido). En este mes debia abonar $308.396,78 y lo abono</t>
-  </si>
-  <si>
-    <t>UF 78</t>
-  </si>
-  <si>
     <t xml:space="preserve">Fernando daniel Minxxo  / Osvaldo </t>
   </si>
   <si>
@@ -869,6 +831,9 @@
   </si>
   <si>
     <t>EN PROCESO DE EJECUCION</t>
+  </si>
+  <si>
+    <t>Deposito 220.000 el 21/07 uf 46 Italia</t>
   </si>
 </sst>
 </file>
@@ -1048,7 +1013,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="18">
+  <fills count="16">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1135,18 +1100,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFF0000"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -1655,7 +1608,7 @@
     <xf numFmtId="44" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="305">
+  <cellXfs count="288">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1948,203 +1901,13 @@
     <xf numFmtId="0" fontId="12" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="18" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="18" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="16" fillId="17" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="17" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="15" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="15" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="17" borderId="18" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="17" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="17" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="17" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="18" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="16" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="16" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="44" fontId="10" fillId="2" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="10" fillId="2" borderId="19" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="19" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="12" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="12" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="44" fontId="7" fillId="14" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="7" fillId="14" borderId="20" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -2152,7 +1915,6 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="44" fontId="7" fillId="14" borderId="20" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="44" fontId="14" fillId="7" borderId="19" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="8" fontId="7" fillId="14" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -2185,6 +1947,94 @@
     <xf numFmtId="167" fontId="16" fillId="4" borderId="23" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="17" fillId="4" borderId="24" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="17" fillId="4" borderId="31" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="15" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="15" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="15" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="17" fillId="15" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="16" fillId="15" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="16" fillId="15" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="16" fillId="15" borderId="23" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="17" fillId="15" borderId="24" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="17" fillId="15" borderId="31" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="44" fontId="10" fillId="2" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="10" fillId="2" borderId="19" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="19" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2194,30 +2044,114 @@
     <xf numFmtId="0" fontId="1" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="15" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="15" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="15" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="17" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="17" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="17" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="44" fontId="17" fillId="17" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="16" fillId="17" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="16" fillId="17" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="16" fillId="17" borderId="23" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="17" fillId="17" borderId="24" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="17" fillId="17" borderId="31" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="17" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="17" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="17" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="14" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="14" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -2303,9 +2237,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -2343,9 +2277,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -2378,26 +2312,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -2430,26 +2347,9 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -2624,31 +2524,31 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E413A25D-5161-4141-BE0B-6E37A2A76CA5}">
   <dimension ref="A1:M141"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="37.5703125" customWidth="1"/>
-    <col min="2" max="2" width="24.7109375" customWidth="1"/>
-    <col min="3" max="3" width="15.85546875" hidden="1" customWidth="1"/>
-    <col min="4" max="4" width="21.7109375" customWidth="1"/>
-    <col min="5" max="5" width="16.7109375" customWidth="1"/>
-    <col min="6" max="6" width="15.5703125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="37.5546875" customWidth="1"/>
+    <col min="2" max="2" width="24.6640625" customWidth="1"/>
+    <col min="3" max="3" width="15.88671875" hidden="1" customWidth="1"/>
+    <col min="4" max="4" width="21.6640625" customWidth="1"/>
+    <col min="5" max="5" width="16.6640625" customWidth="1"/>
+    <col min="6" max="6" width="15.5546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5546875" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="12" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="22.7109375" customWidth="1"/>
+    <col min="10" max="10" width="22.6640625" customWidth="1"/>
     <col min="11" max="11" width="18" customWidth="1"/>
-    <col min="12" max="12" width="18.28515625" customWidth="1"/>
+    <col min="12" max="12" width="18.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1"/>
-      <c r="B1" s="217" t="s">
+      <c r="B1" s="225" t="s">
         <v>146</v>
       </c>
-      <c r="C1" s="217"/>
-      <c r="D1" s="217"/>
-      <c r="E1" s="218"/>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C1" s="225"/>
+      <c r="D1" s="225"/>
+      <c r="E1" s="226"/>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="2"/>
       <c r="B2" s="9" t="s">
         <v>148</v>
@@ -2657,16 +2557,16 @@
       <c r="D2" s="3"/>
       <c r="E2" s="4"/>
     </row>
-    <row r="3" spans="1:5" ht="51.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" ht="51.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="2"/>
-      <c r="B3" s="221" t="s">
+      <c r="B3" s="231" t="s">
         <v>191</v>
       </c>
-      <c r="C3" s="221"/>
-      <c r="D3" s="221"/>
-      <c r="E3" s="222"/>
-    </row>
-    <row r="4" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C3" s="231"/>
+      <c r="D3" s="231"/>
+      <c r="E3" s="232"/>
+    </row>
+    <row r="4" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="5" t="s">
         <v>100</v>
       </c>
@@ -2677,12 +2577,12 @@
       <c r="D4" s="7"/>
       <c r="E4" s="8"/>
     </row>
-    <row r="5" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
         <v>147</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>225</v>
+        <v>214</v>
       </c>
       <c r="C5" s="9"/>
       <c r="D5" s="3" t="s">
@@ -2690,7 +2590,7 @@
       </c>
       <c r="E5" s="10"/>
     </row>
-    <row r="6" spans="1:5" ht="16.149999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" ht="16.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="90" t="s">
         <v>137</v>
       </c>
@@ -2701,95 +2601,95 @@
       </c>
       <c r="E6" s="8"/>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" s="48"/>
-      <c r="B8" s="223" t="s">
-        <v>224</v>
-      </c>
-      <c r="C8" s="223"/>
+      <c r="B8" s="233" t="s">
+        <v>213</v>
+      </c>
+      <c r="C8" s="233"/>
       <c r="D8" s="48"/>
       <c r="E8" s="48"/>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" s="48"/>
-      <c r="B9" s="223"/>
-      <c r="C9" s="223"/>
+      <c r="B9" s="233"/>
+      <c r="C9" s="233"/>
       <c r="D9" s="48"/>
       <c r="E9" s="48"/>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" s="48"/>
-      <c r="B10" s="223"/>
-      <c r="C10" s="223"/>
+      <c r="B10" s="233"/>
+      <c r="C10" s="233"/>
       <c r="D10" s="48"/>
       <c r="E10" s="48"/>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" s="48"/>
       <c r="B11" s="48"/>
       <c r="C11" s="48"/>
       <c r="D11" s="48"/>
       <c r="E11" s="48"/>
     </row>
-    <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A12" s="48"/>
       <c r="B12" s="48"/>
       <c r="C12" s="48"/>
       <c r="D12" s="48"/>
       <c r="E12" s="48"/>
     </row>
-    <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="224" t="s">
+    <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="234" t="s">
         <v>103</v>
       </c>
-      <c r="B13" s="224"/>
-      <c r="C13" s="224"/>
-      <c r="D13" s="224"/>
-      <c r="E13" s="224"/>
-    </row>
-    <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="224"/>
-      <c r="B14" s="224"/>
-      <c r="C14" s="224"/>
-      <c r="D14" s="224"/>
-      <c r="E14" s="224"/>
-    </row>
-    <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="224"/>
-      <c r="B15" s="224"/>
-      <c r="C15" s="224"/>
-      <c r="D15" s="224"/>
-      <c r="E15" s="224"/>
-    </row>
-    <row r="16" spans="1:5" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="224"/>
-      <c r="B16" s="224"/>
-      <c r="C16" s="224"/>
-      <c r="D16" s="224"/>
-      <c r="E16" s="224"/>
-    </row>
-    <row r="17" spans="1:8" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B13" s="234"/>
+      <c r="C13" s="234"/>
+      <c r="D13" s="234"/>
+      <c r="E13" s="234"/>
+    </row>
+    <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="234"/>
+      <c r="B14" s="234"/>
+      <c r="C14" s="234"/>
+      <c r="D14" s="234"/>
+      <c r="E14" s="234"/>
+    </row>
+    <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="234"/>
+      <c r="B15" s="234"/>
+      <c r="C15" s="234"/>
+      <c r="D15" s="234"/>
+      <c r="E15" s="234"/>
+    </row>
+    <row r="16" spans="1:5" ht="53.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="234"/>
+      <c r="B16" s="234"/>
+      <c r="C16" s="234"/>
+      <c r="D16" s="234"/>
+      <c r="E16" s="234"/>
+    </row>
+    <row r="17" spans="1:8" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A17" s="48"/>
       <c r="B17" s="48"/>
       <c r="C17" s="48"/>
       <c r="D17" s="48"/>
       <c r="E17" s="48"/>
     </row>
-    <row r="18" spans="1:8" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:8" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A18" s="178"/>
       <c r="B18" s="48"/>
       <c r="C18" s="48"/>
       <c r="D18" s="48"/>
       <c r="E18" s="48"/>
     </row>
-    <row r="19" spans="1:8" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:8" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A19" s="48"/>
       <c r="B19" s="48"/>
       <c r="C19" s="48"/>
       <c r="D19" s="48"/>
       <c r="E19" s="48"/>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A20" s="179" t="s">
         <v>104</v>
       </c>
@@ -2798,7 +2698,7 @@
       <c r="D20" s="58"/>
       <c r="E20" s="59"/>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A21" s="36" t="s">
         <v>138</v>
       </c>
@@ -2807,25 +2707,25 @@
       <c r="D21" s="117"/>
       <c r="E21" s="152"/>
     </row>
-    <row r="22" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="219" t="s">
+    <row r="22" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="227" t="s">
         <v>163</v>
       </c>
-      <c r="B22" s="220"/>
+      <c r="B22" s="228"/>
       <c r="C22" s="182"/>
       <c r="D22" s="183">
         <v>3382992.69</v>
       </c>
       <c r="E22" s="153" t="s">
-        <v>232</v>
+        <v>221</v>
       </c>
       <c r="H22" s="19"/>
     </row>
-    <row r="23" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="219" t="s">
+    <row r="23" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="227" t="s">
         <v>164</v>
       </c>
-      <c r="B23" s="220"/>
+      <c r="B23" s="228"/>
       <c r="C23" s="182"/>
       <c r="D23" s="183">
         <v>-735800.92</v>
@@ -2833,11 +2733,11 @@
       <c r="E23" s="20"/>
       <c r="H23" s="19"/>
     </row>
-    <row r="24" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="219" t="s">
+    <row r="24" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="227" t="s">
         <v>1</v>
       </c>
-      <c r="B24" s="220"/>
+      <c r="B24" s="228"/>
       <c r="C24" s="182"/>
       <c r="D24" s="184">
         <v>0.23</v>
@@ -2845,7 +2745,7 @@
       <c r="E24" s="20"/>
       <c r="H24" s="19"/>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A25" s="185" t="s">
         <v>105</v>
       </c>
@@ -2857,7 +2757,7 @@
         <v>2647192</v>
       </c>
     </row>
-    <row r="26" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A26" s="185" t="s">
         <v>178</v>
       </c>
@@ -2866,82 +2766,82 @@
       <c r="D26" s="22"/>
       <c r="E26" s="155"/>
     </row>
-    <row r="27" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A27" s="182"/>
       <c r="B27" s="182"/>
       <c r="C27" s="182"/>
       <c r="D27" s="35"/>
       <c r="E27" s="168"/>
     </row>
-    <row r="28" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A28" s="182"/>
       <c r="B28" s="182"/>
       <c r="C28" s="182"/>
       <c r="D28" s="35"/>
       <c r="E28" s="168"/>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A29" s="182" t="s">
-        <v>249</v>
+        <v>238</v>
       </c>
       <c r="B29" s="182"/>
       <c r="C29" s="182"/>
-      <c r="D29" s="267">
+      <c r="D29" s="193">
         <v>37000</v>
       </c>
       <c r="E29" s="168"/>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A30" s="182" t="s">
-        <v>252</v>
+        <v>241</v>
       </c>
       <c r="B30" s="182"/>
       <c r="C30" s="182"/>
-      <c r="D30" s="267">
+      <c r="D30" s="193">
         <f>53000+480000</f>
         <v>533000</v>
       </c>
       <c r="E30" s="156"/>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A31" s="182" t="s">
-        <v>253</v>
+        <v>242</v>
       </c>
       <c r="B31" s="182"/>
       <c r="C31" s="182"/>
-      <c r="D31" s="267">
+      <c r="D31" s="193">
         <v>5837</v>
       </c>
       <c r="E31" s="156" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A32" s="182" t="s">
-        <v>254</v>
+        <v>243</v>
       </c>
       <c r="B32" s="182"/>
       <c r="C32" s="182"/>
-      <c r="D32" s="267">
+      <c r="D32" s="193">
         <v>5837</v>
       </c>
       <c r="E32" s="156" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33" s="185" t="s">
         <v>105</v>
       </c>
       <c r="B33" s="186"/>
       <c r="C33" s="186"/>
       <c r="D33" s="107"/>
-      <c r="E33" s="270">
+      <c r="E33" s="157">
         <f>SUM(D29:D32)</f>
         <v>581674</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A34" s="36" t="s">
         <v>139</v>
       </c>
@@ -2950,13 +2850,13 @@
       <c r="D34" s="22"/>
       <c r="E34" s="155"/>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A35" s="182" t="s">
         <v>189</v>
       </c>
       <c r="B35" s="187"/>
       <c r="C35" s="187"/>
-      <c r="D35" s="267">
+      <c r="D35" s="193">
         <v>12320.76</v>
       </c>
       <c r="E35" s="156" t="str">
@@ -2965,41 +2865,41 @@
       </c>
       <c r="G35" s="66"/>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A36" s="182" t="s">
         <v>150</v>
       </c>
       <c r="B36" s="187"/>
       <c r="C36" s="187"/>
-      <c r="D36" s="267">
+      <c r="D36" s="193">
         <v>923050.1</v>
       </c>
       <c r="E36" s="156" t="s">
-        <v>260</v>
+        <v>249</v>
       </c>
       <c r="G36" s="66"/>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A37" s="182" t="s">
         <v>141</v>
       </c>
       <c r="B37" s="187"/>
       <c r="C37" s="187"/>
-      <c r="D37" s="267">
+      <c r="D37" s="193">
         <v>181264.12</v>
       </c>
       <c r="E37" s="156" t="s">
-        <v>242</v>
+        <v>231</v>
       </c>
       <c r="G37" s="66"/>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A38" s="182" t="s">
         <v>143</v>
       </c>
       <c r="B38" s="187"/>
       <c r="C38" s="187"/>
-      <c r="D38" s="267">
+      <c r="D38" s="193">
         <v>94363</v>
       </c>
       <c r="E38" s="156" t="str">
@@ -3008,13 +2908,13 @@
       </c>
       <c r="G38" s="50"/>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39" s="182" t="s">
         <v>142</v>
       </c>
       <c r="B39" s="187"/>
       <c r="C39" s="187"/>
-      <c r="D39" s="267">
+      <c r="D39" s="193">
         <v>10484.780000000001</v>
       </c>
       <c r="E39" s="156" t="str">
@@ -3022,7 +2922,7 @@
         <v>Debito 12/06</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A40" s="182" t="s">
         <v>151</v>
       </c>
@@ -3031,7 +2931,7 @@
       <c r="D40" s="35"/>
       <c r="E40" s="156"/>
     </row>
-    <row r="41" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="185" t="s">
         <v>140</v>
       </c>
@@ -3043,7 +2943,7 @@
         <v>1221482.76</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42" s="14" t="s">
         <v>106</v>
       </c>
@@ -3052,33 +2952,33 @@
       <c r="D42" s="23"/>
       <c r="E42" s="157"/>
     </row>
-    <row r="43" spans="1:7" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="225" t="s">
+    <row r="43" spans="1:7" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="235" t="s">
         <v>185</v>
       </c>
-      <c r="B43" s="226"/>
+      <c r="B43" s="236"/>
       <c r="C43" s="26"/>
-      <c r="D43" s="269">
+      <c r="D43" s="195">
         <v>7805</v>
       </c>
       <c r="E43" s="20" t="s">
         <v>186</v>
       </c>
     </row>
-    <row r="44" spans="1:7" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="225" t="s">
+    <row r="44" spans="1:7" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A44" s="235" t="s">
         <v>187</v>
       </c>
-      <c r="B44" s="226"/>
+      <c r="B44" s="236"/>
       <c r="C44" s="26"/>
-      <c r="D44" s="269">
+      <c r="D44" s="195">
         <v>214164</v>
       </c>
       <c r="E44" s="20" t="s">
         <v>186</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A45" s="21" t="s">
         <v>107</v>
       </c>
@@ -3090,7 +2990,7 @@
         <v>221969</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A46" s="14" t="s">
         <v>108</v>
       </c>
@@ -3099,7 +2999,7 @@
       <c r="D46" s="28"/>
       <c r="E46" s="158"/>
     </row>
-    <row r="47" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="29" t="s">
         <v>109</v>
       </c>
@@ -3110,9 +3010,9 @@
       <c r="D47" s="30">
         <v>0</v>
       </c>
-      <c r="E47" s="273"/>
-    </row>
-    <row r="48" spans="1:7" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E47" s="198"/>
+    </row>
+    <row r="48" spans="1:7" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="29" t="s">
         <v>109</v>
       </c>
@@ -3120,14 +3020,14 @@
         <v>172</v>
       </c>
       <c r="C48" s="29"/>
-      <c r="D48" s="266">
+      <c r="D48" s="192">
         <v>16378.19</v>
       </c>
-      <c r="E48" s="273" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E48" s="198" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="29" t="s">
         <v>179</v>
       </c>
@@ -3140,7 +3040,7 @@
       </c>
       <c r="E49" s="20"/>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A50" s="29" t="s">
         <v>180</v>
       </c>
@@ -3151,20 +3051,20 @@
       </c>
       <c r="E50" s="20"/>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A51" s="225" t="s">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A51" s="235" t="s">
         <v>110</v>
       </c>
-      <c r="B51" s="226"/>
+      <c r="B51" s="236"/>
       <c r="C51" s="29"/>
       <c r="D51" s="30">
         <v>0</v>
       </c>
       <c r="E51" s="118" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A52" s="32" t="s">
         <v>111</v>
       </c>
@@ -3173,7 +3073,7 @@
       <c r="D52" s="30"/>
       <c r="E52" s="20"/>
     </row>
-    <row r="53" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A53" s="21" t="s">
         <v>112</v>
       </c>
@@ -3185,250 +3085,250 @@
         <v>16378.19</v>
       </c>
     </row>
-    <row r="54" spans="1:6" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:6" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A54" s="14"/>
       <c r="B54" s="21"/>
       <c r="C54" s="21"/>
       <c r="D54" s="22"/>
       <c r="E54" s="160"/>
     </row>
-    <row r="55" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="210" t="s">
+    <row r="55" spans="1:6" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A55" s="229" t="s">
         <v>166</v>
       </c>
-      <c r="B55" s="211"/>
+      <c r="B55" s="230"/>
       <c r="C55" s="29"/>
-      <c r="D55" s="266">
+      <c r="D55" s="192">
         <v>285000</v>
       </c>
       <c r="E55" s="167" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="56" spans="1:6" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="210" t="s">
-        <v>250</v>
-      </c>
-      <c r="B56" s="211"/>
+        <v>232</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" ht="33" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A56" s="229" t="s">
+        <v>239</v>
+      </c>
+      <c r="B56" s="230"/>
       <c r="C56" s="29"/>
-      <c r="D56" s="266">
+      <c r="D56" s="192">
         <f>660000+1400000</f>
         <v>2060000</v>
       </c>
       <c r="E56" s="167" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="57" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="210" t="s">
-        <v>256</v>
-      </c>
-      <c r="B57" s="211"/>
+        <v>246</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A57" s="229" t="s">
+        <v>245</v>
+      </c>
+      <c r="B57" s="230"/>
       <c r="C57" s="29"/>
-      <c r="D57" s="266">
+      <c r="D57" s="192">
         <f>2800000+1400000</f>
         <v>4200000</v>
       </c>
       <c r="E57" s="167" t="s">
-        <v>258</v>
+        <v>247</v>
       </c>
       <c r="F57" s="50"/>
     </row>
-    <row r="58" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" s="92" t="s">
-        <v>251</v>
+        <v>240</v>
       </c>
       <c r="B58" s="17"/>
       <c r="C58" s="29"/>
-      <c r="D58" s="266">
+      <c r="D58" s="192">
         <v>160000</v>
       </c>
       <c r="E58" s="167" t="s">
-        <v>243</v>
+        <v>232</v>
       </c>
       <c r="F58" s="50"/>
     </row>
-    <row r="59" spans="1:6" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:6" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" s="16" t="s">
-        <v>244</v>
+        <v>233</v>
       </c>
       <c r="B59" s="17"/>
       <c r="C59" s="29"/>
-      <c r="D59" s="266">
+      <c r="D59" s="192">
         <v>3000</v>
       </c>
       <c r="E59" s="34" t="s">
-        <v>255</v>
+        <v>244</v>
       </c>
       <c r="F59" s="50"/>
     </row>
-    <row r="60" spans="1:6" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="208" t="s">
-        <v>272</v>
-      </c>
-      <c r="B60" s="209"/>
+    <row r="60" spans="1:6" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A60" s="16" t="s">
+        <v>261</v>
+      </c>
+      <c r="B60" s="17"/>
       <c r="C60" s="29"/>
-      <c r="D60" s="266">
+      <c r="D60" s="192">
         <v>6990</v>
       </c>
       <c r="E60" s="34"/>
       <c r="F60" s="50"/>
     </row>
-    <row r="61" spans="1:6" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="210" t="s">
-        <v>230</v>
-      </c>
-      <c r="B61" s="211"/>
+    <row r="61" spans="1:6" ht="35.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A61" s="229" t="s">
+        <v>219</v>
+      </c>
+      <c r="B61" s="230"/>
       <c r="C61" s="29"/>
-      <c r="D61" s="266">
+      <c r="D61" s="192">
         <v>342000</v>
       </c>
       <c r="E61" s="34" t="s">
-        <v>231</v>
+        <v>220</v>
       </c>
       <c r="F61" s="50"/>
     </row>
-    <row r="62" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A62" s="92" t="s">
-        <v>235</v>
+        <v>224</v>
       </c>
       <c r="B62" s="17"/>
       <c r="C62" s="29"/>
-      <c r="D62" s="266">
+      <c r="D62" s="192">
         <v>67900</v>
       </c>
       <c r="E62" s="34" t="s">
-        <v>247</v>
+        <v>236</v>
       </c>
       <c r="F62" s="50"/>
     </row>
-    <row r="63" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A63" s="92" t="s">
-        <v>236</v>
+        <v>225</v>
       </c>
       <c r="B63" s="17"/>
       <c r="C63" s="29"/>
-      <c r="D63" s="266">
+      <c r="D63" s="192">
         <v>31400</v>
       </c>
       <c r="E63" s="34" t="s">
-        <v>237</v>
+        <v>226</v>
       </c>
       <c r="F63" s="50"/>
     </row>
-    <row r="64" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A64" s="92" t="s">
-        <v>238</v>
+        <v>227</v>
       </c>
       <c r="B64" s="17"/>
       <c r="C64" s="29"/>
-      <c r="D64" s="266">
+      <c r="D64" s="192">
         <v>31400</v>
       </c>
       <c r="E64" s="34" t="s">
-        <v>237</v>
+        <v>226</v>
       </c>
       <c r="F64" s="50"/>
     </row>
-    <row r="65" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A65" s="92" t="s">
-        <v>239</v>
+        <v>228</v>
       </c>
       <c r="B65" s="17"/>
       <c r="C65" s="29"/>
-      <c r="D65" s="266">
+      <c r="D65" s="192">
         <v>31400</v>
       </c>
       <c r="E65" s="34" t="s">
-        <v>237</v>
+        <v>226</v>
       </c>
       <c r="F65" s="50"/>
     </row>
-    <row r="66" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:6" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A66" s="92" t="s">
-        <v>226</v>
+        <v>215</v>
       </c>
       <c r="B66" s="17"/>
       <c r="C66" s="29"/>
-      <c r="D66" s="266">
+      <c r="D66" s="192">
         <v>150000</v>
       </c>
       <c r="E66" s="153" t="s">
-        <v>246</v>
+        <v>235</v>
       </c>
       <c r="F66" s="50"/>
     </row>
-    <row r="67" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:6" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A67" s="92" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B67" s="17"/>
       <c r="C67" s="29"/>
-      <c r="D67" s="266">
+      <c r="D67" s="192">
         <v>292300</v>
       </c>
       <c r="E67" s="167" t="s">
-        <v>233</v>
+        <v>222</v>
       </c>
       <c r="F67" s="50"/>
     </row>
-    <row r="68" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:6" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A68" s="92" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B68" s="17"/>
       <c r="C68" s="29"/>
-      <c r="D68" s="266">
+      <c r="D68" s="192">
         <v>467850</v>
       </c>
       <c r="E68" s="167" t="s">
-        <v>243</v>
+        <v>232</v>
       </c>
       <c r="F68" s="50"/>
     </row>
-    <row r="69" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:6" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A69" s="92" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B69" s="17"/>
       <c r="C69" s="29"/>
-      <c r="D69" s="266">
+      <c r="D69" s="192">
         <v>380000</v>
       </c>
       <c r="E69" s="167" t="s">
-        <v>248</v>
+        <v>237</v>
       </c>
       <c r="F69" s="50"/>
     </row>
-    <row r="70" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A70" s="210" t="s">
-        <v>240</v>
-      </c>
-      <c r="B70" s="211"/>
+    <row r="70" spans="1:6" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A70" s="229" t="s">
+        <v>229</v>
+      </c>
+      <c r="B70" s="230"/>
       <c r="C70" s="29"/>
-      <c r="D70" s="266">
+      <c r="D70" s="192">
         <v>25000</v>
       </c>
       <c r="E70" s="167" t="s">
-        <v>241</v>
+        <v>230</v>
       </c>
       <c r="F70" s="50"/>
     </row>
-    <row r="71" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A71" s="210" t="s">
-        <v>227</v>
-      </c>
-      <c r="B71" s="211"/>
+    <row r="71" spans="1:6" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A71" s="229" t="s">
+        <v>216</v>
+      </c>
+      <c r="B71" s="230"/>
       <c r="C71" s="29"/>
       <c r="D71" s="30">
         <v>0</v>
       </c>
       <c r="E71" s="167" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="F71" s="50"/>
     </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A72" s="21" t="s">
         <v>0</v>
       </c>
@@ -3440,7 +3340,7 @@
         <v>8534240</v>
       </c>
     </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A73" s="14" t="s">
         <v>113</v>
       </c>
@@ -3449,72 +3349,72 @@
       <c r="D73" s="15"/>
       <c r="E73" s="152"/>
     </row>
-    <row r="74" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A74" s="210" t="s">
-        <v>228</v>
-      </c>
-      <c r="B74" s="211"/>
+    <row r="74" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A74" s="229" t="s">
+        <v>217</v>
+      </c>
+      <c r="B74" s="230"/>
       <c r="C74" s="18"/>
-      <c r="D74" s="271">
+      <c r="D74" s="196">
         <v>650000</v>
       </c>
       <c r="E74" s="167" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="75" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A75" s="16" t="s">
         <v>165</v>
       </c>
       <c r="B75" s="17"/>
       <c r="C75" s="18"/>
-      <c r="D75" s="268">
+      <c r="D75" s="194">
         <v>250000</v>
       </c>
       <c r="E75" s="153" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="76" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A76" s="92" t="s">
-        <v>259</v>
-      </c>
-      <c r="B76" s="209"/>
+        <v>248</v>
+      </c>
+      <c r="B76" s="17"/>
       <c r="C76" s="18"/>
-      <c r="D76" s="268">
+      <c r="D76" s="194">
         <v>100000</v>
       </c>
       <c r="E76" s="167" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="77" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A77" s="92" t="s">
-        <v>245</v>
+        <v>234</v>
       </c>
       <c r="B77" s="17"/>
       <c r="C77" s="18"/>
-      <c r="D77" s="268">
+      <c r="D77" s="194">
         <v>100000</v>
       </c>
       <c r="E77" s="153" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="78" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A78" s="92" t="s">
-        <v>229</v>
+        <v>218</v>
       </c>
       <c r="B78" s="17"/>
       <c r="C78" s="18"/>
-      <c r="D78" s="268">
+      <c r="D78" s="194">
         <v>45000</v>
       </c>
       <c r="E78" s="167" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A79" s="21" t="s">
         <v>105</v>
       </c>
@@ -3526,7 +3426,7 @@
         <v>1145000</v>
       </c>
     </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A80" s="14" t="s">
         <v>114</v>
       </c>
@@ -3535,30 +3435,30 @@
       <c r="D80" s="38"/>
       <c r="E80" s="41"/>
     </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A81" s="29" t="s">
         <v>149</v>
       </c>
       <c r="B81" s="91"/>
       <c r="C81" s="91"/>
-      <c r="D81" s="272">
+      <c r="D81" s="197">
         <v>59000</v>
       </c>
       <c r="E81" s="161"/>
     </row>
-    <row r="82" spans="1:8" ht="61.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A82" s="225" t="s">
-        <v>274</v>
-      </c>
-      <c r="B82" s="226"/>
+    <row r="82" spans="1:8" ht="61.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A82" s="235" t="s">
+        <v>263</v>
+      </c>
+      <c r="B82" s="236"/>
       <c r="C82" s="91"/>
-      <c r="D82" s="272">
+      <c r="D82" s="197">
         <f>39523+201766.98</f>
         <v>241289.98</v>
       </c>
       <c r="E82" s="161"/>
     </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A83" s="39" t="s">
         <v>105</v>
       </c>
@@ -3570,14 +3470,14 @@
         <v>300289.98</v>
       </c>
     </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A84" s="29"/>
       <c r="B84" s="29"/>
       <c r="C84" s="29"/>
       <c r="D84" s="42"/>
       <c r="E84" s="43"/>
     </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A85" s="44" t="s">
         <v>115</v>
       </c>
@@ -3586,13 +3486,13 @@
       <c r="D85" s="45"/>
       <c r="E85" s="46"/>
     </row>
-    <row r="86" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A86" s="47"/>
       <c r="D86" s="48"/>
       <c r="E86" s="49"/>
       <c r="F86" s="50"/>
     </row>
-    <row r="87" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A87" s="51" t="s">
         <v>116</v>
       </c>
@@ -3606,16 +3506,16 @@
       <c r="F87" s="56"/>
       <c r="G87" s="50"/>
     </row>
-    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:8" x14ac:dyDescent="0.3">
       <c r="D88" s="48"/>
       <c r="E88" s="48"/>
     </row>
-    <row r="89" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D89" s="48"/>
       <c r="E89" s="48"/>
       <c r="H89" s="57"/>
     </row>
-    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A90" s="11" t="s">
         <v>117</v>
       </c>
@@ -3624,34 +3524,34 @@
       <c r="D90" s="58"/>
       <c r="E90" s="59"/>
     </row>
-    <row r="91" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A91" s="292"/>
-      <c r="B91" s="292"/>
+    <row r="91" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A91" s="237"/>
+      <c r="B91" s="237"/>
       <c r="C91" s="31"/>
-      <c r="D91" s="212"/>
-      <c r="E91" s="214"/>
-    </row>
-    <row r="92" spans="1:8" ht="1.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A92" s="292"/>
-      <c r="B92" s="292"/>
+      <c r="D91" s="238"/>
+      <c r="E91" s="240"/>
+    </row>
+    <row r="92" spans="1:8" ht="1.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A92" s="237"/>
+      <c r="B92" s="237"/>
       <c r="C92" s="31"/>
-      <c r="D92" s="213"/>
-      <c r="E92" s="215"/>
-    </row>
-    <row r="93" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D92" s="239"/>
+      <c r="E92" s="241"/>
+    </row>
+    <row r="93" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A93" s="29"/>
       <c r="B93" s="29"/>
       <c r="D93" s="42"/>
       <c r="E93" s="42"/>
     </row>
-    <row r="94" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A94" s="24"/>
       <c r="B94" s="61"/>
       <c r="C94" s="29"/>
       <c r="D94" s="35"/>
       <c r="E94" s="60"/>
     </row>
-    <row r="95" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A95" s="62" t="s">
         <v>145</v>
       </c>
@@ -3663,15 +3563,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D96" s="48"/>
       <c r="E96" s="48"/>
     </row>
-    <row r="97" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="D97" s="48"/>
       <c r="E97" s="48"/>
     </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A98" s="44" t="s">
         <v>118</v>
       </c>
@@ -3682,11 +3582,11 @@
         <v>3000000</v>
       </c>
     </row>
-    <row r="99" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D99" s="48"/>
       <c r="E99" s="48"/>
     </row>
-    <row r="100" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A100" s="51" t="s">
         <v>119</v>
       </c>
@@ -3698,11 +3598,11 @@
         <v>3000000</v>
       </c>
     </row>
-    <row r="101" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D101" s="48"/>
       <c r="E101" s="48"/>
     </row>
-    <row r="102" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A102" s="64" t="s">
         <v>120</v>
       </c>
@@ -3713,7 +3613,7 @@
       <c r="D102" s="48"/>
       <c r="E102" s="48"/>
     </row>
-    <row r="103" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A103" s="64" t="s">
         <v>121</v>
       </c>
@@ -3724,7 +3624,7 @@
       <c r="D103" s="48"/>
       <c r="E103" s="48"/>
     </row>
-    <row r="104" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A104" s="64" t="s">
         <v>122</v>
       </c>
@@ -3735,7 +3635,7 @@
       <c r="D104" s="48"/>
       <c r="E104" s="48"/>
     </row>
-    <row r="105" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A105" s="64" t="s">
         <v>123</v>
       </c>
@@ -3746,142 +3646,142 @@
       <c r="D105" s="48"/>
       <c r="E105" s="48"/>
     </row>
-    <row r="106" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:5" x14ac:dyDescent="0.3">
       <c r="D106" s="48"/>
       <c r="E106" s="48"/>
     </row>
-    <row r="107" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:5" x14ac:dyDescent="0.3">
       <c r="D107" s="48"/>
       <c r="E107" s="48"/>
     </row>
-    <row r="108" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A108" s="216" t="s">
+    <row r="108" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A108" s="224" t="s">
         <v>174</v>
       </c>
-      <c r="B108" s="216"/>
+      <c r="B108" s="224"/>
       <c r="D108" s="48"/>
       <c r="E108" s="48"/>
     </row>
-    <row r="109" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A109" s="216"/>
-      <c r="B109" s="216"/>
+    <row r="109" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A109" s="224"/>
+      <c r="B109" s="224"/>
       <c r="D109" s="48"/>
       <c r="E109" s="48"/>
     </row>
-    <row r="110" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A110" s="216"/>
-      <c r="B110" s="216"/>
+    <row r="110" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A110" s="224"/>
+      <c r="B110" s="224"/>
       <c r="D110" s="48"/>
       <c r="E110" s="48"/>
     </row>
-    <row r="111" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:5" x14ac:dyDescent="0.3">
       <c r="D111" s="48"/>
       <c r="E111" s="48"/>
     </row>
-    <row r="112" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A112" s="216" t="s">
-        <v>203</v>
-      </c>
-      <c r="B112" s="216"/>
+    <row r="112" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A112" s="224" t="s">
+        <v>202</v>
+      </c>
+      <c r="B112" s="224"/>
       <c r="D112" s="48"/>
       <c r="E112" s="48"/>
     </row>
-    <row r="113" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A113" s="216"/>
-      <c r="B113" s="216"/>
+    <row r="113" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A113" s="224"/>
+      <c r="B113" s="224"/>
       <c r="D113" s="48"/>
       <c r="E113" s="48"/>
     </row>
-    <row r="114" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A114" s="216"/>
-      <c r="B114" s="216"/>
+    <row r="114" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A114" s="224"/>
+      <c r="B114" s="224"/>
       <c r="D114" s="48"/>
       <c r="E114" s="48"/>
     </row>
-    <row r="115" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D115" s="48"/>
       <c r="E115" s="48"/>
     </row>
-    <row r="116" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A116" s="216" t="s">
+    <row r="116" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A116" s="224" t="s">
         <v>181</v>
       </c>
-      <c r="B116" s="216"/>
+      <c r="B116" s="224"/>
       <c r="D116" s="48"/>
       <c r="E116" s="48"/>
     </row>
-    <row r="117" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A117" s="216"/>
-      <c r="B117" s="216"/>
+    <row r="117" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A117" s="224"/>
+      <c r="B117" s="224"/>
       <c r="D117" s="48"/>
       <c r="E117" s="48"/>
     </row>
-    <row r="118" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A118" s="216"/>
-      <c r="B118" s="216"/>
+    <row r="118" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A118" s="224"/>
+      <c r="B118" s="224"/>
       <c r="D118" s="48"/>
       <c r="E118" s="48"/>
     </row>
-    <row r="119" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D119" s="48"/>
       <c r="E119" s="48"/>
     </row>
-    <row r="120" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A120" s="216" t="s">
+    <row r="120" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A120" s="224" t="s">
         <v>184</v>
       </c>
-      <c r="B120" s="216"/>
+      <c r="B120" s="224"/>
       <c r="D120" s="48"/>
       <c r="E120" s="48"/>
     </row>
-    <row r="121" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A121" s="216"/>
-      <c r="B121" s="216"/>
+    <row r="121" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A121" s="224"/>
+      <c r="B121" s="224"/>
       <c r="D121" s="48"/>
       <c r="E121" s="48"/>
     </row>
-    <row r="122" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A122" s="216"/>
-      <c r="B122" s="216"/>
+    <row r="122" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A122" s="224"/>
+      <c r="B122" s="224"/>
       <c r="D122" s="48"/>
       <c r="E122" s="48"/>
     </row>
-    <row r="123" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D123" s="48"/>
       <c r="E123" s="48"/>
     </row>
-    <row r="124" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A124" s="216" t="s">
+    <row r="124" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A124" s="224" t="s">
         <v>183</v>
       </c>
-      <c r="B124" s="216"/>
+      <c r="B124" s="224"/>
       <c r="D124" s="48"/>
       <c r="E124" s="48"/>
     </row>
-    <row r="125" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A125" s="216"/>
-      <c r="B125" s="216"/>
+    <row r="125" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A125" s="224"/>
+      <c r="B125" s="224"/>
       <c r="D125" s="48"/>
       <c r="E125" s="48"/>
     </row>
-    <row r="126" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A126" s="216"/>
-      <c r="B126" s="216"/>
+    <row r="126" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A126" s="224"/>
+      <c r="B126" s="224"/>
       <c r="D126" s="48"/>
       <c r="E126" s="48"/>
     </row>
-    <row r="127" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:5" x14ac:dyDescent="0.3">
       <c r="D127" s="48"/>
       <c r="E127" s="48"/>
     </row>
-    <row r="128" spans="1:5" s="68" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:5" s="68" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A128"/>
       <c r="B128" s="66"/>
       <c r="C128" s="67"/>
       <c r="D128" s="163"/>
       <c r="E128" s="163"/>
     </row>
-    <row r="129" spans="1:13" s="68" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:13" s="68" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A129" s="169" t="s">
         <v>192</v>
       </c>
@@ -3892,7 +3792,7 @@
       <c r="D129" s="164"/>
       <c r="E129" s="164"/>
     </row>
-    <row r="130" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A130" s="26" t="s">
         <v>144</v>
       </c>
@@ -3903,7 +3803,7 @@
       <c r="D130" s="48"/>
       <c r="E130" s="48"/>
     </row>
-    <row r="131" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A131" s="26" t="s">
         <v>124</v>
       </c>
@@ -3915,7 +3815,7 @@
       <c r="E131" s="48"/>
       <c r="F131" s="66"/>
     </row>
-    <row r="132" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A132" s="26" t="s">
         <v>2</v>
       </c>
@@ -3927,9 +3827,9 @@
       <c r="E132" s="48"/>
       <c r="F132" s="66"/>
     </row>
-    <row r="133" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A133" s="26" t="s">
-        <v>234</v>
+        <v>223</v>
       </c>
       <c r="B133" s="146">
         <v>-95000</v>
@@ -3938,7 +3838,7 @@
       <c r="E133" s="48"/>
       <c r="F133" s="66"/>
     </row>
-    <row r="134" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A134" s="72" t="s">
         <v>162</v>
       </c>
@@ -3950,22 +3850,22 @@
       <c r="E134" s="50"/>
       <c r="F134" s="50"/>
     </row>
-    <row r="135" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="136" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A136" s="227" t="s">
+    <row r="135" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="136" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A136" s="223" t="s">
         <v>125</v>
       </c>
-      <c r="B136" s="227"/>
-      <c r="C136" s="227"/>
-    </row>
-    <row r="137" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A137" s="227"/>
-      <c r="B137" s="227"/>
-      <c r="C137" s="227"/>
-    </row>
-    <row r="138" spans="1:13" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B136" s="223"/>
+      <c r="C136" s="223"/>
+    </row>
+    <row r="137" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A137" s="223"/>
+      <c r="B137" s="223"/>
+      <c r="C137" s="223"/>
+    </row>
+    <row r="138" spans="1:13" ht="27" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A138" s="74" t="s">
-        <v>264</v>
+        <v>253</v>
       </c>
       <c r="B138" s="115">
         <v>300000</v>
@@ -3973,9 +3873,9 @@
       <c r="C138" s="75"/>
       <c r="D138" s="56"/>
     </row>
-    <row r="139" spans="1:13" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:13" ht="27" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A139" s="147" t="s">
-        <v>269</v>
+        <v>258</v>
       </c>
       <c r="B139" s="115">
         <v>132000</v>
@@ -3983,7 +3883,7 @@
       <c r="C139" s="75"/>
       <c r="D139" s="56"/>
     </row>
-    <row r="140" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A140" s="76" t="s">
         <v>0</v>
       </c>
@@ -3993,17 +3893,16 @@
       </c>
       <c r="C140" s="78"/>
     </row>
-    <row r="141" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:13" x14ac:dyDescent="0.3">
       <c r="M141" s="79"/>
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="A136:C137"/>
-    <mergeCell ref="A112:B114"/>
-    <mergeCell ref="A124:B126"/>
-    <mergeCell ref="A120:B122"/>
-    <mergeCell ref="A108:B110"/>
-    <mergeCell ref="A116:B118"/>
+    <mergeCell ref="A71:B71"/>
+    <mergeCell ref="A91:B92"/>
+    <mergeCell ref="D91:D92"/>
+    <mergeCell ref="E91:E92"/>
+    <mergeCell ref="A82:B82"/>
     <mergeCell ref="B1:E1"/>
     <mergeCell ref="A24:B24"/>
     <mergeCell ref="A74:B74"/>
@@ -4020,11 +3919,12 @@
     <mergeCell ref="A57:B57"/>
     <mergeCell ref="A61:B61"/>
     <mergeCell ref="A56:B56"/>
-    <mergeCell ref="A71:B71"/>
-    <mergeCell ref="A91:B92"/>
-    <mergeCell ref="D91:D92"/>
-    <mergeCell ref="E91:E92"/>
-    <mergeCell ref="A82:B82"/>
+    <mergeCell ref="A136:C137"/>
+    <mergeCell ref="A112:B114"/>
+    <mergeCell ref="A124:B126"/>
+    <mergeCell ref="A120:B122"/>
+    <mergeCell ref="A108:B110"/>
+    <mergeCell ref="A116:B118"/>
   </mergeCells>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="5" scale="90" orientation="portrait" r:id="rId1"/>
@@ -4035,53 +3935,53 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{533DB7A7-09F4-49CF-B824-70F15C1FF525}">
   <dimension ref="A1:P127"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="4.28515625" customWidth="1"/>
-    <col min="2" max="2" width="25.5703125" customWidth="1"/>
-    <col min="3" max="3" width="0.140625" customWidth="1"/>
-    <col min="4" max="4" width="8.42578125" customWidth="1"/>
-    <col min="5" max="5" width="14.140625" customWidth="1"/>
-    <col min="6" max="6" width="12.28515625" customWidth="1"/>
-    <col min="7" max="7" width="10.5703125" customWidth="1"/>
-    <col min="8" max="8" width="9.5703125" customWidth="1"/>
-    <col min="9" max="9" width="12.42578125" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" customWidth="1"/>
-    <col min="11" max="12" width="12.28515625" customWidth="1"/>
-    <col min="13" max="13" width="14.7109375" customWidth="1"/>
-    <col min="14" max="14" width="14.28515625" customWidth="1"/>
-    <col min="15" max="15" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="4.33203125" customWidth="1"/>
+    <col min="2" max="2" width="25.5546875" customWidth="1"/>
+    <col min="3" max="3" width="0.109375" customWidth="1"/>
+    <col min="4" max="4" width="8.44140625" customWidth="1"/>
+    <col min="5" max="5" width="14.109375" customWidth="1"/>
+    <col min="6" max="6" width="12.33203125" customWidth="1"/>
+    <col min="7" max="7" width="10.5546875" customWidth="1"/>
+    <col min="8" max="8" width="9.5546875" customWidth="1"/>
+    <col min="9" max="9" width="12.44140625" customWidth="1"/>
+    <col min="10" max="10" width="14.44140625" customWidth="1"/>
+    <col min="11" max="12" width="12.33203125" customWidth="1"/>
+    <col min="13" max="13" width="14.6640625" customWidth="1"/>
+    <col min="14" max="14" width="14.33203125" customWidth="1"/>
+    <col min="15" max="15" width="7.33203125" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="12" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="13" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:16" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="93"/>
       <c r="B1" s="94"/>
       <c r="C1" s="94"/>
-      <c r="D1" s="231"/>
-      <c r="E1" s="231"/>
-      <c r="F1" s="231"/>
-      <c r="G1" s="231"/>
-      <c r="H1" s="231"/>
-      <c r="I1" s="231"/>
-      <c r="J1" s="231"/>
-      <c r="K1" s="231"/>
-      <c r="L1" s="231"/>
-      <c r="M1" s="231"/>
+      <c r="D1" s="257"/>
+      <c r="E1" s="257"/>
+      <c r="F1" s="257"/>
+      <c r="G1" s="257"/>
+      <c r="H1" s="257"/>
+      <c r="I1" s="257"/>
+      <c r="J1" s="257"/>
+      <c r="K1" s="257"/>
+      <c r="L1" s="257"/>
+      <c r="M1" s="257"/>
       <c r="N1" s="95"/>
     </row>
-    <row r="2" spans="1:16" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:16" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="96"/>
       <c r="B2" s="97"/>
       <c r="C2" s="98"/>
       <c r="D2" s="98" t="s">
         <v>126</v>
       </c>
-      <c r="E2" s="255">
+      <c r="E2" s="279">
         <v>3000000</v>
       </c>
-      <c r="F2" s="255"/>
+      <c r="F2" s="279"/>
       <c r="G2" s="98"/>
       <c r="H2" s="98"/>
       <c r="I2" s="98" t="s">
@@ -4099,7 +3999,7 @@
         <v>13312274.1</v>
       </c>
     </row>
-    <row r="3" spans="1:16" ht="12.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:16" ht="12.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="102"/>
       <c r="B3" s="103"/>
       <c r="C3" s="103"/>
@@ -4116,228 +4016,228 @@
       <c r="N3" s="106"/>
       <c r="O3" s="80"/>
     </row>
-    <row r="4" spans="1:16" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="232" t="s">
+    <row r="4" spans="1:16" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="258" t="s">
         <v>161</v>
       </c>
-      <c r="B4" s="233"/>
-      <c r="C4" s="233"/>
-      <c r="D4" s="233"/>
-      <c r="E4" s="233"/>
-      <c r="F4" s="233"/>
-      <c r="G4" s="233"/>
-      <c r="H4" s="233"/>
-      <c r="I4" s="233"/>
-      <c r="J4" s="233"/>
-      <c r="K4" s="233"/>
-      <c r="L4" s="233"/>
-      <c r="M4" s="233"/>
-      <c r="N4" s="234"/>
+      <c r="B4" s="259"/>
+      <c r="C4" s="259"/>
+      <c r="D4" s="259"/>
+      <c r="E4" s="259"/>
+      <c r="F4" s="259"/>
+      <c r="G4" s="259"/>
+      <c r="H4" s="259"/>
+      <c r="I4" s="259"/>
+      <c r="J4" s="259"/>
+      <c r="K4" s="259"/>
+      <c r="L4" s="259"/>
+      <c r="M4" s="259"/>
+      <c r="N4" s="260"/>
       <c r="O4" s="80"/>
     </row>
-    <row r="5" spans="1:16" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="235"/>
-      <c r="B5" s="236"/>
-      <c r="C5" s="236"/>
-      <c r="D5" s="236"/>
-      <c r="E5" s="236"/>
-      <c r="F5" s="236"/>
-      <c r="G5" s="236"/>
-      <c r="H5" s="236"/>
-      <c r="I5" s="236"/>
-      <c r="J5" s="236"/>
-      <c r="K5" s="236"/>
-      <c r="L5" s="236"/>
-      <c r="M5" s="236"/>
-      <c r="N5" s="237"/>
+    <row r="5" spans="1:16" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="261"/>
+      <c r="B5" s="262"/>
+      <c r="C5" s="262"/>
+      <c r="D5" s="262"/>
+      <c r="E5" s="262"/>
+      <c r="F5" s="262"/>
+      <c r="G5" s="262"/>
+      <c r="H5" s="262"/>
+      <c r="I5" s="262"/>
+      <c r="J5" s="262"/>
+      <c r="K5" s="262"/>
+      <c r="L5" s="262"/>
+      <c r="M5" s="262"/>
+      <c r="N5" s="263"/>
       <c r="O5" s="80"/>
     </row>
-    <row r="6" spans="1:16" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="235"/>
-      <c r="B6" s="236"/>
-      <c r="C6" s="236"/>
-      <c r="D6" s="236"/>
-      <c r="E6" s="236"/>
-      <c r="F6" s="236"/>
-      <c r="G6" s="236"/>
-      <c r="H6" s="236"/>
-      <c r="I6" s="236"/>
-      <c r="J6" s="236"/>
-      <c r="K6" s="236"/>
-      <c r="L6" s="236"/>
-      <c r="M6" s="236"/>
-      <c r="N6" s="237"/>
+    <row r="6" spans="1:16" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="261"/>
+      <c r="B6" s="262"/>
+      <c r="C6" s="262"/>
+      <c r="D6" s="262"/>
+      <c r="E6" s="262"/>
+      <c r="F6" s="262"/>
+      <c r="G6" s="262"/>
+      <c r="H6" s="262"/>
+      <c r="I6" s="262"/>
+      <c r="J6" s="262"/>
+      <c r="K6" s="262"/>
+      <c r="L6" s="262"/>
+      <c r="M6" s="262"/>
+      <c r="N6" s="263"/>
       <c r="O6" s="80"/>
     </row>
-    <row r="7" spans="1:16" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="235"/>
-      <c r="B7" s="236"/>
-      <c r="C7" s="236"/>
-      <c r="D7" s="236"/>
-      <c r="E7" s="236"/>
-      <c r="F7" s="236"/>
-      <c r="G7" s="236"/>
-      <c r="H7" s="236"/>
-      <c r="I7" s="236"/>
-      <c r="J7" s="236"/>
-      <c r="K7" s="236"/>
-      <c r="L7" s="236"/>
-      <c r="M7" s="236"/>
-      <c r="N7" s="237"/>
+    <row r="7" spans="1:16" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="261"/>
+      <c r="B7" s="262"/>
+      <c r="C7" s="262"/>
+      <c r="D7" s="262"/>
+      <c r="E7" s="262"/>
+      <c r="F7" s="262"/>
+      <c r="G7" s="262"/>
+      <c r="H7" s="262"/>
+      <c r="I7" s="262"/>
+      <c r="J7" s="262"/>
+      <c r="K7" s="262"/>
+      <c r="L7" s="262"/>
+      <c r="M7" s="262"/>
+      <c r="N7" s="263"/>
       <c r="O7" s="80"/>
     </row>
-    <row r="8" spans="1:16" ht="192" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="238"/>
-      <c r="B8" s="239"/>
-      <c r="C8" s="239"/>
-      <c r="D8" s="239"/>
-      <c r="E8" s="239"/>
-      <c r="F8" s="239"/>
-      <c r="G8" s="239"/>
-      <c r="H8" s="239"/>
-      <c r="I8" s="239"/>
-      <c r="J8" s="239"/>
-      <c r="K8" s="239"/>
-      <c r="L8" s="239"/>
-      <c r="M8" s="239"/>
-      <c r="N8" s="240"/>
-    </row>
-    <row r="9" spans="1:16" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="249" t="s">
+    <row r="8" spans="1:16" ht="192" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="264"/>
+      <c r="B8" s="265"/>
+      <c r="C8" s="265"/>
+      <c r="D8" s="265"/>
+      <c r="E8" s="265"/>
+      <c r="F8" s="265"/>
+      <c r="G8" s="265"/>
+      <c r="H8" s="265"/>
+      <c r="I8" s="265"/>
+      <c r="J8" s="265"/>
+      <c r="K8" s="265"/>
+      <c r="L8" s="265"/>
+      <c r="M8" s="265"/>
+      <c r="N8" s="266"/>
+    </row>
+    <row r="9" spans="1:16" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="273" t="s">
         <v>159</v>
       </c>
-      <c r="B9" s="250"/>
-      <c r="C9" s="250"/>
-      <c r="D9" s="250"/>
-      <c r="E9" s="250"/>
-      <c r="F9" s="250"/>
-      <c r="G9" s="250"/>
-      <c r="H9" s="250"/>
-      <c r="I9" s="250"/>
-      <c r="J9" s="250"/>
-      <c r="K9" s="250"/>
-      <c r="L9" s="250"/>
-      <c r="M9" s="250"/>
-      <c r="N9" s="251"/>
-    </row>
-    <row r="10" spans="1:16" ht="59.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="289" t="s">
-        <v>273</v>
-      </c>
-      <c r="B10" s="290"/>
-      <c r="C10" s="290"/>
-      <c r="D10" s="290"/>
-      <c r="E10" s="290"/>
-      <c r="F10" s="290"/>
-      <c r="G10" s="290"/>
-      <c r="H10" s="290"/>
-      <c r="I10" s="290"/>
-      <c r="J10" s="290"/>
-      <c r="K10" s="290"/>
-      <c r="L10" s="290"/>
-      <c r="M10" s="290"/>
-      <c r="N10" s="291"/>
-    </row>
-    <row r="11" spans="1:16" ht="59.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="302" t="s">
-        <v>275</v>
-      </c>
-      <c r="B11" s="303"/>
-      <c r="C11" s="303"/>
-      <c r="D11" s="303"/>
-      <c r="E11" s="303"/>
-      <c r="F11" s="303"/>
-      <c r="G11" s="303"/>
-      <c r="H11" s="303"/>
-      <c r="I11" s="303"/>
-      <c r="J11" s="303"/>
-      <c r="K11" s="303"/>
-      <c r="L11" s="303"/>
-      <c r="M11" s="303"/>
-      <c r="N11" s="304"/>
-    </row>
-    <row r="12" spans="1:16" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="252" t="s">
+      <c r="B9" s="274"/>
+      <c r="C9" s="274"/>
+      <c r="D9" s="274"/>
+      <c r="E9" s="274"/>
+      <c r="F9" s="274"/>
+      <c r="G9" s="274"/>
+      <c r="H9" s="274"/>
+      <c r="I9" s="274"/>
+      <c r="J9" s="274"/>
+      <c r="K9" s="274"/>
+      <c r="L9" s="274"/>
+      <c r="M9" s="274"/>
+      <c r="N9" s="275"/>
+    </row>
+    <row r="10" spans="1:16" ht="59.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="248" t="s">
+        <v>262</v>
+      </c>
+      <c r="B10" s="249"/>
+      <c r="C10" s="249"/>
+      <c r="D10" s="249"/>
+      <c r="E10" s="249"/>
+      <c r="F10" s="249"/>
+      <c r="G10" s="249"/>
+      <c r="H10" s="249"/>
+      <c r="I10" s="249"/>
+      <c r="J10" s="249"/>
+      <c r="K10" s="249"/>
+      <c r="L10" s="249"/>
+      <c r="M10" s="249"/>
+      <c r="N10" s="250"/>
+    </row>
+    <row r="11" spans="1:16" ht="59.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="251" t="s">
+        <v>264</v>
+      </c>
+      <c r="B11" s="252"/>
+      <c r="C11" s="252"/>
+      <c r="D11" s="252"/>
+      <c r="E11" s="252"/>
+      <c r="F11" s="252"/>
+      <c r="G11" s="252"/>
+      <c r="H11" s="252"/>
+      <c r="I11" s="252"/>
+      <c r="J11" s="252"/>
+      <c r="K11" s="252"/>
+      <c r="L11" s="252"/>
+      <c r="M11" s="252"/>
+      <c r="N11" s="253"/>
+    </row>
+    <row r="12" spans="1:16" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="276" t="s">
         <v>160</v>
       </c>
-      <c r="B12" s="253"/>
-      <c r="C12" s="253"/>
-      <c r="D12" s="253"/>
-      <c r="E12" s="253"/>
-      <c r="F12" s="253"/>
-      <c r="G12" s="253"/>
-      <c r="H12" s="253"/>
-      <c r="I12" s="253"/>
-      <c r="J12" s="253"/>
-      <c r="K12" s="253"/>
-      <c r="L12" s="253"/>
-      <c r="M12" s="253"/>
-      <c r="N12" s="254"/>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A13" s="241" t="s">
+      <c r="B12" s="277"/>
+      <c r="C12" s="277"/>
+      <c r="D12" s="277"/>
+      <c r="E12" s="277"/>
+      <c r="F12" s="277"/>
+      <c r="G12" s="277"/>
+      <c r="H12" s="277"/>
+      <c r="I12" s="277"/>
+      <c r="J12" s="277"/>
+      <c r="K12" s="277"/>
+      <c r="L12" s="277"/>
+      <c r="M12" s="277"/>
+      <c r="N12" s="278"/>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A13" s="267" t="s">
         <v>128</v>
       </c>
-      <c r="B13" s="243" t="s">
+      <c r="B13" s="269" t="s">
         <v>129</v>
       </c>
-      <c r="C13" s="243" t="s">
+      <c r="C13" s="269" t="s">
         <v>130</v>
       </c>
-      <c r="D13" s="243" t="s">
+      <c r="D13" s="269" t="s">
         <v>131</v>
       </c>
-      <c r="E13" s="245" t="s">
+      <c r="E13" s="246" t="s">
         <v>132</v>
       </c>
-      <c r="F13" s="243" t="s">
+      <c r="F13" s="269" t="s">
         <v>133</v>
       </c>
-      <c r="G13" s="247" t="s">
+      <c r="G13" s="271" t="s">
         <v>134</v>
       </c>
-      <c r="H13" s="245" t="s">
+      <c r="H13" s="246" t="s">
         <v>135</v>
       </c>
-      <c r="I13" s="245" t="s">
+      <c r="I13" s="246" t="s">
         <v>127</v>
       </c>
-      <c r="J13" s="245" t="s">
+      <c r="J13" s="246" t="s">
         <v>126</v>
       </c>
-      <c r="K13" s="256" t="s">
+      <c r="K13" s="242" t="s">
         <v>176</v>
       </c>
-      <c r="L13" s="258" t="s">
+      <c r="L13" s="244" t="s">
         <v>182</v>
       </c>
       <c r="M13" s="143" t="s">
-        <v>263</v>
-      </c>
-      <c r="N13" s="228" t="s">
+        <v>252</v>
+      </c>
+      <c r="N13" s="254" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="14" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="242"/>
-      <c r="B14" s="244"/>
-      <c r="C14" s="244"/>
-      <c r="D14" s="244"/>
-      <c r="E14" s="246"/>
-      <c r="F14" s="244"/>
-      <c r="G14" s="248"/>
-      <c r="H14" s="246"/>
-      <c r="I14" s="246"/>
-      <c r="J14" s="246"/>
-      <c r="K14" s="257"/>
-      <c r="L14" s="259"/>
+    <row r="14" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="268"/>
+      <c r="B14" s="270"/>
+      <c r="C14" s="270"/>
+      <c r="D14" s="270"/>
+      <c r="E14" s="247"/>
+      <c r="F14" s="270"/>
+      <c r="G14" s="272"/>
+      <c r="H14" s="247"/>
+      <c r="I14" s="247"/>
+      <c r="J14" s="247"/>
+      <c r="K14" s="243"/>
+      <c r="L14" s="245"/>
       <c r="M14" s="144" t="str">
         <f>RESUMEN!B8</f>
         <v>VTO 17/07</v>
       </c>
-      <c r="N14" s="229"/>
-    </row>
-    <row r="15" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N14" s="255"/>
+    </row>
+    <row r="15" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="129">
         <v>1</v>
       </c>
@@ -4385,44 +4285,44 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="16" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="196">
+    <row r="16" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="188">
         <v>2</v>
       </c>
-      <c r="B16" s="293" t="s">
+      <c r="B16" s="214" t="s">
         <v>4</v>
       </c>
-      <c r="C16" s="294"/>
-      <c r="D16" s="295">
+      <c r="C16" s="215"/>
+      <c r="D16" s="216">
         <v>1.18</v>
       </c>
-      <c r="E16" s="296">
+      <c r="E16" s="217">
         <v>3506224.02</v>
       </c>
-      <c r="F16" s="296"/>
-      <c r="G16" s="297">
+      <c r="F16" s="217"/>
+      <c r="G16" s="218">
         <f t="shared" si="0"/>
         <v>3506224.02</v>
       </c>
-      <c r="H16" s="297">
+      <c r="H16" s="218">
         <f t="shared" ref="H16:H79" si="4">IF(G16&gt;0,G16*3%,0)</f>
         <v>105186.7206</v>
       </c>
-      <c r="I16" s="298">
+      <c r="I16" s="219">
         <f t="shared" si="1"/>
         <v>177000</v>
       </c>
-      <c r="J16" s="298">
+      <c r="J16" s="219">
         <f t="shared" si="2"/>
         <v>35400</v>
       </c>
-      <c r="K16" s="298"/>
-      <c r="L16" s="299"/>
-      <c r="M16" s="300">
+      <c r="K16" s="219"/>
+      <c r="L16" s="220"/>
+      <c r="M16" s="221">
         <f>ROUND(SUM(G16:L16),0) + O16</f>
         <v>3823811.02</v>
       </c>
-      <c r="N16" s="301">
+      <c r="N16" s="222">
         <f t="shared" si="3"/>
         <v>3938525.02</v>
       </c>
@@ -4434,7 +4334,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="17" spans="1:15" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:15" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="129">
         <v>3</v>
       </c>
@@ -4483,7 +4383,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="18" spans="1:15" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:15" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="130">
         <v>4</v>
       </c>
@@ -4532,7 +4432,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="19" spans="1:15" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:15" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="129">
         <v>5</v>
       </c>
@@ -4580,7 +4480,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="20" spans="1:15" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:15" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="129">
         <v>6</v>
       </c>
@@ -4628,7 +4528,7 @@
         <v>6.0000000000000005E-2</v>
       </c>
     </row>
-    <row r="21" spans="1:15" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:15" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="129">
         <v>7</v>
       </c>
@@ -4677,7 +4577,7 @@
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="22" spans="1:15" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:15" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="129">
         <v>8</v>
       </c>
@@ -4726,7 +4626,7 @@
         <v>0.08</v>
       </c>
     </row>
-    <row r="23" spans="1:15" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:15" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="129">
         <v>9</v>
       </c>
@@ -4774,7 +4674,7 @@
         <v>0.09</v>
       </c>
     </row>
-    <row r="24" spans="1:15" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:15" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="129">
         <v>10</v>
       </c>
@@ -4822,7 +4722,7 @@
         <v>9.9999999999999992E-2</v>
       </c>
     </row>
-    <row r="25" spans="1:15" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:15" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="129">
         <v>11</v>
       </c>
@@ -4871,46 +4771,46 @@
         <v>0.10999999999999999</v>
       </c>
     </row>
-    <row r="26" spans="1:15" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="196">
+    <row r="26" spans="1:15" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="188">
         <v>12</v>
       </c>
-      <c r="B26" s="293" t="s">
+      <c r="B26" s="214" t="s">
         <v>14</v>
       </c>
-      <c r="C26" s="294"/>
-      <c r="D26" s="295">
+      <c r="C26" s="215"/>
+      <c r="D26" s="216">
         <v>1.17</v>
       </c>
-      <c r="E26" s="296">
+      <c r="E26" s="217">
         <v>4474263.12</v>
       </c>
-      <c r="F26" s="296">
-        <v>0</v>
-      </c>
-      <c r="G26" s="297">
+      <c r="F26" s="217">
+        <v>0</v>
+      </c>
+      <c r="G26" s="218">
         <f t="shared" si="0"/>
         <v>4474263.12</v>
       </c>
-      <c r="H26" s="297">
+      <c r="H26" s="218">
         <f t="shared" si="4"/>
         <v>134227.89360000001</v>
       </c>
-      <c r="I26" s="298">
+      <c r="I26" s="219">
         <f t="shared" si="1"/>
         <v>175500</v>
       </c>
-      <c r="J26" s="298">
+      <c r="J26" s="219">
         <f t="shared" si="2"/>
         <v>35100</v>
       </c>
-      <c r="K26" s="298"/>
-      <c r="L26" s="299"/>
-      <c r="M26" s="300">
+      <c r="K26" s="219"/>
+      <c r="L26" s="220"/>
+      <c r="M26" s="221">
         <f t="shared" si="5"/>
         <v>4819091.12</v>
       </c>
-      <c r="N26" s="301">
+      <c r="N26" s="222">
         <f t="shared" si="3"/>
         <v>4963664.12</v>
       </c>
@@ -4919,7 +4819,7 @@
         <v>0.11999999999999998</v>
       </c>
     </row>
-    <row r="27" spans="1:15" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:15" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="129">
         <v>13</v>
       </c>
@@ -4968,7 +4868,7 @@
         <v>0.12999999999999998</v>
       </c>
     </row>
-    <row r="28" spans="1:15" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:15" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="129">
         <v>14</v>
       </c>
@@ -5014,7 +4914,7 @@
         <v>0.13999999999999999</v>
       </c>
     </row>
-    <row r="29" spans="1:15" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:15" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="130">
         <v>15</v>
       </c>
@@ -5063,7 +4963,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="30" spans="1:15" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:15" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="129">
         <v>16</v>
       </c>
@@ -5112,7 +5012,7 @@
         <v>0.16</v>
       </c>
     </row>
-    <row r="31" spans="1:15" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:15" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="129">
         <v>17</v>
       </c>
@@ -5160,7 +5060,7 @@
         <v>0.17</v>
       </c>
     </row>
-    <row r="32" spans="1:15" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:15" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="130">
         <v>18</v>
       </c>
@@ -5209,7 +5109,7 @@
         <v>0.18000000000000002</v>
       </c>
     </row>
-    <row r="33" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A33" s="130">
         <v>19</v>
       </c>
@@ -5260,7 +5160,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="34" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A34" s="131">
         <v>20</v>
       </c>
@@ -5307,10 +5207,10 @@
         <v>0.20000000000000004</v>
       </c>
       <c r="P34" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="35" spans="1:16" x14ac:dyDescent="0.25">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="35" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A35" s="130">
         <v>21</v>
       </c>
@@ -5359,7 +5259,7 @@
         <v>0.21000000000000005</v>
       </c>
     </row>
-    <row r="36" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A36" s="130">
         <f>A35+1</f>
         <v>22</v>
@@ -5409,7 +5309,7 @@
         <v>0.22000000000000006</v>
       </c>
     </row>
-    <row r="37" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A37" s="129">
         <f t="shared" ref="A37:A100" si="9">A36+1</f>
         <v>23</v>
@@ -5459,7 +5359,7 @@
         <v>0.23000000000000007</v>
       </c>
     </row>
-    <row r="38" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A38" s="129">
         <f t="shared" si="9"/>
         <v>24</v>
@@ -5508,7 +5408,7 @@
         <v>0.24000000000000007</v>
       </c>
     </row>
-    <row r="39" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A39" s="129">
         <f t="shared" si="9"/>
         <v>25</v>
@@ -5558,7 +5458,7 @@
         <v>0.25000000000000006</v>
       </c>
     </row>
-    <row r="40" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A40" s="129">
         <f t="shared" si="9"/>
         <v>26</v>
@@ -5608,7 +5508,7 @@
         <v>0.26000000000000006</v>
       </c>
     </row>
-    <row r="41" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A41" s="129">
         <f t="shared" si="9"/>
         <v>27</v>
@@ -5658,7 +5558,7 @@
         <v>0.27000000000000007</v>
       </c>
     </row>
-    <row r="42" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A42" s="129">
         <f t="shared" si="9"/>
         <v>28</v>
@@ -5705,7 +5605,7 @@
         <v>0.28000000000000008</v>
       </c>
     </row>
-    <row r="43" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A43" s="130">
         <f t="shared" si="9"/>
         <v>29</v>
@@ -5758,7 +5658,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="44" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A44" s="130">
         <f t="shared" si="9"/>
         <v>30</v>
@@ -5808,7 +5708,7 @@
         <v>0.3000000000000001</v>
       </c>
     </row>
-    <row r="45" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A45" s="129">
         <f t="shared" si="9"/>
         <v>31</v>
@@ -5858,7 +5758,7 @@
         <v>0.31000000000000011</v>
       </c>
     </row>
-    <row r="46" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A46" s="129">
         <f t="shared" si="9"/>
         <v>32</v>
@@ -5907,7 +5807,7 @@
         <v>0.32000000000000012</v>
       </c>
     </row>
-    <row r="47" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A47" s="131">
         <f t="shared" si="9"/>
         <v>33</v>
@@ -5956,10 +5856,10 @@
         <v>0.33000000000000013</v>
       </c>
       <c r="P47" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="48" spans="1:16" x14ac:dyDescent="0.25">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="48" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A48" s="129">
         <f t="shared" si="9"/>
         <v>34</v>
@@ -6009,16 +5909,16 @@
         <v>0.34000000000000014</v>
       </c>
     </row>
-    <row r="49" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A49" s="274">
+    <row r="49" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A49" s="199">
         <f t="shared" si="9"/>
         <v>35</v>
       </c>
-      <c r="B49" s="275" t="s">
+      <c r="B49" s="200" t="s">
         <v>36</v>
       </c>
-      <c r="C49" s="276"/>
-      <c r="D49" s="277">
+      <c r="C49" s="201"/>
+      <c r="D49" s="202">
         <v>1.1200000000000001</v>
       </c>
       <c r="E49" s="84">
@@ -6028,24 +5928,24 @@
         <f>E49</f>
         <v>183314.35</v>
       </c>
-      <c r="G49" s="278">
+      <c r="G49" s="203">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H49" s="278">
+      <c r="H49" s="203">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="I49" s="279">
+      <c r="I49" s="204">
         <f t="shared" si="11"/>
         <v>168000</v>
       </c>
-      <c r="J49" s="279">
+      <c r="J49" s="204">
         <f t="shared" si="12"/>
         <v>33600.000000000007</v>
       </c>
-      <c r="K49" s="279"/>
-      <c r="L49" s="280"/>
+      <c r="K49" s="204"/>
+      <c r="L49" s="205"/>
       <c r="M49" s="112">
         <f t="shared" si="5"/>
         <v>201600.35</v>
@@ -6062,7 +5962,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="50" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A50" s="129">
         <f t="shared" si="9"/>
         <v>36</v>
@@ -6115,7 +6015,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="51" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A51" s="129">
         <f t="shared" si="9"/>
         <v>37</v>
@@ -6164,10 +6064,10 @@
         <v>0.37000000000000016</v>
       </c>
       <c r="P51" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="52" spans="1:16" x14ac:dyDescent="0.25">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="52" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A52" s="129">
         <f t="shared" si="9"/>
         <v>38</v>
@@ -6217,7 +6117,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="53" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A53" s="129">
         <f t="shared" si="9"/>
         <v>39</v>
@@ -6267,7 +6167,7 @@
         <v>0.39000000000000018</v>
       </c>
     </row>
-    <row r="54" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A54" s="129">
         <f t="shared" si="9"/>
         <v>40</v>
@@ -6317,7 +6217,7 @@
         <v>0.40000000000000019</v>
       </c>
     </row>
-    <row r="55" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A55" s="129">
         <f t="shared" si="9"/>
         <v>41</v>
@@ -6366,7 +6266,7 @@
         <v>0.4100000000000002</v>
       </c>
     </row>
-    <row r="56" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A56" s="131">
         <f t="shared" si="9"/>
         <v>42</v>
@@ -6415,10 +6315,10 @@
         <v>0.42000000000000021</v>
       </c>
       <c r="P56" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="57" spans="1:16" x14ac:dyDescent="0.25">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="57" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A57" s="131">
         <f t="shared" si="9"/>
         <v>43</v>
@@ -6470,10 +6370,10 @@
         <v>0.43000000000000022</v>
       </c>
       <c r="P57" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="58" spans="1:16" x14ac:dyDescent="0.25">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="58" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A58" s="130">
         <f t="shared" si="9"/>
         <v>44</v>
@@ -6523,16 +6423,16 @@
         <v>0.44000000000000022</v>
       </c>
       <c r="P58" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="59" spans="1:16" x14ac:dyDescent="0.25">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="59" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A59" s="130">
         <f t="shared" si="9"/>
         <v>45</v>
       </c>
       <c r="B59" s="114" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C59" s="113"/>
       <c r="D59" s="110">
@@ -6576,12 +6476,12 @@
         <v>0.45000000000000023</v>
       </c>
     </row>
-    <row r="60" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A60" s="130">
+    <row r="60" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A60" s="286">
         <f t="shared" si="9"/>
         <v>46</v>
       </c>
-      <c r="B60" s="114" t="s">
+      <c r="B60" s="287" t="s">
         <v>45</v>
       </c>
       <c r="C60" s="113"/>
@@ -6628,7 +6528,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="61" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A61" s="131">
         <f t="shared" si="9"/>
         <v>47</v>
@@ -6676,10 +6576,10 @@
         <v>0.47000000000000025</v>
       </c>
       <c r="P61" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="62" spans="1:16" x14ac:dyDescent="0.25">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="62" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A62" s="130">
         <f t="shared" si="9"/>
         <v>48</v>
@@ -6695,7 +6595,7 @@
         <v>236077.48</v>
       </c>
       <c r="F62" s="84">
-        <f t="shared" ref="F62:F68" si="13">E62</f>
+        <f t="shared" ref="F62:F67" si="13">E62</f>
         <v>236077.48</v>
       </c>
       <c r="G62" s="111">
@@ -6732,7 +6632,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="63" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A63" s="130">
         <f t="shared" si="9"/>
         <v>49</v>
@@ -6782,7 +6682,7 @@
         <v>0.49000000000000027</v>
       </c>
     </row>
-    <row r="64" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A64" s="130">
         <f t="shared" si="9"/>
         <v>50</v>
@@ -6832,7 +6732,7 @@
         <v>0.50000000000000022</v>
       </c>
     </row>
-    <row r="65" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A65" s="130">
         <f t="shared" si="9"/>
         <v>51</v>
@@ -6882,7 +6782,7 @@
         <v>0.51000000000000023</v>
       </c>
     </row>
-    <row r="66" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A66" s="130">
         <f t="shared" si="9"/>
         <v>52</v>
@@ -6932,7 +6832,7 @@
         <v>0.52000000000000024</v>
       </c>
     </row>
-    <row r="67" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A67" s="130">
         <f t="shared" si="9"/>
         <v>53</v>
@@ -6982,7 +6882,7 @@
         <v>0.53000000000000025</v>
       </c>
     </row>
-    <row r="68" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A68" s="130">
         <f t="shared" si="9"/>
         <v>54</v>
@@ -7031,7 +6931,7 @@
         <v>0.54000000000000026</v>
       </c>
     </row>
-    <row r="69" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A69" s="130">
         <f t="shared" si="9"/>
         <v>55</v>
@@ -7080,7 +6980,7 @@
         <v>0.55000000000000027</v>
       </c>
     </row>
-    <row r="70" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A70" s="130">
         <f t="shared" si="9"/>
         <v>56</v>
@@ -7129,7 +7029,7 @@
         <v>0.56000000000000028</v>
       </c>
     </row>
-    <row r="71" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A71" s="130">
         <f t="shared" si="9"/>
         <v>57</v>
@@ -7179,7 +7079,7 @@
         <v>0.57000000000000028</v>
       </c>
     </row>
-    <row r="72" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A72" s="130">
         <f t="shared" si="9"/>
         <v>58</v>
@@ -7195,7 +7095,7 @@
         <v>139219.57999999999</v>
       </c>
       <c r="F72" s="84">
-        <f t="shared" ref="F72:F73" si="14">E72</f>
+        <f t="shared" ref="F72" si="14">E72</f>
         <v>139219.57999999999</v>
       </c>
       <c r="G72" s="85">
@@ -7229,10 +7129,10 @@
         <v>0.58000000000000029</v>
       </c>
       <c r="P72" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="73" spans="1:16" x14ac:dyDescent="0.25">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="73" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A73" s="130">
         <f t="shared" si="9"/>
         <v>59</v>
@@ -7281,7 +7181,7 @@
         <v>0.5900000000000003</v>
       </c>
     </row>
-    <row r="74" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A74" s="130">
         <f t="shared" si="9"/>
         <v>60</v>
@@ -7330,7 +7230,7 @@
         <v>0.60000000000000031</v>
       </c>
     </row>
-    <row r="75" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A75" s="130">
         <f t="shared" si="9"/>
         <v>61</v>
@@ -7380,7 +7280,7 @@
         <v>0.61000000000000032</v>
       </c>
     </row>
-    <row r="76" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A76" s="130">
         <f t="shared" si="9"/>
         <v>62</v>
@@ -7429,7 +7329,7 @@
         <v>0.62000000000000033</v>
       </c>
     </row>
-    <row r="77" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A77" s="130">
         <f t="shared" si="9"/>
         <v>63</v>
@@ -7479,10 +7379,10 @@
         <v>0.63000000000000034</v>
       </c>
       <c r="P77" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="78" spans="1:16" x14ac:dyDescent="0.25">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="78" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A78" s="130">
         <f t="shared" si="9"/>
         <v>64</v>
@@ -7531,7 +7431,7 @@
         <v>0.64000000000000035</v>
       </c>
     </row>
-    <row r="79" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A79" s="130">
         <f t="shared" si="9"/>
         <v>65</v>
@@ -7583,47 +7483,47 @@
         <v>173</v>
       </c>
     </row>
-    <row r="80" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A80" s="206">
+    <row r="80" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A80" s="190">
         <f t="shared" si="9"/>
         <v>66</v>
       </c>
-      <c r="B80" s="207" t="s">
+      <c r="B80" s="191" t="s">
         <v>65</v>
       </c>
-      <c r="C80" s="281"/>
-      <c r="D80" s="282">
+      <c r="C80" s="206"/>
+      <c r="D80" s="207">
         <v>1.34</v>
       </c>
-      <c r="E80" s="283">
+      <c r="E80" s="208">
         <v>538997.66</v>
       </c>
-      <c r="F80" s="283">
+      <c r="F80" s="208">
         <v>201818.66</v>
       </c>
-      <c r="G80" s="284">
+      <c r="G80" s="209">
         <f t="shared" si="15"/>
         <v>337179</v>
       </c>
-      <c r="H80" s="284">
+      <c r="H80" s="209">
         <f t="shared" ref="H80:H117" si="18">IF(G80&gt;0,G80*3%,0)</f>
         <v>10115.369999999999</v>
       </c>
-      <c r="I80" s="285">
+      <c r="I80" s="210">
         <f t="shared" si="16"/>
         <v>201000</v>
       </c>
-      <c r="J80" s="285">
+      <c r="J80" s="210">
         <f t="shared" si="17"/>
         <v>40200.000000000007</v>
       </c>
-      <c r="K80" s="285"/>
-      <c r="L80" s="286"/>
-      <c r="M80" s="287">
+      <c r="K80" s="210"/>
+      <c r="L80" s="211"/>
+      <c r="M80" s="212">
         <f t="shared" si="5"/>
         <v>588494.66</v>
       </c>
-      <c r="N80" s="288">
+      <c r="N80" s="213">
         <f t="shared" si="8"/>
         <v>606149.66</v>
       </c>
@@ -7632,7 +7532,7 @@
         <v>0.66000000000000036</v>
       </c>
     </row>
-    <row r="81" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A81" s="130">
         <f t="shared" si="9"/>
         <v>67</v>
@@ -7681,49 +7581,49 @@
         <v>0.67000000000000037</v>
       </c>
     </row>
-    <row r="82" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A82" s="196">
+    <row r="82" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A82" s="188">
         <f t="shared" si="9"/>
         <v>68</v>
       </c>
-      <c r="B82" s="197" t="s">
+      <c r="B82" s="189" t="s">
         <v>67</v>
       </c>
-      <c r="C82" s="294"/>
-      <c r="D82" s="295">
+      <c r="C82" s="215"/>
+      <c r="D82" s="216">
         <v>1.17</v>
       </c>
-      <c r="E82" s="296">
+      <c r="E82" s="217">
         <v>6827757.6799999997</v>
       </c>
-      <c r="F82" s="296">
-        <v>0</v>
-      </c>
-      <c r="G82" s="297">
+      <c r="F82" s="217">
+        <v>0</v>
+      </c>
+      <c r="G82" s="218">
         <f t="shared" si="15"/>
         <v>6827757.6799999997</v>
       </c>
-      <c r="H82" s="297">
+      <c r="H82" s="218">
         <f t="shared" si="18"/>
         <v>204832.73039999997</v>
       </c>
-      <c r="I82" s="298">
+      <c r="I82" s="219">
         <f t="shared" si="16"/>
         <v>175500</v>
       </c>
-      <c r="J82" s="298">
+      <c r="J82" s="219">
         <f t="shared" si="17"/>
         <v>35100</v>
       </c>
-      <c r="K82" s="298">
+      <c r="K82" s="219">
         <v>95000</v>
       </c>
-      <c r="L82" s="299"/>
-      <c r="M82" s="300">
+      <c r="L82" s="220"/>
+      <c r="M82" s="221">
         <f t="shared" si="19"/>
         <v>7338190.6799999997</v>
       </c>
-      <c r="N82" s="301">
+      <c r="N82" s="222">
         <f t="shared" si="8"/>
         <v>7558336.6799999997</v>
       </c>
@@ -7732,7 +7632,7 @@
         <v>0.68000000000000038</v>
       </c>
     </row>
-    <row r="83" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A83" s="130">
         <f t="shared" si="9"/>
         <v>69</v>
@@ -7767,7 +7667,7 @@
         <v>40500.000000000007</v>
       </c>
       <c r="K83" s="125" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="L83" s="148"/>
       <c r="M83" s="86">
@@ -7783,7 +7683,7 @@
         <v>0.69000000000000039</v>
       </c>
     </row>
-    <row r="84" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A84" s="130">
         <f t="shared" si="9"/>
         <v>70</v>
@@ -7836,7 +7736,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="85" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A85" s="130">
         <f t="shared" si="9"/>
         <v>71</v>
@@ -7886,7 +7786,7 @@
         <v>0.71000000000000041</v>
       </c>
     </row>
-    <row r="86" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A86" s="130">
         <f t="shared" si="9"/>
         <v>72</v>
@@ -7936,7 +7836,7 @@
         <v>0.72000000000000042</v>
       </c>
     </row>
-    <row r="87" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A87" s="130">
         <f t="shared" si="9"/>
         <v>73</v>
@@ -7986,7 +7886,7 @@
         <v>0.73000000000000043</v>
       </c>
     </row>
-    <row r="88" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A88" s="129">
         <f t="shared" si="9"/>
         <v>74</v>
@@ -8035,7 +7935,7 @@
         <v>0.74000000000000044</v>
       </c>
     </row>
-    <row r="89" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A89" s="129">
         <f t="shared" si="9"/>
         <v>75</v>
@@ -8085,7 +7985,7 @@
         <v>0.75000000000000044</v>
       </c>
     </row>
-    <row r="90" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A90" s="129">
         <f t="shared" si="9"/>
         <v>76</v>
@@ -8135,7 +8035,7 @@
         <v>0.76000000000000045</v>
       </c>
     </row>
-    <row r="91" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A91" s="129">
         <f t="shared" si="9"/>
         <v>77</v>
@@ -8185,7 +8085,7 @@
         <v>0.77000000000000046</v>
       </c>
     </row>
-    <row r="92" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A92" s="131">
         <f t="shared" si="9"/>
         <v>78</v>
@@ -8234,16 +8134,16 @@
         <v>0.78000000000000047</v>
       </c>
       <c r="P92" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="93" spans="1:16" x14ac:dyDescent="0.25">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="93" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A93" s="129">
         <f t="shared" si="9"/>
         <v>79</v>
       </c>
       <c r="B93" s="88" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C93" s="87"/>
       <c r="D93" s="82">
@@ -8287,10 +8187,10 @@
         <v>0.79000000000000048</v>
       </c>
       <c r="P93" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="94" spans="1:16" x14ac:dyDescent="0.25">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="94" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A94" s="130">
         <f t="shared" si="9"/>
         <v>80</v>
@@ -8340,7 +8240,7 @@
         <v>0.80000000000000049</v>
       </c>
     </row>
-    <row r="95" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A95" s="130">
         <f t="shared" si="9"/>
         <v>81</v>
@@ -8390,10 +8290,10 @@
         <v>0.8100000000000005</v>
       </c>
       <c r="P95" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="96" spans="1:16" x14ac:dyDescent="0.25">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="96" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A96" s="130">
         <f t="shared" si="9"/>
         <v>82</v>
@@ -8442,7 +8342,7 @@
         <v>0.82000000000000051</v>
       </c>
     </row>
-    <row r="97" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A97" s="130">
         <f t="shared" si="9"/>
         <v>83</v>
@@ -8492,7 +8392,7 @@
         <v>0.83000000000000052</v>
       </c>
     </row>
-    <row r="98" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A98" s="130">
         <f t="shared" si="9"/>
         <v>84</v>
@@ -8539,7 +8439,7 @@
         <v>0.84000000000000052</v>
       </c>
     </row>
-    <row r="99" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A99" s="129">
         <f t="shared" si="9"/>
         <v>85</v>
@@ -8589,48 +8489,48 @@
         <v>0.85000000000000053</v>
       </c>
     </row>
-    <row r="100" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A100" s="206">
+    <row r="100" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A100" s="190">
         <f t="shared" si="9"/>
         <v>86</v>
       </c>
-      <c r="B100" s="207" t="s">
+      <c r="B100" s="191" t="s">
         <v>84</v>
       </c>
-      <c r="C100" s="281"/>
-      <c r="D100" s="282">
+      <c r="C100" s="206"/>
+      <c r="D100" s="207">
         <v>0.82</v>
       </c>
-      <c r="E100" s="283">
+      <c r="E100" s="208">
         <v>139219.85999999999</v>
       </c>
-      <c r="F100" s="283">
+      <c r="F100" s="208">
         <f>E100</f>
         <v>139219.85999999999</v>
       </c>
-      <c r="G100" s="284">
+      <c r="G100" s="209">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="H100" s="284">
+      <c r="H100" s="209">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="I100" s="285">
+      <c r="I100" s="210">
         <f t="shared" si="16"/>
         <v>123000</v>
       </c>
-      <c r="J100" s="285">
+      <c r="J100" s="210">
         <f t="shared" si="17"/>
         <v>24600</v>
       </c>
-      <c r="K100" s="285"/>
-      <c r="L100" s="286"/>
-      <c r="M100" s="287">
+      <c r="K100" s="210"/>
+      <c r="L100" s="211"/>
+      <c r="M100" s="212">
         <f t="shared" si="19"/>
         <v>147600.85999999999</v>
       </c>
-      <c r="N100" s="288">
+      <c r="N100" s="213">
         <f t="shared" ref="N100:N117" si="22">ROUND(M100*3%,0) + M100</f>
         <v>152028.85999999999</v>
       </c>
@@ -8639,7 +8539,7 @@
         <v>0.86000000000000054</v>
       </c>
     </row>
-    <row r="101" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A101" s="129">
         <f t="shared" ref="A101:A117" si="23">A100+1</f>
         <v>87</v>
@@ -8689,7 +8589,7 @@
         <v>0.87000000000000055</v>
       </c>
     </row>
-    <row r="102" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A102" s="129">
         <f t="shared" si="23"/>
         <v>88</v>
@@ -8739,7 +8639,7 @@
         <v>0.88000000000000056</v>
       </c>
     </row>
-    <row r="103" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A103" s="129">
         <f t="shared" si="23"/>
         <v>89</v>
@@ -8789,7 +8689,7 @@
         <v>0.89000000000000057</v>
       </c>
     </row>
-    <row r="104" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A104" s="129">
         <f t="shared" si="23"/>
         <v>90</v>
@@ -8839,7 +8739,7 @@
         <v>0.90000000000000058</v>
       </c>
     </row>
-    <row r="105" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A105" s="129">
         <f t="shared" si="23"/>
         <v>91</v>
@@ -8888,7 +8788,7 @@
         <v>0.91000000000000059</v>
       </c>
     </row>
-    <row r="106" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A106" s="129">
         <f t="shared" si="23"/>
         <v>92</v>
@@ -8937,7 +8837,7 @@
         <v>0.9200000000000006</v>
       </c>
     </row>
-    <row r="107" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A107" s="130">
         <f t="shared" si="23"/>
         <v>93</v>
@@ -8986,7 +8886,7 @@
         <v>0.9300000000000006</v>
       </c>
     </row>
-    <row r="108" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A108" s="130">
         <f t="shared" si="23"/>
         <v>94</v>
@@ -9036,7 +8936,7 @@
         <v>0.94000000000000061</v>
       </c>
     </row>
-    <row r="109" spans="1:16" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:16" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A109" s="130">
         <f t="shared" si="23"/>
         <v>95</v>
@@ -9086,7 +8986,7 @@
         <v>0.95000000000000062</v>
       </c>
     </row>
-    <row r="110" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A110" s="130">
         <f t="shared" si="23"/>
         <v>96</v>
@@ -9138,7 +9038,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="111" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A111" s="130">
         <f t="shared" si="23"/>
         <v>97</v>
@@ -9188,7 +9088,7 @@
         <v>0.97000000000000064</v>
       </c>
     </row>
-    <row r="112" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A112" s="130">
         <f t="shared" si="23"/>
         <v>98</v>
@@ -9238,7 +9138,7 @@
         <v>0.98000000000000065</v>
       </c>
     </row>
-    <row r="113" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A113" s="130">
         <f t="shared" si="23"/>
         <v>99</v>
@@ -9288,7 +9188,7 @@
         <v>0.99000000000000066</v>
       </c>
     </row>
-    <row r="114" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A114" s="130">
         <f t="shared" si="23"/>
         <v>100</v>
@@ -9335,7 +9235,7 @@
         <v>1.0000000000000007</v>
       </c>
     </row>
-    <row r="115" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A115" s="130">
         <f t="shared" si="23"/>
         <v>101</v>
@@ -9384,7 +9284,7 @@
         <v>1.0100000000000007</v>
       </c>
     </row>
-    <row r="116" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A116" s="130">
         <f t="shared" si="23"/>
         <v>102</v>
@@ -9434,7 +9334,7 @@
         <v>1.0200000000000007</v>
       </c>
     </row>
-    <row r="117" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A117" s="130">
         <f t="shared" si="23"/>
         <v>103</v>
@@ -9484,7 +9384,7 @@
         <v>1.0300000000000007</v>
       </c>
     </row>
-    <row r="118" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A118" s="130"/>
       <c r="B118" s="108"/>
       <c r="C118" s="113"/>
@@ -9501,7 +9401,7 @@
       <c r="N118" s="140"/>
       <c r="O118" s="50"/>
     </row>
-    <row r="119" spans="1:15" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:15" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A119" s="132"/>
       <c r="B119" s="133"/>
       <c r="C119" s="133"/>
@@ -9544,105 +9444,99 @@
         <v>40891254.560000002</v>
       </c>
     </row>
-    <row r="120" spans="1:15" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:15" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B120" s="89"/>
       <c r="C120" s="89"/>
     </row>
-    <row r="121" spans="1:15" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="122" spans="1:15" ht="9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B122" s="230" t="s">
+    <row r="121" spans="1:15" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="122" spans="1:15" ht="9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B122" s="256" t="s">
         <v>103</v>
       </c>
-      <c r="C122" s="230"/>
-      <c r="D122" s="230"/>
-      <c r="E122" s="230"/>
-      <c r="F122" s="230"/>
-      <c r="G122" s="230"/>
-      <c r="H122" s="230"/>
-      <c r="I122" s="230"/>
-      <c r="J122" s="230"/>
-      <c r="K122" s="230"/>
-      <c r="L122" s="230"/>
-      <c r="M122" s="230"/>
-    </row>
-    <row r="123" spans="1:15" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B123" s="230"/>
-      <c r="C123" s="230"/>
-      <c r="D123" s="230"/>
-      <c r="E123" s="230"/>
-      <c r="F123" s="230"/>
-      <c r="G123" s="230"/>
-      <c r="H123" s="230"/>
-      <c r="I123" s="230"/>
-      <c r="J123" s="230"/>
-      <c r="K123" s="230"/>
-      <c r="L123" s="230"/>
-      <c r="M123" s="230"/>
-    </row>
-    <row r="124" spans="1:15" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B124" s="230"/>
-      <c r="C124" s="230"/>
-      <c r="D124" s="230"/>
-      <c r="E124" s="230"/>
-      <c r="F124" s="230"/>
-      <c r="G124" s="230"/>
-      <c r="H124" s="230"/>
-      <c r="I124" s="230"/>
-      <c r="J124" s="230"/>
-      <c r="K124" s="230"/>
-      <c r="L124" s="230"/>
-      <c r="M124" s="230"/>
-    </row>
-    <row r="125" spans="1:15" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B125" s="230"/>
-      <c r="C125" s="230"/>
-      <c r="D125" s="230"/>
-      <c r="E125" s="230"/>
-      <c r="F125" s="230"/>
-      <c r="G125" s="230"/>
-      <c r="H125" s="230"/>
-      <c r="I125" s="230"/>
-      <c r="J125" s="230"/>
-      <c r="K125" s="230"/>
-      <c r="L125" s="230"/>
-      <c r="M125" s="230"/>
-    </row>
-    <row r="126" spans="1:15" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B126" s="230"/>
-      <c r="C126" s="230"/>
-      <c r="D126" s="230"/>
-      <c r="E126" s="230"/>
-      <c r="F126" s="230"/>
-      <c r="G126" s="230"/>
-      <c r="H126" s="230"/>
-      <c r="I126" s="230"/>
-      <c r="J126" s="230"/>
-      <c r="K126" s="230"/>
-      <c r="L126" s="230"/>
-      <c r="M126" s="230"/>
-    </row>
-    <row r="127" spans="1:15" ht="67.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B127" s="230"/>
-      <c r="C127" s="230"/>
-      <c r="D127" s="230"/>
-      <c r="E127" s="230"/>
-      <c r="F127" s="230"/>
-      <c r="G127" s="230"/>
-      <c r="H127" s="230"/>
-      <c r="I127" s="230"/>
-      <c r="J127" s="230"/>
-      <c r="K127" s="230"/>
-      <c r="L127" s="230"/>
-      <c r="M127" s="230"/>
+      <c r="C122" s="256"/>
+      <c r="D122" s="256"/>
+      <c r="E122" s="256"/>
+      <c r="F122" s="256"/>
+      <c r="G122" s="256"/>
+      <c r="H122" s="256"/>
+      <c r="I122" s="256"/>
+      <c r="J122" s="256"/>
+      <c r="K122" s="256"/>
+      <c r="L122" s="256"/>
+      <c r="M122" s="256"/>
+    </row>
+    <row r="123" spans="1:15" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B123" s="256"/>
+      <c r="C123" s="256"/>
+      <c r="D123" s="256"/>
+      <c r="E123" s="256"/>
+      <c r="F123" s="256"/>
+      <c r="G123" s="256"/>
+      <c r="H123" s="256"/>
+      <c r="I123" s="256"/>
+      <c r="J123" s="256"/>
+      <c r="K123" s="256"/>
+      <c r="L123" s="256"/>
+      <c r="M123" s="256"/>
+    </row>
+    <row r="124" spans="1:15" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B124" s="256"/>
+      <c r="C124" s="256"/>
+      <c r="D124" s="256"/>
+      <c r="E124" s="256"/>
+      <c r="F124" s="256"/>
+      <c r="G124" s="256"/>
+      <c r="H124" s="256"/>
+      <c r="I124" s="256"/>
+      <c r="J124" s="256"/>
+      <c r="K124" s="256"/>
+      <c r="L124" s="256"/>
+      <c r="M124" s="256"/>
+    </row>
+    <row r="125" spans="1:15" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B125" s="256"/>
+      <c r="C125" s="256"/>
+      <c r="D125" s="256"/>
+      <c r="E125" s="256"/>
+      <c r="F125" s="256"/>
+      <c r="G125" s="256"/>
+      <c r="H125" s="256"/>
+      <c r="I125" s="256"/>
+      <c r="J125" s="256"/>
+      <c r="K125" s="256"/>
+      <c r="L125" s="256"/>
+      <c r="M125" s="256"/>
+    </row>
+    <row r="126" spans="1:15" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B126" s="256"/>
+      <c r="C126" s="256"/>
+      <c r="D126" s="256"/>
+      <c r="E126" s="256"/>
+      <c r="F126" s="256"/>
+      <c r="G126" s="256"/>
+      <c r="H126" s="256"/>
+      <c r="I126" s="256"/>
+      <c r="J126" s="256"/>
+      <c r="K126" s="256"/>
+      <c r="L126" s="256"/>
+      <c r="M126" s="256"/>
+    </row>
+    <row r="127" spans="1:15" ht="67.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B127" s="256"/>
+      <c r="C127" s="256"/>
+      <c r="D127" s="256"/>
+      <c r="E127" s="256"/>
+      <c r="F127" s="256"/>
+      <c r="G127" s="256"/>
+      <c r="H127" s="256"/>
+      <c r="I127" s="256"/>
+      <c r="J127" s="256"/>
+      <c r="K127" s="256"/>
+      <c r="L127" s="256"/>
+      <c r="M127" s="256"/>
     </row>
   </sheetData>
   <mergeCells count="21">
-    <mergeCell ref="K13:K14"/>
-    <mergeCell ref="L13:L14"/>
-    <mergeCell ref="J13:J14"/>
-    <mergeCell ref="A10:N10"/>
-    <mergeCell ref="A11:N11"/>
-    <mergeCell ref="N13:N14"/>
     <mergeCell ref="B122:M127"/>
     <mergeCell ref="D1:M1"/>
     <mergeCell ref="A4:N8"/>
@@ -9658,6 +9552,12 @@
     <mergeCell ref="A12:N12"/>
     <mergeCell ref="E2:F2"/>
     <mergeCell ref="I13:I14"/>
+    <mergeCell ref="K13:K14"/>
+    <mergeCell ref="L13:L14"/>
+    <mergeCell ref="J13:J14"/>
+    <mergeCell ref="A10:N10"/>
+    <mergeCell ref="A11:N11"/>
+    <mergeCell ref="N13:N14"/>
   </mergeCells>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="3" scale="80" orientation="portrait" r:id="rId1"/>
@@ -9666,17 +9566,17 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{56D35F41-74CB-4294-A7A2-EC3C67574818}">
-  <dimension ref="C3:M41"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="C3:N9"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="3" max="3" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.6640625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="13" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="3:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="3:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C3" s="19"/>
     </row>
-    <row r="4" spans="3:13" ht="13.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="3:14" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C4" s="173" t="s">
         <v>193</v>
       </c>
@@ -9692,7 +9592,7 @@
       <c r="K4" s="19"/>
       <c r="L4" s="19"/>
     </row>
-    <row r="5" spans="3:13" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="3:14" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C5" s="175" t="s">
         <v>194</v>
       </c>
@@ -9704,11 +9604,12 @@
         <v>196</v>
       </c>
       <c r="J5" s="172"/>
-      <c r="K5" s="205"/>
-      <c r="L5" s="205"/>
-      <c r="M5" s="205"/>
-    </row>
-    <row r="6" spans="3:13" x14ac:dyDescent="0.25">
+      <c r="K5" s="19"/>
+      <c r="L5" s="19"/>
+      <c r="M5" s="19"/>
+      <c r="N5" s="19"/>
+    </row>
+    <row r="6" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C6" s="175" t="s">
         <v>197</v>
       </c>
@@ -9721,390 +9622,58 @@
       <c r="G6" t="s">
         <v>128</v>
       </c>
-      <c r="H6" t="s">
-        <v>201</v>
+      <c r="H6">
+        <v>46</v>
       </c>
       <c r="J6" s="172"/>
-      <c r="K6" s="205"/>
-      <c r="L6" s="205"/>
-      <c r="M6" s="205"/>
-    </row>
-    <row r="7" spans="3:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K6" s="19"/>
+      <c r="L6" s="19"/>
+      <c r="M6" s="19"/>
+      <c r="N6" s="19"/>
+    </row>
+    <row r="7" spans="3:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C7" s="47" t="s">
         <v>200</v>
       </c>
       <c r="J7" s="172"/>
-      <c r="K7" s="205"/>
-      <c r="L7" s="205"/>
-      <c r="M7" s="205"/>
-    </row>
-    <row r="8" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C8" s="260" t="s">
-        <v>213</v>
-      </c>
-      <c r="D8" s="261"/>
-      <c r="E8" s="261"/>
-      <c r="F8" s="261"/>
-      <c r="G8" s="261"/>
-      <c r="H8" s="261"/>
-      <c r="I8" s="261"/>
-      <c r="J8" s="262"/>
-      <c r="K8" s="205"/>
-      <c r="L8" s="205"/>
-      <c r="M8" s="205"/>
-    </row>
-    <row r="9" spans="3:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C9" s="263"/>
-      <c r="D9" s="264"/>
-      <c r="E9" s="264"/>
-      <c r="F9" s="264"/>
-      <c r="G9" s="264"/>
-      <c r="H9" s="264"/>
-      <c r="I9" s="264"/>
-      <c r="J9" s="265"/>
-    </row>
-    <row r="11" spans="3:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="12" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C12" s="188" t="s">
-        <v>193</v>
-      </c>
-      <c r="D12" s="189">
-        <v>1</v>
-      </c>
-      <c r="E12" s="170"/>
-      <c r="F12" s="170"/>
-      <c r="G12" s="170"/>
-      <c r="H12" s="170"/>
-      <c r="I12" s="170"/>
-      <c r="J12" s="171"/>
-    </row>
-    <row r="13" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C13" s="190" t="s">
-        <v>194</v>
-      </c>
-      <c r="D13" s="191"/>
-      <c r="E13" t="s">
-        <v>195</v>
-      </c>
-      <c r="G13" t="s">
-        <v>196</v>
-      </c>
-      <c r="J13" s="172"/>
-      <c r="K13" s="205"/>
-      <c r="L13" s="205"/>
-    </row>
-    <row r="14" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C14" s="190" t="s">
-        <v>197</v>
-      </c>
-      <c r="D14" s="191" t="s">
-        <v>198</v>
-      </c>
-      <c r="E14" t="s">
-        <v>199</v>
-      </c>
-      <c r="G14" t="s">
-        <v>128</v>
-      </c>
-      <c r="H14" t="s">
-        <v>214</v>
-      </c>
-      <c r="J14" s="172"/>
-      <c r="K14" s="205"/>
-      <c r="L14" s="205"/>
-    </row>
-    <row r="15" spans="3:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C15" s="47" t="s">
-        <v>200</v>
-      </c>
-      <c r="J15" s="172"/>
-      <c r="K15" s="205"/>
-      <c r="L15" s="205"/>
-    </row>
-    <row r="16" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C16" s="260" t="s">
-        <v>215</v>
-      </c>
-      <c r="D16" s="261"/>
-      <c r="E16" s="261"/>
-      <c r="F16" s="261"/>
-      <c r="G16" s="261"/>
-      <c r="H16" s="261"/>
-      <c r="I16" s="261"/>
-      <c r="J16" s="262"/>
-      <c r="K16" s="205"/>
-      <c r="L16" s="205"/>
-    </row>
-    <row r="17" spans="3:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C17" s="263"/>
-      <c r="D17" s="264"/>
-      <c r="E17" s="264"/>
-      <c r="F17" s="264"/>
-      <c r="G17" s="264"/>
-      <c r="H17" s="264"/>
-      <c r="I17" s="264"/>
-      <c r="J17" s="265"/>
-    </row>
-    <row r="19" spans="3:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="20" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C20" s="192" t="s">
-        <v>193</v>
-      </c>
-      <c r="D20" s="193">
-        <v>1</v>
-      </c>
-      <c r="E20" s="170"/>
-      <c r="F20" s="170"/>
-      <c r="G20" s="170"/>
-      <c r="H20" s="170"/>
-      <c r="I20" s="170"/>
-      <c r="J20" s="171"/>
-    </row>
-    <row r="21" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C21" s="194" t="s">
-        <v>194</v>
-      </c>
-      <c r="D21" s="195"/>
-      <c r="E21" t="s">
-        <v>195</v>
-      </c>
-      <c r="G21" t="s">
-        <v>196</v>
-      </c>
-      <c r="J21" s="172"/>
-      <c r="K21" s="205"/>
-      <c r="L21" s="205"/>
-    </row>
-    <row r="22" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C22" s="194" t="s">
-        <v>197</v>
-      </c>
-      <c r="D22" s="195" t="s">
-        <v>198</v>
-      </c>
-      <c r="E22" t="s">
-        <v>199</v>
-      </c>
-      <c r="G22" t="s">
-        <v>128</v>
-      </c>
-      <c r="H22" t="s">
-        <v>216</v>
-      </c>
-      <c r="J22" s="172"/>
-      <c r="K22" s="205"/>
-      <c r="L22" s="205"/>
-    </row>
-    <row r="23" spans="3:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C23" s="47" t="s">
-        <v>200</v>
-      </c>
-      <c r="J23" s="172"/>
-      <c r="K23" s="205"/>
-      <c r="L23" s="205"/>
-    </row>
-    <row r="24" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C24" s="260" t="s">
-        <v>217</v>
-      </c>
-      <c r="D24" s="261"/>
-      <c r="E24" s="261"/>
-      <c r="F24" s="261"/>
-      <c r="G24" s="261"/>
-      <c r="H24" s="261"/>
-      <c r="I24" s="261"/>
-      <c r="J24" s="262"/>
-      <c r="K24" s="205"/>
-      <c r="L24" s="205"/>
-    </row>
-    <row r="25" spans="3:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C25" s="263"/>
-      <c r="D25" s="264"/>
-      <c r="E25" s="264"/>
-      <c r="F25" s="264"/>
-      <c r="G25" s="264"/>
-      <c r="H25" s="264"/>
-      <c r="I25" s="264"/>
-      <c r="J25" s="265"/>
-    </row>
-    <row r="27" spans="3:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="28" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C28" s="198" t="s">
-        <v>193</v>
-      </c>
-      <c r="D28" s="199">
-        <v>1</v>
-      </c>
-      <c r="E28" s="170"/>
-      <c r="F28" s="170"/>
-      <c r="G28" s="170"/>
-      <c r="H28" s="170"/>
-      <c r="I28" s="170"/>
-      <c r="J28" s="171"/>
-    </row>
-    <row r="29" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C29" s="200" t="s">
-        <v>194</v>
-      </c>
-      <c r="D29" s="201"/>
-      <c r="E29" t="s">
-        <v>195</v>
-      </c>
-      <c r="G29" t="s">
-        <v>196</v>
-      </c>
-      <c r="J29" s="172"/>
-      <c r="K29" s="205"/>
-      <c r="L29" s="205"/>
-      <c r="M29" s="205"/>
-    </row>
-    <row r="30" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C30" s="200" t="s">
-        <v>197</v>
-      </c>
-      <c r="D30" s="201" t="s">
-        <v>198</v>
-      </c>
-      <c r="E30" t="s">
-        <v>199</v>
-      </c>
-      <c r="G30" t="s">
-        <v>128</v>
-      </c>
-      <c r="H30" t="s">
-        <v>218</v>
-      </c>
-      <c r="J30" s="172"/>
-      <c r="K30" s="205"/>
-      <c r="L30" s="205"/>
-      <c r="M30" s="205"/>
-    </row>
-    <row r="31" spans="3:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C31" s="47" t="s">
-        <v>200</v>
-      </c>
-      <c r="J31" s="172"/>
-      <c r="K31" s="205"/>
-      <c r="L31" s="205"/>
-      <c r="M31" s="205"/>
-    </row>
-    <row r="32" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C32" s="260" t="s">
-        <v>219</v>
-      </c>
-      <c r="D32" s="261"/>
-      <c r="E32" s="261"/>
-      <c r="F32" s="261"/>
-      <c r="G32" s="261"/>
-      <c r="H32" s="261"/>
-      <c r="I32" s="261"/>
-      <c r="J32" s="262"/>
-      <c r="K32" s="205"/>
-      <c r="L32" s="205"/>
-      <c r="M32" s="205"/>
-    </row>
-    <row r="33" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C33" s="263"/>
-      <c r="D33" s="264"/>
-      <c r="E33" s="264"/>
-      <c r="F33" s="264"/>
-      <c r="G33" s="264"/>
-      <c r="H33" s="264"/>
-      <c r="I33" s="264"/>
-      <c r="J33" s="265"/>
-    </row>
-    <row r="35" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="36" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C36" s="202" t="s">
-        <v>193</v>
-      </c>
-      <c r="D36" s="203">
-        <v>1</v>
-      </c>
-      <c r="E36" s="170"/>
-      <c r="F36" s="170"/>
-      <c r="G36" s="170"/>
-      <c r="H36" s="170"/>
-      <c r="I36" s="170"/>
-      <c r="J36" s="171"/>
-    </row>
-    <row r="37" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C37" s="204" t="s">
-        <v>194</v>
-      </c>
-      <c r="D37" s="205"/>
-      <c r="E37" t="s">
-        <v>195</v>
-      </c>
-      <c r="G37" t="s">
-        <v>196</v>
-      </c>
-      <c r="H37" t="s">
-        <v>220</v>
-      </c>
-      <c r="J37" s="172"/>
-      <c r="K37" s="205"/>
-      <c r="L37" s="205"/>
-    </row>
-    <row r="38" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C38" s="204" t="s">
-        <v>197</v>
-      </c>
-      <c r="D38" s="205" t="s">
-        <v>198</v>
-      </c>
-      <c r="E38" t="s">
-        <v>199</v>
-      </c>
-      <c r="G38" t="s">
-        <v>128</v>
-      </c>
-      <c r="H38" t="s">
-        <v>222</v>
-      </c>
-      <c r="J38" s="172"/>
-      <c r="K38" s="205"/>
-      <c r="L38" s="205"/>
-    </row>
-    <row r="39" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C39" s="47" t="s">
-        <v>200</v>
-      </c>
-      <c r="J39" s="172"/>
-      <c r="K39" s="205"/>
-      <c r="L39" s="205"/>
-    </row>
-    <row r="40" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C40" s="260" t="s">
-        <v>221</v>
-      </c>
-      <c r="D40" s="261"/>
-      <c r="E40" s="261"/>
-      <c r="F40" s="261"/>
-      <c r="G40" s="261"/>
-      <c r="H40" s="261"/>
-      <c r="I40" s="261"/>
-      <c r="J40" s="262"/>
-      <c r="K40" s="205"/>
-      <c r="L40" s="205"/>
-    </row>
-    <row r="41" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C41" s="263"/>
-      <c r="D41" s="264"/>
-      <c r="E41" s="264"/>
-      <c r="F41" s="264"/>
-      <c r="G41" s="264"/>
-      <c r="H41" s="264"/>
-      <c r="I41" s="264"/>
-      <c r="J41" s="265"/>
+      <c r="K7" s="19"/>
+      <c r="L7" s="19"/>
+      <c r="M7" s="19"/>
+      <c r="N7" s="19"/>
+    </row>
+    <row r="8" spans="3:14" x14ac:dyDescent="0.3">
+      <c r="C8" s="280" t="s">
+        <v>265</v>
+      </c>
+      <c r="D8" s="281"/>
+      <c r="E8" s="281"/>
+      <c r="F8" s="281"/>
+      <c r="G8" s="281"/>
+      <c r="H8" s="281"/>
+      <c r="I8" s="281"/>
+      <c r="J8" s="282"/>
+      <c r="K8" s="19"/>
+      <c r="L8" s="19"/>
+      <c r="M8" s="19"/>
+      <c r="N8" s="19"/>
+    </row>
+    <row r="9" spans="3:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C9" s="283"/>
+      <c r="D9" s="284"/>
+      <c r="E9" s="284"/>
+      <c r="F9" s="284"/>
+      <c r="G9" s="284"/>
+      <c r="H9" s="284"/>
+      <c r="I9" s="284"/>
+      <c r="J9" s="285"/>
+      <c r="K9" s="19"/>
+      <c r="L9" s="19"/>
+      <c r="M9" s="19"/>
+      <c r="N9" s="19"/>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="1">
     <mergeCell ref="C8:J9"/>
-    <mergeCell ref="C16:J17"/>
-    <mergeCell ref="C24:J25"/>
-    <mergeCell ref="C32:J33"/>
-    <mergeCell ref="C40:J41"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/2026/ITALIA/Junio/Junio ITALIA.xlsx
+++ b/2026/ITALIA/Junio/Junio ITALIA.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\2026\ITALIA\Junio\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistemax\Desktop\rc-consorcio2025\2026\ITALIA\Junio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80F98B45-C46E-4D13-83CC-F62569811E89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{199E7320-D09D-42A3-AFD2-CB43BBE00682}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="4" r:id="rId1"/>
@@ -22,6 +22,11 @@
     <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$E$140</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
+  <extLst>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -1960,198 +1965,198 @@
     <xf numFmtId="167" fontId="16" fillId="15" borderId="23" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="17" fillId="15" borderId="24" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="17" fillId="15" borderId="31" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="44" fontId="10" fillId="2" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="10" fillId="2" borderId="19" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="19" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="15" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="15" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="15" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="12" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="12" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="16" fillId="14" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="16" fillId="14" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="44" fontId="10" fillId="2" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="10" fillId="2" borderId="19" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="19" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="15" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="15" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="15" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -2237,9 +2242,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -2277,9 +2282,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -2312,9 +2317,26 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -2347,9 +2369,26 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -2524,31 +2563,31 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E413A25D-5161-4141-BE0B-6E37A2A76CA5}">
   <dimension ref="A1:M141"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="37.5546875" customWidth="1"/>
-    <col min="2" max="2" width="24.6640625" customWidth="1"/>
-    <col min="3" max="3" width="15.88671875" hidden="1" customWidth="1"/>
-    <col min="4" max="4" width="21.6640625" customWidth="1"/>
-    <col min="5" max="5" width="16.6640625" customWidth="1"/>
-    <col min="6" max="6" width="15.5546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="37.5703125" customWidth="1"/>
+    <col min="2" max="2" width="24.7109375" customWidth="1"/>
+    <col min="3" max="3" width="15.85546875" hidden="1" customWidth="1"/>
+    <col min="4" max="4" width="21.7109375" customWidth="1"/>
+    <col min="5" max="5" width="16.7109375" customWidth="1"/>
+    <col min="6" max="6" width="15.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5703125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="12" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="22.6640625" customWidth="1"/>
+    <col min="10" max="10" width="22.7109375" customWidth="1"/>
     <col min="11" max="11" width="18" customWidth="1"/>
-    <col min="12" max="12" width="18.33203125" customWidth="1"/>
+    <col min="12" max="12" width="18.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1"/>
-      <c r="B1" s="225" t="s">
+      <c r="B1" s="234" t="s">
         <v>146</v>
       </c>
-      <c r="C1" s="225"/>
-      <c r="D1" s="225"/>
-      <c r="E1" s="226"/>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="C1" s="234"/>
+      <c r="D1" s="234"/>
+      <c r="E1" s="235"/>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="2"/>
       <c r="B2" s="9" t="s">
         <v>148</v>
@@ -2557,16 +2596,16 @@
       <c r="D2" s="3"/>
       <c r="E2" s="4"/>
     </row>
-    <row r="3" spans="1:5" ht="51.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:5" ht="51.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="2"/>
-      <c r="B3" s="231" t="s">
+      <c r="B3" s="238" t="s">
         <v>191</v>
       </c>
-      <c r="C3" s="231"/>
-      <c r="D3" s="231"/>
-      <c r="E3" s="232"/>
-    </row>
-    <row r="4" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C3" s="238"/>
+      <c r="D3" s="238"/>
+      <c r="E3" s="239"/>
+    </row>
+    <row r="4" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="5" t="s">
         <v>100</v>
       </c>
@@ -2577,7 +2616,7 @@
       <c r="D4" s="7"/>
       <c r="E4" s="8"/>
     </row>
-    <row r="5" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
         <v>147</v>
       </c>
@@ -2590,7 +2629,7 @@
       </c>
       <c r="E5" s="10"/>
     </row>
-    <row r="6" spans="1:5" ht="16.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:5" ht="16.149999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="90" t="s">
         <v>137</v>
       </c>
@@ -2601,95 +2640,95 @@
       </c>
       <c r="E6" s="8"/>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="48"/>
-      <c r="B8" s="233" t="s">
+      <c r="B8" s="240" t="s">
         <v>213</v>
       </c>
-      <c r="C8" s="233"/>
+      <c r="C8" s="240"/>
       <c r="D8" s="48"/>
       <c r="E8" s="48"/>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="48"/>
-      <c r="B9" s="233"/>
-      <c r="C9" s="233"/>
+      <c r="B9" s="240"/>
+      <c r="C9" s="240"/>
       <c r="D9" s="48"/>
       <c r="E9" s="48"/>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="48"/>
-      <c r="B10" s="233"/>
-      <c r="C10" s="233"/>
+      <c r="B10" s="240"/>
+      <c r="C10" s="240"/>
       <c r="D10" s="48"/>
       <c r="E10" s="48"/>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="48"/>
       <c r="B11" s="48"/>
       <c r="C11" s="48"/>
       <c r="D11" s="48"/>
       <c r="E11" s="48"/>
     </row>
-    <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A12" s="48"/>
       <c r="B12" s="48"/>
       <c r="C12" s="48"/>
       <c r="D12" s="48"/>
       <c r="E12" s="48"/>
     </row>
-    <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="234" t="s">
+    <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="241" t="s">
         <v>103</v>
       </c>
-      <c r="B13" s="234"/>
-      <c r="C13" s="234"/>
-      <c r="D13" s="234"/>
-      <c r="E13" s="234"/>
-    </row>
-    <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="234"/>
-      <c r="B14" s="234"/>
-      <c r="C14" s="234"/>
-      <c r="D14" s="234"/>
-      <c r="E14" s="234"/>
-    </row>
-    <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="234"/>
-      <c r="B15" s="234"/>
-      <c r="C15" s="234"/>
-      <c r="D15" s="234"/>
-      <c r="E15" s="234"/>
-    </row>
-    <row r="16" spans="1:5" ht="53.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="234"/>
-      <c r="B16" s="234"/>
-      <c r="C16" s="234"/>
-      <c r="D16" s="234"/>
-      <c r="E16" s="234"/>
-    </row>
-    <row r="17" spans="1:8" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B13" s="241"/>
+      <c r="C13" s="241"/>
+      <c r="D13" s="241"/>
+      <c r="E13" s="241"/>
+    </row>
+    <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="241"/>
+      <c r="B14" s="241"/>
+      <c r="C14" s="241"/>
+      <c r="D14" s="241"/>
+      <c r="E14" s="241"/>
+    </row>
+    <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="241"/>
+      <c r="B15" s="241"/>
+      <c r="C15" s="241"/>
+      <c r="D15" s="241"/>
+      <c r="E15" s="241"/>
+    </row>
+    <row r="16" spans="1:5" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="241"/>
+      <c r="B16" s="241"/>
+      <c r="C16" s="241"/>
+      <c r="D16" s="241"/>
+      <c r="E16" s="241"/>
+    </row>
+    <row r="17" spans="1:8" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" s="48"/>
       <c r="B17" s="48"/>
       <c r="C17" s="48"/>
       <c r="D17" s="48"/>
       <c r="E17" s="48"/>
     </row>
-    <row r="18" spans="1:8" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:8" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="178"/>
       <c r="B18" s="48"/>
       <c r="C18" s="48"/>
       <c r="D18" s="48"/>
       <c r="E18" s="48"/>
     </row>
-    <row r="19" spans="1:8" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:8" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="48"/>
       <c r="B19" s="48"/>
       <c r="C19" s="48"/>
       <c r="D19" s="48"/>
       <c r="E19" s="48"/>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" s="179" t="s">
         <v>104</v>
       </c>
@@ -2698,7 +2737,7 @@
       <c r="D20" s="58"/>
       <c r="E20" s="59"/>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="36" t="s">
         <v>138</v>
       </c>
@@ -2707,11 +2746,11 @@
       <c r="D21" s="117"/>
       <c r="E21" s="152"/>
     </row>
-    <row r="22" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="227" t="s">
+    <row r="22" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="236" t="s">
         <v>163</v>
       </c>
-      <c r="B22" s="228"/>
+      <c r="B22" s="237"/>
       <c r="C22" s="182"/>
       <c r="D22" s="183">
         <v>3382992.69</v>
@@ -2721,11 +2760,11 @@
       </c>
       <c r="H22" s="19"/>
     </row>
-    <row r="23" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="227" t="s">
+    <row r="23" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="236" t="s">
         <v>164</v>
       </c>
-      <c r="B23" s="228"/>
+      <c r="B23" s="237"/>
       <c r="C23" s="182"/>
       <c r="D23" s="183">
         <v>-735800.92</v>
@@ -2733,11 +2772,11 @@
       <c r="E23" s="20"/>
       <c r="H23" s="19"/>
     </row>
-    <row r="24" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="227" t="s">
+    <row r="24" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="236" t="s">
         <v>1</v>
       </c>
-      <c r="B24" s="228"/>
+      <c r="B24" s="237"/>
       <c r="C24" s="182"/>
       <c r="D24" s="184">
         <v>0.23</v>
@@ -2745,7 +2784,7 @@
       <c r="E24" s="20"/>
       <c r="H24" s="19"/>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" s="185" t="s">
         <v>105</v>
       </c>
@@ -2757,7 +2796,7 @@
         <v>2647192</v>
       </c>
     </row>
-    <row r="26" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A26" s="185" t="s">
         <v>178</v>
       </c>
@@ -2766,21 +2805,21 @@
       <c r="D26" s="22"/>
       <c r="E26" s="155"/>
     </row>
-    <row r="27" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27" s="182"/>
       <c r="B27" s="182"/>
       <c r="C27" s="182"/>
       <c r="D27" s="35"/>
       <c r="E27" s="168"/>
     </row>
-    <row r="28" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A28" s="182"/>
       <c r="B28" s="182"/>
       <c r="C28" s="182"/>
       <c r="D28" s="35"/>
       <c r="E28" s="168"/>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" s="182" t="s">
         <v>238</v>
       </c>
@@ -2791,7 +2830,7 @@
       </c>
       <c r="E29" s="168"/>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" s="182" t="s">
         <v>241</v>
       </c>
@@ -2803,7 +2842,7 @@
       </c>
       <c r="E30" s="156"/>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" s="182" t="s">
         <v>242</v>
       </c>
@@ -2816,7 +2855,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" s="182" t="s">
         <v>243</v>
       </c>
@@ -2829,7 +2868,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" s="185" t="s">
         <v>105</v>
       </c>
@@ -2841,7 +2880,7 @@
         <v>581674</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" s="36" t="s">
         <v>139</v>
       </c>
@@ -2850,7 +2889,7 @@
       <c r="D34" s="22"/>
       <c r="E34" s="155"/>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" s="182" t="s">
         <v>189</v>
       </c>
@@ -2865,7 +2904,7 @@
       </c>
       <c r="G35" s="66"/>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" s="182" t="s">
         <v>150</v>
       </c>
@@ -2879,7 +2918,7 @@
       </c>
       <c r="G36" s="66"/>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" s="182" t="s">
         <v>141</v>
       </c>
@@ -2893,7 +2932,7 @@
       </c>
       <c r="G37" s="66"/>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" s="182" t="s">
         <v>143</v>
       </c>
@@ -2908,7 +2947,7 @@
       </c>
       <c r="G38" s="50"/>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" s="182" t="s">
         <v>142</v>
       </c>
@@ -2922,7 +2961,7 @@
         <v>Debito 12/06</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" s="182" t="s">
         <v>151</v>
       </c>
@@ -2931,7 +2970,7 @@
       <c r="D40" s="35"/>
       <c r="E40" s="156"/>
     </row>
-    <row r="41" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="185" t="s">
         <v>140</v>
       </c>
@@ -2943,7 +2982,7 @@
         <v>1221482.76</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42" s="14" t="s">
         <v>106</v>
       </c>
@@ -2952,11 +2991,11 @@
       <c r="D42" s="23"/>
       <c r="E42" s="157"/>
     </row>
-    <row r="43" spans="1:7" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="235" t="s">
+    <row r="43" spans="1:7" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="232" t="s">
         <v>185</v>
       </c>
-      <c r="B43" s="236"/>
+      <c r="B43" s="233"/>
       <c r="C43" s="26"/>
       <c r="D43" s="195">
         <v>7805</v>
@@ -2965,11 +3004,11 @@
         <v>186</v>
       </c>
     </row>
-    <row r="44" spans="1:7" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="235" t="s">
+    <row r="44" spans="1:7" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="232" t="s">
         <v>187</v>
       </c>
-      <c r="B44" s="236"/>
+      <c r="B44" s="233"/>
       <c r="C44" s="26"/>
       <c r="D44" s="195">
         <v>214164</v>
@@ -2978,7 +3017,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" s="21" t="s">
         <v>107</v>
       </c>
@@ -2990,7 +3029,7 @@
         <v>221969</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" s="14" t="s">
         <v>108</v>
       </c>
@@ -2999,7 +3038,7 @@
       <c r="D46" s="28"/>
       <c r="E46" s="158"/>
     </row>
-    <row r="47" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="29" t="s">
         <v>109</v>
       </c>
@@ -3012,7 +3051,7 @@
       </c>
       <c r="E47" s="198"/>
     </row>
-    <row r="48" spans="1:7" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:7" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="29" t="s">
         <v>109</v>
       </c>
@@ -3027,7 +3066,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="49" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="29" t="s">
         <v>179</v>
       </c>
@@ -3040,7 +3079,7 @@
       </c>
       <c r="E49" s="20"/>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" s="29" t="s">
         <v>180</v>
       </c>
@@ -3051,11 +3090,11 @@
       </c>
       <c r="E50" s="20"/>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A51" s="235" t="s">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A51" s="232" t="s">
         <v>110</v>
       </c>
-      <c r="B51" s="236"/>
+      <c r="B51" s="233"/>
       <c r="C51" s="29"/>
       <c r="D51" s="30">
         <v>0</v>
@@ -3064,7 +3103,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" s="32" t="s">
         <v>111</v>
       </c>
@@ -3073,7 +3112,7 @@
       <c r="D52" s="30"/>
       <c r="E52" s="20"/>
     </row>
-    <row r="53" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A53" s="21" t="s">
         <v>112</v>
       </c>
@@ -3085,18 +3124,18 @@
         <v>16378.19</v>
       </c>
     </row>
-    <row r="54" spans="1:6" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:6" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A54" s="14"/>
       <c r="B54" s="21"/>
       <c r="C54" s="21"/>
       <c r="D54" s="22"/>
       <c r="E54" s="160"/>
     </row>
-    <row r="55" spans="1:6" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A55" s="229" t="s">
+    <row r="55" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A55" s="225" t="s">
         <v>166</v>
       </c>
-      <c r="B55" s="230"/>
+      <c r="B55" s="226"/>
       <c r="C55" s="29"/>
       <c r="D55" s="192">
         <v>285000</v>
@@ -3105,11 +3144,11 @@
         <v>232</v>
       </c>
     </row>
-    <row r="56" spans="1:6" ht="33" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="229" t="s">
+    <row r="56" spans="1:6" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A56" s="225" t="s">
         <v>239</v>
       </c>
-      <c r="B56" s="230"/>
+      <c r="B56" s="226"/>
       <c r="C56" s="29"/>
       <c r="D56" s="192">
         <f>660000+1400000</f>
@@ -3119,11 +3158,11 @@
         <v>246</v>
       </c>
     </row>
-    <row r="57" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A57" s="229" t="s">
+    <row r="57" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A57" s="225" t="s">
         <v>245</v>
       </c>
-      <c r="B57" s="230"/>
+      <c r="B57" s="226"/>
       <c r="C57" s="29"/>
       <c r="D57" s="192">
         <f>2800000+1400000</f>
@@ -3134,7 +3173,7 @@
       </c>
       <c r="F57" s="50"/>
     </row>
-    <row r="58" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="92" t="s">
         <v>240</v>
       </c>
@@ -3148,7 +3187,7 @@
       </c>
       <c r="F58" s="50"/>
     </row>
-    <row r="59" spans="1:6" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:6" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="16" t="s">
         <v>233</v>
       </c>
@@ -3162,7 +3201,7 @@
       </c>
       <c r="F59" s="50"/>
     </row>
-    <row r="60" spans="1:6" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:6" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="16" t="s">
         <v>261</v>
       </c>
@@ -3174,11 +3213,11 @@
       <c r="E60" s="34"/>
       <c r="F60" s="50"/>
     </row>
-    <row r="61" spans="1:6" ht="35.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A61" s="229" t="s">
+    <row r="61" spans="1:6" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A61" s="225" t="s">
         <v>219</v>
       </c>
-      <c r="B61" s="230"/>
+      <c r="B61" s="226"/>
       <c r="C61" s="29"/>
       <c r="D61" s="192">
         <v>342000</v>
@@ -3188,7 +3227,7 @@
       </c>
       <c r="F61" s="50"/>
     </row>
-    <row r="62" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="92" t="s">
         <v>224</v>
       </c>
@@ -3202,7 +3241,7 @@
       </c>
       <c r="F62" s="50"/>
     </row>
-    <row r="63" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="92" t="s">
         <v>225</v>
       </c>
@@ -3216,7 +3255,7 @@
       </c>
       <c r="F63" s="50"/>
     </row>
-    <row r="64" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="92" t="s">
         <v>227</v>
       </c>
@@ -3230,7 +3269,7 @@
       </c>
       <c r="F64" s="50"/>
     </row>
-    <row r="65" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="92" t="s">
         <v>228</v>
       </c>
@@ -3244,7 +3283,7 @@
       </c>
       <c r="F65" s="50"/>
     </row>
-    <row r="66" spans="1:6" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="92" t="s">
         <v>215</v>
       </c>
@@ -3258,7 +3297,7 @@
       </c>
       <c r="F66" s="50"/>
     </row>
-    <row r="67" spans="1:6" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="92" t="s">
         <v>204</v>
       </c>
@@ -3272,7 +3311,7 @@
       </c>
       <c r="F67" s="50"/>
     </row>
-    <row r="68" spans="1:6" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="92" t="s">
         <v>204</v>
       </c>
@@ -3286,7 +3325,7 @@
       </c>
       <c r="F68" s="50"/>
     </row>
-    <row r="69" spans="1:6" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="92" t="s">
         <v>204</v>
       </c>
@@ -3300,11 +3339,11 @@
       </c>
       <c r="F69" s="50"/>
     </row>
-    <row r="70" spans="1:6" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A70" s="229" t="s">
+    <row r="70" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A70" s="225" t="s">
         <v>229</v>
       </c>
-      <c r="B70" s="230"/>
+      <c r="B70" s="226"/>
       <c r="C70" s="29"/>
       <c r="D70" s="192">
         <v>25000</v>
@@ -3314,11 +3353,11 @@
       </c>
       <c r="F70" s="50"/>
     </row>
-    <row r="71" spans="1:6" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A71" s="229" t="s">
+    <row r="71" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A71" s="225" t="s">
         <v>216</v>
       </c>
-      <c r="B71" s="230"/>
+      <c r="B71" s="226"/>
       <c r="C71" s="29"/>
       <c r="D71" s="30">
         <v>0</v>
@@ -3328,7 +3367,7 @@
       </c>
       <c r="F71" s="50"/>
     </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" s="21" t="s">
         <v>0</v>
       </c>
@@ -3340,7 +3379,7 @@
         <v>8534240</v>
       </c>
     </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" s="14" t="s">
         <v>113</v>
       </c>
@@ -3349,11 +3388,11 @@
       <c r="D73" s="15"/>
       <c r="E73" s="152"/>
     </row>
-    <row r="74" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A74" s="229" t="s">
+    <row r="74" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A74" s="225" t="s">
         <v>217</v>
       </c>
-      <c r="B74" s="230"/>
+      <c r="B74" s="226"/>
       <c r="C74" s="18"/>
       <c r="D74" s="196">
         <v>650000</v>
@@ -3362,7 +3401,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="75" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="16" t="s">
         <v>165</v>
       </c>
@@ -3375,7 +3414,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="76" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="92" t="s">
         <v>248</v>
       </c>
@@ -3388,7 +3427,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="77" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="92" t="s">
         <v>234</v>
       </c>
@@ -3401,7 +3440,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="78" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="92" t="s">
         <v>218</v>
       </c>
@@ -3414,7 +3453,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" s="21" t="s">
         <v>105</v>
       </c>
@@ -3426,7 +3465,7 @@
         <v>1145000</v>
       </c>
     </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" s="14" t="s">
         <v>114</v>
       </c>
@@ -3435,7 +3474,7 @@
       <c r="D80" s="38"/>
       <c r="E80" s="41"/>
     </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A81" s="29" t="s">
         <v>149</v>
       </c>
@@ -3446,11 +3485,11 @@
       </c>
       <c r="E81" s="161"/>
     </row>
-    <row r="82" spans="1:8" ht="61.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A82" s="235" t="s">
+    <row r="82" spans="1:8" ht="61.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A82" s="232" t="s">
         <v>263</v>
       </c>
-      <c r="B82" s="236"/>
+      <c r="B82" s="233"/>
       <c r="C82" s="91"/>
       <c r="D82" s="197">
         <f>39523+201766.98</f>
@@ -3458,7 +3497,7 @@
       </c>
       <c r="E82" s="161"/>
     </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A83" s="39" t="s">
         <v>105</v>
       </c>
@@ -3470,14 +3509,14 @@
         <v>300289.98</v>
       </c>
     </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A84" s="29"/>
       <c r="B84" s="29"/>
       <c r="C84" s="29"/>
       <c r="D84" s="42"/>
       <c r="E84" s="43"/>
     </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A85" s="44" t="s">
         <v>115</v>
       </c>
@@ -3486,13 +3525,13 @@
       <c r="D85" s="45"/>
       <c r="E85" s="46"/>
     </row>
-    <row r="86" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A86" s="47"/>
       <c r="D86" s="48"/>
       <c r="E86" s="49"/>
       <c r="F86" s="50"/>
     </row>
-    <row r="87" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A87" s="51" t="s">
         <v>116</v>
       </c>
@@ -3506,16 +3545,16 @@
       <c r="F87" s="56"/>
       <c r="G87" s="50"/>
     </row>
-    <row r="88" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
       <c r="D88" s="48"/>
       <c r="E88" s="48"/>
     </row>
-    <row r="89" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="D89" s="48"/>
       <c r="E89" s="48"/>
       <c r="H89" s="57"/>
     </row>
-    <row r="90" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A90" s="11" t="s">
         <v>117</v>
       </c>
@@ -3524,34 +3563,34 @@
       <c r="D90" s="58"/>
       <c r="E90" s="59"/>
     </row>
-    <row r="91" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A91" s="237"/>
-      <c r="B91" s="237"/>
+    <row r="91" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A91" s="227"/>
+      <c r="B91" s="227"/>
       <c r="C91" s="31"/>
-      <c r="D91" s="238"/>
-      <c r="E91" s="240"/>
-    </row>
-    <row r="92" spans="1:8" ht="1.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A92" s="237"/>
-      <c r="B92" s="237"/>
+      <c r="D91" s="228"/>
+      <c r="E91" s="230"/>
+    </row>
+    <row r="92" spans="1:8" ht="1.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A92" s="227"/>
+      <c r="B92" s="227"/>
       <c r="C92" s="31"/>
-      <c r="D92" s="239"/>
-      <c r="E92" s="241"/>
-    </row>
-    <row r="93" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D92" s="229"/>
+      <c r="E92" s="231"/>
+    </row>
+    <row r="93" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="29"/>
       <c r="B93" s="29"/>
       <c r="D93" s="42"/>
       <c r="E93" s="42"/>
     </row>
-    <row r="94" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A94" s="24"/>
       <c r="B94" s="61"/>
       <c r="C94" s="29"/>
       <c r="D94" s="35"/>
       <c r="E94" s="60"/>
     </row>
-    <row r="95" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A95" s="62" t="s">
         <v>145</v>
       </c>
@@ -3563,15 +3602,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D96" s="48"/>
       <c r="E96" s="48"/>
     </row>
-    <row r="97" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="D97" s="48"/>
       <c r="E97" s="48"/>
     </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A98" s="44" t="s">
         <v>118</v>
       </c>
@@ -3582,11 +3621,11 @@
         <v>3000000</v>
       </c>
     </row>
-    <row r="99" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="D99" s="48"/>
       <c r="E99" s="48"/>
     </row>
-    <row r="100" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A100" s="51" t="s">
         <v>119</v>
       </c>
@@ -3598,11 +3637,11 @@
         <v>3000000</v>
       </c>
     </row>
-    <row r="101" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="D101" s="48"/>
       <c r="E101" s="48"/>
     </row>
-    <row r="102" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A102" s="64" t="s">
         <v>120</v>
       </c>
@@ -3613,7 +3652,7 @@
       <c r="D102" s="48"/>
       <c r="E102" s="48"/>
     </row>
-    <row r="103" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A103" s="64" t="s">
         <v>121</v>
       </c>
@@ -3624,7 +3663,7 @@
       <c r="D103" s="48"/>
       <c r="E103" s="48"/>
     </row>
-    <row r="104" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A104" s="64" t="s">
         <v>122</v>
       </c>
@@ -3635,7 +3674,7 @@
       <c r="D104" s="48"/>
       <c r="E104" s="48"/>
     </row>
-    <row r="105" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A105" s="64" t="s">
         <v>123</v>
       </c>
@@ -3646,142 +3685,142 @@
       <c r="D105" s="48"/>
       <c r="E105" s="48"/>
     </row>
-    <row r="106" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:5" x14ac:dyDescent="0.25">
       <c r="D106" s="48"/>
       <c r="E106" s="48"/>
     </row>
-    <row r="107" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:5" x14ac:dyDescent="0.25">
       <c r="D107" s="48"/>
       <c r="E107" s="48"/>
     </row>
-    <row r="108" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A108" s="224" t="s">
+    <row r="108" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A108" s="243" t="s">
         <v>174</v>
       </c>
-      <c r="B108" s="224"/>
+      <c r="B108" s="243"/>
       <c r="D108" s="48"/>
       <c r="E108" s="48"/>
     </row>
-    <row r="109" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A109" s="224"/>
-      <c r="B109" s="224"/>
+    <row r="109" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A109" s="243"/>
+      <c r="B109" s="243"/>
       <c r="D109" s="48"/>
       <c r="E109" s="48"/>
     </row>
-    <row r="110" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A110" s="224"/>
-      <c r="B110" s="224"/>
+    <row r="110" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A110" s="243"/>
+      <c r="B110" s="243"/>
       <c r="D110" s="48"/>
       <c r="E110" s="48"/>
     </row>
-    <row r="111" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:5" x14ac:dyDescent="0.25">
       <c r="D111" s="48"/>
       <c r="E111" s="48"/>
     </row>
-    <row r="112" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A112" s="224" t="s">
+    <row r="112" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A112" s="243" t="s">
         <v>202</v>
       </c>
-      <c r="B112" s="224"/>
+      <c r="B112" s="243"/>
       <c r="D112" s="48"/>
       <c r="E112" s="48"/>
     </row>
-    <row r="113" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A113" s="224"/>
-      <c r="B113" s="224"/>
+    <row r="113" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A113" s="243"/>
+      <c r="B113" s="243"/>
       <c r="D113" s="48"/>
       <c r="E113" s="48"/>
     </row>
-    <row r="114" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A114" s="224"/>
-      <c r="B114" s="224"/>
+    <row r="114" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A114" s="243"/>
+      <c r="B114" s="243"/>
       <c r="D114" s="48"/>
       <c r="E114" s="48"/>
     </row>
-    <row r="115" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D115" s="48"/>
       <c r="E115" s="48"/>
     </row>
-    <row r="116" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A116" s="224" t="s">
+    <row r="116" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A116" s="243" t="s">
         <v>181</v>
       </c>
-      <c r="B116" s="224"/>
+      <c r="B116" s="243"/>
       <c r="D116" s="48"/>
       <c r="E116" s="48"/>
     </row>
-    <row r="117" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A117" s="224"/>
-      <c r="B117" s="224"/>
+    <row r="117" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A117" s="243"/>
+      <c r="B117" s="243"/>
       <c r="D117" s="48"/>
       <c r="E117" s="48"/>
     </row>
-    <row r="118" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A118" s="224"/>
-      <c r="B118" s="224"/>
+    <row r="118" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A118" s="243"/>
+      <c r="B118" s="243"/>
       <c r="D118" s="48"/>
       <c r="E118" s="48"/>
     </row>
-    <row r="119" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D119" s="48"/>
       <c r="E119" s="48"/>
     </row>
-    <row r="120" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A120" s="224" t="s">
+    <row r="120" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A120" s="243" t="s">
         <v>184</v>
       </c>
-      <c r="B120" s="224"/>
+      <c r="B120" s="243"/>
       <c r="D120" s="48"/>
       <c r="E120" s="48"/>
     </row>
-    <row r="121" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A121" s="224"/>
-      <c r="B121" s="224"/>
+    <row r="121" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A121" s="243"/>
+      <c r="B121" s="243"/>
       <c r="D121" s="48"/>
       <c r="E121" s="48"/>
     </row>
-    <row r="122" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A122" s="224"/>
-      <c r="B122" s="224"/>
+    <row r="122" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A122" s="243"/>
+      <c r="B122" s="243"/>
       <c r="D122" s="48"/>
       <c r="E122" s="48"/>
     </row>
-    <row r="123" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D123" s="48"/>
       <c r="E123" s="48"/>
     </row>
-    <row r="124" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A124" s="224" t="s">
+    <row r="124" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A124" s="243" t="s">
         <v>183</v>
       </c>
-      <c r="B124" s="224"/>
+      <c r="B124" s="243"/>
       <c r="D124" s="48"/>
       <c r="E124" s="48"/>
     </row>
-    <row r="125" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A125" s="224"/>
-      <c r="B125" s="224"/>
+    <row r="125" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A125" s="243"/>
+      <c r="B125" s="243"/>
       <c r="D125" s="48"/>
       <c r="E125" s="48"/>
     </row>
-    <row r="126" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A126" s="224"/>
-      <c r="B126" s="224"/>
+    <row r="126" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A126" s="243"/>
+      <c r="B126" s="243"/>
       <c r="D126" s="48"/>
       <c r="E126" s="48"/>
     </row>
-    <row r="127" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:5" x14ac:dyDescent="0.25">
       <c r="D127" s="48"/>
       <c r="E127" s="48"/>
     </row>
-    <row r="128" spans="1:5" s="68" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:5" s="68" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A128"/>
       <c r="B128" s="66"/>
       <c r="C128" s="67"/>
       <c r="D128" s="163"/>
       <c r="E128" s="163"/>
     </row>
-    <row r="129" spans="1:13" s="68" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:13" s="68" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A129" s="169" t="s">
         <v>192</v>
       </c>
@@ -3792,7 +3831,7 @@
       <c r="D129" s="164"/>
       <c r="E129" s="164"/>
     </row>
-    <row r="130" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A130" s="26" t="s">
         <v>144</v>
       </c>
@@ -3803,7 +3842,7 @@
       <c r="D130" s="48"/>
       <c r="E130" s="48"/>
     </row>
-    <row r="131" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A131" s="26" t="s">
         <v>124</v>
       </c>
@@ -3815,7 +3854,7 @@
       <c r="E131" s="48"/>
       <c r="F131" s="66"/>
     </row>
-    <row r="132" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A132" s="26" t="s">
         <v>2</v>
       </c>
@@ -3827,7 +3866,7 @@
       <c r="E132" s="48"/>
       <c r="F132" s="66"/>
     </row>
-    <row r="133" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A133" s="26" t="s">
         <v>223</v>
       </c>
@@ -3838,7 +3877,7 @@
       <c r="E133" s="48"/>
       <c r="F133" s="66"/>
     </row>
-    <row r="134" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A134" s="72" t="s">
         <v>162</v>
       </c>
@@ -3850,20 +3889,20 @@
       <c r="E134" s="50"/>
       <c r="F134" s="50"/>
     </row>
-    <row r="135" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="136" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A136" s="223" t="s">
+    <row r="135" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="136" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A136" s="242" t="s">
         <v>125</v>
       </c>
-      <c r="B136" s="223"/>
-      <c r="C136" s="223"/>
-    </row>
-    <row r="137" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A137" s="223"/>
-      <c r="B137" s="223"/>
-      <c r="C137" s="223"/>
-    </row>
-    <row r="138" spans="1:13" ht="27" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B136" s="242"/>
+      <c r="C136" s="242"/>
+    </row>
+    <row r="137" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A137" s="242"/>
+      <c r="B137" s="242"/>
+      <c r="C137" s="242"/>
+    </row>
+    <row r="138" spans="1:13" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A138" s="74" t="s">
         <v>253</v>
       </c>
@@ -3873,7 +3912,7 @@
       <c r="C138" s="75"/>
       <c r="D138" s="56"/>
     </row>
-    <row r="139" spans="1:13" ht="27" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:13" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A139" s="147" t="s">
         <v>258</v>
       </c>
@@ -3883,7 +3922,7 @@
       <c r="C139" s="75"/>
       <c r="D139" s="56"/>
     </row>
-    <row r="140" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A140" s="76" t="s">
         <v>0</v>
       </c>
@@ -3893,16 +3932,17 @@
       </c>
       <c r="C140" s="78"/>
     </row>
-    <row r="141" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:13" x14ac:dyDescent="0.25">
       <c r="M141" s="79"/>
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="A71:B71"/>
-    <mergeCell ref="A91:B92"/>
-    <mergeCell ref="D91:D92"/>
-    <mergeCell ref="E91:E92"/>
-    <mergeCell ref="A82:B82"/>
+    <mergeCell ref="A136:C137"/>
+    <mergeCell ref="A112:B114"/>
+    <mergeCell ref="A124:B126"/>
+    <mergeCell ref="A120:B122"/>
+    <mergeCell ref="A108:B110"/>
+    <mergeCell ref="A116:B118"/>
     <mergeCell ref="B1:E1"/>
     <mergeCell ref="A24:B24"/>
     <mergeCell ref="A74:B74"/>
@@ -3919,12 +3959,11 @@
     <mergeCell ref="A57:B57"/>
     <mergeCell ref="A61:B61"/>
     <mergeCell ref="A56:B56"/>
-    <mergeCell ref="A136:C137"/>
-    <mergeCell ref="A112:B114"/>
-    <mergeCell ref="A124:B126"/>
-    <mergeCell ref="A120:B122"/>
-    <mergeCell ref="A108:B110"/>
-    <mergeCell ref="A116:B118"/>
+    <mergeCell ref="A71:B71"/>
+    <mergeCell ref="A91:B92"/>
+    <mergeCell ref="D91:D92"/>
+    <mergeCell ref="E91:E92"/>
+    <mergeCell ref="A82:B82"/>
   </mergeCells>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="5" scale="90" orientation="portrait" r:id="rId1"/>
@@ -3935,53 +3974,53 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{533DB7A7-09F4-49CF-B824-70F15C1FF525}">
   <dimension ref="A1:P127"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="4.33203125" customWidth="1"/>
-    <col min="2" max="2" width="25.5546875" customWidth="1"/>
-    <col min="3" max="3" width="0.109375" customWidth="1"/>
-    <col min="4" max="4" width="8.44140625" customWidth="1"/>
-    <col min="5" max="5" width="14.109375" customWidth="1"/>
-    <col min="6" max="6" width="12.33203125" customWidth="1"/>
-    <col min="7" max="7" width="10.5546875" customWidth="1"/>
-    <col min="8" max="8" width="9.5546875" customWidth="1"/>
-    <col min="9" max="9" width="12.44140625" customWidth="1"/>
-    <col min="10" max="10" width="14.44140625" customWidth="1"/>
-    <col min="11" max="12" width="12.33203125" customWidth="1"/>
-    <col min="13" max="13" width="14.6640625" customWidth="1"/>
-    <col min="14" max="14" width="14.33203125" customWidth="1"/>
-    <col min="15" max="15" width="7.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="4.28515625" customWidth="1"/>
+    <col min="2" max="2" width="25.5703125" customWidth="1"/>
+    <col min="3" max="3" width="0.140625" customWidth="1"/>
+    <col min="4" max="4" width="8.42578125" customWidth="1"/>
+    <col min="5" max="5" width="14.140625" customWidth="1"/>
+    <col min="6" max="6" width="12.28515625" customWidth="1"/>
+    <col min="7" max="7" width="10.5703125" customWidth="1"/>
+    <col min="8" max="8" width="9.5703125" customWidth="1"/>
+    <col min="9" max="9" width="12.42578125" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" customWidth="1"/>
+    <col min="11" max="12" width="12.28515625" customWidth="1"/>
+    <col min="13" max="13" width="14.7109375" customWidth="1"/>
+    <col min="14" max="14" width="14.28515625" customWidth="1"/>
+    <col min="15" max="15" width="7.28515625" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="12" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="13" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:16" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="93"/>
       <c r="B1" s="94"/>
       <c r="C1" s="94"/>
-      <c r="D1" s="257"/>
-      <c r="E1" s="257"/>
-      <c r="F1" s="257"/>
-      <c r="G1" s="257"/>
-      <c r="H1" s="257"/>
-      <c r="I1" s="257"/>
-      <c r="J1" s="257"/>
-      <c r="K1" s="257"/>
-      <c r="L1" s="257"/>
-      <c r="M1" s="257"/>
+      <c r="D1" s="245"/>
+      <c r="E1" s="245"/>
+      <c r="F1" s="245"/>
+      <c r="G1" s="245"/>
+      <c r="H1" s="245"/>
+      <c r="I1" s="245"/>
+      <c r="J1" s="245"/>
+      <c r="K1" s="245"/>
+      <c r="L1" s="245"/>
+      <c r="M1" s="245"/>
       <c r="N1" s="95"/>
     </row>
-    <row r="2" spans="1:16" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:16" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="96"/>
       <c r="B2" s="97"/>
       <c r="C2" s="98"/>
       <c r="D2" s="98" t="s">
         <v>126</v>
       </c>
-      <c r="E2" s="279">
+      <c r="E2" s="269">
         <v>3000000</v>
       </c>
-      <c r="F2" s="279"/>
+      <c r="F2" s="269"/>
       <c r="G2" s="98"/>
       <c r="H2" s="98"/>
       <c r="I2" s="98" t="s">
@@ -3999,7 +4038,7 @@
         <v>13312274.1</v>
       </c>
     </row>
-    <row r="3" spans="1:16" ht="12.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:16" ht="12.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="102"/>
       <c r="B3" s="103"/>
       <c r="C3" s="103"/>
@@ -4016,228 +4055,228 @@
       <c r="N3" s="106"/>
       <c r="O3" s="80"/>
     </row>
-    <row r="4" spans="1:16" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="258" t="s">
+    <row r="4" spans="1:16" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="246" t="s">
         <v>161</v>
       </c>
-      <c r="B4" s="259"/>
-      <c r="C4" s="259"/>
-      <c r="D4" s="259"/>
-      <c r="E4" s="259"/>
-      <c r="F4" s="259"/>
-      <c r="G4" s="259"/>
-      <c r="H4" s="259"/>
-      <c r="I4" s="259"/>
-      <c r="J4" s="259"/>
-      <c r="K4" s="259"/>
-      <c r="L4" s="259"/>
-      <c r="M4" s="259"/>
-      <c r="N4" s="260"/>
+      <c r="B4" s="247"/>
+      <c r="C4" s="247"/>
+      <c r="D4" s="247"/>
+      <c r="E4" s="247"/>
+      <c r="F4" s="247"/>
+      <c r="G4" s="247"/>
+      <c r="H4" s="247"/>
+      <c r="I4" s="247"/>
+      <c r="J4" s="247"/>
+      <c r="K4" s="247"/>
+      <c r="L4" s="247"/>
+      <c r="M4" s="247"/>
+      <c r="N4" s="248"/>
       <c r="O4" s="80"/>
     </row>
-    <row r="5" spans="1:16" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="261"/>
-      <c r="B5" s="262"/>
-      <c r="C5" s="262"/>
-      <c r="D5" s="262"/>
-      <c r="E5" s="262"/>
-      <c r="F5" s="262"/>
-      <c r="G5" s="262"/>
-      <c r="H5" s="262"/>
-      <c r="I5" s="262"/>
-      <c r="J5" s="262"/>
-      <c r="K5" s="262"/>
-      <c r="L5" s="262"/>
-      <c r="M5" s="262"/>
-      <c r="N5" s="263"/>
+    <row r="5" spans="1:16" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="249"/>
+      <c r="B5" s="250"/>
+      <c r="C5" s="250"/>
+      <c r="D5" s="250"/>
+      <c r="E5" s="250"/>
+      <c r="F5" s="250"/>
+      <c r="G5" s="250"/>
+      <c r="H5" s="250"/>
+      <c r="I5" s="250"/>
+      <c r="J5" s="250"/>
+      <c r="K5" s="250"/>
+      <c r="L5" s="250"/>
+      <c r="M5" s="250"/>
+      <c r="N5" s="251"/>
       <c r="O5" s="80"/>
     </row>
-    <row r="6" spans="1:16" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="261"/>
-      <c r="B6" s="262"/>
-      <c r="C6" s="262"/>
-      <c r="D6" s="262"/>
-      <c r="E6" s="262"/>
-      <c r="F6" s="262"/>
-      <c r="G6" s="262"/>
-      <c r="H6" s="262"/>
-      <c r="I6" s="262"/>
-      <c r="J6" s="262"/>
-      <c r="K6" s="262"/>
-      <c r="L6" s="262"/>
-      <c r="M6" s="262"/>
-      <c r="N6" s="263"/>
+    <row r="6" spans="1:16" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="249"/>
+      <c r="B6" s="250"/>
+      <c r="C6" s="250"/>
+      <c r="D6" s="250"/>
+      <c r="E6" s="250"/>
+      <c r="F6" s="250"/>
+      <c r="G6" s="250"/>
+      <c r="H6" s="250"/>
+      <c r="I6" s="250"/>
+      <c r="J6" s="250"/>
+      <c r="K6" s="250"/>
+      <c r="L6" s="250"/>
+      <c r="M6" s="250"/>
+      <c r="N6" s="251"/>
       <c r="O6" s="80"/>
     </row>
-    <row r="7" spans="1:16" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="261"/>
-      <c r="B7" s="262"/>
-      <c r="C7" s="262"/>
-      <c r="D7" s="262"/>
-      <c r="E7" s="262"/>
-      <c r="F7" s="262"/>
-      <c r="G7" s="262"/>
-      <c r="H7" s="262"/>
-      <c r="I7" s="262"/>
-      <c r="J7" s="262"/>
-      <c r="K7" s="262"/>
-      <c r="L7" s="262"/>
-      <c r="M7" s="262"/>
-      <c r="N7" s="263"/>
+    <row r="7" spans="1:16" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="249"/>
+      <c r="B7" s="250"/>
+      <c r="C7" s="250"/>
+      <c r="D7" s="250"/>
+      <c r="E7" s="250"/>
+      <c r="F7" s="250"/>
+      <c r="G7" s="250"/>
+      <c r="H7" s="250"/>
+      <c r="I7" s="250"/>
+      <c r="J7" s="250"/>
+      <c r="K7" s="250"/>
+      <c r="L7" s="250"/>
+      <c r="M7" s="250"/>
+      <c r="N7" s="251"/>
       <c r="O7" s="80"/>
     </row>
-    <row r="8" spans="1:16" ht="192" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="264"/>
-      <c r="B8" s="265"/>
-      <c r="C8" s="265"/>
-      <c r="D8" s="265"/>
-      <c r="E8" s="265"/>
-      <c r="F8" s="265"/>
-      <c r="G8" s="265"/>
-      <c r="H8" s="265"/>
-      <c r="I8" s="265"/>
-      <c r="J8" s="265"/>
-      <c r="K8" s="265"/>
-      <c r="L8" s="265"/>
-      <c r="M8" s="265"/>
-      <c r="N8" s="266"/>
-    </row>
-    <row r="9" spans="1:16" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="273" t="s">
+    <row r="8" spans="1:16" ht="192" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="252"/>
+      <c r="B8" s="253"/>
+      <c r="C8" s="253"/>
+      <c r="D8" s="253"/>
+      <c r="E8" s="253"/>
+      <c r="F8" s="253"/>
+      <c r="G8" s="253"/>
+      <c r="H8" s="253"/>
+      <c r="I8" s="253"/>
+      <c r="J8" s="253"/>
+      <c r="K8" s="253"/>
+      <c r="L8" s="253"/>
+      <c r="M8" s="253"/>
+      <c r="N8" s="254"/>
+    </row>
+    <row r="9" spans="1:16" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="263" t="s">
         <v>159</v>
       </c>
-      <c r="B9" s="274"/>
-      <c r="C9" s="274"/>
-      <c r="D9" s="274"/>
-      <c r="E9" s="274"/>
-      <c r="F9" s="274"/>
-      <c r="G9" s="274"/>
-      <c r="H9" s="274"/>
-      <c r="I9" s="274"/>
-      <c r="J9" s="274"/>
-      <c r="K9" s="274"/>
-      <c r="L9" s="274"/>
-      <c r="M9" s="274"/>
-      <c r="N9" s="275"/>
-    </row>
-    <row r="10" spans="1:16" ht="59.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="248" t="s">
+      <c r="B9" s="264"/>
+      <c r="C9" s="264"/>
+      <c r="D9" s="264"/>
+      <c r="E9" s="264"/>
+      <c r="F9" s="264"/>
+      <c r="G9" s="264"/>
+      <c r="H9" s="264"/>
+      <c r="I9" s="264"/>
+      <c r="J9" s="264"/>
+      <c r="K9" s="264"/>
+      <c r="L9" s="264"/>
+      <c r="M9" s="264"/>
+      <c r="N9" s="265"/>
+    </row>
+    <row r="10" spans="1:16" ht="59.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="274" t="s">
         <v>262</v>
       </c>
-      <c r="B10" s="249"/>
-      <c r="C10" s="249"/>
-      <c r="D10" s="249"/>
-      <c r="E10" s="249"/>
-      <c r="F10" s="249"/>
-      <c r="G10" s="249"/>
-      <c r="H10" s="249"/>
-      <c r="I10" s="249"/>
-      <c r="J10" s="249"/>
-      <c r="K10" s="249"/>
-      <c r="L10" s="249"/>
-      <c r="M10" s="249"/>
-      <c r="N10" s="250"/>
-    </row>
-    <row r="11" spans="1:16" ht="59.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="251" t="s">
+      <c r="B10" s="275"/>
+      <c r="C10" s="275"/>
+      <c r="D10" s="275"/>
+      <c r="E10" s="275"/>
+      <c r="F10" s="275"/>
+      <c r="G10" s="275"/>
+      <c r="H10" s="275"/>
+      <c r="I10" s="275"/>
+      <c r="J10" s="275"/>
+      <c r="K10" s="275"/>
+      <c r="L10" s="275"/>
+      <c r="M10" s="275"/>
+      <c r="N10" s="276"/>
+    </row>
+    <row r="11" spans="1:16" ht="59.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="277" t="s">
         <v>264</v>
       </c>
-      <c r="B11" s="252"/>
-      <c r="C11" s="252"/>
-      <c r="D11" s="252"/>
-      <c r="E11" s="252"/>
-      <c r="F11" s="252"/>
-      <c r="G11" s="252"/>
-      <c r="H11" s="252"/>
-      <c r="I11" s="252"/>
-      <c r="J11" s="252"/>
-      <c r="K11" s="252"/>
-      <c r="L11" s="252"/>
-      <c r="M11" s="252"/>
-      <c r="N11" s="253"/>
-    </row>
-    <row r="12" spans="1:16" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="276" t="s">
+      <c r="B11" s="278"/>
+      <c r="C11" s="278"/>
+      <c r="D11" s="278"/>
+      <c r="E11" s="278"/>
+      <c r="F11" s="278"/>
+      <c r="G11" s="278"/>
+      <c r="H11" s="278"/>
+      <c r="I11" s="278"/>
+      <c r="J11" s="278"/>
+      <c r="K11" s="278"/>
+      <c r="L11" s="278"/>
+      <c r="M11" s="278"/>
+      <c r="N11" s="279"/>
+    </row>
+    <row r="12" spans="1:16" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="266" t="s">
         <v>160</v>
       </c>
-      <c r="B12" s="277"/>
-      <c r="C12" s="277"/>
-      <c r="D12" s="277"/>
-      <c r="E12" s="277"/>
-      <c r="F12" s="277"/>
-      <c r="G12" s="277"/>
-      <c r="H12" s="277"/>
-      <c r="I12" s="277"/>
-      <c r="J12" s="277"/>
-      <c r="K12" s="277"/>
-      <c r="L12" s="277"/>
-      <c r="M12" s="277"/>
-      <c r="N12" s="278"/>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A13" s="267" t="s">
+      <c r="B12" s="267"/>
+      <c r="C12" s="267"/>
+      <c r="D12" s="267"/>
+      <c r="E12" s="267"/>
+      <c r="F12" s="267"/>
+      <c r="G12" s="267"/>
+      <c r="H12" s="267"/>
+      <c r="I12" s="267"/>
+      <c r="J12" s="267"/>
+      <c r="K12" s="267"/>
+      <c r="L12" s="267"/>
+      <c r="M12" s="267"/>
+      <c r="N12" s="268"/>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A13" s="255" t="s">
         <v>128</v>
       </c>
-      <c r="B13" s="269" t="s">
+      <c r="B13" s="257" t="s">
         <v>129</v>
       </c>
-      <c r="C13" s="269" t="s">
+      <c r="C13" s="257" t="s">
         <v>130</v>
       </c>
-      <c r="D13" s="269" t="s">
+      <c r="D13" s="257" t="s">
         <v>131</v>
       </c>
-      <c r="E13" s="246" t="s">
+      <c r="E13" s="259" t="s">
         <v>132</v>
       </c>
-      <c r="F13" s="269" t="s">
+      <c r="F13" s="257" t="s">
         <v>133</v>
       </c>
-      <c r="G13" s="271" t="s">
+      <c r="G13" s="261" t="s">
         <v>134</v>
       </c>
-      <c r="H13" s="246" t="s">
+      <c r="H13" s="259" t="s">
         <v>135</v>
       </c>
-      <c r="I13" s="246" t="s">
+      <c r="I13" s="259" t="s">
         <v>127</v>
       </c>
-      <c r="J13" s="246" t="s">
+      <c r="J13" s="259" t="s">
         <v>126</v>
       </c>
-      <c r="K13" s="242" t="s">
+      <c r="K13" s="270" t="s">
         <v>176</v>
       </c>
-      <c r="L13" s="244" t="s">
+      <c r="L13" s="272" t="s">
         <v>182</v>
       </c>
       <c r="M13" s="143" t="s">
         <v>252</v>
       </c>
-      <c r="N13" s="254" t="s">
+      <c r="N13" s="280" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="14" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="268"/>
-      <c r="B14" s="270"/>
-      <c r="C14" s="270"/>
-      <c r="D14" s="270"/>
-      <c r="E14" s="247"/>
-      <c r="F14" s="270"/>
-      <c r="G14" s="272"/>
-      <c r="H14" s="247"/>
-      <c r="I14" s="247"/>
-      <c r="J14" s="247"/>
-      <c r="K14" s="243"/>
-      <c r="L14" s="245"/>
+    <row r="14" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="256"/>
+      <c r="B14" s="258"/>
+      <c r="C14" s="258"/>
+      <c r="D14" s="258"/>
+      <c r="E14" s="260"/>
+      <c r="F14" s="258"/>
+      <c r="G14" s="262"/>
+      <c r="H14" s="260"/>
+      <c r="I14" s="260"/>
+      <c r="J14" s="260"/>
+      <c r="K14" s="271"/>
+      <c r="L14" s="273"/>
       <c r="M14" s="144" t="str">
         <f>RESUMEN!B8</f>
         <v>VTO 17/07</v>
       </c>
-      <c r="N14" s="255"/>
-    </row>
-    <row r="15" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N14" s="281"/>
+    </row>
+    <row r="15" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="129">
         <v>1</v>
       </c>
@@ -4285,7 +4324,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="16" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="188">
         <v>2</v>
       </c>
@@ -4334,7 +4373,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="17" spans="1:15" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:15" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="129">
         <v>3</v>
       </c>
@@ -4383,7 +4422,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="18" spans="1:15" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:15" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="130">
         <v>4</v>
       </c>
@@ -4432,7 +4471,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="19" spans="1:15" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:15" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="129">
         <v>5</v>
       </c>
@@ -4480,7 +4519,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="20" spans="1:15" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:15" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="129">
         <v>6</v>
       </c>
@@ -4528,7 +4567,7 @@
         <v>6.0000000000000005E-2</v>
       </c>
     </row>
-    <row r="21" spans="1:15" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:15" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="129">
         <v>7</v>
       </c>
@@ -4577,7 +4616,7 @@
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="22" spans="1:15" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:15" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="129">
         <v>8</v>
       </c>
@@ -4626,7 +4665,7 @@
         <v>0.08</v>
       </c>
     </row>
-    <row r="23" spans="1:15" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:15" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="129">
         <v>9</v>
       </c>
@@ -4674,7 +4713,7 @@
         <v>0.09</v>
       </c>
     </row>
-    <row r="24" spans="1:15" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:15" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="129">
         <v>10</v>
       </c>
@@ -4722,7 +4761,7 @@
         <v>9.9999999999999992E-2</v>
       </c>
     </row>
-    <row r="25" spans="1:15" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:15" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="129">
         <v>11</v>
       </c>
@@ -4771,7 +4810,7 @@
         <v>0.10999999999999999</v>
       </c>
     </row>
-    <row r="26" spans="1:15" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:15" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="188">
         <v>12</v>
       </c>
@@ -4819,7 +4858,7 @@
         <v>0.11999999999999998</v>
       </c>
     </row>
-    <row r="27" spans="1:15" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:15" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="129">
         <v>13</v>
       </c>
@@ -4868,7 +4907,7 @@
         <v>0.12999999999999998</v>
       </c>
     </row>
-    <row r="28" spans="1:15" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:15" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="129">
         <v>14</v>
       </c>
@@ -4914,7 +4953,7 @@
         <v>0.13999999999999999</v>
       </c>
     </row>
-    <row r="29" spans="1:15" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:15" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="130">
         <v>15</v>
       </c>
@@ -4963,7 +5002,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="30" spans="1:15" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:15" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="129">
         <v>16</v>
       </c>
@@ -5012,7 +5051,7 @@
         <v>0.16</v>
       </c>
     </row>
-    <row r="31" spans="1:15" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:15" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="129">
         <v>17</v>
       </c>
@@ -5060,7 +5099,7 @@
         <v>0.17</v>
       </c>
     </row>
-    <row r="32" spans="1:15" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:15" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="130">
         <v>18</v>
       </c>
@@ -5109,7 +5148,7 @@
         <v>0.18000000000000002</v>
       </c>
     </row>
-    <row r="33" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A33" s="130">
         <v>19</v>
       </c>
@@ -5160,7 +5199,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="34" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A34" s="131">
         <v>20</v>
       </c>
@@ -5210,7 +5249,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="35" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A35" s="130">
         <v>21</v>
       </c>
@@ -5259,7 +5298,7 @@
         <v>0.21000000000000005</v>
       </c>
     </row>
-    <row r="36" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A36" s="130">
         <f>A35+1</f>
         <v>22</v>
@@ -5309,7 +5348,7 @@
         <v>0.22000000000000006</v>
       </c>
     </row>
-    <row r="37" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A37" s="129">
         <f t="shared" ref="A37:A100" si="9">A36+1</f>
         <v>23</v>
@@ -5359,7 +5398,7 @@
         <v>0.23000000000000007</v>
       </c>
     </row>
-    <row r="38" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A38" s="129">
         <f t="shared" si="9"/>
         <v>24</v>
@@ -5408,7 +5447,7 @@
         <v>0.24000000000000007</v>
       </c>
     </row>
-    <row r="39" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A39" s="129">
         <f t="shared" si="9"/>
         <v>25</v>
@@ -5458,7 +5497,7 @@
         <v>0.25000000000000006</v>
       </c>
     </row>
-    <row r="40" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A40" s="129">
         <f t="shared" si="9"/>
         <v>26</v>
@@ -5508,7 +5547,7 @@
         <v>0.26000000000000006</v>
       </c>
     </row>
-    <row r="41" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A41" s="129">
         <f t="shared" si="9"/>
         <v>27</v>
@@ -5558,7 +5597,7 @@
         <v>0.27000000000000007</v>
       </c>
     </row>
-    <row r="42" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A42" s="129">
         <f t="shared" si="9"/>
         <v>28</v>
@@ -5605,7 +5644,7 @@
         <v>0.28000000000000008</v>
       </c>
     </row>
-    <row r="43" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A43" s="130">
         <f t="shared" si="9"/>
         <v>29</v>
@@ -5658,7 +5697,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="44" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A44" s="130">
         <f t="shared" si="9"/>
         <v>30</v>
@@ -5708,7 +5747,7 @@
         <v>0.3000000000000001</v>
       </c>
     </row>
-    <row r="45" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A45" s="129">
         <f t="shared" si="9"/>
         <v>31</v>
@@ -5758,7 +5797,7 @@
         <v>0.31000000000000011</v>
       </c>
     </row>
-    <row r="46" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A46" s="129">
         <f t="shared" si="9"/>
         <v>32</v>
@@ -5807,7 +5846,7 @@
         <v>0.32000000000000012</v>
       </c>
     </row>
-    <row r="47" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A47" s="131">
         <f t="shared" si="9"/>
         <v>33</v>
@@ -5859,7 +5898,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="48" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A48" s="129">
         <f t="shared" si="9"/>
         <v>34</v>
@@ -5909,7 +5948,7 @@
         <v>0.34000000000000014</v>
       </c>
     </row>
-    <row r="49" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A49" s="199">
         <f t="shared" si="9"/>
         <v>35</v>
@@ -5962,7 +6001,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="50" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A50" s="129">
         <f t="shared" si="9"/>
         <v>36</v>
@@ -6015,7 +6054,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="51" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A51" s="129">
         <f t="shared" si="9"/>
         <v>37</v>
@@ -6067,7 +6106,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="52" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A52" s="129">
         <f t="shared" si="9"/>
         <v>38</v>
@@ -6117,7 +6156,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="53" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A53" s="129">
         <f t="shared" si="9"/>
         <v>39</v>
@@ -6167,7 +6206,7 @@
         <v>0.39000000000000018</v>
       </c>
     </row>
-    <row r="54" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A54" s="129">
         <f t="shared" si="9"/>
         <v>40</v>
@@ -6217,7 +6256,7 @@
         <v>0.40000000000000019</v>
       </c>
     </row>
-    <row r="55" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A55" s="129">
         <f t="shared" si="9"/>
         <v>41</v>
@@ -6266,7 +6305,7 @@
         <v>0.4100000000000002</v>
       </c>
     </row>
-    <row r="56" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A56" s="131">
         <f t="shared" si="9"/>
         <v>42</v>
@@ -6318,7 +6357,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="57" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A57" s="131">
         <f t="shared" si="9"/>
         <v>43</v>
@@ -6373,7 +6412,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="58" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A58" s="130">
         <f t="shared" si="9"/>
         <v>44</v>
@@ -6426,7 +6465,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="59" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A59" s="130">
         <f t="shared" si="9"/>
         <v>45</v>
@@ -6476,12 +6515,12 @@
         <v>0.45000000000000023</v>
       </c>
     </row>
-    <row r="60" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A60" s="286">
+    <row r="60" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A60" s="223">
         <f t="shared" si="9"/>
         <v>46</v>
       </c>
-      <c r="B60" s="287" t="s">
+      <c r="B60" s="224" t="s">
         <v>45</v>
       </c>
       <c r="C60" s="113"/>
@@ -6528,7 +6567,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="61" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A61" s="131">
         <f t="shared" si="9"/>
         <v>47</v>
@@ -6579,7 +6618,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="62" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A62" s="130">
         <f t="shared" si="9"/>
         <v>48</v>
@@ -6632,7 +6671,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="63" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A63" s="130">
         <f t="shared" si="9"/>
         <v>49</v>
@@ -6682,7 +6721,7 @@
         <v>0.49000000000000027</v>
       </c>
     </row>
-    <row r="64" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A64" s="130">
         <f t="shared" si="9"/>
         <v>50</v>
@@ -6732,7 +6771,7 @@
         <v>0.50000000000000022</v>
       </c>
     </row>
-    <row r="65" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A65" s="130">
         <f t="shared" si="9"/>
         <v>51</v>
@@ -6782,7 +6821,7 @@
         <v>0.51000000000000023</v>
       </c>
     </row>
-    <row r="66" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A66" s="130">
         <f t="shared" si="9"/>
         <v>52</v>
@@ -6832,7 +6871,7 @@
         <v>0.52000000000000024</v>
       </c>
     </row>
-    <row r="67" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A67" s="130">
         <f t="shared" si="9"/>
         <v>53</v>
@@ -6882,7 +6921,7 @@
         <v>0.53000000000000025</v>
       </c>
     </row>
-    <row r="68" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A68" s="130">
         <f t="shared" si="9"/>
         <v>54</v>
@@ -6931,7 +6970,7 @@
         <v>0.54000000000000026</v>
       </c>
     </row>
-    <row r="69" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A69" s="130">
         <f t="shared" si="9"/>
         <v>55</v>
@@ -6980,7 +7019,7 @@
         <v>0.55000000000000027</v>
       </c>
     </row>
-    <row r="70" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A70" s="130">
         <f t="shared" si="9"/>
         <v>56</v>
@@ -7029,7 +7068,7 @@
         <v>0.56000000000000028</v>
       </c>
     </row>
-    <row r="71" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A71" s="130">
         <f t="shared" si="9"/>
         <v>57</v>
@@ -7079,7 +7118,7 @@
         <v>0.57000000000000028</v>
       </c>
     </row>
-    <row r="72" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A72" s="130">
         <f t="shared" si="9"/>
         <v>58</v>
@@ -7132,7 +7171,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="73" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A73" s="130">
         <f t="shared" si="9"/>
         <v>59</v>
@@ -7181,7 +7220,7 @@
         <v>0.5900000000000003</v>
       </c>
     </row>
-    <row r="74" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A74" s="130">
         <f t="shared" si="9"/>
         <v>60</v>
@@ -7230,7 +7269,7 @@
         <v>0.60000000000000031</v>
       </c>
     </row>
-    <row r="75" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A75" s="130">
         <f t="shared" si="9"/>
         <v>61</v>
@@ -7280,7 +7319,7 @@
         <v>0.61000000000000032</v>
       </c>
     </row>
-    <row r="76" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A76" s="130">
         <f t="shared" si="9"/>
         <v>62</v>
@@ -7329,7 +7368,7 @@
         <v>0.62000000000000033</v>
       </c>
     </row>
-    <row r="77" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A77" s="130">
         <f t="shared" si="9"/>
         <v>63</v>
@@ -7382,7 +7421,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="78" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A78" s="130">
         <f t="shared" si="9"/>
         <v>64</v>
@@ -7431,7 +7470,7 @@
         <v>0.64000000000000035</v>
       </c>
     </row>
-    <row r="79" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A79" s="130">
         <f t="shared" si="9"/>
         <v>65</v>
@@ -7483,7 +7522,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="80" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A80" s="190">
         <f t="shared" si="9"/>
         <v>66</v>
@@ -7532,7 +7571,7 @@
         <v>0.66000000000000036</v>
       </c>
     </row>
-    <row r="81" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A81" s="130">
         <f t="shared" si="9"/>
         <v>67</v>
@@ -7581,7 +7620,7 @@
         <v>0.67000000000000037</v>
       </c>
     </row>
-    <row r="82" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A82" s="188">
         <f t="shared" si="9"/>
         <v>68</v>
@@ -7632,7 +7671,7 @@
         <v>0.68000000000000038</v>
       </c>
     </row>
-    <row r="83" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A83" s="130">
         <f t="shared" si="9"/>
         <v>69</v>
@@ -7683,7 +7722,7 @@
         <v>0.69000000000000039</v>
       </c>
     </row>
-    <row r="84" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A84" s="130">
         <f t="shared" si="9"/>
         <v>70</v>
@@ -7736,7 +7775,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="85" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A85" s="130">
         <f t="shared" si="9"/>
         <v>71</v>
@@ -7786,7 +7825,7 @@
         <v>0.71000000000000041</v>
       </c>
     </row>
-    <row r="86" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A86" s="130">
         <f t="shared" si="9"/>
         <v>72</v>
@@ -7836,7 +7875,7 @@
         <v>0.72000000000000042</v>
       </c>
     </row>
-    <row r="87" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A87" s="130">
         <f t="shared" si="9"/>
         <v>73</v>
@@ -7886,7 +7925,7 @@
         <v>0.73000000000000043</v>
       </c>
     </row>
-    <row r="88" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A88" s="129">
         <f t="shared" si="9"/>
         <v>74</v>
@@ -7935,7 +7974,7 @@
         <v>0.74000000000000044</v>
       </c>
     </row>
-    <row r="89" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A89" s="129">
         <f t="shared" si="9"/>
         <v>75</v>
@@ -7985,7 +8024,7 @@
         <v>0.75000000000000044</v>
       </c>
     </row>
-    <row r="90" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A90" s="129">
         <f t="shared" si="9"/>
         <v>76</v>
@@ -8035,7 +8074,7 @@
         <v>0.76000000000000045</v>
       </c>
     </row>
-    <row r="91" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A91" s="129">
         <f t="shared" si="9"/>
         <v>77</v>
@@ -8085,7 +8124,7 @@
         <v>0.77000000000000046</v>
       </c>
     </row>
-    <row r="92" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A92" s="131">
         <f t="shared" si="9"/>
         <v>78</v>
@@ -8137,7 +8176,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="93" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A93" s="129">
         <f t="shared" si="9"/>
         <v>79</v>
@@ -8190,7 +8229,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="94" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A94" s="130">
         <f t="shared" si="9"/>
         <v>80</v>
@@ -8240,7 +8279,7 @@
         <v>0.80000000000000049</v>
       </c>
     </row>
-    <row r="95" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A95" s="130">
         <f t="shared" si="9"/>
         <v>81</v>
@@ -8293,7 +8332,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="96" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A96" s="130">
         <f t="shared" si="9"/>
         <v>82</v>
@@ -8342,7 +8381,7 @@
         <v>0.82000000000000051</v>
       </c>
     </row>
-    <row r="97" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A97" s="130">
         <f t="shared" si="9"/>
         <v>83</v>
@@ -8392,7 +8431,7 @@
         <v>0.83000000000000052</v>
       </c>
     </row>
-    <row r="98" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A98" s="130">
         <f t="shared" si="9"/>
         <v>84</v>
@@ -8439,7 +8478,7 @@
         <v>0.84000000000000052</v>
       </c>
     </row>
-    <row r="99" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A99" s="129">
         <f t="shared" si="9"/>
         <v>85</v>
@@ -8489,7 +8528,7 @@
         <v>0.85000000000000053</v>
       </c>
     </row>
-    <row r="100" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A100" s="190">
         <f t="shared" si="9"/>
         <v>86</v>
@@ -8539,7 +8578,7 @@
         <v>0.86000000000000054</v>
       </c>
     </row>
-    <row r="101" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A101" s="129">
         <f t="shared" ref="A101:A117" si="23">A100+1</f>
         <v>87</v>
@@ -8589,7 +8628,7 @@
         <v>0.87000000000000055</v>
       </c>
     </row>
-    <row r="102" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A102" s="129">
         <f t="shared" si="23"/>
         <v>88</v>
@@ -8639,7 +8678,7 @@
         <v>0.88000000000000056</v>
       </c>
     </row>
-    <row r="103" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A103" s="129">
         <f t="shared" si="23"/>
         <v>89</v>
@@ -8689,7 +8728,7 @@
         <v>0.89000000000000057</v>
       </c>
     </row>
-    <row r="104" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A104" s="129">
         <f t="shared" si="23"/>
         <v>90</v>
@@ -8739,7 +8778,7 @@
         <v>0.90000000000000058</v>
       </c>
     </row>
-    <row r="105" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A105" s="129">
         <f t="shared" si="23"/>
         <v>91</v>
@@ -8788,7 +8827,7 @@
         <v>0.91000000000000059</v>
       </c>
     </row>
-    <row r="106" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A106" s="129">
         <f t="shared" si="23"/>
         <v>92</v>
@@ -8837,7 +8876,7 @@
         <v>0.9200000000000006</v>
       </c>
     </row>
-    <row r="107" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A107" s="130">
         <f t="shared" si="23"/>
         <v>93</v>
@@ -8886,7 +8925,7 @@
         <v>0.9300000000000006</v>
       </c>
     </row>
-    <row r="108" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A108" s="130">
         <f t="shared" si="23"/>
         <v>94</v>
@@ -8936,7 +8975,7 @@
         <v>0.94000000000000061</v>
       </c>
     </row>
-    <row r="109" spans="1:16" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:16" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109" s="130">
         <f t="shared" si="23"/>
         <v>95</v>
@@ -8986,7 +9025,7 @@
         <v>0.95000000000000062</v>
       </c>
     </row>
-    <row r="110" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A110" s="130">
         <f t="shared" si="23"/>
         <v>96</v>
@@ -9038,7 +9077,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="111" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A111" s="130">
         <f t="shared" si="23"/>
         <v>97</v>
@@ -9088,7 +9127,7 @@
         <v>0.97000000000000064</v>
       </c>
     </row>
-    <row r="112" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A112" s="130">
         <f t="shared" si="23"/>
         <v>98</v>
@@ -9138,7 +9177,7 @@
         <v>0.98000000000000065</v>
       </c>
     </row>
-    <row r="113" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A113" s="130">
         <f t="shared" si="23"/>
         <v>99</v>
@@ -9188,7 +9227,7 @@
         <v>0.99000000000000066</v>
       </c>
     </row>
-    <row r="114" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A114" s="130">
         <f t="shared" si="23"/>
         <v>100</v>
@@ -9235,7 +9274,7 @@
         <v>1.0000000000000007</v>
       </c>
     </row>
-    <row r="115" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A115" s="130">
         <f t="shared" si="23"/>
         <v>101</v>
@@ -9284,7 +9323,7 @@
         <v>1.0100000000000007</v>
       </c>
     </row>
-    <row r="116" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A116" s="130">
         <f t="shared" si="23"/>
         <v>102</v>
@@ -9334,7 +9373,7 @@
         <v>1.0200000000000007</v>
       </c>
     </row>
-    <row r="117" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A117" s="130">
         <f t="shared" si="23"/>
         <v>103</v>
@@ -9384,7 +9423,7 @@
         <v>1.0300000000000007</v>
       </c>
     </row>
-    <row r="118" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A118" s="130"/>
       <c r="B118" s="108"/>
       <c r="C118" s="113"/>
@@ -9401,7 +9440,7 @@
       <c r="N118" s="140"/>
       <c r="O118" s="50"/>
     </row>
-    <row r="119" spans="1:15" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:15" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A119" s="132"/>
       <c r="B119" s="133"/>
       <c r="C119" s="133"/>
@@ -9444,99 +9483,104 @@
         <v>40891254.560000002</v>
       </c>
     </row>
-    <row r="120" spans="1:15" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:15" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B120" s="89"/>
       <c r="C120" s="89"/>
     </row>
-    <row r="121" spans="1:15" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="122" spans="1:15" ht="9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B122" s="256" t="s">
+    <row r="121" spans="1:15" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="122" spans="1:15" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B122" s="244" t="s">
         <v>103</v>
       </c>
-      <c r="C122" s="256"/>
-      <c r="D122" s="256"/>
-      <c r="E122" s="256"/>
-      <c r="F122" s="256"/>
-      <c r="G122" s="256"/>
-      <c r="H122" s="256"/>
-      <c r="I122" s="256"/>
-      <c r="J122" s="256"/>
-      <c r="K122" s="256"/>
-      <c r="L122" s="256"/>
-      <c r="M122" s="256"/>
-    </row>
-    <row r="123" spans="1:15" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B123" s="256"/>
-      <c r="C123" s="256"/>
-      <c r="D123" s="256"/>
-      <c r="E123" s="256"/>
-      <c r="F123" s="256"/>
-      <c r="G123" s="256"/>
-      <c r="H123" s="256"/>
-      <c r="I123" s="256"/>
-      <c r="J123" s="256"/>
-      <c r="K123" s="256"/>
-      <c r="L123" s="256"/>
-      <c r="M123" s="256"/>
-    </row>
-    <row r="124" spans="1:15" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B124" s="256"/>
-      <c r="C124" s="256"/>
-      <c r="D124" s="256"/>
-      <c r="E124" s="256"/>
-      <c r="F124" s="256"/>
-      <c r="G124" s="256"/>
-      <c r="H124" s="256"/>
-      <c r="I124" s="256"/>
-      <c r="J124" s="256"/>
-      <c r="K124" s="256"/>
-      <c r="L124" s="256"/>
-      <c r="M124" s="256"/>
-    </row>
-    <row r="125" spans="1:15" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B125" s="256"/>
-      <c r="C125" s="256"/>
-      <c r="D125" s="256"/>
-      <c r="E125" s="256"/>
-      <c r="F125" s="256"/>
-      <c r="G125" s="256"/>
-      <c r="H125" s="256"/>
-      <c r="I125" s="256"/>
-      <c r="J125" s="256"/>
-      <c r="K125" s="256"/>
-      <c r="L125" s="256"/>
-      <c r="M125" s="256"/>
-    </row>
-    <row r="126" spans="1:15" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B126" s="256"/>
-      <c r="C126" s="256"/>
-      <c r="D126" s="256"/>
-      <c r="E126" s="256"/>
-      <c r="F126" s="256"/>
-      <c r="G126" s="256"/>
-      <c r="H126" s="256"/>
-      <c r="I126" s="256"/>
-      <c r="J126" s="256"/>
-      <c r="K126" s="256"/>
-      <c r="L126" s="256"/>
-      <c r="M126" s="256"/>
-    </row>
-    <row r="127" spans="1:15" ht="67.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B127" s="256"/>
-      <c r="C127" s="256"/>
-      <c r="D127" s="256"/>
-      <c r="E127" s="256"/>
-      <c r="F127" s="256"/>
-      <c r="G127" s="256"/>
-      <c r="H127" s="256"/>
-      <c r="I127" s="256"/>
-      <c r="J127" s="256"/>
-      <c r="K127" s="256"/>
-      <c r="L127" s="256"/>
-      <c r="M127" s="256"/>
+      <c r="C122" s="244"/>
+      <c r="D122" s="244"/>
+      <c r="E122" s="244"/>
+      <c r="F122" s="244"/>
+      <c r="G122" s="244"/>
+      <c r="H122" s="244"/>
+      <c r="I122" s="244"/>
+      <c r="J122" s="244"/>
+      <c r="K122" s="244"/>
+      <c r="L122" s="244"/>
+      <c r="M122" s="244"/>
+    </row>
+    <row r="123" spans="1:15" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B123" s="244"/>
+      <c r="C123" s="244"/>
+      <c r="D123" s="244"/>
+      <c r="E123" s="244"/>
+      <c r="F123" s="244"/>
+      <c r="G123" s="244"/>
+      <c r="H123" s="244"/>
+      <c r="I123" s="244"/>
+      <c r="J123" s="244"/>
+      <c r="K123" s="244"/>
+      <c r="L123" s="244"/>
+      <c r="M123" s="244"/>
+    </row>
+    <row r="124" spans="1:15" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B124" s="244"/>
+      <c r="C124" s="244"/>
+      <c r="D124" s="244"/>
+      <c r="E124" s="244"/>
+      <c r="F124" s="244"/>
+      <c r="G124" s="244"/>
+      <c r="H124" s="244"/>
+      <c r="I124" s="244"/>
+      <c r="J124" s="244"/>
+      <c r="K124" s="244"/>
+      <c r="L124" s="244"/>
+      <c r="M124" s="244"/>
+    </row>
+    <row r="125" spans="1:15" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B125" s="244"/>
+      <c r="C125" s="244"/>
+      <c r="D125" s="244"/>
+      <c r="E125" s="244"/>
+      <c r="F125" s="244"/>
+      <c r="G125" s="244"/>
+      <c r="H125" s="244"/>
+      <c r="I125" s="244"/>
+      <c r="J125" s="244"/>
+      <c r="K125" s="244"/>
+      <c r="L125" s="244"/>
+      <c r="M125" s="244"/>
+    </row>
+    <row r="126" spans="1:15" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B126" s="244"/>
+      <c r="C126" s="244"/>
+      <c r="D126" s="244"/>
+      <c r="E126" s="244"/>
+      <c r="F126" s="244"/>
+      <c r="G126" s="244"/>
+      <c r="H126" s="244"/>
+      <c r="I126" s="244"/>
+      <c r="J126" s="244"/>
+      <c r="K126" s="244"/>
+      <c r="L126" s="244"/>
+      <c r="M126" s="244"/>
+    </row>
+    <row r="127" spans="1:15" ht="67.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B127" s="244"/>
+      <c r="C127" s="244"/>
+      <c r="D127" s="244"/>
+      <c r="E127" s="244"/>
+      <c r="F127" s="244"/>
+      <c r="G127" s="244"/>
+      <c r="H127" s="244"/>
+      <c r="I127" s="244"/>
+      <c r="J127" s="244"/>
+      <c r="K127" s="244"/>
+      <c r="L127" s="244"/>
+      <c r="M127" s="244"/>
     </row>
   </sheetData>
   <mergeCells count="21">
+    <mergeCell ref="L13:L14"/>
+    <mergeCell ref="J13:J14"/>
+    <mergeCell ref="A10:N10"/>
+    <mergeCell ref="A11:N11"/>
+    <mergeCell ref="N13:N14"/>
     <mergeCell ref="B122:M127"/>
     <mergeCell ref="D1:M1"/>
     <mergeCell ref="A4:N8"/>
@@ -9553,11 +9597,6 @@
     <mergeCell ref="E2:F2"/>
     <mergeCell ref="I13:I14"/>
     <mergeCell ref="K13:K14"/>
-    <mergeCell ref="L13:L14"/>
-    <mergeCell ref="J13:J14"/>
-    <mergeCell ref="A10:N10"/>
-    <mergeCell ref="A11:N11"/>
-    <mergeCell ref="N13:N14"/>
   </mergeCells>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="3" scale="80" orientation="portrait" r:id="rId1"/>
@@ -9567,16 +9606,16 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{56D35F41-74CB-4294-A7A2-EC3C67574818}">
   <dimension ref="C3:N9"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="3" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.7109375" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="13" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="3:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="3:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C3" s="19"/>
     </row>
-    <row r="4" spans="3:14" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="3:14" ht="13.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C4" s="173" t="s">
         <v>193</v>
       </c>
@@ -9592,7 +9631,7 @@
       <c r="K4" s="19"/>
       <c r="L4" s="19"/>
     </row>
-    <row r="5" spans="3:14" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="3:14" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C5" s="175" t="s">
         <v>194</v>
       </c>
@@ -9609,7 +9648,7 @@
       <c r="M5" s="19"/>
       <c r="N5" s="19"/>
     </row>
-    <row r="6" spans="3:14" x14ac:dyDescent="0.3">
+    <row r="6" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C6" s="175" t="s">
         <v>197</v>
       </c>
@@ -9631,7 +9670,7 @@
       <c r="M6" s="19"/>
       <c r="N6" s="19"/>
     </row>
-    <row r="7" spans="3:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="3:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C7" s="47" t="s">
         <v>200</v>
       </c>
@@ -9641,31 +9680,31 @@
       <c r="M7" s="19"/>
       <c r="N7" s="19"/>
     </row>
-    <row r="8" spans="3:14" x14ac:dyDescent="0.3">
-      <c r="C8" s="280" t="s">
+    <row r="8" spans="3:14" x14ac:dyDescent="0.25">
+      <c r="C8" s="282" t="s">
         <v>265</v>
       </c>
-      <c r="D8" s="281"/>
-      <c r="E8" s="281"/>
-      <c r="F8" s="281"/>
-      <c r="G8" s="281"/>
-      <c r="H8" s="281"/>
-      <c r="I8" s="281"/>
-      <c r="J8" s="282"/>
+      <c r="D8" s="283"/>
+      <c r="E8" s="283"/>
+      <c r="F8" s="283"/>
+      <c r="G8" s="283"/>
+      <c r="H8" s="283"/>
+      <c r="I8" s="283"/>
+      <c r="J8" s="284"/>
       <c r="K8" s="19"/>
       <c r="L8" s="19"/>
       <c r="M8" s="19"/>
       <c r="N8" s="19"/>
     </row>
-    <row r="9" spans="3:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C9" s="283"/>
-      <c r="D9" s="284"/>
-      <c r="E9" s="284"/>
-      <c r="F9" s="284"/>
-      <c r="G9" s="284"/>
-      <c r="H9" s="284"/>
-      <c r="I9" s="284"/>
-      <c r="J9" s="285"/>
+    <row r="9" spans="3:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C9" s="285"/>
+      <c r="D9" s="286"/>
+      <c r="E9" s="286"/>
+      <c r="F9" s="286"/>
+      <c r="G9" s="286"/>
+      <c r="H9" s="286"/>
+      <c r="I9" s="286"/>
+      <c r="J9" s="287"/>
       <c r="K9" s="19"/>
       <c r="L9" s="19"/>
       <c r="M9" s="19"/>
